--- a/database/event/7732/event_7732_evp_summary.xlsx
+++ b/database/event/7732/event_7732_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.4505</v>
+        <v>8.172800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>6.615349999999999</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3.953488091499631</v>
+        <v>2.8803</v>
       </c>
       <c r="E2" t="n">
-        <v>122.9772</v>
+        <v>8.172800000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>17.14734458152936</v>
+        <v>1.6481</v>
       </c>
       <c r="G2" t="n">
-        <v>105.829841436276</v>
+        <v>6.5247</v>
       </c>
       <c r="H2" t="n">
-        <v>17.10247170101087</v>
+        <v>1.6481</v>
       </c>
       <c r="I2" t="n">
-        <v>14.01697422917901</v>
+        <v>1.6481</v>
       </c>
       <c r="J2" t="n">
-        <v>105.829841436276</v>
+        <v>6.8953</v>
       </c>
       <c r="K2" t="n">
         <v>53</v>
@@ -541,7 +529,7 @@
         <v>174</v>
       </c>
       <c r="M2" t="n">
-        <v>119.8468</v>
+        <v>8.5434</v>
       </c>
       <c r="N2" t="n">
         <v>227</v>
@@ -554,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.094900000000001</v>
+        <v>7.2042</v>
       </c>
       <c r="C3" t="n">
-        <v>6.36643</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3.656372372641817</v>
+        <v>2.489</v>
       </c>
       <c r="E3" t="n">
-        <v>113.7351</v>
+        <v>7.2042</v>
       </c>
       <c r="F3" t="n">
-        <v>28.99389803621965</v>
+        <v>1.762</v>
       </c>
       <c r="G3" t="n">
-        <v>84.74120752474751</v>
+        <v>5.4422</v>
       </c>
       <c r="H3" t="n">
-        <v>35.2646885644311</v>
+        <v>1.762</v>
       </c>
       <c r="I3" t="n">
-        <v>22.90386989236247</v>
+        <v>1.762</v>
       </c>
       <c r="J3" t="n">
-        <v>84.74120752474751</v>
+        <v>5.4422</v>
       </c>
       <c r="K3" t="n">
         <v>42</v>
@@ -587,7 +575,7 @@
         <v>172</v>
       </c>
       <c r="M3" t="n">
-        <v>107.6451</v>
+        <v>7.2042</v>
       </c>
       <c r="N3" t="n">
         <v>214</v>
@@ -600,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.4925</v>
+        <v>6.3806</v>
       </c>
       <c r="C4" t="n">
-        <v>5.24475</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.523876356908337</v>
+        <v>2.1563</v>
       </c>
       <c r="E4" t="n">
-        <v>78.5077</v>
+        <v>6.3806</v>
       </c>
       <c r="F4" t="n">
-        <v>18.77177073820434</v>
+        <v>1.7614</v>
       </c>
       <c r="G4" t="n">
-        <v>59.73591792710412</v>
+        <v>4.6192</v>
       </c>
       <c r="H4" t="n">
-        <v>18.88660182342456</v>
+        <v>1.7614</v>
       </c>
       <c r="I4" t="n">
-        <v>18.10777288225242</v>
+        <v>1.7614</v>
       </c>
       <c r="J4" t="n">
-        <v>59.73591792710412</v>
+        <v>4.6192</v>
       </c>
       <c r="K4" t="n">
         <v>62</v>
@@ -633,7 +621,7 @@
         <v>117</v>
       </c>
       <c r="M4" t="n">
-        <v>77.8437</v>
+        <v>6.3806</v>
       </c>
       <c r="N4" t="n">
         <v>179</v>
@@ -646,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.0257</v>
+        <v>5.0272</v>
       </c>
       <c r="C5" t="n">
-        <v>4.91799</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2.249141673958952</v>
+        <v>1.6095</v>
       </c>
       <c r="E5" t="n">
-        <v>69.9618</v>
+        <v>5.0272</v>
       </c>
       <c r="F5" t="n">
-        <v>19.69006585139249</v>
+        <v>1.7194</v>
       </c>
       <c r="G5" t="n">
-        <v>50.27172677764039</v>
+        <v>3.3077</v>
       </c>
       <c r="H5" t="n">
-        <v>19.97632440405997</v>
+        <v>1.7194</v>
       </c>
       <c r="I5" t="n">
-        <v>12.9743137882039</v>
+        <v>1.7194</v>
       </c>
       <c r="J5" t="n">
-        <v>50.27172677764039</v>
+        <v>3.3077</v>
       </c>
       <c r="K5" t="n">
         <v>42</v>
@@ -679,7 +667,7 @@
         <v>172</v>
       </c>
       <c r="M5" t="n">
-        <v>63.246</v>
+        <v>5.0271</v>
       </c>
       <c r="N5" t="n">
         <v>214</v>
@@ -688,127 +676,127 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7211</v>
+        <v>3.6123</v>
       </c>
       <c r="C6" t="n">
-        <v>4.00477</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.589559038784466</v>
+        <v>1.0379</v>
       </c>
       <c r="E6" t="n">
-        <v>49.4448</v>
+        <v>3.6123</v>
       </c>
       <c r="F6" t="n">
-        <v>24.78851489070887</v>
+        <v>3.9465</v>
       </c>
       <c r="G6" t="n">
-        <v>24.65630271710948</v>
+        <v>-0.3342</v>
       </c>
       <c r="H6" t="n">
-        <v>27.27558280736172</v>
+        <v>3.9465</v>
       </c>
       <c r="I6" t="n">
-        <v>17.71506924601843</v>
+        <v>3.9649</v>
       </c>
       <c r="J6" t="n">
-        <v>24.65630271710948</v>
+        <v>-0.3342</v>
       </c>
       <c r="K6" t="n">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="L6" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="M6" t="n">
-        <v>42.3714</v>
+        <v>3.6307</v>
       </c>
       <c r="N6" t="n">
-        <v>122</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7361</v>
+        <v>3.4178</v>
       </c>
       <c r="C7" t="n">
-        <v>3.31527</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.181903958097653</v>
+        <v>0.9594</v>
       </c>
       <c r="E7" t="n">
-        <v>36.7643</v>
+        <v>3.4178</v>
       </c>
       <c r="F7" t="n">
-        <v>26.45847006409559</v>
+        <v>1.76</v>
       </c>
       <c r="G7" t="n">
-        <v>10.30583010482754</v>
+        <v>1.6578</v>
       </c>
       <c r="H7" t="n">
-        <v>30.20486072277219</v>
+        <v>1.76</v>
       </c>
       <c r="I7" t="n">
-        <v>24.75553018000401</v>
+        <v>1.76</v>
       </c>
       <c r="J7" t="n">
-        <v>10.30583010482754</v>
+        <v>1.6578</v>
       </c>
       <c r="K7" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="L7" t="n">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="M7" t="n">
-        <v>35.0614</v>
+        <v>3.4178</v>
       </c>
       <c r="N7" t="n">
-        <v>227</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3148</v>
+        <v>3.151</v>
       </c>
       <c r="C8" t="n">
-        <v>3.02036</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1.02774724277462</v>
+        <v>0.8516</v>
       </c>
       <c r="E8" t="n">
-        <v>31.9691</v>
+        <v>3.151</v>
       </c>
       <c r="F8" t="n">
-        <v>2.613458254954093</v>
+        <v>1.7591</v>
       </c>
       <c r="G8" t="n">
-        <v>29.35564369472172</v>
+        <v>1.3919</v>
       </c>
       <c r="H8" t="n">
-        <v>2.613458254954093</v>
+        <v>1.7591</v>
       </c>
       <c r="I8" t="n">
-        <v>2.141958054318045</v>
+        <v>1.7591</v>
       </c>
       <c r="J8" t="n">
-        <v>29.35564369472172</v>
+        <v>1.3919</v>
       </c>
       <c r="K8" t="n">
         <v>53</v>
@@ -817,7 +805,7 @@
         <v>174</v>
       </c>
       <c r="M8" t="n">
-        <v>31.4976</v>
+        <v>3.151</v>
       </c>
       <c r="N8" t="n">
         <v>227</v>
@@ -826,173 +814,173 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1565</v>
+        <v>2.9819</v>
       </c>
       <c r="C9" t="n">
-        <v>2.90955</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9726924903972566</v>
+        <v>0.7833</v>
       </c>
       <c r="E9" t="n">
-        <v>30.2566</v>
+        <v>2.9819</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1128944229226238</v>
+        <v>1.5735</v>
       </c>
       <c r="G9" t="n">
-        <v>30.36946344785475</v>
+        <v>1.4084</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1128944229226238</v>
+        <v>1.5735</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07332318189819897</v>
+        <v>1.5735</v>
       </c>
       <c r="J9" t="n">
-        <v>30.36946344785475</v>
+        <v>1.4084</v>
       </c>
       <c r="K9" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L9" t="n">
-        <v>172</v>
+        <v>117</v>
       </c>
       <c r="M9" t="n">
-        <v>30.2961</v>
+        <v>2.9819</v>
       </c>
       <c r="N9" t="n">
-        <v>214</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1243</v>
+        <v>2.9483</v>
       </c>
       <c r="C10" t="n">
-        <v>2.88701</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9616542516285301</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>29.9132</v>
+        <v>2.9483</v>
       </c>
       <c r="F10" t="n">
-        <v>1.997168306389464</v>
+        <v>0.2593</v>
       </c>
       <c r="G10" t="n">
-        <v>27.91604530404445</v>
+        <v>2.689</v>
       </c>
       <c r="H10" t="n">
-        <v>1.997168306389464</v>
+        <v>0.2593</v>
       </c>
       <c r="I10" t="n">
-        <v>1.204477793028697</v>
+        <v>0.2593</v>
       </c>
       <c r="J10" t="n">
-        <v>27.91604530404445</v>
+        <v>2.689</v>
       </c>
       <c r="K10" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L10" t="n">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="M10" t="n">
-        <v>29.1205</v>
+        <v>2.9483</v>
       </c>
       <c r="N10" t="n">
-        <v>156</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0SAMAS</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.9731</v>
+        <v>2.5673</v>
       </c>
       <c r="C11" t="n">
-        <v>2.78117</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9107563180478898</v>
+        <v>0.6158</v>
       </c>
       <c r="E11" t="n">
-        <v>28.33</v>
+        <v>2.5673</v>
       </c>
       <c r="F11" t="n">
-        <v>28.32998267587606</v>
+        <v>0.3419</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2.2254</v>
       </c>
       <c r="H11" t="n">
-        <v>33.86310837307456</v>
+        <v>0.3419</v>
       </c>
       <c r="I11" t="n">
-        <v>10.99678261599844</v>
+        <v>0.3419</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2.2254</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="M11" t="n">
-        <v>10.9968</v>
+        <v>2.5673</v>
       </c>
       <c r="N11" t="n">
-        <v>21</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.7499</v>
+        <v>2.4774</v>
       </c>
       <c r="C12" t="n">
-        <v>2.62493</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8380038014576884</v>
+        <v>0.5795</v>
       </c>
       <c r="E12" t="n">
-        <v>26.0669</v>
+        <v>2.4774</v>
       </c>
       <c r="F12" t="n">
-        <v>18.21686631019911</v>
+        <v>0.1219</v>
       </c>
       <c r="G12" t="n">
-        <v>7.850076852490274</v>
+        <v>2.3555</v>
       </c>
       <c r="H12" t="n">
-        <v>18.25713300915135</v>
+        <v>0.1219</v>
       </c>
       <c r="I12" t="n">
-        <v>11.01074516531293</v>
+        <v>0.1219</v>
       </c>
       <c r="J12" t="n">
-        <v>7.850076852490274</v>
+        <v>2.3555</v>
       </c>
       <c r="K12" t="n">
         <v>39</v>
@@ -1001,7 +989,7 @@
         <v>117</v>
       </c>
       <c r="M12" t="n">
-        <v>18.8608</v>
+        <v>2.4774</v>
       </c>
       <c r="N12" t="n">
         <v>156</v>
@@ -1010,219 +998,219 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7825</v>
+        <v>2.0799</v>
       </c>
       <c r="C13" t="n">
-        <v>1.94775</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5533732771233478</v>
+        <v>0.4189</v>
       </c>
       <c r="E13" t="n">
-        <v>17.2132</v>
+        <v>2.0799</v>
       </c>
       <c r="F13" t="n">
-        <v>32.55424832973972</v>
+        <v>1.7447</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.34102120901074</v>
+        <v>0.3352</v>
       </c>
       <c r="H13" t="n">
-        <v>43.83225101942151</v>
+        <v>1.7447</v>
       </c>
       <c r="I13" t="n">
-        <v>26.43491427459957</v>
+        <v>1.7447</v>
       </c>
       <c r="J13" t="n">
-        <v>-15.34102120901074</v>
+        <v>0.3352</v>
       </c>
       <c r="K13" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="L13" t="n">
         <v>117</v>
       </c>
       <c r="M13" t="n">
-        <v>11.0939</v>
+        <v>2.0799</v>
       </c>
       <c r="N13" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7287</v>
+        <v>1.966</v>
       </c>
       <c r="C14" t="n">
-        <v>1.91009</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5389115200496906</v>
+        <v>0.3729</v>
       </c>
       <c r="E14" t="n">
-        <v>16.7634</v>
+        <v>1.966</v>
       </c>
       <c r="F14" t="n">
-        <v>4.865355707626433</v>
+        <v>1.9046</v>
       </c>
       <c r="G14" t="n">
-        <v>11.89802405081623</v>
+        <v>0.0614</v>
       </c>
       <c r="H14" t="n">
-        <v>4.865355707626433</v>
+        <v>1.9046</v>
       </c>
       <c r="I14" t="n">
-        <v>2.482836160077406</v>
+        <v>1.9135</v>
       </c>
       <c r="J14" t="n">
-        <v>11.89802405081623</v>
+        <v>0.0614</v>
       </c>
       <c r="K14" t="n">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="L14" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="M14" t="n">
-        <v>14.3809</v>
+        <v>1.9749</v>
       </c>
       <c r="N14" t="n">
-        <v>102</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6986</v>
+        <v>1.8706</v>
       </c>
       <c r="C15" t="n">
-        <v>1.88902</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5308742167968435</v>
+        <v>0.3343</v>
       </c>
       <c r="E15" t="n">
-        <v>16.5134</v>
+        <v>1.8706</v>
       </c>
       <c r="F15" t="n">
-        <v>13.92506120580701</v>
+        <v>0.4546</v>
       </c>
       <c r="G15" t="n">
-        <v>2.588310227245218</v>
+        <v>1.416</v>
       </c>
       <c r="H15" t="n">
-        <v>13.92506120580701</v>
+        <v>0.4546</v>
       </c>
       <c r="I15" t="n">
-        <v>7.106087934922131</v>
+        <v>0.4546</v>
       </c>
       <c r="J15" t="n">
-        <v>2.588310227245218</v>
+        <v>1.416</v>
       </c>
       <c r="K15" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L15" t="n">
-        <v>69</v>
+        <v>172</v>
       </c>
       <c r="M15" t="n">
-        <v>9.6944</v>
+        <v>1.8706</v>
       </c>
       <c r="N15" t="n">
-        <v>102</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6575</v>
+        <v>1.8334</v>
       </c>
       <c r="C16" t="n">
-        <v>1.86025</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5199763404129876</v>
+        <v>0.3193</v>
       </c>
       <c r="E16" t="n">
-        <v>16.1744</v>
+        <v>1.8334</v>
       </c>
       <c r="F16" t="n">
-        <v>23.88053896517366</v>
+        <v>0.7813</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.706156834792681</v>
+        <v>1.0521</v>
       </c>
       <c r="H16" t="n">
-        <v>25.80394113997189</v>
+        <v>0.7813</v>
       </c>
       <c r="I16" t="n">
-        <v>46.28748204489802</v>
+        <v>0.7813</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.706156834792681</v>
+        <v>1.0521</v>
       </c>
       <c r="K16" t="n">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="L16" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M16" t="n">
-        <v>38.5813</v>
+        <v>1.8334</v>
       </c>
       <c r="N16" t="n">
-        <v>180</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.5805</v>
+        <v>1.806</v>
       </c>
       <c r="C17" t="n">
-        <v>1.80635</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4997657768734528</v>
+        <v>0.3082</v>
       </c>
       <c r="E17" t="n">
-        <v>15.5457</v>
+        <v>1.806</v>
       </c>
       <c r="F17" t="n">
-        <v>13.02805784825353</v>
+        <v>0.6244</v>
       </c>
       <c r="G17" t="n">
-        <v>2.517654567080138</v>
+        <v>1.1816</v>
       </c>
       <c r="H17" t="n">
-        <v>13.02805784825353</v>
+        <v>0.6244</v>
       </c>
       <c r="I17" t="n">
-        <v>12.49081834935648</v>
+        <v>0.6244</v>
       </c>
       <c r="J17" t="n">
-        <v>2.517654567080138</v>
+        <v>1.1816</v>
       </c>
       <c r="K17" t="n">
         <v>62</v>
@@ -1231,7 +1219,7 @@
         <v>117</v>
       </c>
       <c r="M17" t="n">
-        <v>15.0085</v>
+        <v>1.806</v>
       </c>
       <c r="N17" t="n">
         <v>179</v>
@@ -1240,35 +1228,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4494</v>
+        <v>1.6236</v>
       </c>
       <c r="C18" t="n">
-        <v>1.71458</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4659587216076345</v>
+        <v>0.2345</v>
       </c>
       <c r="E18" t="n">
-        <v>14.4941</v>
+        <v>1.6236</v>
       </c>
       <c r="F18" t="n">
-        <v>6.239926232279956</v>
+        <v>1.4034</v>
       </c>
       <c r="G18" t="n">
-        <v>8.254184046429655</v>
+        <v>0.2202</v>
       </c>
       <c r="H18" t="n">
-        <v>6.239926232279956</v>
+        <v>1.4034</v>
       </c>
       <c r="I18" t="n">
-        <v>3.184292252555235</v>
+        <v>1.4034</v>
       </c>
       <c r="J18" t="n">
-        <v>8.254184046429655</v>
+        <v>0.2202</v>
       </c>
       <c r="K18" t="n">
         <v>33</v>
@@ -1277,7 +1265,7 @@
         <v>69</v>
       </c>
       <c r="M18" t="n">
-        <v>11.4385</v>
+        <v>1.6236</v>
       </c>
       <c r="N18" t="n">
         <v>102</v>
@@ -1290,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2697</v>
+        <v>1.587</v>
       </c>
       <c r="C19" t="n">
-        <v>1.58879</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4208474940337045</v>
+        <v>0.2198</v>
       </c>
       <c r="E19" t="n">
-        <v>13.0909</v>
+        <v>1.587</v>
       </c>
       <c r="F19" t="n">
-        <v>19.80435887113452</v>
+        <v>1.7282</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.713478271244152</v>
+        <v>-0.1412</v>
       </c>
       <c r="H19" t="n">
-        <v>20.11628128815909</v>
+        <v>1.7282</v>
       </c>
       <c r="I19" t="n">
-        <v>16.48705528256338</v>
+        <v>1.7282</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.713478271244152</v>
+        <v>-0.1412</v>
       </c>
       <c r="K19" t="n">
         <v>53</v>
@@ -1323,7 +1311,7 @@
         <v>51</v>
       </c>
       <c r="M19" t="n">
-        <v>9.7736</v>
+        <v>1.587</v>
       </c>
       <c r="N19" t="n">
         <v>104</v>
@@ -1332,173 +1320,173 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1525</v>
+        <v>1.4431</v>
       </c>
       <c r="C20" t="n">
-        <v>1.50675</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3921717010800931</v>
+        <v>0.1616</v>
       </c>
       <c r="E20" t="n">
-        <v>12.1989</v>
+        <v>1.4431</v>
       </c>
       <c r="F20" t="n">
-        <v>6.649026962275548</v>
+        <v>1.4431</v>
       </c>
       <c r="G20" t="n">
-        <v>5.549864527581436</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>6.649026962275548</v>
+        <v>1.4431</v>
       </c>
       <c r="I20" t="n">
-        <v>5.449460242277382</v>
+        <v>1.4431</v>
       </c>
       <c r="J20" t="n">
-        <v>5.549864527581436</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="L20" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>10.9993</v>
+        <v>1.4431</v>
       </c>
       <c r="N20" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.781</v>
+        <v>1.4194</v>
       </c>
       <c r="C21" t="n">
-        <v>1.2467</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3050860124561415</v>
+        <v>0.152</v>
       </c>
       <c r="E21" t="n">
-        <v>9.49</v>
+        <v>1.4194</v>
       </c>
       <c r="F21" t="n">
-        <v>9.490004380161897</v>
+        <v>0.6194</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H21" t="n">
-        <v>9.490004380161897</v>
+        <v>0.6194</v>
       </c>
       <c r="I21" t="n">
-        <v>16.28954360099954</v>
+        <v>0.6194</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M21" t="n">
-        <v>16.2895</v>
+        <v>1.4194</v>
       </c>
       <c r="N21" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6752</v>
+        <v>1.3217</v>
       </c>
       <c r="C22" t="n">
-        <v>1.17264</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2812879094897668</v>
+        <v>0.1126</v>
       </c>
       <c r="E22" t="n">
-        <v>8.749700000000001</v>
+        <v>1.3217</v>
       </c>
       <c r="F22" t="n">
-        <v>8.749740676912289</v>
+        <v>1.3217</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>8.749740676912289</v>
+        <v>1.3217</v>
       </c>
       <c r="I22" t="n">
-        <v>9.336063505777545</v>
+        <v>1.3217</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>9.3361</v>
+        <v>1.3217</v>
       </c>
       <c r="N22" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.6505</v>
+        <v>1.2217</v>
       </c>
       <c r="C23" t="n">
-        <v>1.15535</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2757789198820551</v>
+        <v>0.0722</v>
       </c>
       <c r="E23" t="n">
-        <v>8.5784</v>
+        <v>1.2217</v>
       </c>
       <c r="F23" t="n">
-        <v>8.965020951043364</v>
+        <v>1.36</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3866428845849619</v>
+        <v>-0.1383</v>
       </c>
       <c r="H23" t="n">
-        <v>8.965020951043364</v>
+        <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>16.08158397403655</v>
+        <v>1.3663</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3866428845849619</v>
+        <v>-0.1383</v>
       </c>
       <c r="K23" t="n">
         <v>116</v>
@@ -1507,7 +1495,7 @@
         <v>64</v>
       </c>
       <c r="M23" t="n">
-        <v>15.6949</v>
+        <v>1.228</v>
       </c>
       <c r="N23" t="n">
         <v>180</v>
@@ -1516,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kwezz</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3958</v>
+        <v>1.1953</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9770599999999999</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2205031484162619</v>
+        <v>0.0615</v>
       </c>
       <c r="E24" t="n">
-        <v>6.859</v>
+        <v>1.1953</v>
       </c>
       <c r="F24" t="n">
-        <v>6.858970122763785</v>
+        <v>0.9677</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="H24" t="n">
-        <v>6.858970122763785</v>
+        <v>0.9677</v>
       </c>
       <c r="I24" t="n">
-        <v>12.40978614994891</v>
+        <v>0.9677</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="K24" t="n">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M24" t="n">
-        <v>12.4098</v>
+        <v>1.1953</v>
       </c>
       <c r="N24" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>kwezz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.332</v>
+        <v>1.1885</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9324</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2070492848427299</v>
+        <v>0.0588</v>
       </c>
       <c r="E25" t="n">
-        <v>6.4405</v>
+        <v>1.1885</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.440475479764766</v>
+        <v>1.1885</v>
       </c>
       <c r="G25" t="n">
-        <v>12.88094977174616</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.440475479764766</v>
+        <v>1.1885</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.182989229125569</v>
+        <v>1.1885</v>
       </c>
       <c r="J25" t="n">
-        <v>12.88094977174616</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="L25" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>8.698</v>
+        <v>1.1885</v>
       </c>
       <c r="N25" t="n">
-        <v>214</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26">
@@ -1612,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.1906</v>
+        <v>1.1682</v>
       </c>
       <c r="C26" t="n">
-        <v>0.83342</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1777182011466523</v>
+        <v>0.0506</v>
       </c>
       <c r="E26" t="n">
-        <v>5.5281</v>
+        <v>1.1682</v>
       </c>
       <c r="F26" t="n">
-        <v>13.81157913130972</v>
+        <v>1.4761</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.283477420784141</v>
+        <v>-0.3079</v>
       </c>
       <c r="H26" t="n">
-        <v>13.81157913130972</v>
+        <v>1.4761</v>
       </c>
       <c r="I26" t="n">
-        <v>11.31979939112498</v>
+        <v>1.4761</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.283477420784141</v>
+        <v>-0.3079</v>
       </c>
       <c r="K26" t="n">
         <v>53</v>
@@ -1645,7 +1633,7 @@
         <v>51</v>
       </c>
       <c r="M26" t="n">
-        <v>3.0363</v>
+        <v>1.1682</v>
       </c>
       <c r="N26" t="n">
         <v>104</v>
@@ -1654,231 +1642,231 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8788</v>
+        <v>1.1273</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6151599999999999</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1155535839241591</v>
+        <v>0.034</v>
       </c>
       <c r="E27" t="n">
-        <v>3.5944</v>
+        <v>1.1273</v>
       </c>
       <c r="F27" t="n">
-        <v>34.39682900568945</v>
+        <v>1.1273</v>
       </c>
       <c r="G27" t="n">
-        <v>-30.80241964960231</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>49.05420171146999</v>
+        <v>1.1273</v>
       </c>
       <c r="I27" t="n">
-        <v>25.03281427544087</v>
+        <v>1.1273</v>
       </c>
       <c r="J27" t="n">
-        <v>-30.80241964960231</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.1273</v>
+      </c>
+      <c r="N27" t="n">
         <v>69</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-5.7696</v>
-      </c>
-      <c r="N27" t="n">
-        <v>102</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>0SAMAS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5299</v>
+        <v>0.822</v>
       </c>
       <c r="C28" t="n">
-        <v>0.37093</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.04988550575579632</v>
+        <v>-0.0893</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5517</v>
+        <v>0.822</v>
       </c>
       <c r="F28" t="n">
-        <v>1.551738358365923</v>
+        <v>0.822</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.551738358365923</v>
+        <v>0.822</v>
       </c>
       <c r="I28" t="n">
-        <v>2.663550893483775</v>
+        <v>0.822</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.6636</v>
+        <v>0.822</v>
       </c>
       <c r="N28" t="n">
-        <v>111</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2746</v>
+        <v>0.79</v>
       </c>
       <c r="C29" t="n">
-        <v>0.19222</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.004292896695722631</v>
+        <v>-0.1022</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1335</v>
+        <v>0.79</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1335348288110945</v>
+        <v>-0.2715</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1.0615</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1335348288110945</v>
+        <v>-0.2715</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1920423568984297</v>
+        <v>-0.2715</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1.0615</v>
       </c>
       <c r="K29" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M29" t="n">
-        <v>0.192</v>
+        <v>0.79</v>
       </c>
       <c r="N29" t="n">
-        <v>93</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2436</v>
+        <v>0.7655</v>
       </c>
       <c r="C30" t="n">
-        <v>0.17052</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.001117936688086166</v>
+        <v>-0.1121</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0348</v>
+        <v>0.7655</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.03477453450346746</v>
+        <v>0.2497</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.5158</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.03477453450346746</v>
+        <v>0.2497</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.05969030922502405</v>
+        <v>0.2497</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.5158</v>
       </c>
       <c r="K30" t="n">
-        <v>111</v>
+        <v>39</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0597</v>
+        <v>0.7655000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>111</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1387</v>
+        <v>0.7648</v>
       </c>
       <c r="C31" t="n">
-        <v>0.09708999999999998</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.01954444796961566</v>
+        <v>-0.1124</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6079</v>
+        <v>0.7648</v>
       </c>
       <c r="F31" t="n">
-        <v>11.54281280103127</v>
+        <v>1.7648</v>
       </c>
       <c r="G31" t="n">
-        <v>-12.15076232761326</v>
+        <v>-1</v>
       </c>
       <c r="H31" t="n">
-        <v>11.54281280103127</v>
+        <v>1.7648</v>
       </c>
       <c r="I31" t="n">
-        <v>7.496878417164636</v>
+        <v>1.7648</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.15076232761326</v>
+        <v>-1</v>
       </c>
       <c r="K31" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L31" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M31" t="n">
-        <v>-4.6539</v>
+        <v>0.7647999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32">
@@ -1888,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0883</v>
+        <v>0.748</v>
       </c>
       <c r="C32" t="n">
-        <v>0.06181</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.02851656614869261</v>
+        <v>-0.1192</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.887</v>
+        <v>0.748</v>
       </c>
       <c r="F32" t="n">
-        <v>23.97688193513304</v>
+        <v>1.748</v>
       </c>
       <c r="G32" t="n">
-        <v>-24.86391813675888</v>
+        <v>-1</v>
       </c>
       <c r="H32" t="n">
-        <v>25.95625053447412</v>
+        <v>1.748</v>
       </c>
       <c r="I32" t="n">
-        <v>13.24571547893267</v>
+        <v>1.748</v>
       </c>
       <c r="J32" t="n">
-        <v>-24.86391813675888</v>
+        <v>-1</v>
       </c>
       <c r="K32" t="n">
         <v>33</v>
@@ -1921,7 +1909,7 @@
         <v>69</v>
       </c>
       <c r="M32" t="n">
-        <v>-11.6182</v>
+        <v>0.748</v>
       </c>
       <c r="N32" t="n">
         <v>102</v>
@@ -1930,35 +1918,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1229</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.08603</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0670087748385038</v>
+        <v>-0.1776</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.0844</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>3.032383715420464</v>
+        <v>1.7636</v>
       </c>
       <c r="G33" t="n">
-        <v>-5.116758418826772</v>
+        <v>-1.1603</v>
       </c>
       <c r="H33" t="n">
-        <v>3.032383715420464</v>
+        <v>1.7636</v>
       </c>
       <c r="I33" t="n">
-        <v>1.82880873558863</v>
+        <v>1.7636</v>
       </c>
       <c r="J33" t="n">
-        <v>-5.116758418826772</v>
+        <v>-1.1603</v>
       </c>
       <c r="K33" t="n">
         <v>39</v>
@@ -1967,7 +1955,7 @@
         <v>117</v>
       </c>
       <c r="M33" t="n">
-        <v>-3.2879</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>156</v>
@@ -1976,1596 +1964,1596 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.1653</v>
+        <v>0.5646</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.11571</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.07489121772691447</v>
+        <v>-0.1933</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.3296</v>
+        <v>0.5646</v>
       </c>
       <c r="F34" t="n">
-        <v>-2.329565942870776</v>
+        <v>0.5646</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-2.329565942870776</v>
+        <v>0.5646</v>
       </c>
       <c r="I34" t="n">
-        <v>-2.557719308409666</v>
+        <v>0.5646</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-2.5577</v>
+        <v>0.5646</v>
       </c>
       <c r="N34" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3256</v>
+        <v>0.5148</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.22792</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1052831733900773</v>
+        <v>-0.2134</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.2749</v>
+        <v>0.5148</v>
       </c>
       <c r="F35" t="n">
-        <v>-3.274938003828714</v>
+        <v>0.5148</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-3.274938003828714</v>
+        <v>0.5148</v>
       </c>
       <c r="I35" t="n">
-        <v>-3.595679354719155</v>
+        <v>0.5148</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-3.5957</v>
+        <v>0.5148</v>
       </c>
       <c r="N35" t="n">
-        <v>71</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3796</v>
+        <v>0.4763</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.26572</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1157204517218225</v>
+        <v>-0.2289</v>
       </c>
       <c r="E36" t="n">
-        <v>-3.5996</v>
+        <v>0.4763</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1207404640812608</v>
+        <v>0.4347</v>
       </c>
       <c r="G36" t="n">
-        <v>-3.720340409268136</v>
+        <v>0.0416</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1207404640812608</v>
+        <v>0.4347</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1157614758717243</v>
+        <v>0.4347</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.720340409268136</v>
+        <v>0.0416</v>
       </c>
       <c r="K36" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="L36" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="M36" t="n">
-        <v>-3.6046</v>
+        <v>0.4762999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>179</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6429</v>
+        <v>0.4402</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.45003</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1679940605005133</v>
+        <v>-0.2435</v>
       </c>
       <c r="E37" t="n">
-        <v>-5.2256</v>
+        <v>0.4402</v>
       </c>
       <c r="F37" t="n">
-        <v>2.110439649253724</v>
+        <v>1.154</v>
       </c>
       <c r="G37" t="n">
-        <v>-7.336062276643901</v>
+        <v>-0.7138</v>
       </c>
       <c r="H37" t="n">
-        <v>2.110439649253724</v>
+        <v>1.154</v>
       </c>
       <c r="I37" t="n">
-        <v>3.78573710278503</v>
+        <v>1.154</v>
       </c>
       <c r="J37" t="n">
-        <v>-7.336062276643901</v>
+        <v>-0.7138</v>
       </c>
       <c r="K37" t="n">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="L37" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="M37" t="n">
-        <v>-3.5503</v>
+        <v>0.4401999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>180</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.6695</v>
+        <v>0.3539</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.46865</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1734099423998835</v>
+        <v>-0.2784</v>
       </c>
       <c r="E38" t="n">
-        <v>-5.3941</v>
+        <v>0.3539</v>
       </c>
       <c r="F38" t="n">
-        <v>-5.394089029811203</v>
+        <v>0.3539</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-5.394089029811203</v>
+        <v>0.3539</v>
       </c>
       <c r="I38" t="n">
-        <v>-9.258926015088301</v>
+        <v>0.3539</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-9.258900000000001</v>
+        <v>0.3539</v>
       </c>
       <c r="N38" t="n">
-        <v>111</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.7014</v>
+        <v>0.3128</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.49098</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1799470010729105</v>
+        <v>-0.295</v>
       </c>
       <c r="E39" t="n">
-        <v>-5.5974</v>
+        <v>0.3128</v>
       </c>
       <c r="F39" t="n">
-        <v>-5.597430752825528</v>
+        <v>0.3128</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-5.597430752825528</v>
+        <v>0.3128</v>
       </c>
       <c r="I39" t="n">
-        <v>-10.1273102795967</v>
+        <v>0.3128</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-10.1273</v>
+        <v>0.3128</v>
       </c>
       <c r="N39" t="n">
-        <v>117</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.7931</v>
+        <v>0.3108</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5551699999999999</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1989088692507065</v>
+        <v>-0.2958</v>
       </c>
       <c r="E40" t="n">
-        <v>-6.1873</v>
+        <v>0.3108</v>
       </c>
       <c r="F40" t="n">
-        <v>-6.187258554548182</v>
+        <v>1.3108</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-6.187258554548182</v>
+        <v>1.3108</v>
       </c>
       <c r="I40" t="n">
-        <v>-8.898170807829601</v>
+        <v>1.3108</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K40" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M40" t="n">
-        <v>-8.898199999999999</v>
+        <v>0.3108</v>
       </c>
       <c r="N40" t="n">
-        <v>93</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.806</v>
+        <v>0.2899</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2016050055674057</v>
+        <v>-0.3042</v>
       </c>
       <c r="E41" t="n">
-        <v>-6.2711</v>
+        <v>0.2899</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.071540318852854</v>
+        <v>1.1828</v>
       </c>
       <c r="G41" t="n">
-        <v>-5.199584242035645</v>
+        <v>-0.8929</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.071540318852854</v>
+        <v>1.1828</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6959488668838123</v>
+        <v>1.1828</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.199584242035645</v>
+        <v>-0.8929</v>
       </c>
       <c r="K41" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L41" t="n">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="M41" t="n">
-        <v>-5.8955</v>
+        <v>0.2899</v>
       </c>
       <c r="N41" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.8123</v>
+        <v>0.1191</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.5686099999999999</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2029184584847916</v>
+        <v>-0.3732</v>
       </c>
       <c r="E42" t="n">
-        <v>-6.312</v>
+        <v>0.1191</v>
       </c>
       <c r="F42" t="n">
-        <v>-6.311980822500693</v>
+        <v>0.1191</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-6.311980822500693</v>
+        <v>0.1191</v>
       </c>
       <c r="I42" t="n">
-        <v>-6.930164511302307</v>
+        <v>0.1191</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-6.9302</v>
+        <v>0.1191</v>
       </c>
       <c r="N42" t="n">
-        <v>71</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>m1N1</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.8683999999999999</v>
+        <v>0.0588</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.60788</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.214700209999904</v>
+        <v>-0.3976</v>
       </c>
       <c r="E43" t="n">
-        <v>-6.6785</v>
+        <v>0.0588</v>
       </c>
       <c r="F43" t="n">
-        <v>14.22139749251309</v>
+        <v>0.0588</v>
       </c>
       <c r="G43" t="n">
-        <v>-20.89986143426353</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>14.22139749251309</v>
+        <v>0.0588</v>
       </c>
       <c r="I43" t="n">
-        <v>8.576822199092947</v>
+        <v>0.0588</v>
       </c>
       <c r="J43" t="n">
-        <v>-20.89986143426353</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L43" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-12.323</v>
+        <v>0.0588</v>
       </c>
       <c r="N43" t="n">
-        <v>156</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.9132</v>
+        <v>0.0035</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.6392399999999999</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2242161518939854</v>
+        <v>-0.4199</v>
       </c>
       <c r="E44" t="n">
-        <v>-6.9745</v>
+        <v>0.0035</v>
       </c>
       <c r="F44" t="n">
-        <v>-8.764237469312516</v>
+        <v>0.9324</v>
       </c>
       <c r="G44" t="n">
-        <v>1.789770674041602</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>-8.764237469312516</v>
+        <v>0.9324</v>
       </c>
       <c r="I44" t="n">
-        <v>-8.402825614907876</v>
+        <v>0.9324</v>
       </c>
       <c r="J44" t="n">
-        <v>1.789770674041602</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="L44" t="n">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="M44" t="n">
-        <v>-6.6131</v>
+        <v>0.003500000000000059</v>
       </c>
       <c r="N44" t="n">
-        <v>179</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-1.1471</v>
+        <v>-0.005</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.80297</v>
+        <v>-0</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2750258206261219</v>
+        <v>-0.4234</v>
       </c>
       <c r="E45" t="n">
-        <v>-8.555</v>
+        <v>-0.005</v>
       </c>
       <c r="F45" t="n">
-        <v>-8.015394842192382</v>
+        <v>-0.4567</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.5395573215838048</v>
+        <v>0.4517</v>
       </c>
       <c r="H45" t="n">
-        <v>-8.015394842192382</v>
+        <v>-0.4567</v>
       </c>
       <c r="I45" t="n">
-        <v>-14.37813095403582</v>
+        <v>-0.4567</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.5395573215838048</v>
+        <v>0.4517</v>
       </c>
       <c r="K45" t="n">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="L45" t="n">
-        <v>64</v>
+        <v>174</v>
       </c>
       <c r="M45" t="n">
-        <v>-14.9177</v>
+        <v>-0.005000000000000004</v>
       </c>
       <c r="N45" t="n">
-        <v>180</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-1.253</v>
+        <v>-0.0101</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.8770999999999999</v>
+        <v>-0</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2987253405879433</v>
+        <v>-0.4254</v>
       </c>
       <c r="E46" t="n">
-        <v>-9.2921</v>
+        <v>-0.0101</v>
       </c>
       <c r="F46" t="n">
-        <v>-9.292149344449138</v>
+        <v>-0.0101</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-9.292149344449138</v>
+        <v>-0.0101</v>
       </c>
       <c r="I46" t="n">
-        <v>-9.914819145881296</v>
+        <v>-0.0101</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-9.9148</v>
+        <v>-0.0101</v>
       </c>
       <c r="N46" t="n">
-        <v>69</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cabbi</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-1.2591</v>
+        <v>-0.0458</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.88137</v>
+        <v>-0</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3001205198391202</v>
+        <v>-0.4399</v>
       </c>
       <c r="E47" t="n">
-        <v>-9.3355</v>
+        <v>-0.0458</v>
       </c>
       <c r="F47" t="n">
-        <v>-9.335547785099324</v>
+        <v>-0.3497</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.3039</v>
       </c>
       <c r="H47" t="n">
-        <v>-9.335547785099324</v>
+        <v>-0.3497</v>
       </c>
       <c r="I47" t="n">
-        <v>-16.8906044977828</v>
+        <v>-0.3513</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.3039</v>
       </c>
       <c r="K47" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M47" t="n">
-        <v>-16.8906</v>
+        <v>-0.0474</v>
       </c>
       <c r="N47" t="n">
-        <v>117</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>Cabbi</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-1.3365</v>
+        <v>-0.0742</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.93555</v>
+        <v>-0</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3177312208596572</v>
+        <v>-0.4513</v>
       </c>
       <c r="E48" t="n">
-        <v>-9.8833</v>
+        <v>-0.0742</v>
       </c>
       <c r="F48" t="n">
-        <v>-9.883346186203154</v>
+        <v>-0.0742</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-9.883346186203154</v>
+        <v>-0.0742</v>
       </c>
       <c r="I48" t="n">
-        <v>-14.21367827809629</v>
+        <v>-0.0742</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-14.2137</v>
+        <v>-0.0742</v>
       </c>
       <c r="N48" t="n">
-        <v>93</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>dennyslaw</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-1.4345</v>
+        <v>-0.1659</v>
       </c>
       <c r="C49" t="n">
-        <v>-1.00415</v>
+        <v>-0</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.340387971955227</v>
+        <v>-0.4884</v>
       </c>
       <c r="E49" t="n">
-        <v>-10.5881</v>
+        <v>-0.1659</v>
       </c>
       <c r="F49" t="n">
-        <v>-10.58810700236186</v>
+        <v>-0.1659</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-10.58810700236186</v>
+        <v>-0.1659</v>
       </c>
       <c r="I49" t="n">
-        <v>-15.22722604978845</v>
+        <v>-0.1659</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-15.2272</v>
+        <v>-0.1659</v>
       </c>
       <c r="N49" t="n">
-        <v>93</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-1.5461</v>
+        <v>-0.1669</v>
       </c>
       <c r="C50" t="n">
-        <v>-1.08227</v>
+        <v>-0</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3666642437033315</v>
+        <v>-0.4888</v>
       </c>
       <c r="E50" t="n">
-        <v>-11.4055</v>
+        <v>-0.1669</v>
       </c>
       <c r="F50" t="n">
-        <v>-11.40545661461156</v>
+        <v>-0.1669</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-11.40545661461156</v>
+        <v>-0.1669</v>
       </c>
       <c r="I50" t="n">
-        <v>-16.4026927601888</v>
+        <v>-0.1669</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-16.4027</v>
+        <v>-0.1669</v>
       </c>
       <c r="N50" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MistR</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-1.8094</v>
+        <v>-0.1774</v>
       </c>
       <c r="C51" t="n">
-        <v>-1.26658</v>
+        <v>-0</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4306792619593033</v>
+        <v>-0.493</v>
       </c>
       <c r="E51" t="n">
-        <v>-13.3967</v>
+        <v>-0.1774</v>
       </c>
       <c r="F51" t="n">
-        <v>-13.39670753678437</v>
+        <v>-0.1774</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-13.39670753678437</v>
+        <v>-0.1774</v>
       </c>
       <c r="I51" t="n">
-        <v>-24.23837291449131</v>
+        <v>-0.1774</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-24.2384</v>
+        <v>-0.1774</v>
       </c>
       <c r="N51" t="n">
-        <v>117</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.9814</v>
+        <v>-0.2568</v>
       </c>
       <c r="C52" t="n">
-        <v>-1.38698</v>
+        <v>-0</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4741344950520834</v>
+        <v>-0.5251</v>
       </c>
       <c r="E52" t="n">
-        <v>-14.7484</v>
+        <v>-0.2568</v>
       </c>
       <c r="F52" t="n">
-        <v>4.250316365550731</v>
+        <v>-0.2568</v>
       </c>
       <c r="G52" t="n">
-        <v>-18.99874222292092</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>4.250316365550731</v>
+        <v>-0.2568</v>
       </c>
       <c r="I52" t="n">
-        <v>3.483506711971991</v>
+        <v>-0.2568</v>
       </c>
       <c r="J52" t="n">
-        <v>-18.99874222292092</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="L52" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-15.5152</v>
+        <v>-0.2568</v>
       </c>
       <c r="N52" t="n">
-        <v>104</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-2.0374</v>
+        <v>-0.2839</v>
       </c>
       <c r="C53" t="n">
-        <v>-1.42618</v>
+        <v>-0</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4885507697596138</v>
+        <v>-0.5361</v>
       </c>
       <c r="E53" t="n">
-        <v>-15.1969</v>
+        <v>-0.2839</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.433879324282851</v>
+        <v>-0.7194</v>
       </c>
       <c r="G53" t="n">
-        <v>-13.76297912106037</v>
+        <v>0.4355</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.433879324282851</v>
+        <v>-0.7194</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9312824477300987</v>
+        <v>-0.7194</v>
       </c>
       <c r="J53" t="n">
-        <v>-13.76297912106037</v>
+        <v>0.4355</v>
       </c>
       <c r="K53" t="n">
         <v>42</v>
       </c>
       <c r="L53" t="n">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="M53" t="n">
-        <v>-14.6943</v>
+        <v>-0.2839</v>
       </c>
       <c r="N53" t="n">
-        <v>122</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>m1N1</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-2.102</v>
+        <v>-0.3084</v>
       </c>
       <c r="C54" t="n">
-        <v>-1.4714</v>
+        <v>-0</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5053722822971367</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>-15.7201</v>
+        <v>-0.3084</v>
       </c>
       <c r="F54" t="n">
-        <v>-15.72010835240014</v>
+        <v>-0.3084</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-15.6745562240397</v>
+        <v>-0.3084</v>
       </c>
       <c r="I54" t="n">
-        <v>-5.090190938734541</v>
+        <v>-0.3084</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-5.0902</v>
+        <v>-0.3084</v>
       </c>
       <c r="N54" t="n">
-        <v>21</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-2.1522</v>
+        <v>-0.3167</v>
       </c>
       <c r="C55" t="n">
-        <v>-1.50654</v>
+        <v>-0</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5185665045535768</v>
+        <v>-0.5493</v>
       </c>
       <c r="E55" t="n">
-        <v>-16.1305</v>
+        <v>-0.3167</v>
       </c>
       <c r="F55" t="n">
-        <v>-16.13052778132904</v>
+        <v>-0.3167</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-16.07249902406243</v>
+        <v>-0.3167</v>
       </c>
       <c r="I55" t="n">
-        <v>-27.58836172687005</v>
+        <v>-0.3167</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-27.5884</v>
+        <v>-0.3167</v>
       </c>
       <c r="N55" t="n">
-        <v>111</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-2.1571</v>
+        <v>-0.5928</v>
       </c>
       <c r="C56" t="n">
-        <v>-1.50997</v>
+        <v>-0</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5198611434618249</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>-16.1708</v>
+        <v>-0.5928</v>
       </c>
       <c r="F56" t="n">
-        <v>-16.17079881444226</v>
+        <v>-0.5928</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-16.11208601623911</v>
+        <v>-0.5928</v>
       </c>
       <c r="I56" t="n">
-        <v>-17.19176188330668</v>
+        <v>-0.5928</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-17.1918</v>
+        <v>-0.5928</v>
       </c>
       <c r="N56" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IceBerg</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-2.3003</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="C57" t="n">
-        <v>-1.61021</v>
+        <v>-0</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5581889231143707</v>
+        <v>-0.6663</v>
       </c>
       <c r="E57" t="n">
-        <v>-17.363</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>-17.36302258719497</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-17.32928619948315</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>-31.35350235061127</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>117</v>
+        <v>48</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-31.3535</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>117</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>aliStair</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-2.3505</v>
+        <v>-0.6201</v>
       </c>
       <c r="C58" t="n">
-        <v>-1.64535</v>
+        <v>-0</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5718541346190038</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>-17.7881</v>
+        <v>-0.6201</v>
       </c>
       <c r="F58" t="n">
-        <v>-17.78809260594403</v>
+        <v>0.7229</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>-1.343</v>
       </c>
       <c r="H58" t="n">
-        <v>-17.78514862389053</v>
+        <v>0.7229</v>
       </c>
       <c r="I58" t="n">
-        <v>-19.52699307674579</v>
+        <v>0.7229</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>-1.343</v>
       </c>
       <c r="K58" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M58" t="n">
-        <v>-19.527</v>
+        <v>-0.6201</v>
       </c>
       <c r="N58" t="n">
-        <v>71</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-2.4157</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="C59" t="n">
-        <v>-1.69099</v>
+        <v>-0</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5897929769298254</v>
+        <v>-0.6732</v>
       </c>
       <c r="E59" t="n">
-        <v>-18.3461</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>-18.34609816881526</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-18.40183001679664</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>-5.975852015763856</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-5.9759</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="N59" t="n">
-        <v>21</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2.4232</v>
+        <v>-0.6635</v>
       </c>
       <c r="C60" t="n">
-        <v>-1.69624</v>
+        <v>-0</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5918497826350815</v>
+        <v>-0.6894</v>
       </c>
       <c r="E60" t="n">
-        <v>-18.4101</v>
+        <v>-0.6635</v>
       </c>
       <c r="F60" t="n">
-        <v>10.85018272339457</v>
+        <v>-0.6635</v>
       </c>
       <c r="G60" t="n">
-        <v>-29.26025988290456</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>10.85018272339457</v>
+        <v>-0.6635</v>
       </c>
       <c r="I60" t="n">
-        <v>7.047025892514</v>
+        <v>-0.6635</v>
       </c>
       <c r="J60" t="n">
-        <v>-29.26025988290456</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="L60" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-22.2132</v>
+        <v>-0.6635</v>
       </c>
       <c r="N60" t="n">
-        <v>122</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>IceBerg</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-2.4413</v>
+        <v>-0.7432</v>
       </c>
       <c r="C61" t="n">
-        <v>-1.70891</v>
+        <v>-0</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5968936949180945</v>
+        <v>-0.7216</v>
       </c>
       <c r="E61" t="n">
-        <v>-18.567</v>
+        <v>-0.7432</v>
       </c>
       <c r="F61" t="n">
-        <v>-19.34045589524591</v>
+        <v>-0.7432</v>
       </c>
       <c r="G61" t="n">
-        <v>0.7734828188317469</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-19.55422746544846</v>
+        <v>-0.7432</v>
       </c>
       <c r="I61" t="n">
-        <v>-12.70016835384797</v>
+        <v>-0.7432</v>
       </c>
       <c r="J61" t="n">
-        <v>0.7734828188317469</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="L61" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-11.9267</v>
+        <v>-0.7432</v>
       </c>
       <c r="N61" t="n">
-        <v>214</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>aliStair</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-2.6136</v>
+        <v>-0.7456</v>
       </c>
       <c r="C62" t="n">
-        <v>-1.82952</v>
+        <v>-0</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6454442992760259</v>
+        <v>-0.7226</v>
       </c>
       <c r="E62" t="n">
-        <v>-20.0772</v>
+        <v>-0.7456</v>
       </c>
       <c r="F62" t="n">
-        <v>-20.07718799681309</v>
+        <v>-0.7456</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-20.45434961126249</v>
+        <v>-0.7456</v>
       </c>
       <c r="I62" t="n">
-        <v>-15.18261002073092</v>
+        <v>-0.7456</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-15.1826</v>
+        <v>-0.7456</v>
       </c>
       <c r="N62" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-2.8655</v>
+        <v>-0.7509</v>
       </c>
       <c r="C63" t="n">
-        <v>-2.00585</v>
+        <v>-0</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7191311432831253</v>
+        <v>-0.7247</v>
       </c>
       <c r="E63" t="n">
-        <v>-22.3693</v>
+        <v>-0.7509</v>
       </c>
       <c r="F63" t="n">
-        <v>-22.36929069518969</v>
+        <v>-0.7509</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-23.52846705464475</v>
+        <v>-0.7509</v>
       </c>
       <c r="I63" t="n">
-        <v>-17.46442915396311</v>
+        <v>-0.7509</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-17.4644</v>
+        <v>-0.7509</v>
       </c>
       <c r="N63" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>dennyslaw</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-2.8979</v>
+        <v>-0.8004</v>
       </c>
       <c r="C64" t="n">
-        <v>-2.02853</v>
+        <v>-0</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7288490502439433</v>
+        <v>-0.7447</v>
       </c>
       <c r="E64" t="n">
-        <v>-22.6716</v>
+        <v>-0.8004</v>
       </c>
       <c r="F64" t="n">
-        <v>-22.67157587333245</v>
+        <v>0.1469</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>-0.9473</v>
       </c>
       <c r="H64" t="n">
-        <v>-23.96696584803491</v>
+        <v>0.1469</v>
       </c>
       <c r="I64" t="n">
-        <v>-7.783086847557727</v>
+        <v>0.1469</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>-0.9473</v>
       </c>
       <c r="K64" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M64" t="n">
-        <v>-7.7831</v>
+        <v>-0.8004</v>
       </c>
       <c r="N64" t="n">
-        <v>21</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-2.923</v>
+        <v>-0.8519</v>
       </c>
       <c r="C65" t="n">
-        <v>-2.0461</v>
+        <v>-0</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7364332492389644</v>
+        <v>-0.7655</v>
       </c>
       <c r="E65" t="n">
-        <v>-22.9075</v>
+        <v>-0.8519</v>
       </c>
       <c r="F65" t="n">
-        <v>-22.90748993934725</v>
+        <v>-0.8519</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-24.31485589759397</v>
+        <v>-0.8519</v>
       </c>
       <c r="I65" t="n">
-        <v>-25.94420191135027</v>
+        <v>-0.8519</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-25.9442</v>
+        <v>-0.8519</v>
       </c>
       <c r="N65" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-3.0072</v>
+        <v>-0.8767</v>
       </c>
       <c r="C66" t="n">
-        <v>-2.10504</v>
+        <v>-0</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7620227463031719</v>
+        <v>-0.7755</v>
       </c>
       <c r="E66" t="n">
-        <v>-23.7035</v>
+        <v>-0.8767</v>
       </c>
       <c r="F66" t="n">
-        <v>-23.70347674080829</v>
+        <v>-0.8767</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-25.52634882506148</v>
+        <v>-0.8767</v>
       </c>
       <c r="I66" t="n">
-        <v>-27.2368773545759</v>
+        <v>-0.8767</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-27.2369</v>
+        <v>-0.8767</v>
       </c>
       <c r="N66" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-3.0257</v>
+        <v>-0.898</v>
       </c>
       <c r="C67" t="n">
-        <v>-2.11799</v>
+        <v>-0</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7677078889065535</v>
+        <v>-0.7841</v>
       </c>
       <c r="E67" t="n">
-        <v>-23.8803</v>
+        <v>-0.898</v>
       </c>
       <c r="F67" t="n">
-        <v>-20.75662177917143</v>
+        <v>-0.898</v>
       </c>
       <c r="G67" t="n">
-        <v>-3.123696986525475</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-21.32114876708556</v>
+        <v>-0.898</v>
       </c>
       <c r="I67" t="n">
-        <v>-17.47454976271445</v>
+        <v>-0.898</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.123696986525475</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="L67" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-20.5982</v>
+        <v>-0.898</v>
       </c>
       <c r="N67" t="n">
-        <v>227</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-3.0359</v>
+        <v>-0.9895</v>
       </c>
       <c r="C68" t="n">
-        <v>-2.12513</v>
+        <v>-0</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7708436833410873</v>
+        <v>-0.8211000000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>-23.9779</v>
+        <v>-0.9895</v>
       </c>
       <c r="F68" t="n">
-        <v>-23.97786077583181</v>
+        <v>-0.9895</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-25.95780259621892</v>
+        <v>-0.9895</v>
       </c>
       <c r="I68" t="n">
-        <v>-19.26764728791508</v>
+        <v>-0.9895</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3577,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-19.2676</v>
+        <v>-0.9895</v>
       </c>
       <c r="N68" t="n">
         <v>48</v>
@@ -3586,185 +3574,185 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>MistR</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-3.066</v>
+        <v>-1.1521</v>
       </c>
       <c r="C69" t="n">
-        <v>-2.1462</v>
+        <v>-0</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7801487001742011</v>
+        <v>-0.8868</v>
       </c>
       <c r="E69" t="n">
-        <v>-24.2673</v>
+        <v>-1.1521</v>
       </c>
       <c r="F69" t="n">
-        <v>-24.26730259518242</v>
+        <v>-1.1521</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-26.4208401826737</v>
+        <v>-1.1521</v>
       </c>
       <c r="I69" t="n">
-        <v>-19.61134529023202</v>
+        <v>-1.1521</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-19.6113</v>
+        <v>-1.1521</v>
       </c>
       <c r="N69" t="n">
-        <v>48</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-3.2015</v>
+        <v>-1.2351</v>
       </c>
       <c r="C70" t="n">
-        <v>-2.24105</v>
+        <v>-0</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8226000920367945</v>
+        <v>-0.9203</v>
       </c>
       <c r="E70" t="n">
-        <v>-25.5878</v>
+        <v>-1.2351</v>
       </c>
       <c r="F70" t="n">
-        <v>-25.5877954341581</v>
+        <v>-1.2351</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-28.64035649851382</v>
+        <v>-1.2351</v>
       </c>
       <c r="I70" t="n">
-        <v>-31.44533986692496</v>
+        <v>-1.2351</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-31.4453</v>
+        <v>-1.2351</v>
       </c>
       <c r="N70" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-3.3744</v>
+        <v>-1.2374</v>
       </c>
       <c r="C71" t="n">
-        <v>-2.36208</v>
+        <v>-0</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8782275185887838</v>
+        <v>-0.9212</v>
       </c>
       <c r="E71" t="n">
-        <v>-27.3181</v>
+        <v>-1.2374</v>
       </c>
       <c r="F71" t="n">
-        <v>-14.65311124882528</v>
+        <v>-1.2374</v>
       </c>
       <c r="G71" t="n">
-        <v>-12.66503071084389</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-14.65311124882528</v>
+        <v>-1.2374</v>
       </c>
       <c r="I71" t="n">
-        <v>-26.28496244634638</v>
+        <v>-1.2374</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.66503071084389</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="L71" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-38.95</v>
+        <v>-1.2374</v>
       </c>
       <c r="N71" t="n">
-        <v>180</v>
+        <v>111</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-3.488</v>
+        <v>-1.5052</v>
       </c>
       <c r="C72" t="n">
-        <v>-2.4416</v>
+        <v>-0</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9157207418926685</v>
+        <v>-1.0294</v>
       </c>
       <c r="E72" t="n">
-        <v>-28.4844</v>
+        <v>-1.5052</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.119583210656451</v>
+        <v>-1.5052</v>
       </c>
       <c r="G72" t="n">
-        <v>-27.36482281505674</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.119583210656451</v>
+        <v>-1.5052</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.073414830835566</v>
+        <v>-1.5052</v>
       </c>
       <c r="J72" t="n">
-        <v>-27.36482281505674</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="L72" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-28.4382</v>
+        <v>-1.5052</v>
       </c>
       <c r="N72" t="n">
-        <v>179</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73">
@@ -3774,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-3.6438</v>
+        <v>-1.6828</v>
       </c>
       <c r="C73" t="n">
-        <v>-2.55066</v>
+        <v>-0</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9683116089138413</v>
+        <v>-1.1012</v>
       </c>
       <c r="E73" t="n">
-        <v>-30.1203</v>
+        <v>-1.6828</v>
       </c>
       <c r="F73" t="n">
-        <v>-30.12029734163902</v>
+        <v>-1.6828</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-37.77658333824984</v>
+        <v>-1.6828</v>
       </c>
       <c r="I73" t="n">
-        <v>-28.04035051911328</v>
+        <v>-1.6828</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3807,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-28.0404</v>
+        <v>-1.6828</v>
       </c>
       <c r="N73" t="n">
         <v>48</v>
@@ -3816,139 +3804,139 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-3.8834</v>
+        <v>-1.8246</v>
       </c>
       <c r="C74" t="n">
-        <v>-2.71838</v>
+        <v>-0</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.052093029223106</v>
+        <v>-1.1585</v>
       </c>
       <c r="E74" t="n">
-        <v>-32.7264</v>
+        <v>-1.8246</v>
       </c>
       <c r="F74" t="n">
-        <v>-5.630106493821308</v>
+        <v>-1.0609</v>
       </c>
       <c r="G74" t="n">
-        <v>-27.09629539948216</v>
+        <v>-0.7637</v>
       </c>
       <c r="H74" t="n">
-        <v>-5.630106493821308</v>
+        <v>-1.0609</v>
       </c>
       <c r="I74" t="n">
-        <v>-4.614365631533959</v>
+        <v>-1.0658</v>
       </c>
       <c r="J74" t="n">
-        <v>-27.09629539948216</v>
+        <v>-0.7637</v>
       </c>
       <c r="K74" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="L74" t="n">
-        <v>174</v>
+        <v>64</v>
       </c>
       <c r="M74" t="n">
-        <v>-31.7107</v>
+        <v>-1.8295</v>
       </c>
       <c r="N74" t="n">
-        <v>227</v>
+        <v>180</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-4.0695</v>
+        <v>-2.1033</v>
       </c>
       <c r="C75" t="n">
-        <v>-2.84865</v>
+        <v>-0</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.119564511049136</v>
+        <v>-1.271</v>
       </c>
       <c r="E75" t="n">
-        <v>-34.8252</v>
+        <v>-2.1033</v>
       </c>
       <c r="F75" t="n">
-        <v>-29.79900449312398</v>
+        <v>-1.6497</v>
       </c>
       <c r="G75" t="n">
-        <v>-5.02616506543615</v>
+        <v>-0.4536</v>
       </c>
       <c r="H75" t="n">
-        <v>-37.04238922589143</v>
+        <v>-1.6497</v>
       </c>
       <c r="I75" t="n">
-        <v>-30.35948395317905</v>
+        <v>-1.6497</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.02616506543615</v>
+        <v>-0.4536</v>
       </c>
       <c r="K75" t="n">
         <v>53</v>
       </c>
       <c r="L75" t="n">
-        <v>51</v>
+        <v>174</v>
       </c>
       <c r="M75" t="n">
-        <v>-35.3856</v>
+        <v>-2.1033</v>
       </c>
       <c r="N75" t="n">
-        <v>104</v>
+        <v>227</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-4.3523</v>
+        <v>-2.3379</v>
       </c>
       <c r="C76" t="n">
-        <v>-3.046609999999999</v>
+        <v>-0</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.226429337989436</v>
+        <v>-1.3658</v>
       </c>
       <c r="E76" t="n">
-        <v>-38.1493</v>
+        <v>-2.3379</v>
       </c>
       <c r="F76" t="n">
-        <v>-38.14930647189858</v>
+        <v>-2.3333</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>-0.0046</v>
       </c>
       <c r="H76" t="n">
-        <v>-61.69172873317198</v>
+        <v>-2.3333</v>
       </c>
       <c r="I76" t="n">
-        <v>-20.03391190819502</v>
+        <v>-2.3333</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>-0.0046</v>
       </c>
       <c r="K76" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M76" t="n">
-        <v>-20.0339</v>
+        <v>-2.3379</v>
       </c>
       <c r="N76" t="n">
-        <v>21</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3966,52 +3954,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -4051,10 +4039,10 @@
         <v>1.33</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5601181734819014</v>
+        <v>0.5258</v>
       </c>
       <c r="J2" t="n">
-        <v>16.80354520445704</v>
+        <v>15.774</v>
       </c>
     </row>
     <row r="3">
@@ -4091,10 +4079,10 @@
         <v>1.29</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4858518218613949</v>
+        <v>0.4737</v>
       </c>
       <c r="J3" t="n">
-        <v>14.57555465584185</v>
+        <v>14.211</v>
       </c>
     </row>
     <row r="4">
@@ -4131,10 +4119,10 @@
         <v>1.08</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1118991452305651</v>
+        <v>0.1355</v>
       </c>
       <c r="J4" t="n">
-        <v>3.356974356916953</v>
+        <v>4.065</v>
       </c>
     </row>
     <row r="5">
@@ -4171,10 +4159,10 @@
         <v>1.07</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0947772510373415</v>
+        <v>0.1162</v>
       </c>
       <c r="J5" t="n">
-        <v>2.843317531120245</v>
+        <v>3.486</v>
       </c>
     </row>
     <row r="6">
@@ -4211,10 +4199,10 @@
         <v>0.74</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4131812964241247</v>
+        <v>-0.4851</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.39543889272374</v>
+        <v>-14.553</v>
       </c>
     </row>
     <row r="7">
@@ -4251,10 +4239,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03456245320444711</v>
+        <v>0.1072</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.036873596133413</v>
+        <v>3.216</v>
       </c>
     </row>
     <row r="8">
@@ -4291,10 +4279,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.04956617466677306</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.486985240003192</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="9">
@@ -4331,10 +4319,10 @@
         <v>0.99</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.09331063590772429</v>
+        <v>-0.0142</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.799319077231729</v>
+        <v>-0.426</v>
       </c>
     </row>
     <row r="10">
@@ -4371,10 +4359,10 @@
         <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1312446094963181</v>
+        <v>-0.0973</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.937338284889544</v>
+        <v>-2.919</v>
       </c>
     </row>
     <row r="11">
@@ -4411,10 +4399,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3115380930868833</v>
+        <v>-0.3156</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.3461427926065</v>
+        <v>-9.468</v>
       </c>
     </row>
     <row r="12">
@@ -4451,10 +4439,10 @@
         <v>1.36</v>
       </c>
       <c r="I12" t="n">
-        <v>0.402922076019039</v>
+        <v>0.6555</v>
       </c>
       <c r="J12" t="n">
-        <v>7.655519444361741</v>
+        <v>12.4545</v>
       </c>
     </row>
     <row r="13">
@@ -4491,10 +4479,10 @@
         <v>0.95</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2744220987191076</v>
+        <v>-0.046</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.214019875663045</v>
+        <v>-0.874</v>
       </c>
     </row>
     <row r="14">
@@ -4531,10 +4519,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6403574378404695</v>
+        <v>-0.497</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.16679131896892</v>
+        <v>-9.443</v>
       </c>
     </row>
     <row r="15">
@@ -4571,10 +4559,10 @@
         <v>0.61</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7571889278217104</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.3865896286125</v>
+        <v>-11.4817</v>
       </c>
     </row>
     <row r="16">
@@ -4611,10 +4599,10 @@
         <v>0.59</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7860551094857444</v>
+        <v>-0.6301</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.93504708022914</v>
+        <v>-11.9719</v>
       </c>
     </row>
     <row r="17">
@@ -4651,10 +4639,10 @@
         <v>1.71</v>
       </c>
       <c r="I17" t="n">
-        <v>1.179552072300831</v>
+        <v>1.5652</v>
       </c>
       <c r="J17" t="n">
-        <v>22.41148937371578</v>
+        <v>29.7388</v>
       </c>
     </row>
     <row r="18">
@@ -4691,10 +4679,10 @@
         <v>1.6</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9944047105128304</v>
+        <v>1.36</v>
       </c>
       <c r="J18" t="n">
-        <v>18.89368949974378</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="19">
@@ -4731,10 +4719,10 @@
         <v>1.49</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8025625721818128</v>
+        <v>1.1425</v>
       </c>
       <c r="J19" t="n">
-        <v>15.24868887145444</v>
+        <v>21.7075</v>
       </c>
     </row>
     <row r="20">
@@ -4771,10 +4759,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1094435268539535</v>
+        <v>-0.3313</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.079427010225117</v>
+        <v>-6.2947</v>
       </c>
     </row>
     <row r="21">
@@ -4811,10 +4799,10 @@
         <v>0.85</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2707926132950398</v>
+        <v>-0.6367</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.145059652605757</v>
+        <v>-12.0973</v>
       </c>
     </row>
     <row r="22">
@@ -4851,10 +4839,10 @@
         <v>1.19</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1276079104656936</v>
+        <v>0.4322</v>
       </c>
       <c r="J22" t="n">
-        <v>2.424550298848178</v>
+        <v>8.2118</v>
       </c>
     </row>
     <row r="23">
@@ -4891,10 +4879,10 @@
         <v>1.08</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.06148293364038827</v>
+        <v>0.2594</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.168175739167377</v>
+        <v>4.9286</v>
       </c>
     </row>
     <row r="24">
@@ -4931,10 +4919,10 @@
         <v>0.7</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6109580869967235</v>
+        <v>-0.4799</v>
       </c>
       <c r="J24" t="n">
-        <v>-11.60820365293775</v>
+        <v>-9.1181</v>
       </c>
     </row>
     <row r="25">
@@ -4971,10 +4959,10 @@
         <v>0.66</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6697187338888505</v>
+        <v>-0.5354</v>
       </c>
       <c r="J25" t="n">
-        <v>-12.72465594388816</v>
+        <v>-10.1726</v>
       </c>
     </row>
     <row r="26">
@@ -5011,10 +4999,10 @@
         <v>0.52</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8715629273347199</v>
+        <v>-0.7156</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.55969561935968</v>
+        <v>-13.5964</v>
       </c>
     </row>
     <row r="27">
@@ -5051,10 +5039,10 @@
         <v>1.73</v>
       </c>
       <c r="I27" t="n">
-        <v>1.228705458779888</v>
+        <v>1.6059</v>
       </c>
       <c r="J27" t="n">
-        <v>23.34540371681788</v>
+        <v>30.5121</v>
       </c>
     </row>
     <row r="28">
@@ -5091,10 +5079,10 @@
         <v>1.5</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8378162092410673</v>
+        <v>1.1677</v>
       </c>
       <c r="J28" t="n">
-        <v>15.91850797558028</v>
+        <v>22.1863</v>
       </c>
     </row>
     <row r="29">
@@ -5131,10 +5119,10 @@
         <v>1.32</v>
       </c>
       <c r="I29" t="n">
-        <v>0.527160782837974</v>
+        <v>0.7645</v>
       </c>
       <c r="J29" t="n">
-        <v>10.0160548739215</v>
+        <v>14.5255</v>
       </c>
     </row>
     <row r="30">
@@ -5171,10 +5159,10 @@
         <v>1.17</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2720383452075059</v>
+        <v>0.3753</v>
       </c>
       <c r="J30" t="n">
-        <v>5.168728558942611</v>
+        <v>7.1307</v>
       </c>
     </row>
     <row r="31">
@@ -5211,10 +5199,10 @@
         <v>0.84</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2707926132950398</v>
+        <v>-0.6592</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.145059652605757</v>
+        <v>-12.5248</v>
       </c>
     </row>
     <row r="32">
@@ -5251,10 +5239,10 @@
         <v>2.21</v>
       </c>
       <c r="I32" t="n">
-        <v>1.639315072882294</v>
+        <v>1.322</v>
       </c>
       <c r="J32" t="n">
-        <v>22.95041102035212</v>
+        <v>18.508</v>
       </c>
     </row>
     <row r="33">
@@ -5291,10 +5279,10 @@
         <v>1.73</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9914007699098364</v>
+        <v>0.8573</v>
       </c>
       <c r="J33" t="n">
-        <v>13.87961077873771</v>
+        <v>12.0022</v>
       </c>
     </row>
     <row r="34">
@@ -5331,10 +5319,10 @@
         <v>1.5</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6769816058833326</v>
+        <v>0.5775</v>
       </c>
       <c r="J34" t="n">
-        <v>9.477742482366656</v>
+        <v>8.085000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -5371,10 +5359,10 @@
         <v>1.27</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3351177906886713</v>
+        <v>0.3007</v>
       </c>
       <c r="J35" t="n">
-        <v>4.691649069641397</v>
+        <v>4.2098</v>
       </c>
     </row>
     <row r="36">
@@ -5411,10 +5399,10 @@
         <v>1.19</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2172265863969534</v>
+        <v>0.1972</v>
       </c>
       <c r="J36" t="n">
-        <v>3.041172209557347</v>
+        <v>2.7608</v>
       </c>
     </row>
     <row r="37">
@@ -5451,10 +5439,10 @@
         <v>1.08</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1008596095840295</v>
+        <v>0.3495</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.412034534176413</v>
+        <v>4.893</v>
       </c>
     </row>
     <row r="38">
@@ -5491,10 +5479,10 @@
         <v>0.7</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.5098739809385736</v>
+        <v>-0.3628</v>
       </c>
       <c r="J38" t="n">
-        <v>-7.13823573314003</v>
+        <v>-5.0792</v>
       </c>
     </row>
     <row r="39">
@@ -5531,10 +5519,10 @@
         <v>0.59</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6136980802093881</v>
+        <v>-0.5614</v>
       </c>
       <c r="J39" t="n">
-        <v>-8.591773122931434</v>
+        <v>-7.8596</v>
       </c>
     </row>
     <row r="40">
@@ -5571,10 +5559,10 @@
         <v>0.44</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7704927515381992</v>
+        <v>-0.7725</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.78689852153479</v>
+        <v>-10.815</v>
       </c>
     </row>
     <row r="41">
@@ -5611,10 +5599,10 @@
         <v>0.37</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8432773422172551</v>
+        <v>-0.8616</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.80588279104157</v>
+        <v>-12.0624</v>
       </c>
     </row>
     <row r="42">
@@ -5651,10 +5639,10 @@
         <v>1.13</v>
       </c>
       <c r="I42" t="n">
-        <v>0.02607642927297927</v>
+        <v>0.3146</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5476050147325646</v>
+        <v>6.6066</v>
       </c>
     </row>
     <row r="43">
@@ -5691,10 +5679,10 @@
         <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.09107426737514188</v>
+        <v>0.1566</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.912559614877979</v>
+        <v>3.2886</v>
       </c>
     </row>
     <row r="44">
@@ -5731,10 +5719,10 @@
         <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.09107426737514188</v>
+        <v>0.1566</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.912559614877979</v>
+        <v>3.2886</v>
       </c>
     </row>
     <row r="45">
@@ -5771,10 +5759,10 @@
         <v>0.76</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4154257663692505</v>
+        <v>-0.4152</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.723941093754261</v>
+        <v>-8.719200000000001</v>
       </c>
     </row>
     <row r="46">
@@ -5811,10 +5799,10 @@
         <v>0.53</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6848513249009773</v>
+        <v>-0.7153</v>
       </c>
       <c r="J46" t="n">
-        <v>-14.38187782292052</v>
+        <v>-15.0213</v>
       </c>
     </row>
     <row r="47">
@@ -5851,10 +5839,10 @@
         <v>1.56</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8121064292856195</v>
+        <v>1.3106</v>
       </c>
       <c r="J47" t="n">
-        <v>17.05423501499801</v>
+        <v>27.5226</v>
       </c>
     </row>
     <row r="48">
@@ -5891,10 +5879,10 @@
         <v>1.47</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6696112271816703</v>
+        <v>1.1309</v>
       </c>
       <c r="J48" t="n">
-        <v>14.06183577081508</v>
+        <v>23.7489</v>
       </c>
     </row>
     <row r="49">
@@ -5931,10 +5919,10 @@
         <v>1.2</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2510630195350574</v>
+        <v>0.4757</v>
       </c>
       <c r="J49" t="n">
-        <v>5.272323410236206</v>
+        <v>9.989699999999999</v>
       </c>
     </row>
     <row r="50">
@@ -5971,10 +5959,10 @@
         <v>1.17</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2022979180607895</v>
+        <v>0.3976</v>
       </c>
       <c r="J50" t="n">
-        <v>4.248256279276579</v>
+        <v>8.349600000000001</v>
       </c>
     </row>
     <row r="51">
@@ -6011,10 +5999,10 @@
         <v>0.91</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1551869413014452</v>
+        <v>-0.4658</v>
       </c>
       <c r="J51" t="n">
-        <v>-3.258925767330349</v>
+        <v>-9.7818</v>
       </c>
     </row>
     <row r="52">
@@ -6051,10 +6039,10 @@
         <v>1.36</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2630480778421975</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>4.734865401159555</v>
+        <v>11.5128</v>
       </c>
     </row>
     <row r="53">
@@ -6091,10 +6079,10 @@
         <v>0.82</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.4254469421231494</v>
+        <v>-0.3168</v>
       </c>
       <c r="J53" t="n">
-        <v>-7.658044958216689</v>
+        <v>-5.7024</v>
       </c>
     </row>
     <row r="54">
@@ -6131,10 +6119,10 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.4724328440234613</v>
+        <v>-0.3794</v>
       </c>
       <c r="J54" t="n">
-        <v>-8.503791192422304</v>
+        <v>-6.8292</v>
       </c>
     </row>
     <row r="55">
@@ -6171,10 +6159,10 @@
         <v>0.73</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5318597488340944</v>
+        <v>-0.4524</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.573475479013698</v>
+        <v>-8.1432</v>
       </c>
     </row>
     <row r="56">
@@ -6211,10 +6199,10 @@
         <v>0.71</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5556191417567745</v>
+        <v>-0.4804</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.00114455162194</v>
+        <v>-8.6472</v>
       </c>
     </row>
     <row r="57">
@@ -6251,10 +6239,10 @@
         <v>2.12</v>
       </c>
       <c r="I57" t="n">
-        <v>1.637943424509258</v>
+        <v>2.0168</v>
       </c>
       <c r="J57" t="n">
-        <v>29.48298164116665</v>
+        <v>36.3024</v>
       </c>
     </row>
     <row r="58">
@@ -6291,10 +6279,10 @@
         <v>1.53</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7934729524036532</v>
+        <v>1.2186</v>
       </c>
       <c r="J58" t="n">
-        <v>14.28251314326576</v>
+        <v>21.9348</v>
       </c>
     </row>
     <row r="59">
@@ -6331,10 +6319,10 @@
         <v>1.24</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3470348376335017</v>
+        <v>0.5397</v>
       </c>
       <c r="J59" t="n">
-        <v>6.246627077403032</v>
+        <v>9.714600000000001</v>
       </c>
     </row>
     <row r="60">
@@ -6371,10 +6359,10 @@
         <v>0.93</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1114092513139165</v>
+        <v>-0.4263</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.005366523650496</v>
+        <v>-7.6734</v>
       </c>
     </row>
     <row r="61">
@@ -6411,10 +6399,10 @@
         <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2041203494672616</v>
+        <v>-0.6633</v>
       </c>
       <c r="J61" t="n">
-        <v>-3.674166290410708</v>
+        <v>-11.9394</v>
       </c>
     </row>
     <row r="62">
@@ -6451,10 +6439,10 @@
         <v>2.88</v>
       </c>
       <c r="I62" t="n">
-        <v>2.152964110281077</v>
+        <v>2.5208</v>
       </c>
       <c r="J62" t="n">
-        <v>36.6003898747783</v>
+        <v>42.8536</v>
       </c>
     </row>
     <row r="63">
@@ -6491,10 +6479,10 @@
         <v>1.89</v>
       </c>
       <c r="I63" t="n">
-        <v>1.042260102063574</v>
+        <v>1.7456</v>
       </c>
       <c r="J63" t="n">
-        <v>17.71842173508076</v>
+        <v>29.6752</v>
       </c>
     </row>
     <row r="64">
@@ -6531,10 +6519,10 @@
         <v>1.58</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6270055043761954</v>
+        <v>1.1656</v>
       </c>
       <c r="J64" t="n">
-        <v>10.65909357439532</v>
+        <v>19.8152</v>
       </c>
     </row>
     <row r="65">
@@ -6571,10 +6559,10 @@
         <v>0.91</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2650502655051893</v>
+        <v>-0.5312</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.505854513588218</v>
+        <v>-9.0304</v>
       </c>
     </row>
     <row r="66">
@@ -6611,10 +6599,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4659101604477096</v>
+        <v>-0.9503</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.920472727611063</v>
+        <v>-16.1551</v>
       </c>
     </row>
     <row r="67">
@@ -6651,10 +6639,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.2538490482787155</v>
+        <v>0.0017</v>
       </c>
       <c r="J67" t="n">
-        <v>-4.315433820738162</v>
+        <v>0.0289</v>
       </c>
     </row>
     <row r="68">
@@ -6691,10 +6679,10 @@
         <v>0.75</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.480525948215044</v>
+        <v>-0.3155</v>
       </c>
       <c r="J68" t="n">
-        <v>-8.168941119655747</v>
+        <v>-5.3635</v>
       </c>
     </row>
     <row r="69">
@@ -6731,10 +6719,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5429883919627717</v>
+        <v>-0.4263</v>
       </c>
       <c r="J69" t="n">
-        <v>-9.230802663367118</v>
+        <v>-7.2471</v>
       </c>
     </row>
     <row r="70">
@@ -6771,10 +6759,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6874586695259544</v>
+        <v>-0.6294</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.68679738194122</v>
+        <v>-10.6998</v>
       </c>
     </row>
     <row r="71">
@@ -6811,10 +6799,10 @@
         <v>0.52</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7340785824803331</v>
+        <v>-0.6835</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.47933590216566</v>
+        <v>-11.6195</v>
       </c>
     </row>
     <row r="72">
@@ -6851,10 +6839,10 @@
         <v>1.61</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8888432579496952</v>
+        <v>1.4209</v>
       </c>
       <c r="J72" t="n">
-        <v>17.7768651589939</v>
+        <v>28.418</v>
       </c>
     </row>
     <row r="73">
@@ -6891,10 +6879,10 @@
         <v>1.57</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8333214462691247</v>
+        <v>1.3443</v>
       </c>
       <c r="J73" t="n">
-        <v>16.66642892538249</v>
+        <v>26.886</v>
       </c>
     </row>
     <row r="74">
@@ -6931,10 +6919,10 @@
         <v>1.35</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5150801777967916</v>
+        <v>0.8889</v>
       </c>
       <c r="J74" t="n">
-        <v>10.30160355593583</v>
+        <v>17.778</v>
       </c>
     </row>
     <row r="75">
@@ -6971,10 +6959,10 @@
         <v>1.1</v>
       </c>
       <c r="I75" t="n">
-        <v>0.161957192497854</v>
+        <v>0.2214</v>
       </c>
       <c r="J75" t="n">
-        <v>3.239143849957079</v>
+        <v>4.428</v>
       </c>
     </row>
     <row r="76">
@@ -7011,10 +6999,10 @@
         <v>0.53</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.557796820007588</v>
+        <v>-1.3072</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.15593640015176</v>
+        <v>-26.144</v>
       </c>
     </row>
     <row r="77">
@@ -7051,10 +7039,10 @@
         <v>1.35</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3759300628973677</v>
+        <v>0.6373</v>
       </c>
       <c r="J77" t="n">
-        <v>7.518601257947354</v>
+        <v>12.746</v>
       </c>
     </row>
     <row r="78">
@@ -7091,10 +7079,10 @@
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1177105671660987</v>
+        <v>0.0722</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.354211343321974</v>
+        <v>1.444</v>
       </c>
     </row>
     <row r="79">
@@ -7131,10 +7119,10 @@
         <v>0.71</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4629496065574952</v>
+        <v>-0.4731</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.258992131149903</v>
+        <v>-9.462</v>
       </c>
     </row>
     <row r="80">
@@ -7171,10 +7159,10 @@
         <v>0.64</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5488516119193002</v>
+        <v>-0.5684</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.977032238386</v>
+        <v>-11.368</v>
       </c>
     </row>
     <row r="81">
@@ -7211,10 +7199,10 @@
         <v>0.57</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6333098670788619</v>
+        <v>-0.6583</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.66619734157724</v>
+        <v>-13.166</v>
       </c>
     </row>
     <row r="82">
@@ -7251,10 +7239,10 @@
         <v>1.35</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4493194158292622</v>
+        <v>0.9268</v>
       </c>
       <c r="J82" t="n">
-        <v>10.33434656407303</v>
+        <v>21.3164</v>
       </c>
     </row>
     <row r="83">
@@ -7291,10 +7279,10 @@
         <v>1.2</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2332736768397884</v>
+        <v>0.5651</v>
       </c>
       <c r="J83" t="n">
-        <v>5.365294567315133</v>
+        <v>12.9973</v>
       </c>
     </row>
     <row r="84">
@@ -7331,10 +7319,10 @@
         <v>1.15</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1711488915084798</v>
+        <v>0.4067</v>
       </c>
       <c r="J84" t="n">
-        <v>3.936424504695035</v>
+        <v>9.354100000000001</v>
       </c>
     </row>
     <row r="85">
@@ -7371,10 +7359,10 @@
         <v>1.07</v>
       </c>
       <c r="I85" t="n">
-        <v>0.05928174569576963</v>
+        <v>0.1651</v>
       </c>
       <c r="J85" t="n">
-        <v>1.363480151002701</v>
+        <v>3.7973</v>
       </c>
     </row>
     <row r="86">
@@ -7411,10 +7399,10 @@
         <v>1.04</v>
       </c>
       <c r="I86" t="n">
-        <v>0.01532380054024827</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>0.3524474124257103</v>
+        <v>1.5318</v>
       </c>
     </row>
     <row r="87">
@@ -7451,10 +7439,10 @@
         <v>1.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3206566066513885</v>
+        <v>0.5425</v>
       </c>
       <c r="J87" t="n">
-        <v>7.375101952981936</v>
+        <v>12.4775</v>
       </c>
     </row>
     <row r="88">
@@ -7491,10 +7479,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.08427206111677804</v>
+        <v>0.002</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.938257405685895</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="89">
@@ -7531,10 +7519,10 @@
         <v>0.93</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1414197713103098</v>
+        <v>-0.1432</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.252654740137125</v>
+        <v>-3.2936</v>
       </c>
     </row>
     <row r="90">
@@ -7571,10 +7559,10 @@
         <v>0.79</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2868467480218624</v>
+        <v>-0.3818</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.597475204502835</v>
+        <v>-8.7814</v>
       </c>
     </row>
     <row r="91">
@@ -7611,10 +7599,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4144290604084722</v>
+        <v>-0.5471</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.531868389394859</v>
+        <v>-12.5833</v>
       </c>
     </row>
     <row r="92">
@@ -7651,10 +7639,10 @@
         <v>1.81</v>
       </c>
       <c r="I92" t="n">
-        <v>1.074502518121595</v>
+        <v>1.769</v>
       </c>
       <c r="J92" t="n">
-        <v>30.08607050740465</v>
+        <v>49.532</v>
       </c>
     </row>
     <row r="93">
@@ -7691,10 +7679,10 @@
         <v>1.34</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4418551820956259</v>
+        <v>0.8927</v>
       </c>
       <c r="J93" t="n">
-        <v>12.37194509867752</v>
+        <v>24.9956</v>
       </c>
     </row>
     <row r="94">
@@ -7731,10 +7719,10 @@
         <v>1.17</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2080978460452349</v>
+        <v>0.4473</v>
       </c>
       <c r="J94" t="n">
-        <v>5.826739689266577</v>
+        <v>12.5244</v>
       </c>
     </row>
     <row r="95">
@@ -7771,10 +7759,10 @@
         <v>0.98</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.04651319996524537</v>
+        <v>-0.2179</v>
       </c>
       <c r="J95" t="n">
-        <v>-1.30236959902687</v>
+        <v>-6.1012</v>
       </c>
     </row>
     <row r="96">
@@ -7811,10 +7799,10 @@
         <v>0.62</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4035498275654902</v>
+        <v>-1.1206</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.29939517183373</v>
+        <v>-31.3768</v>
       </c>
     </row>
     <row r="97">
@@ -7851,10 +7839,10 @@
         <v>1.49</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5386333184634391</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="J97" t="n">
-        <v>15.08173291697629</v>
+        <v>21.6916</v>
       </c>
     </row>
     <row r="98">
@@ -7891,10 +7879,10 @@
         <v>0.93</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1705436023413663</v>
+        <v>-0.1432</v>
       </c>
       <c r="J98" t="n">
-        <v>-4.775220865558257</v>
+        <v>-4.0096</v>
       </c>
     </row>
     <row r="99">
@@ -7931,10 +7919,10 @@
         <v>0.92</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1796722385945363</v>
+        <v>-0.1647</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.030822680647017</v>
+        <v>-4.6116</v>
       </c>
     </row>
     <row r="100">
@@ -7971,10 +7959,10 @@
         <v>0.67</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4429023935149316</v>
+        <v>-0.5471</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.40126701841809</v>
+        <v>-15.3188</v>
       </c>
     </row>
     <row r="101">
@@ -8011,10 +7999,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4429023935149316</v>
+        <v>-0.5471</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.40126701841809</v>
+        <v>-15.3188</v>
       </c>
     </row>
     <row r="102">
@@ -8051,10 +8039,10 @@
         <v>1.88</v>
       </c>
       <c r="I102" t="n">
-        <v>0.938204684096747</v>
+        <v>1.8234</v>
       </c>
       <c r="J102" t="n">
-        <v>18.76409368193494</v>
+        <v>36.468</v>
       </c>
     </row>
     <row r="103">
@@ -8091,10 +8079,10 @@
         <v>1.43</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4593917005035961</v>
+        <v>1.0628</v>
       </c>
       <c r="J103" t="n">
-        <v>9.187834010071922</v>
+        <v>21.256</v>
       </c>
     </row>
     <row r="104">
@@ -8131,10 +8119,10 @@
         <v>1.39</v>
       </c>
       <c r="I104" t="n">
-        <v>0.413151164128836</v>
+        <v>0.9774</v>
       </c>
       <c r="J104" t="n">
-        <v>8.26302328257672</v>
+        <v>19.548</v>
       </c>
     </row>
     <row r="105">
@@ -8171,10 +8159,10 @@
         <v>0.83</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2481359502250428</v>
+        <v>-0.6656</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.962719004500856</v>
+        <v>-13.312</v>
       </c>
     </row>
     <row r="106">
@@ -8211,10 +8199,10 @@
         <v>0.63</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4971812579357753</v>
+        <v>-1.1082</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.943625158715506</v>
+        <v>-22.164</v>
       </c>
     </row>
     <row r="107">
@@ -8251,10 +8239,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1933736251374867</v>
+        <v>0.5347</v>
       </c>
       <c r="J107" t="n">
-        <v>3.867472502749734</v>
+        <v>10.694</v>
       </c>
     </row>
     <row r="108">
@@ -8291,10 +8279,10 @@
         <v>1.06</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1058759819485755</v>
+        <v>0.1726</v>
       </c>
       <c r="J108" t="n">
-        <v>-2.117519638971511</v>
+        <v>3.452</v>
       </c>
     </row>
     <row r="109">
@@ -8331,10 +8319,10 @@
         <v>1.01</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1551179611496944</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.102359222993889</v>
+        <v>1.254</v>
       </c>
     </row>
     <row r="110">
@@ -8371,10 +8359,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.400237423041993</v>
+        <v>-0.4445</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.00474846083986</v>
+        <v>-8.890000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -8411,10 +8399,10 @@
         <v>0.67</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4774940538149979</v>
+        <v>-0.5514</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.549881076299959</v>
+        <v>-11.028</v>
       </c>
     </row>
     <row r="112">
@@ -8451,10 +8439,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3752947963339017</v>
+        <v>0.6302</v>
       </c>
       <c r="J112" t="n">
-        <v>9.007075112013641</v>
+        <v>15.1248</v>
       </c>
     </row>
     <row r="113">
@@ -8491,10 +8479,10 @@
         <v>1.29</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2726343979889876</v>
+        <v>0.516</v>
       </c>
       <c r="J113" t="n">
-        <v>6.543225551735702</v>
+        <v>12.384</v>
       </c>
     </row>
     <row r="114">
@@ -8531,10 +8519,10 @@
         <v>1.04</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.01675528352883776</v>
+        <v>0.1262</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.4021268046921063</v>
+        <v>3.0288</v>
       </c>
     </row>
     <row r="115">
@@ -8571,10 +8559,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3067214304537322</v>
+        <v>-0.3626</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.361314330889574</v>
+        <v>-8.702400000000001</v>
       </c>
     </row>
     <row r="116">
@@ -8611,10 +8599,10 @@
         <v>0.35</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.8786554286317729</v>
+        <v>-0.9283</v>
       </c>
       <c r="J116" t="n">
-        <v>-21.08773028716255</v>
+        <v>-22.2792</v>
       </c>
     </row>
     <row r="117">
@@ -8651,10 +8639,10 @@
         <v>1.3</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4197000941336603</v>
+        <v>0.4914</v>
       </c>
       <c r="J117" t="n">
-        <v>10.07280225920785</v>
+        <v>11.7936</v>
       </c>
     </row>
     <row r="118">
@@ -8691,10 +8679,10 @@
         <v>1.12</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1502790989789239</v>
+        <v>0.2257</v>
       </c>
       <c r="J118" t="n">
-        <v>3.606698375494172</v>
+        <v>5.4168</v>
       </c>
     </row>
     <row r="119">
@@ -8731,10 +8719,10 @@
         <v>1.11</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1364096607248959</v>
+        <v>0.2078</v>
       </c>
       <c r="J119" t="n">
-        <v>3.2738318573975</v>
+        <v>4.9872</v>
       </c>
     </row>
     <row r="120">
@@ -8771,10 +8759,10 @@
         <v>1.01</v>
       </c>
       <c r="I120" t="n">
-        <v>0.001577499250766502</v>
+        <v>-0.0076</v>
       </c>
       <c r="J120" t="n">
-        <v>0.03785998201839604</v>
+        <v>-0.1824</v>
       </c>
     </row>
     <row r="121">
@@ -8811,10 +8799,10 @@
         <v>0.9</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.10430401445662</v>
+        <v>-0.2515</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.503296346958881</v>
+        <v>-6.036</v>
       </c>
     </row>
     <row r="122">
@@ -8851,10 +8839,10 @@
         <v>1.57</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6501706902699064</v>
+        <v>1.3405</v>
       </c>
       <c r="J122" t="n">
-        <v>13.00341380539813</v>
+        <v>26.81</v>
       </c>
     </row>
     <row r="123">
@@ -8891,10 +8879,10 @@
         <v>1.4</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4601910453420583</v>
+        <v>0.9948</v>
       </c>
       <c r="J123" t="n">
-        <v>9.203820906841166</v>
+        <v>19.896</v>
       </c>
     </row>
     <row r="124">
@@ -8931,10 +8919,10 @@
         <v>1.15</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1876742312987079</v>
+        <v>0.3556</v>
       </c>
       <c r="J124" t="n">
-        <v>3.753484625974158</v>
+        <v>7.112</v>
       </c>
     </row>
     <row r="125">
@@ -8971,10 +8959,10 @@
         <v>1.07</v>
       </c>
       <c r="I125" t="n">
-        <v>0.09378781723894597</v>
+        <v>0.1301</v>
       </c>
       <c r="J125" t="n">
-        <v>1.875756344778919</v>
+        <v>2.602</v>
       </c>
     </row>
     <row r="126">
@@ -9011,10 +8999,10 @@
         <v>1.01</v>
       </c>
       <c r="I126" t="n">
-        <v>0.02291532798471545</v>
+        <v>-0.0791</v>
       </c>
       <c r="J126" t="n">
-        <v>0.4583065596943091</v>
+        <v>-1.582</v>
       </c>
     </row>
     <row r="127">
@@ -9051,10 +9039,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.1357623145356754</v>
+        <v>-0.0594</v>
       </c>
       <c r="J127" t="n">
-        <v>-2.715246290713509</v>
+        <v>-1.188</v>
       </c>
     </row>
     <row r="128">
@@ -9091,10 +9079,10 @@
         <v>0.91</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1654053374723497</v>
+        <v>-0.1154</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.308106749446994</v>
+        <v>-2.308</v>
       </c>
     </row>
     <row r="129">
@@ -9131,10 +9119,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2222444903175967</v>
+        <v>-0.2232</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.444889806351934</v>
+        <v>-4.464</v>
       </c>
     </row>
     <row r="130">
@@ -9171,10 +9159,10 @@
         <v>0.74</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3194490745970717</v>
+        <v>-0.4201</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.388981491941434</v>
+        <v>-8.401999999999999</v>
       </c>
     </row>
     <row r="131">
@@ -9211,10 +9199,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.367854296039946</v>
+        <v>-0.4927</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.35708592079892</v>
+        <v>-9.853999999999999</v>
       </c>
     </row>
     <row r="132">
@@ -9251,10 +9239,10 @@
         <v>1.26</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2909469096239177</v>
+        <v>0.4339</v>
       </c>
       <c r="J132" t="n">
-        <v>12.21977020420455</v>
+        <v>18.2238</v>
       </c>
     </row>
     <row r="133">
@@ -9291,10 +9279,10 @@
         <v>1.19</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1951534025144411</v>
+        <v>0.3337</v>
       </c>
       <c r="J133" t="n">
-        <v>8.196442905606528</v>
+        <v>14.0154</v>
       </c>
     </row>
     <row r="134">
@@ -9331,10 +9319,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1286295766776049</v>
+        <v>0.2546</v>
       </c>
       <c r="J134" t="n">
-        <v>5.402442220459405</v>
+        <v>10.6932</v>
       </c>
     </row>
     <row r="135">
@@ -9371,10 +9359,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.03460467343735497</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="J135" t="n">
-        <v>1.453396284368909</v>
+        <v>4.0992</v>
       </c>
     </row>
     <row r="136">
@@ -9411,10 +9399,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2052922209685598</v>
+        <v>-0.3319</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.62227328067951</v>
+        <v>-13.9398</v>
       </c>
     </row>
     <row r="137">
@@ -9451,10 +9439,10 @@
         <v>1.13</v>
       </c>
       <c r="I137" t="n">
-        <v>0.04900336270568012</v>
+        <v>0.2671</v>
       </c>
       <c r="J137" t="n">
-        <v>2.058141233638565</v>
+        <v>11.2182</v>
       </c>
     </row>
     <row r="138">
@@ -9491,10 +9479,10 @@
         <v>1.09</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.004970608425447732</v>
+        <v>0.1992</v>
       </c>
       <c r="J138" t="n">
-        <v>-0.2087655538688047</v>
+        <v>8.366400000000001</v>
       </c>
     </row>
     <row r="139">
@@ -9531,10 +9519,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.04763119920205498</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.000510366486309</v>
+        <v>4.1832</v>
       </c>
     </row>
     <row r="140">
@@ -9571,10 +9559,10 @@
         <v>1.01</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.07023091335494394</v>
+        <v>0.0171</v>
       </c>
       <c r="J140" t="n">
-        <v>-2.949698360907646</v>
+        <v>0.7181999999999999</v>
       </c>
     </row>
     <row r="141">
@@ -9611,10 +9599,10 @@
         <v>0.87</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.200243201717279</v>
+        <v>-0.2851</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.41021447212572</v>
+        <v>-11.9742</v>
       </c>
     </row>
     <row r="142">
@@ -9651,10 +9639,10 @@
         <v>1.61</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6319004751137643</v>
+        <v>0.9307</v>
       </c>
       <c r="J142" t="n">
-        <v>12.63800950227529</v>
+        <v>18.614</v>
       </c>
     </row>
     <row r="143">
@@ -9691,10 +9679,10 @@
         <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1272816735628505</v>
+        <v>0.0605</v>
       </c>
       <c r="J143" t="n">
-        <v>-2.545633471257011</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="144">
@@ -9731,10 +9719,10 @@
         <v>0.63</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.5293830843401119</v>
+        <v>-0.5877</v>
       </c>
       <c r="J144" t="n">
-        <v>-10.58766168680224</v>
+        <v>-11.754</v>
       </c>
     </row>
     <row r="145">
@@ -9771,10 +9759,10 @@
         <v>0.61</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5512673478828095</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="J145" t="n">
-        <v>-11.02534695765619</v>
+        <v>-12.268</v>
       </c>
     </row>
     <row r="146">
@@ -9811,10 +9799,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6053320305056028</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.10664061011206</v>
+        <v>-13.518</v>
       </c>
     </row>
     <row r="147">
@@ -9851,10 +9839,10 @@
         <v>1.95</v>
       </c>
       <c r="I147" t="n">
-        <v>1.366982824455613</v>
+        <v>1.8904</v>
       </c>
       <c r="J147" t="n">
-        <v>27.33965648911227</v>
+        <v>37.808</v>
       </c>
     </row>
     <row r="148">
@@ -9891,10 +9879,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5271861591178026</v>
+        <v>0.8922</v>
       </c>
       <c r="J148" t="n">
-        <v>10.54372318235605</v>
+        <v>17.844</v>
       </c>
     </row>
     <row r="149">
@@ -9931,10 +9919,10 @@
         <v>1.2</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3130976452898621</v>
+        <v>0.4989</v>
       </c>
       <c r="J149" t="n">
-        <v>6.261952905797241</v>
+        <v>9.978</v>
       </c>
     </row>
     <row r="150">
@@ -9971,10 +9959,10 @@
         <v>0.91</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.08150083921282544</v>
+        <v>-0.4559</v>
       </c>
       <c r="J150" t="n">
-        <v>-1.630016784256509</v>
+        <v>-9.118</v>
       </c>
     </row>
     <row r="151">
@@ -10011,10 +9999,10 @@
         <v>0.72</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2497144873004038</v>
+        <v>-0.9171</v>
       </c>
       <c r="J151" t="n">
-        <v>-4.994289746008076</v>
+        <v>-18.342</v>
       </c>
     </row>
     <row r="152">
@@ -10051,10 +10039,10 @@
         <v>1.09</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0111931660761304</v>
+        <v>0.2932</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.2014769893703472</v>
+        <v>5.2776</v>
       </c>
     </row>
     <row r="153">
@@ -10091,10 +10079,10 @@
         <v>0.9</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2281859475081968</v>
+        <v>-0.1165</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.107347055147542</v>
+        <v>-2.097</v>
       </c>
     </row>
     <row r="154">
@@ -10131,10 +10119,10 @@
         <v>0.77</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3626587550231374</v>
+        <v>-0.355</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.527857590416473</v>
+        <v>-6.39</v>
       </c>
     </row>
     <row r="155">
@@ -10171,10 +10159,10 @@
         <v>0.6</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.547376745364158</v>
+        <v>-0.6051</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.852781416554844</v>
+        <v>-10.8918</v>
       </c>
     </row>
     <row r="156">
@@ -10211,10 +10199,10 @@
         <v>0.59</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5583513841901562</v>
+        <v>-0.6182</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.05032491542281</v>
+        <v>-11.1276</v>
       </c>
     </row>
     <row r="157">
@@ -10251,10 +10239,10 @@
         <v>1.51</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8234693762321463</v>
+        <v>1.2091</v>
       </c>
       <c r="J157" t="n">
-        <v>14.82244877217863</v>
+        <v>21.7638</v>
       </c>
     </row>
     <row r="158">
@@ -10291,10 +10279,10 @@
         <v>1.33</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5541949046306488</v>
+        <v>0.8219</v>
       </c>
       <c r="J158" t="n">
-        <v>9.975508283351678</v>
+        <v>14.7942</v>
       </c>
     </row>
     <row r="159">
@@ -10331,10 +10319,10 @@
         <v>1.27</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4714901011143409</v>
+        <v>0.6662</v>
       </c>
       <c r="J159" t="n">
-        <v>8.486821820058136</v>
+        <v>11.9916</v>
       </c>
     </row>
     <row r="160">
@@ -10371,10 +10359,10 @@
         <v>1.22</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4047676821330338</v>
+        <v>0.524</v>
       </c>
       <c r="J160" t="n">
-        <v>7.285818278394609</v>
+        <v>9.432</v>
       </c>
     </row>
     <row r="161">
@@ -10411,10 +10399,10 @@
         <v>1.01</v>
       </c>
       <c r="I161" t="n">
-        <v>0.08039156097529065</v>
+        <v>-0.0883</v>
       </c>
       <c r="J161" t="n">
-        <v>1.447048097555232</v>
+        <v>-1.5894</v>
       </c>
     </row>
     <row r="162">
@@ -10451,10 +10439,10 @@
         <v>1.45</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3873701862362202</v>
+        <v>0.7016</v>
       </c>
       <c r="J162" t="n">
-        <v>8.134773910960623</v>
+        <v>14.7336</v>
       </c>
     </row>
     <row r="163">
@@ -10491,10 +10479,10 @@
         <v>1.15</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.01552400624385152</v>
+        <v>0.3047</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.3260041311208819</v>
+        <v>6.3987</v>
       </c>
     </row>
     <row r="164">
@@ -10531,10 +10519,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.06971989364136941</v>
+        <v>0.2232</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.464117766468757</v>
+        <v>4.6872</v>
       </c>
     </row>
     <row r="165">
@@ -10571,10 +10559,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3120548936987056</v>
+        <v>-0.2809</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.553152767672819</v>
+        <v>-5.8989</v>
       </c>
     </row>
     <row r="166">
@@ -10611,10 +10599,10 @@
         <v>0.49</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7149613268274668</v>
+        <v>-0.7765</v>
       </c>
       <c r="J166" t="n">
-        <v>-15.0141878633768</v>
+        <v>-16.3065</v>
       </c>
     </row>
     <row r="167">
@@ -10651,10 +10639,10 @@
         <v>1.68</v>
       </c>
       <c r="I167" t="n">
-        <v>1.034209083240988</v>
+        <v>1.5857</v>
       </c>
       <c r="J167" t="n">
-        <v>21.71839074806075</v>
+        <v>33.2997</v>
       </c>
     </row>
     <row r="168">
@@ -10691,10 +10679,10 @@
         <v>1.67</v>
       </c>
       <c r="I168" t="n">
-        <v>1.019829958735224</v>
+        <v>1.5672</v>
       </c>
       <c r="J168" t="n">
-        <v>21.41642913343971</v>
+        <v>32.9112</v>
       </c>
     </row>
     <row r="169">
@@ -10731,10 +10719,10 @@
         <v>1.05</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0632475711449785</v>
+        <v>0.1006</v>
       </c>
       <c r="J169" t="n">
-        <v>1.328198994044549</v>
+        <v>2.1126</v>
       </c>
     </row>
     <row r="170">
@@ -10771,10 +10759,10 @@
         <v>0.78</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1988231515762616</v>
+        <v>-0.7675</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.175286183101493</v>
+        <v>-16.1175</v>
       </c>
     </row>
     <row r="171">
@@ -10811,10 +10799,10 @@
         <v>0.63</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3236702553317297</v>
+        <v>-1.096</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.797075361966323</v>
+        <v>-23.016</v>
       </c>
     </row>
     <row r="172">
@@ -10851,10 +10839,10 @@
         <v>1.34</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4207553857894895</v>
+        <v>0.5436</v>
       </c>
       <c r="J172" t="n">
-        <v>12.62266157368468</v>
+        <v>16.308</v>
       </c>
     </row>
     <row r="173">
@@ -10891,10 +10879,10 @@
         <v>1.29</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3513851994985352</v>
+        <v>0.4788</v>
       </c>
       <c r="J173" t="n">
-        <v>10.54155598495606</v>
+        <v>14.364</v>
       </c>
     </row>
     <row r="174">
@@ -10931,10 +10919,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2532918920255375</v>
+        <v>0.3826</v>
       </c>
       <c r="J174" t="n">
-        <v>7.598756760766125</v>
+        <v>11.478</v>
       </c>
     </row>
     <row r="175">
@@ -10971,10 +10959,10 @@
         <v>0.82</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2238237057970278</v>
+        <v>-0.373</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.714711173910835</v>
+        <v>-11.19</v>
       </c>
     </row>
     <row r="176">
@@ -11011,10 +10999,10 @@
         <v>0.76</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2898895938280902</v>
+        <v>-0.456</v>
       </c>
       <c r="J176" t="n">
-        <v>-8.696687814842704</v>
+        <v>-13.68</v>
       </c>
     </row>
     <row r="177">
@@ -11051,10 +11039,10 @@
         <v>1.29</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3126256239080084</v>
+        <v>0.4965</v>
       </c>
       <c r="J177" t="n">
-        <v>9.378768717240252</v>
+        <v>14.895</v>
       </c>
     </row>
     <row r="178">
@@ -11091,10 +11079,10 @@
         <v>1.07</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.01994071431023076</v>
+        <v>0.1603</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.5982214293069228</v>
+        <v>4.809</v>
       </c>
     </row>
     <row r="179">
@@ -11131,10 +11119,10 @@
         <v>1.05</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.03552061959202061</v>
+        <v>0.1196</v>
       </c>
       <c r="J179" t="n">
-        <v>-1.065618587760618</v>
+        <v>3.588</v>
       </c>
     </row>
     <row r="180">
@@ -11171,10 +11159,10 @@
         <v>1</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0721795458946263</v>
+        <v>-0.0211</v>
       </c>
       <c r="J180" t="n">
-        <v>-2.165386376838789</v>
+        <v>-0.633</v>
       </c>
     </row>
     <row r="181">
@@ -11211,10 +11199,10 @@
         <v>0.75</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2919331429806097</v>
+        <v>-0.4599</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.75799428941829</v>
+        <v>-13.797</v>
       </c>
     </row>
     <row r="182">
@@ -11251,10 +11239,10 @@
         <v>1.17</v>
       </c>
       <c r="I182" t="n">
-        <v>0.1177525028962383</v>
+        <v>0.4463</v>
       </c>
       <c r="J182" t="n">
-        <v>2.119545052132289</v>
+        <v>8.0334</v>
       </c>
     </row>
     <row r="183">
@@ -11291,10 +11279,10 @@
         <v>0.73</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.3765725469500248</v>
+        <v>-0.3804</v>
       </c>
       <c r="J183" t="n">
-        <v>-6.778305845100447</v>
+        <v>-6.8472</v>
       </c>
     </row>
     <row r="184">
@@ -11331,10 +11319,10 @@
         <v>0.71</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3939746650768223</v>
+        <v>-0.4209</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.091543971382801</v>
+        <v>-7.5762</v>
       </c>
     </row>
     <row r="185">
@@ -11371,10 +11359,10 @@
         <v>0.57</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.5393526230732547</v>
+        <v>-0.6281</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.708347215318584</v>
+        <v>-11.3058</v>
       </c>
     </row>
     <row r="186">
@@ -11411,10 +11399,10 @@
         <v>0.47</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.64422523306529</v>
+        <v>-0.7575</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.59605419517522</v>
+        <v>-13.635</v>
       </c>
     </row>
     <row r="187">
@@ -11451,10 +11439,10 @@
         <v>1.47</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7290229799799288</v>
+        <v>1.0891</v>
       </c>
       <c r="J187" t="n">
-        <v>13.12241363963872</v>
+        <v>19.6038</v>
       </c>
     </row>
     <row r="188">
@@ -11491,10 +11479,10 @@
         <v>1.46</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7136197928145693</v>
+        <v>1.068</v>
       </c>
       <c r="J188" t="n">
-        <v>12.84515627066225</v>
+        <v>19.224</v>
       </c>
     </row>
     <row r="189">
@@ -11531,10 +11519,10 @@
         <v>1.34</v>
       </c>
       <c r="I189" t="n">
-        <v>0.5409397711759689</v>
+        <v>0.7794</v>
       </c>
       <c r="J189" t="n">
-        <v>9.736915881167441</v>
+        <v>14.0292</v>
       </c>
     </row>
     <row r="190">
@@ -11571,10 +11559,10 @@
         <v>1.33</v>
       </c>
       <c r="I190" t="n">
-        <v>0.5278568496202096</v>
+        <v>0.7524</v>
       </c>
       <c r="J190" t="n">
-        <v>9.501423293163773</v>
+        <v>13.5432</v>
       </c>
     </row>
     <row r="191">
@@ -11611,10 +11599,10 @@
         <v>1.13</v>
       </c>
       <c r="I191" t="n">
-        <v>0.2168156459791253</v>
+        <v>0.2598</v>
       </c>
       <c r="J191" t="n">
-        <v>3.902681627624256</v>
+        <v>4.6764</v>
       </c>
     </row>
     <row r="192">
@@ -11651,10 +11639,10 @@
         <v>1.69</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5928930037494441</v>
+        <v>1.5737</v>
       </c>
       <c r="J192" t="n">
-        <v>13.04364608248777</v>
+        <v>34.6214</v>
       </c>
     </row>
     <row r="193">
@@ -11691,10 +11679,10 @@
         <v>1.2</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1544681572600229</v>
+        <v>0.5004</v>
       </c>
       <c r="J193" t="n">
-        <v>3.398299459720503</v>
+        <v>11.0088</v>
       </c>
     </row>
     <row r="194">
@@ -11731,10 +11719,10 @@
         <v>1.08</v>
       </c>
       <c r="I194" t="n">
-        <v>0.04189299111010322</v>
+        <v>0.1666</v>
       </c>
       <c r="J194" t="n">
-        <v>0.9216458044222708</v>
+        <v>3.6652</v>
       </c>
     </row>
     <row r="195">
@@ -11771,10 +11759,10 @@
         <v>1.08</v>
       </c>
       <c r="I195" t="n">
-        <v>0.04189299111010322</v>
+        <v>0.1666</v>
       </c>
       <c r="J195" t="n">
-        <v>0.9216458044222708</v>
+        <v>3.6652</v>
       </c>
     </row>
     <row r="196">
@@ -11811,10 +11799,10 @@
         <v>1.07</v>
       </c>
       <c r="I196" t="n">
-        <v>0.03222141434789018</v>
+        <v>0.1365</v>
       </c>
       <c r="J196" t="n">
-        <v>0.708871115653584</v>
+        <v>3.003</v>
       </c>
     </row>
     <row r="197">
@@ -11851,10 +11839,10 @@
         <v>0.97</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.1329959594767182</v>
+        <v>-0.0226</v>
       </c>
       <c r="J197" t="n">
-        <v>-2.925911108487799</v>
+        <v>-0.4972</v>
       </c>
     </row>
     <row r="198">
@@ -11891,10 +11879,10 @@
         <v>0.97</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1329959594767182</v>
+        <v>-0.0226</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.925911108487799</v>
+        <v>-0.4972</v>
       </c>
     </row>
     <row r="199">
@@ -11931,10 +11919,10 @@
         <v>0.87</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2535592825151913</v>
+        <v>-0.2299</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.578304215334209</v>
+        <v>-5.0578</v>
       </c>
     </row>
     <row r="200">
@@ -11971,10 +11959,10 @@
         <v>0.86</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2651398751367735</v>
+        <v>-0.249</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.833077253009018</v>
+        <v>-5.478</v>
       </c>
     </row>
     <row r="201">
@@ -12011,10 +11999,10 @@
         <v>0.74</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4186615484827784</v>
+        <v>-0.4388</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.210554066621125</v>
+        <v>-9.653600000000001</v>
       </c>
     </row>
     <row r="202">
@@ -12051,10 +12039,10 @@
         <v>1.66</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5294573127848465</v>
+        <v>1.5548</v>
       </c>
       <c r="J202" t="n">
-        <v>11.11860356848178</v>
+        <v>32.6508</v>
       </c>
     </row>
     <row r="203">
@@ -12091,10 +12079,10 @@
         <v>1.27</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2283315637644961</v>
+        <v>0.7499</v>
       </c>
       <c r="J203" t="n">
-        <v>4.794962839054419</v>
+        <v>15.7479</v>
       </c>
     </row>
     <row r="204">
@@ -12131,10 +12119,10 @@
         <v>1.15</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1361496549162176</v>
+        <v>0.4234</v>
       </c>
       <c r="J204" t="n">
-        <v>2.859142753240569</v>
+        <v>8.891400000000001</v>
       </c>
     </row>
     <row r="205">
@@ -12171,10 +12159,10 @@
         <v>0.89</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1153531947562787</v>
+        <v>-0.488</v>
       </c>
       <c r="J205" t="n">
-        <v>-2.422417089881853</v>
+        <v>-10.248</v>
       </c>
     </row>
     <row r="206">
@@ -12211,10 +12199,10 @@
         <v>0.78</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2655318684508425</v>
+        <v>-0.7644</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.576169237467694</v>
+        <v>-16.0524</v>
       </c>
     </row>
     <row r="207">
@@ -12251,10 +12239,10 @@
         <v>1.42</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2975138389023865</v>
+        <v>0.6966</v>
       </c>
       <c r="J207" t="n">
-        <v>6.247790616950116</v>
+        <v>14.6286</v>
       </c>
     </row>
     <row r="208">
@@ -12291,10 +12279,10 @@
         <v>0.87</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2698032307732648</v>
+        <v>-0.2516</v>
       </c>
       <c r="J208" t="n">
-        <v>-5.665867846238561</v>
+        <v>-5.2836</v>
       </c>
     </row>
     <row r="209">
@@ -12331,10 +12319,10 @@
         <v>0.84</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3064535980093619</v>
+        <v>-0.3014</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.435525558196601</v>
+        <v>-6.3294</v>
       </c>
     </row>
     <row r="210">
@@ -12371,10 +12359,10 @@
         <v>0.77</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3934411272366346</v>
+        <v>-0.4076</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.262263671969327</v>
+        <v>-8.5596</v>
       </c>
     </row>
     <row r="211">
@@ -12411,10 +12399,10 @@
         <v>0.72</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4554547348057989</v>
+        <v>-0.4778</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.564549430921776</v>
+        <v>-10.0338</v>
       </c>
     </row>
     <row r="212">
@@ -12451,10 +12439,10 @@
         <v>1.04</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.01280169894833234</v>
+        <v>0.1638</v>
       </c>
       <c r="J212" t="n">
-        <v>-0.4352577642432994</v>
+        <v>5.5692</v>
       </c>
     </row>
     <row r="213">
@@ -12491,10 +12479,10 @@
         <v>0.9</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1958768240825403</v>
+        <v>-0.1632</v>
       </c>
       <c r="J213" t="n">
-        <v>-6.65981201880637</v>
+        <v>-5.5488</v>
       </c>
     </row>
     <row r="214">
@@ -12531,10 +12519,10 @@
         <v>0.9</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1958768240825403</v>
+        <v>-0.1632</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.65981201880637</v>
+        <v>-5.5488</v>
       </c>
     </row>
     <row r="215">
@@ -12571,10 +12559,10 @@
         <v>0.87</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2278498124200279</v>
+        <v>-0.2299</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.746893622280949</v>
+        <v>-7.8166</v>
       </c>
     </row>
     <row r="216">
@@ -12611,10 +12599,10 @@
         <v>0.7</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4467764756011847</v>
+        <v>-0.4947</v>
       </c>
       <c r="J216" t="n">
-        <v>-15.19040017044028</v>
+        <v>-16.8198</v>
       </c>
     </row>
     <row r="217">
@@ -12651,10 +12639,10 @@
         <v>1.44</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3385954150535141</v>
+        <v>1.1212</v>
       </c>
       <c r="J217" t="n">
-        <v>11.51224411181948</v>
+        <v>38.1208</v>
       </c>
     </row>
     <row r="218">
@@ -12691,10 +12679,10 @@
         <v>1.32</v>
       </c>
       <c r="I218" t="n">
-        <v>0.247105910702457</v>
+        <v>0.8618</v>
       </c>
       <c r="J218" t="n">
-        <v>8.40160096388354</v>
+        <v>29.3012</v>
       </c>
     </row>
     <row r="219">
@@ -12731,10 +12719,10 @@
         <v>1.3</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2316437371590527</v>
+        <v>0.8159</v>
       </c>
       <c r="J219" t="n">
-        <v>7.875887063407793</v>
+        <v>27.7406</v>
       </c>
     </row>
     <row r="220">
@@ -12771,10 +12759,10 @@
         <v>0.89</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1411043137344144</v>
+        <v>-0.4907</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.797546666970089</v>
+        <v>-16.6838</v>
       </c>
     </row>
     <row r="221">
@@ -12811,10 +12799,10 @@
         <v>0.84</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2073725308428283</v>
+        <v>-0.6213</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.050666048656161</v>
+        <v>-21.1242</v>
       </c>
     </row>
     <row r="222">
@@ -12851,10 +12839,10 @@
         <v>1.44</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4114957450314715</v>
+        <v>1.1612</v>
       </c>
       <c r="J222" t="n">
-        <v>12.34487235094414</v>
+        <v>34.836</v>
       </c>
     </row>
     <row r="223">
@@ -12891,10 +12879,10 @@
         <v>1.09</v>
       </c>
       <c r="I223" t="n">
-        <v>0.06259658203940459</v>
+        <v>0.3003</v>
       </c>
       <c r="J223" t="n">
-        <v>1.877897461182138</v>
+        <v>9.009</v>
       </c>
     </row>
     <row r="224">
@@ -12931,10 +12919,10 @@
         <v>0.97</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.05386144105603898</v>
+        <v>-0.2121</v>
       </c>
       <c r="J224" t="n">
-        <v>-1.615843231681169</v>
+        <v>-6.363</v>
       </c>
     </row>
     <row r="225">
@@ -12971,10 +12959,10 @@
         <v>0.96</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.06569695655615787</v>
+        <v>-0.2482</v>
       </c>
       <c r="J225" t="n">
-        <v>-1.970908696684736</v>
+        <v>-7.446</v>
       </c>
     </row>
     <row r="226">
@@ -13011,10 +12999,10 @@
         <v>0.95</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.07760175236794772</v>
+        <v>-0.2822</v>
       </c>
       <c r="J226" t="n">
-        <v>-2.328052571038432</v>
+        <v>-8.465999999999999</v>
       </c>
     </row>
     <row r="227">
@@ -13051,10 +13039,10 @@
         <v>1.14</v>
       </c>
       <c r="I227" t="n">
-        <v>0.03995559099864458</v>
+        <v>0.2846</v>
       </c>
       <c r="J227" t="n">
-        <v>1.198667729959337</v>
+        <v>8.538</v>
       </c>
     </row>
     <row r="228">
@@ -13091,10 +13079,10 @@
         <v>1.04</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.06001503854669837</v>
+        <v>0.102</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.800451156400951</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="229">
@@ -13131,10 +13119,10 @@
         <v>1.02</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.08157139180252482</v>
+        <v>0.0479</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.447141754075744</v>
+        <v>1.437</v>
       </c>
     </row>
     <row r="230">
@@ -13171,10 +13159,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.08157139180252482</v>
+        <v>0.0479</v>
       </c>
       <c r="J230" t="n">
-        <v>-2.447141754075744</v>
+        <v>1.437</v>
       </c>
     </row>
     <row r="231">
@@ -13211,10 +13199,10 @@
         <v>0.9</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2418436373130938</v>
+        <v>-0.2351</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.255309119392815</v>
+        <v>-7.053</v>
       </c>
     </row>
     <row r="232">
@@ -13251,10 +13239,10 @@
         <v>2.47</v>
       </c>
       <c r="I232" t="n">
-        <v>1.041096732258402</v>
+        <v>2.0593</v>
       </c>
       <c r="J232" t="n">
-        <v>15.61645098387603</v>
+        <v>30.8895</v>
       </c>
     </row>
     <row r="233">
@@ -13291,10 +13279,10 @@
         <v>1.73</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5280008585902349</v>
+        <v>1.4994</v>
       </c>
       <c r="J233" t="n">
-        <v>7.920012878853524</v>
+        <v>22.491</v>
       </c>
     </row>
     <row r="234">
@@ -13331,10 +13319,10 @@
         <v>1.62</v>
       </c>
       <c r="I234" t="n">
-        <v>0.442144268669918</v>
+        <v>1.2867</v>
       </c>
       <c r="J234" t="n">
-        <v>6.632164030048769</v>
+        <v>19.3005</v>
       </c>
     </row>
     <row r="235">
@@ -13371,10 +13359,10 @@
         <v>1.04</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.01678444722136225</v>
+        <v>-0.0484</v>
       </c>
       <c r="J235" t="n">
-        <v>-0.2517667083204337</v>
+        <v>-0.726</v>
       </c>
     </row>
     <row r="236">
@@ -13411,10 +13399,10 @@
         <v>0.95</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1279093655300956</v>
+        <v>-0.4118</v>
       </c>
       <c r="J236" t="n">
-        <v>-1.918640482951435</v>
+        <v>-6.177</v>
       </c>
     </row>
     <row r="237">
@@ -13451,10 +13439,10 @@
         <v>1.01</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1703976716078331</v>
+        <v>0.2003</v>
       </c>
       <c r="J237" t="n">
-        <v>-2.555965074117496</v>
+        <v>3.0045</v>
       </c>
     </row>
     <row r="238">
@@ -13491,10 +13479,10 @@
         <v>0.67</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.5698834936615247</v>
+        <v>-0.4205</v>
       </c>
       <c r="J238" t="n">
-        <v>-8.54825240492287</v>
+        <v>-6.3075</v>
       </c>
     </row>
     <row r="239">
@@ -13531,10 +13519,10 @@
         <v>0.55</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.6963881714151625</v>
+        <v>-0.6269</v>
       </c>
       <c r="J239" t="n">
-        <v>-10.44582257122744</v>
+        <v>-9.403499999999999</v>
       </c>
     </row>
     <row r="240">
@@ -13571,10 +13559,10 @@
         <v>0.51</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.742565283884199</v>
+        <v>-0.6828</v>
       </c>
       <c r="J240" t="n">
-        <v>-11.13847925826298</v>
+        <v>-10.242</v>
       </c>
     </row>
     <row r="241">
@@ -13611,10 +13599,10 @@
         <v>0.5</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7541330344635686</v>
+        <v>-0.6965</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.31199551695353</v>
+        <v>-10.4475</v>
       </c>
     </row>
     <row r="242">
@@ -13651,10 +13639,10 @@
         <v>0.95</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.2147181939759513</v>
+        <v>-0.0044</v>
       </c>
       <c r="J242" t="n">
-        <v>-3.864927491567123</v>
+        <v>-0.07920000000000001</v>
       </c>
     </row>
     <row r="243">
@@ -13691,10 +13679,10 @@
         <v>0.9</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.2799716777259491</v>
+        <v>-0.0961</v>
       </c>
       <c r="J243" t="n">
-        <v>-5.039490199067084</v>
+        <v>-1.7298</v>
       </c>
     </row>
     <row r="244">
@@ -13731,10 +13719,10 @@
         <v>0.74</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.474588429401271</v>
+        <v>-0.3776</v>
       </c>
       <c r="J244" t="n">
-        <v>-8.542591729222877</v>
+        <v>-6.7968</v>
       </c>
     </row>
     <row r="245">
@@ -13771,10 +13759,10 @@
         <v>0.63</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.6069284756501959</v>
+        <v>-0.5507</v>
       </c>
       <c r="J245" t="n">
-        <v>-10.92471256170353</v>
+        <v>-9.912599999999999</v>
       </c>
     </row>
     <row r="246">
@@ -13811,10 +13799,10 @@
         <v>0.51</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7572659137569631</v>
+        <v>-0.7107</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.63078644762533</v>
+        <v>-12.7926</v>
       </c>
     </row>
     <row r="247">
@@ -13851,10 +13839,10 @@
         <v>1.8</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6094105062490425</v>
+        <v>1.6852</v>
       </c>
       <c r="J247" t="n">
-        <v>10.96938911248276</v>
+        <v>30.3336</v>
       </c>
     </row>
     <row r="248">
@@ -13891,10 +13879,10 @@
         <v>1.54</v>
       </c>
       <c r="I248" t="n">
-        <v>0.4009955985223113</v>
+        <v>1.1974</v>
       </c>
       <c r="J248" t="n">
-        <v>7.217920773401603</v>
+        <v>21.5532</v>
       </c>
     </row>
     <row r="249">
@@ -13931,10 +13919,10 @@
         <v>1.32</v>
       </c>
       <c r="I249" t="n">
-        <v>0.2299712578759193</v>
+        <v>0.6876</v>
       </c>
       <c r="J249" t="n">
-        <v>4.139482641766548</v>
+        <v>12.3768</v>
       </c>
     </row>
     <row r="250">
@@ -13971,10 +13959,10 @@
         <v>1.28</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1962823135052836</v>
+        <v>0.5966</v>
       </c>
       <c r="J250" t="n">
-        <v>3.533081643095104</v>
+        <v>10.7388</v>
       </c>
     </row>
     <row r="251">
@@ -14011,10 +13999,10 @@
         <v>1.15</v>
       </c>
       <c r="I251" t="n">
-        <v>0.08561667022498765</v>
+        <v>0.2884</v>
       </c>
       <c r="J251" t="n">
-        <v>1.541100064049778</v>
+        <v>5.1912</v>
       </c>
     </row>
     <row r="252">
@@ -14051,10 +14039,10 @@
         <v>1.96</v>
       </c>
       <c r="I252" t="n">
-        <v>0.5236563150475446</v>
+        <v>1.2142</v>
       </c>
       <c r="J252" t="n">
-        <v>10.99678261599844</v>
+        <v>25.4982</v>
       </c>
     </row>
     <row r="253">
@@ -14091,10 +14079,10 @@
         <v>1.04</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.2423900447016448</v>
+        <v>0.0588</v>
       </c>
       <c r="J253" t="n">
-        <v>-5.090190938734541</v>
+        <v>1.2348</v>
       </c>
     </row>
     <row r="254">
@@ -14131,10 +14119,10 @@
         <v>1.01</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2845643817030408</v>
+        <v>-0.0101</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.975852015763856</v>
+        <v>-0.2121</v>
       </c>
     </row>
     <row r="255">
@@ -14171,10 +14159,10 @@
         <v>0.95</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3706231832170346</v>
+        <v>-0.1659</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.783086847557727</v>
+        <v>-3.4839</v>
       </c>
     </row>
     <row r="256">
@@ -14211,10 +14199,10 @@
         <v>0.52</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.953995805152144</v>
+        <v>-0.7509</v>
       </c>
       <c r="J256" t="n">
-        <v>-20.03391190819502</v>
+        <v>-15.7689</v>
       </c>
     </row>
     <row r="257">
@@ -14251,10 +14239,10 @@
         <v>1.42</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2208890038890341</v>
+        <v>1.0765</v>
       </c>
       <c r="J257" t="n">
-        <v>4.638669081669716</v>
+        <v>22.6065</v>
       </c>
     </row>
     <row r="258">
@@ -14291,10 +14279,10 @@
         <v>1.34</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1731363959625863</v>
+        <v>0.9035</v>
       </c>
       <c r="J258" t="n">
-        <v>3.635864315214311</v>
+        <v>18.9735</v>
       </c>
     </row>
     <row r="259">
@@ -14331,10 +14319,10 @@
         <v>1.16</v>
       </c>
       <c r="I259" t="n">
-        <v>0.06977355358022165</v>
+        <v>0.4371</v>
       </c>
       <c r="J259" t="n">
-        <v>1.465244625184655</v>
+        <v>9.1791</v>
       </c>
     </row>
     <row r="260">
@@ -14371,10 +14359,10 @@
         <v>1.06</v>
       </c>
       <c r="I260" t="n">
-        <v>0.01591021092527709</v>
+        <v>0.1323</v>
       </c>
       <c r="J260" t="n">
-        <v>0.3341144294308189</v>
+        <v>2.7783</v>
       </c>
     </row>
     <row r="261">
@@ -14411,10 +14399,10 @@
         <v>0.84</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3111696977979593</v>
+        <v>-0.623</v>
       </c>
       <c r="J261" t="n">
-        <v>-6.534563653757146</v>
+        <v>-13.083</v>
       </c>
     </row>
     <row r="262">
@@ -14451,10 +14439,10 @@
         <v>1.45</v>
       </c>
       <c r="I262" t="n">
-        <v>0.414449634925999</v>
+        <v>1.1276</v>
       </c>
       <c r="J262" t="n">
-        <v>9.117891968371978</v>
+        <v>24.8072</v>
       </c>
     </row>
     <row r="263">
@@ -14491,10 +14479,10 @@
         <v>1.3</v>
       </c>
       <c r="I263" t="n">
-        <v>0.2645254936541605</v>
+        <v>0.8</v>
       </c>
       <c r="J263" t="n">
-        <v>5.819560860391531</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="264">
@@ -14531,10 +14519,10 @@
         <v>1.18</v>
       </c>
       <c r="I264" t="n">
-        <v>0.1513362011629473</v>
+        <v>0.4763</v>
       </c>
       <c r="J264" t="n">
-        <v>3.32939642558484</v>
+        <v>10.4786</v>
       </c>
     </row>
     <row r="265">
@@ -14571,10 +14559,10 @@
         <v>1.06</v>
       </c>
       <c r="I265" t="n">
-        <v>0.03396474488553568</v>
+        <v>0.1218</v>
       </c>
       <c r="J265" t="n">
-        <v>0.7472243874817849</v>
+        <v>2.6796</v>
       </c>
     </row>
     <row r="266">
@@ -14611,10 +14599,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.101211613247839</v>
+        <v>-0.3553</v>
       </c>
       <c r="J266" t="n">
-        <v>-2.226655491452458</v>
+        <v>-7.8166</v>
       </c>
     </row>
     <row r="267">
@@ -14651,10 +14639,10 @@
         <v>1.83</v>
       </c>
       <c r="I267" t="n">
-        <v>0.7112397516261587</v>
+        <v>1.1411</v>
       </c>
       <c r="J267" t="n">
-        <v>15.64727453577549</v>
+        <v>25.1042</v>
       </c>
     </row>
     <row r="268">
@@ -14691,10 +14679,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1779440317448475</v>
+        <v>0.5022</v>
       </c>
       <c r="J268" t="n">
-        <v>3.914768698386646</v>
+        <v>11.0484</v>
       </c>
     </row>
     <row r="269">
@@ -14731,10 +14719,10 @@
         <v>0.63</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.5150453080074028</v>
+        <v>-0.5987</v>
       </c>
       <c r="J269" t="n">
-        <v>-11.33099677616286</v>
+        <v>-13.1714</v>
       </c>
     </row>
     <row r="270">
@@ -14771,10 +14759,10 @@
         <v>0.63</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5150453080074028</v>
+        <v>-0.5987</v>
       </c>
       <c r="J270" t="n">
-        <v>-11.33099677616286</v>
+        <v>-13.1714</v>
       </c>
     </row>
     <row r="271">
@@ -14811,10 +14799,10 @@
         <v>0.33</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.8230375057904324</v>
+        <v>-0.9472</v>
       </c>
       <c r="J271" t="n">
-        <v>-18.10682512738951</v>
+        <v>-20.8384</v>
       </c>
     </row>
     <row r="272">
@@ -14851,10 +14839,10 @@
         <v>2.14</v>
       </c>
       <c r="I272" t="n">
-        <v>1.018648370954564</v>
+        <v>2.0593</v>
       </c>
       <c r="J272" t="n">
-        <v>17.31702230622759</v>
+        <v>35.0081</v>
       </c>
     </row>
     <row r="273">
@@ -14891,10 +14879,10 @@
         <v>1.5</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4518440435134168</v>
+        <v>1.1082</v>
       </c>
       <c r="J273" t="n">
-        <v>7.681348739728087</v>
+        <v>18.8394</v>
       </c>
     </row>
     <row r="274">
@@ -14931,10 +14919,10 @@
         <v>1.23</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2018313696753621</v>
+        <v>0.4772</v>
       </c>
       <c r="J274" t="n">
-        <v>3.431133284481156</v>
+        <v>8.112399999999999</v>
       </c>
     </row>
     <row r="275">
@@ -14971,10 +14959,10 @@
         <v>1.19</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1621918434530244</v>
+        <v>0.3828</v>
       </c>
       <c r="J275" t="n">
-        <v>2.757261338701415</v>
+        <v>6.5076</v>
       </c>
     </row>
     <row r="276">
@@ -15011,10 +14999,10 @@
         <v>1.09</v>
       </c>
       <c r="I276" t="n">
-        <v>0.06362260871216735</v>
+        <v>0.1279</v>
       </c>
       <c r="J276" t="n">
-        <v>1.081584348106845</v>
+        <v>2.1743</v>
       </c>
     </row>
     <row r="277">
@@ -15051,10 +15039,10 @@
         <v>1.1</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.01668261681626497</v>
+        <v>0.3459</v>
       </c>
       <c r="J277" t="n">
-        <v>-0.2836044858765045</v>
+        <v>5.8803</v>
       </c>
     </row>
     <row r="278">
@@ -15091,10 +15079,10 @@
         <v>0.91</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.227298192701306</v>
+        <v>-0.0617</v>
       </c>
       <c r="J278" t="n">
-        <v>-3.864069275922202</v>
+        <v>-1.0489</v>
       </c>
     </row>
     <row r="279">
@@ -15131,10 +15119,10 @@
         <v>0.64</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.5088571446482485</v>
+        <v>-0.5219</v>
       </c>
       <c r="J279" t="n">
-        <v>-8.650571459020224</v>
+        <v>-8.872299999999999</v>
       </c>
     </row>
     <row r="280">
@@ -15171,10 +15159,10 @@
         <v>0.49</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.669555652364247</v>
+        <v>-0.7275</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.3824460901922</v>
+        <v>-12.3675</v>
       </c>
     </row>
     <row r="281">
@@ -15211,10 +15199,10 @@
         <v>0.41</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.7536914105168504</v>
+        <v>-0.8274</v>
       </c>
       <c r="J281" t="n">
-        <v>-12.81275397878646</v>
+        <v>-14.0658</v>
       </c>
     </row>
     <row r="282">
@@ -15251,10 +15239,10 @@
         <v>2.16</v>
       </c>
       <c r="I282" t="n">
-        <v>0.8416626282771631</v>
+        <v>2.0593</v>
       </c>
       <c r="J282" t="n">
-        <v>14.30826468071177</v>
+        <v>35.0081</v>
       </c>
     </row>
     <row r="283">
@@ -15291,10 +15279,10 @@
         <v>1.76</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5550019577165114</v>
+        <v>1.604</v>
       </c>
       <c r="J283" t="n">
-        <v>9.435033281180694</v>
+        <v>27.268</v>
       </c>
     </row>
     <row r="284">
@@ -15331,10 +15319,10 @@
         <v>1.21</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1181812550817704</v>
+        <v>0.4265</v>
       </c>
       <c r="J284" t="n">
-        <v>2.009081336390096</v>
+        <v>7.2505</v>
       </c>
     </row>
     <row r="285">
@@ -15371,10 +15359,10 @@
         <v>1.18</v>
       </c>
       <c r="I285" t="n">
-        <v>0.0930193647698536</v>
+        <v>0.3551</v>
       </c>
       <c r="J285" t="n">
-        <v>1.581329201087511</v>
+        <v>6.0367</v>
       </c>
     </row>
     <row r="286">
@@ -15411,10 +15399,10 @@
         <v>0.9</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2168923145489283</v>
+        <v>-0.5325</v>
       </c>
       <c r="J286" t="n">
-        <v>-3.687169347331781</v>
+        <v>-9.0525</v>
       </c>
     </row>
     <row r="287">
@@ -15451,10 +15439,10 @@
         <v>1.04</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.1367651593296968</v>
+        <v>0.1873</v>
       </c>
       <c r="J287" t="n">
-        <v>-2.325007708604845</v>
+        <v>3.1841</v>
       </c>
     </row>
     <row r="288">
@@ -15491,10 +15479,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.2237806326902181</v>
+        <v>-0.0585</v>
       </c>
       <c r="J288" t="n">
-        <v>-3.804270755733708</v>
+        <v>-0.9945000000000001</v>
       </c>
     </row>
     <row r="289">
@@ -15531,10 +15519,10 @@
         <v>0.82</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3196077781502235</v>
+        <v>-0.2851</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.433332228553799</v>
+        <v>-4.8467</v>
       </c>
     </row>
     <row r="290">
@@ -15571,10 +15559,10 @@
         <v>0.74</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3825906687454017</v>
+        <v>-0.4194</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.504041368671828</v>
+        <v>-7.1298</v>
       </c>
     </row>
     <row r="291">
@@ -15611,10 +15599,10 @@
         <v>0.58</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5163623364080017</v>
+        <v>-0.6393</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.778159718936028</v>
+        <v>-10.8681</v>
       </c>
     </row>
     <row r="292">
@@ -15651,10 +15639,10 @@
         <v>1.93</v>
       </c>
       <c r="I292" t="n">
-        <v>0.6702843496705684</v>
+        <v>1.87</v>
       </c>
       <c r="J292" t="n">
-        <v>10.72454959472909</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="293">
@@ -15691,10 +15679,10 @@
         <v>1.62</v>
       </c>
       <c r="I293" t="n">
-        <v>0.4294663499929385</v>
+        <v>1.3138</v>
       </c>
       <c r="J293" t="n">
-        <v>6.871461599887017</v>
+        <v>21.0208</v>
       </c>
     </row>
     <row r="294">
@@ -15731,10 +15719,10 @@
         <v>1.47</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3185629124082522</v>
+        <v>0.9769</v>
       </c>
       <c r="J294" t="n">
-        <v>5.097006598532035</v>
+        <v>15.6304</v>
       </c>
     </row>
     <row r="295">
@@ -15771,10 +15759,10 @@
         <v>1.37</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2381676373594984</v>
+        <v>0.7608</v>
       </c>
       <c r="J295" t="n">
-        <v>3.810682197751974</v>
+        <v>12.1728</v>
       </c>
     </row>
     <row r="296">
@@ -15811,10 +15799,10 @@
         <v>1.15</v>
       </c>
       <c r="I296" t="n">
-        <v>0.05634418493686844</v>
+        <v>0.2643</v>
       </c>
       <c r="J296" t="n">
-        <v>0.9015069589898951</v>
+        <v>4.2288</v>
       </c>
     </row>
     <row r="297">
@@ -15851,10 +15839,10 @@
         <v>0.91</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.25946131345174</v>
+        <v>-0.0969</v>
       </c>
       <c r="J297" t="n">
-        <v>-4.15138101522784</v>
+        <v>-1.5504</v>
       </c>
     </row>
     <row r="298">
@@ -15891,10 +15879,10 @@
         <v>0.88</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.2849407197898328</v>
+        <v>-0.1496</v>
       </c>
       <c r="J298" t="n">
-        <v>-4.559051516637324</v>
+        <v>-2.3936</v>
       </c>
     </row>
     <row r="299">
@@ -15931,10 +15919,10 @@
         <v>0.87</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2933499296331767</v>
+        <v>-0.1668</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.693598874130828</v>
+        <v>-2.6688</v>
       </c>
     </row>
     <row r="300">
@@ -15971,10 +15959,10 @@
         <v>0.67</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4495820448787265</v>
+        <v>-0.508</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.193312718059624</v>
+        <v>-8.128</v>
       </c>
     </row>
     <row r="301">
@@ -16011,10 +15999,10 @@
         <v>0.6</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5077319713696417</v>
+        <v>-0.604</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.123711541914266</v>
+        <v>-9.664</v>
       </c>
     </row>
     <row r="302">
@@ -16051,10 +16039,10 @@
         <v>1.99</v>
       </c>
       <c r="I302" t="n">
-        <v>0.7563103397838159</v>
+        <v>2.058</v>
       </c>
       <c r="J302" t="n">
-        <v>18.15144815481158</v>
+        <v>49.392</v>
       </c>
     </row>
     <row r="303">
@@ -16091,10 +16079,10 @@
         <v>1.43</v>
       </c>
       <c r="I303" t="n">
-        <v>0.3313708996018173</v>
+        <v>1.1341</v>
       </c>
       <c r="J303" t="n">
-        <v>7.952901590443616</v>
+        <v>27.2184</v>
       </c>
     </row>
     <row r="304">
@@ -16131,10 +16119,10 @@
         <v>0.95</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1120580535285533</v>
+        <v>-0.2878</v>
       </c>
       <c r="J304" t="n">
-        <v>-2.689393284685279</v>
+        <v>-6.9072</v>
       </c>
     </row>
     <row r="305">
@@ -16171,10 +16159,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.6143185018335194</v>
+        <v>-1.2264</v>
       </c>
       <c r="J305" t="n">
-        <v>-14.74364404400447</v>
+        <v>-29.4336</v>
       </c>
     </row>
     <row r="306">
@@ -16211,10 +16199,10 @@
         <v>0.54</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6381766023597937</v>
+        <v>-1.2665</v>
       </c>
       <c r="J306" t="n">
-        <v>-15.31623845663505</v>
+        <v>-30.396</v>
       </c>
     </row>
     <row r="307">
@@ -16251,10 +16239,10 @@
         <v>1.48</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4025662616547389</v>
+        <v>0.7211</v>
       </c>
       <c r="J307" t="n">
-        <v>9.661590279713733</v>
+        <v>17.3064</v>
       </c>
     </row>
     <row r="308">
@@ -16291,10 +16279,10 @@
         <v>1.19</v>
       </c>
       <c r="I308" t="n">
-        <v>0.07917069014063127</v>
+        <v>0.3481</v>
       </c>
       <c r="J308" t="n">
-        <v>1.900096563375151</v>
+        <v>8.3544</v>
       </c>
     </row>
     <row r="309">
@@ -16331,10 +16319,10 @@
         <v>0.99</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.121147038103005</v>
+        <v>-0.0675</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.907528914472119</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="310">
@@ -16371,10 +16359,10 @@
         <v>0.93</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1859087536344744</v>
+        <v>-0.1932</v>
       </c>
       <c r="J310" t="n">
-        <v>-4.461810087227386</v>
+        <v>-4.6368</v>
       </c>
     </row>
     <row r="311">
@@ -16411,10 +16399,10 @@
         <v>0.71</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4220179397117613</v>
+        <v>-0.5175</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.12843055308227</v>
+        <v>-12.42</v>
       </c>
     </row>
     <row r="312">
@@ -16451,10 +16439,10 @@
         <v>1.8</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5867030452710498</v>
+        <v>1.681</v>
       </c>
       <c r="J312" t="n">
-        <v>10.5606548148789</v>
+        <v>30.258</v>
       </c>
     </row>
     <row r="313">
@@ -16491,10 +16479,10 @@
         <v>1.42</v>
       </c>
       <c r="I313" t="n">
-        <v>0.2789673443200156</v>
+        <v>0.9152</v>
       </c>
       <c r="J313" t="n">
-        <v>5.021412197760281</v>
+        <v>16.4736</v>
       </c>
     </row>
     <row r="314">
@@ -16531,10 +16519,10 @@
         <v>1.4</v>
       </c>
       <c r="I314" t="n">
-        <v>0.2640234298639381</v>
+        <v>0.8658</v>
       </c>
       <c r="J314" t="n">
-        <v>4.752421737550885</v>
+        <v>15.5844</v>
       </c>
     </row>
     <row r="315">
@@ -16571,10 +16559,10 @@
         <v>1.26</v>
       </c>
       <c r="I315" t="n">
-        <v>0.1453372279326156</v>
+        <v>0.5471</v>
       </c>
       <c r="J315" t="n">
-        <v>2.61607010278708</v>
+        <v>9.847799999999999</v>
       </c>
     </row>
     <row r="316">
@@ -16611,10 +16599,10 @@
         <v>1.26</v>
       </c>
       <c r="I316" t="n">
-        <v>0.1453372279326156</v>
+        <v>0.5471</v>
       </c>
       <c r="J316" t="n">
-        <v>2.61607010278708</v>
+        <v>9.847799999999999</v>
       </c>
     </row>
     <row r="317">
@@ -16651,10 +16639,10 @@
         <v>1.46</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2695600443041907</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="J317" t="n">
-        <v>4.852080797475432</v>
+        <v>13.7808</v>
       </c>
     </row>
     <row r="318">
@@ -16691,10 +16679,10 @@
         <v>0.88</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.3395082483403988</v>
+        <v>-0.1936</v>
       </c>
       <c r="J318" t="n">
-        <v>-6.111148470127178</v>
+        <v>-3.4848</v>
       </c>
     </row>
     <row r="319">
@@ -16731,10 +16719,10 @@
         <v>0.85</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.3644289431228325</v>
+        <v>-0.2592</v>
       </c>
       <c r="J319" t="n">
-        <v>-6.559720976210984</v>
+        <v>-4.6656</v>
       </c>
     </row>
     <row r="320">
@@ -16771,10 +16759,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5267258020609088</v>
+        <v>-0.5048</v>
       </c>
       <c r="J320" t="n">
-        <v>-9.481064437096359</v>
+        <v>-9.086399999999999</v>
       </c>
     </row>
     <row r="321">
@@ -16811,10 +16799,10 @@
         <v>0.46</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.7560531336665214</v>
+        <v>-0.7936</v>
       </c>
       <c r="J321" t="n">
-        <v>-13.60895640599738</v>
+        <v>-14.2848</v>
       </c>
     </row>
     <row r="322">
@@ -16851,10 +16839,10 @@
         <v>1.51</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3747794289659718</v>
+        <v>1.2693</v>
       </c>
       <c r="J322" t="n">
-        <v>8.994706295183324</v>
+        <v>30.4632</v>
       </c>
     </row>
     <row r="323">
@@ -16891,10 +16879,10 @@
         <v>1.43</v>
       </c>
       <c r="I323" t="n">
-        <v>0.3130523552356253</v>
+        <v>1.1067</v>
       </c>
       <c r="J323" t="n">
-        <v>7.513256525655008</v>
+        <v>26.5608</v>
       </c>
     </row>
     <row r="324">
@@ -16931,10 +16919,10 @@
         <v>1.05</v>
       </c>
       <c r="I324" t="n">
-        <v>0.01662134627190759</v>
+        <v>0.1085</v>
       </c>
       <c r="J324" t="n">
-        <v>0.3989123105257822</v>
+        <v>2.604</v>
       </c>
     </row>
     <row r="325">
@@ -16971,10 +16959,10 @@
         <v>0.91</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1648061651105889</v>
+        <v>-0.4308</v>
       </c>
       <c r="J325" t="n">
-        <v>-3.955347962654134</v>
+        <v>-10.3392</v>
       </c>
     </row>
     <row r="326">
@@ -17011,10 +16999,10 @@
         <v>0.83</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.271265762625599</v>
+        <v>-0.6428</v>
       </c>
       <c r="J326" t="n">
-        <v>-6.510378303014377</v>
+        <v>-15.4272</v>
       </c>
     </row>
     <row r="327">
@@ -17051,10 +17039,10 @@
         <v>1.11</v>
       </c>
       <c r="I327" t="n">
-        <v>0.1107600816710765</v>
+        <v>0.2802</v>
       </c>
       <c r="J327" t="n">
-        <v>2.658241960105836</v>
+        <v>6.7248</v>
       </c>
     </row>
     <row r="328">
@@ -17091,10 +17079,10 @@
         <v>1.11</v>
       </c>
       <c r="I328" t="n">
-        <v>0.1107600816710765</v>
+        <v>0.2802</v>
       </c>
       <c r="J328" t="n">
-        <v>2.658241960105836</v>
+        <v>6.7248</v>
       </c>
     </row>
     <row r="329">
@@ -17131,10 +17119,10 @@
         <v>1.01</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.01172291999973354</v>
+        <v>0.0853</v>
       </c>
       <c r="J329" t="n">
-        <v>-0.2813500799936051</v>
+        <v>2.0472</v>
       </c>
     </row>
     <row r="330">
@@ -17171,10 +17159,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1886537846284624</v>
+        <v>-0.3424</v>
       </c>
       <c r="J330" t="n">
-        <v>-4.527690831083099</v>
+        <v>-8.217599999999999</v>
       </c>
     </row>
     <row r="331">
@@ -17211,10 +17199,10 @@
         <v>0.49</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.480446668290456</v>
+        <v>-0.7637</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.53072003897094</v>
+        <v>-18.3288</v>
       </c>
     </row>
     <row r="332">
@@ -17251,10 +17239,10 @@
         <v>1.69</v>
       </c>
       <c r="I332" t="n">
-        <v>0.4844646083797282</v>
+        <v>1.491</v>
       </c>
       <c r="J332" t="n">
-        <v>8.720362950835106</v>
+        <v>26.838</v>
       </c>
     </row>
     <row r="333">
@@ -17291,10 +17279,10 @@
         <v>1.54</v>
       </c>
       <c r="I333" t="n">
-        <v>0.3693396434437899</v>
+        <v>1.2023</v>
       </c>
       <c r="J333" t="n">
-        <v>6.648113581988218</v>
+        <v>21.6414</v>
       </c>
     </row>
     <row r="334">
@@ -17331,10 +17319,10 @@
         <v>1.48</v>
       </c>
       <c r="I334" t="n">
-        <v>0.3230238575628092</v>
+        <v>1.0775</v>
       </c>
       <c r="J334" t="n">
-        <v>5.814429436130565</v>
+        <v>19.395</v>
       </c>
     </row>
     <row r="335">
@@ -17371,10 +17359,10 @@
         <v>1.27</v>
       </c>
       <c r="I335" t="n">
-        <v>0.168003639718002</v>
+        <v>0.5777</v>
       </c>
       <c r="J335" t="n">
-        <v>3.024065514924036</v>
+        <v>10.3986</v>
       </c>
     </row>
     <row r="336">
@@ -17411,10 +17399,10 @@
         <v>1.06</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.0009098949161317847</v>
+        <v>0.0473</v>
       </c>
       <c r="J336" t="n">
-        <v>-0.01637810849037212</v>
+        <v>0.8514</v>
       </c>
     </row>
     <row r="337">
@@ -17451,10 +17439,10 @@
         <v>1.1</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.05124496209878647</v>
+        <v>0.3025</v>
       </c>
       <c r="J337" t="n">
-        <v>-0.9224093177781565</v>
+        <v>5.445</v>
       </c>
     </row>
     <row r="338">
@@ -17491,10 +17479,10 @@
         <v>0.9</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.2374834272230948</v>
+        <v>-0.1249</v>
       </c>
       <c r="J338" t="n">
-        <v>-4.274701690015707</v>
+        <v>-2.2482</v>
       </c>
     </row>
     <row r="339">
@@ -17531,10 +17519,10 @@
         <v>0.68</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.4251275356244566</v>
+        <v>-0.5011</v>
       </c>
       <c r="J339" t="n">
-        <v>-7.652295641240219</v>
+        <v>-9.0198</v>
       </c>
     </row>
     <row r="340">
@@ -17571,10 +17559,10 @@
         <v>0.68</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4251275356244566</v>
+        <v>-0.5011</v>
       </c>
       <c r="J340" t="n">
-        <v>-7.652295641240219</v>
+        <v>-9.0198</v>
       </c>
     </row>
     <row r="341">
@@ -17611,10 +17599,10 @@
         <v>0.68</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4251275356244566</v>
+        <v>-0.5011</v>
       </c>
       <c r="J341" t="n">
-        <v>-7.652295641240219</v>
+        <v>-9.0198</v>
       </c>
     </row>
     <row r="342">
@@ -17651,10 +17639,10 @@
         <v>1.38</v>
       </c>
       <c r="I342" t="n">
-        <v>0.2195794388248553</v>
+        <v>0.6095</v>
       </c>
       <c r="J342" t="n">
-        <v>5.269906531796527</v>
+        <v>14.628</v>
       </c>
     </row>
     <row r="343">
@@ -17691,10 +17679,10 @@
         <v>1.06</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.04618003138851348</v>
+        <v>0.1384</v>
       </c>
       <c r="J343" t="n">
-        <v>-1.108320753324324</v>
+        <v>3.3216</v>
       </c>
     </row>
     <row r="344">
@@ -17731,10 +17719,10 @@
         <v>1.01</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.1045106786285666</v>
+        <v>0.0129</v>
       </c>
       <c r="J344" t="n">
-        <v>-2.508256287085598</v>
+        <v>0.3096</v>
       </c>
     </row>
     <row r="345">
@@ -17771,10 +17759,10 @@
         <v>0.89</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.273052980366387</v>
+        <v>-0.2551</v>
       </c>
       <c r="J345" t="n">
-        <v>-6.553271528793287</v>
+        <v>-6.1224</v>
       </c>
     </row>
     <row r="346">
@@ -17811,10 +17799,10 @@
         <v>0.84</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3450563130976236</v>
+        <v>-0.3332</v>
       </c>
       <c r="J346" t="n">
-        <v>-8.281351514342967</v>
+        <v>-7.9968</v>
       </c>
     </row>
     <row r="347">
@@ -17851,10 +17839,10 @@
         <v>1.78</v>
       </c>
       <c r="I347" t="n">
-        <v>0.8569183685758787</v>
+        <v>1.0401</v>
       </c>
       <c r="J347" t="n">
-        <v>20.56604084582109</v>
+        <v>24.9624</v>
       </c>
     </row>
     <row r="348">
@@ -17891,10 +17879,10 @@
         <v>1.17</v>
       </c>
       <c r="I348" t="n">
-        <v>0.1636366126639447</v>
+        <v>0.3107</v>
       </c>
       <c r="J348" t="n">
-        <v>3.927278703934674</v>
+        <v>7.4568</v>
       </c>
     </row>
     <row r="349">
@@ -17931,10 +17919,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.07694589605109102</v>
+        <v>-0.1804</v>
       </c>
       <c r="J349" t="n">
-        <v>-1.846701505226184</v>
+        <v>-4.3296</v>
       </c>
     </row>
     <row r="350">
@@ -17971,10 +17959,10 @@
         <v>0.82</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.197386509068488</v>
+        <v>-0.3718</v>
       </c>
       <c r="J350" t="n">
-        <v>-4.737276217643712</v>
+        <v>-8.9232</v>
       </c>
     </row>
     <row r="351">
@@ -18011,10 +17999,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3241652311683102</v>
+        <v>-0.5461</v>
       </c>
       <c r="J351" t="n">
-        <v>-7.779965548039445</v>
+        <v>-13.1064</v>
       </c>
     </row>
     <row r="352">
@@ -18051,10 +18039,10 @@
         <v>1.78</v>
       </c>
       <c r="I352" t="n">
-        <v>0.5621638721350821</v>
+        <v>1.7226</v>
       </c>
       <c r="J352" t="n">
-        <v>11.24327744270164</v>
+        <v>34.452</v>
       </c>
     </row>
     <row r="353">
@@ -18091,10 +18079,10 @@
         <v>1.46</v>
       </c>
       <c r="I353" t="n">
-        <v>0.3324978714285163</v>
+        <v>1.1152</v>
       </c>
       <c r="J353" t="n">
-        <v>6.649957428570326</v>
+        <v>22.304</v>
       </c>
     </row>
     <row r="354">
@@ -18131,10 +18119,10 @@
         <v>1.2</v>
       </c>
       <c r="I354" t="n">
-        <v>0.142164001859333</v>
+        <v>0.4815</v>
       </c>
       <c r="J354" t="n">
-        <v>2.843280037186661</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="355">
@@ -18171,10 +18159,10 @@
         <v>0.92</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.1379025380667984</v>
+        <v>-0.4348</v>
       </c>
       <c r="J355" t="n">
-        <v>-2.758050761335968</v>
+        <v>-8.696</v>
       </c>
     </row>
     <row r="356">
@@ -18211,10 +18199,10 @@
         <v>0.9</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.1644915385256828</v>
+        <v>-0.4907</v>
       </c>
       <c r="J356" t="n">
-        <v>-3.289830770513657</v>
+        <v>-9.814</v>
       </c>
     </row>
     <row r="357">
@@ -18251,10 +18239,10 @@
         <v>1.05</v>
       </c>
       <c r="I357" t="n">
-        <v>-0.07416164512747821</v>
+        <v>0.1804</v>
       </c>
       <c r="J357" t="n">
-        <v>-1.483232902549564</v>
+        <v>3.608</v>
       </c>
     </row>
     <row r="358">
@@ -18291,10 +18279,10 @@
         <v>0.93</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.1926050505908758</v>
+        <v>-0.1087</v>
       </c>
       <c r="J358" t="n">
-        <v>-3.852101011817515</v>
+        <v>-2.174</v>
       </c>
     </row>
     <row r="359">
@@ -18331,10 +18319,10 @@
         <v>0.87</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.2432086351108016</v>
+        <v>-0.235</v>
       </c>
       <c r="J359" t="n">
-        <v>-4.864172702216031</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="360">
@@ -18371,10 +18359,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.2993519775043703</v>
+        <v>-0.3367</v>
       </c>
       <c r="J360" t="n">
-        <v>-5.987039550087405</v>
+        <v>-6.734</v>
       </c>
     </row>
     <row r="361">
@@ -18411,10 +18399,10 @@
         <v>0.79</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3187413052139239</v>
+        <v>-0.3676</v>
       </c>
       <c r="J361" t="n">
-        <v>-6.374826104278478</v>
+        <v>-7.352</v>
       </c>
     </row>
     <row r="362">
@@ -18451,10 +18439,10 @@
         <v>1.49</v>
       </c>
       <c r="I362" t="n">
-        <v>0.3437727178825312</v>
+        <v>1.1435</v>
       </c>
       <c r="J362" t="n">
-        <v>6.187908921885561</v>
+        <v>20.583</v>
       </c>
     </row>
     <row r="363">
@@ -18491,10 +18479,10 @@
         <v>1.47</v>
       </c>
       <c r="I363" t="n">
-        <v>0.3285471407483878</v>
+        <v>1.1022</v>
       </c>
       <c r="J363" t="n">
-        <v>5.913848533470979</v>
+        <v>19.8396</v>
       </c>
     </row>
     <row r="364">
@@ -18531,10 +18519,10 @@
         <v>1.22</v>
       </c>
       <c r="I364" t="n">
-        <v>0.1464764811539478</v>
+        <v>0.4965</v>
       </c>
       <c r="J364" t="n">
-        <v>2.63657666077106</v>
+        <v>8.936999999999999</v>
       </c>
     </row>
     <row r="365">
@@ -18571,10 +18559,10 @@
         <v>1.22</v>
       </c>
       <c r="I365" t="n">
-        <v>0.1464764811539478</v>
+        <v>0.4965</v>
       </c>
       <c r="J365" t="n">
-        <v>2.63657666077106</v>
+        <v>8.936999999999999</v>
       </c>
     </row>
     <row r="366">
@@ -18611,10 +18599,10 @@
         <v>1.2</v>
       </c>
       <c r="I366" t="n">
-        <v>0.1308812033321753</v>
+        <v>0.4471</v>
       </c>
       <c r="J366" t="n">
-        <v>2.355861659979155</v>
+        <v>8.047800000000001</v>
       </c>
     </row>
     <row r="367">
@@ -18651,10 +18639,10 @@
         <v>1.21</v>
       </c>
       <c r="I367" t="n">
-        <v>0.0064089037247008</v>
+        <v>0.4271</v>
       </c>
       <c r="J367" t="n">
-        <v>0.1153602670446144</v>
+        <v>7.6878</v>
       </c>
     </row>
     <row r="368">
@@ -18691,10 +18679,10 @@
         <v>1.21</v>
       </c>
       <c r="I368" t="n">
-        <v>0.0064089037247008</v>
+        <v>0.4271</v>
       </c>
       <c r="J368" t="n">
-        <v>0.1153602670446144</v>
+        <v>7.6878</v>
       </c>
     </row>
     <row r="369">
@@ -18731,10 +18719,10 @@
         <v>0.97</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.2335005749578991</v>
+        <v>-0.039</v>
       </c>
       <c r="J369" t="n">
-        <v>-4.203010349242184</v>
+        <v>-0.702</v>
       </c>
     </row>
     <row r="370">
@@ -18771,10 +18759,10 @@
         <v>0.79</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.3974904580627678</v>
+        <v>-0.3766</v>
       </c>
       <c r="J370" t="n">
-        <v>-7.154828245129821</v>
+        <v>-6.7788</v>
       </c>
     </row>
     <row r="371">
@@ -18811,10 +18799,10 @@
         <v>0.41</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.7493357246284944</v>
+        <v>-0.857</v>
       </c>
       <c r="J371" t="n">
-        <v>-13.4880430433129</v>
+        <v>-15.426</v>
       </c>
     </row>
     <row r="372">
@@ -18851,10 +18839,10 @@
         <v>1.51</v>
       </c>
       <c r="I372" t="n">
-        <v>0.4002464832227665</v>
+        <v>1.2795</v>
       </c>
       <c r="J372" t="n">
-        <v>11.60714801346023</v>
+        <v>37.1055</v>
       </c>
     </row>
     <row r="373">
@@ -18891,10 +18879,10 @@
         <v>1.45</v>
       </c>
       <c r="I373" t="n">
-        <v>0.3505657316824039</v>
+        <v>1.1584</v>
       </c>
       <c r="J373" t="n">
-        <v>10.16640621878971</v>
+        <v>33.5936</v>
       </c>
     </row>
     <row r="374">
@@ -18931,10 +18919,10 @@
         <v>1.2</v>
       </c>
       <c r="I374" t="n">
-        <v>0.1348112249065077</v>
+        <v>0.59</v>
       </c>
       <c r="J374" t="n">
-        <v>3.909525522288724</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="375">
@@ -18971,10 +18959,10 @@
         <v>0.77</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.3441332369319756</v>
+        <v>-0.7814</v>
       </c>
       <c r="J375" t="n">
-        <v>-9.979863871027291</v>
+        <v>-22.6606</v>
       </c>
     </row>
     <row r="376">
@@ -19011,10 +18999,10 @@
         <v>0.7</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.4342991009750668</v>
+        <v>-0.9394</v>
       </c>
       <c r="J376" t="n">
-        <v>-12.59467392827694</v>
+        <v>-27.2426</v>
       </c>
     </row>
     <row r="377">
@@ -19051,10 +19039,10 @@
         <v>1.48</v>
       </c>
       <c r="I377" t="n">
-        <v>0.4046943525778292</v>
+        <v>0.7308</v>
       </c>
       <c r="J377" t="n">
-        <v>11.73613622475705</v>
+        <v>21.1932</v>
       </c>
     </row>
     <row r="378">
@@ -19091,10 +19079,10 @@
         <v>1.26</v>
       </c>
       <c r="I378" t="n">
-        <v>0.1539100726786705</v>
+        <v>0.4571</v>
       </c>
       <c r="J378" t="n">
-        <v>4.463392107681443</v>
+        <v>13.2559</v>
       </c>
     </row>
     <row r="379">
@@ -19131,10 +19119,10 @@
         <v>0.96</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.1575605851362002</v>
+        <v>-0.1263</v>
       </c>
       <c r="J379" t="n">
-        <v>-4.569256968949807</v>
+        <v>-3.6627</v>
       </c>
     </row>
     <row r="380">
@@ -19171,10 +19159,10 @@
         <v>0.8</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.324487983770569</v>
+        <v>-0.3903</v>
       </c>
       <c r="J380" t="n">
-        <v>-9.4101515293465</v>
+        <v>-11.3187</v>
       </c>
     </row>
     <row r="381">
@@ -19211,10 +19199,10 @@
         <v>0.65</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.4760658682558963</v>
+        <v>-0.5888</v>
       </c>
       <c r="J381" t="n">
-        <v>-13.80591017942099</v>
+        <v>-17.0752</v>
       </c>
     </row>
     <row r="382">
@@ -19251,10 +19239,10 @@
         <v>1.75</v>
       </c>
       <c r="I382" t="n">
-        <v>0.5609737742916368</v>
+        <v>1.7138</v>
       </c>
       <c r="J382" t="n">
-        <v>13.46337058299928</v>
+        <v>41.1312</v>
       </c>
     </row>
     <row r="383">
@@ -19291,10 +19279,10 @@
         <v>1.31</v>
       </c>
       <c r="I383" t="n">
-        <v>0.2033294695459645</v>
+        <v>0.8378</v>
       </c>
       <c r="J383" t="n">
-        <v>4.879907269103148</v>
+        <v>20.1072</v>
       </c>
     </row>
     <row r="384">
@@ -19331,10 +19319,10 @@
         <v>1.14</v>
       </c>
       <c r="I384" t="n">
-        <v>0.0641639466661941</v>
+        <v>0.3777</v>
       </c>
       <c r="J384" t="n">
-        <v>1.539934719988658</v>
+        <v>9.0648</v>
       </c>
     </row>
     <row r="385">
@@ -19371,10 +19359,10 @@
         <v>1.12</v>
       </c>
       <c r="I385" t="n">
-        <v>0.0480580488473026</v>
+        <v>0.3177</v>
       </c>
       <c r="J385" t="n">
-        <v>1.153393172335262</v>
+        <v>7.6248</v>
       </c>
     </row>
     <row r="386">
@@ -19411,10 +19399,10 @@
         <v>0.48</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.7402004177042549</v>
+        <v>-1.3939</v>
       </c>
       <c r="J386" t="n">
-        <v>-17.76481002490212</v>
+        <v>-33.4536</v>
       </c>
     </row>
     <row r="387">
@@ -19451,10 +19439,10 @@
         <v>1.34</v>
       </c>
       <c r="I387" t="n">
-        <v>0.2937928274836343</v>
+        <v>0.5763</v>
       </c>
       <c r="J387" t="n">
-        <v>7.051027859607224</v>
+        <v>13.8312</v>
       </c>
     </row>
     <row r="388">
@@ -19491,10 +19479,10 @@
         <v>1.1</v>
       </c>
       <c r="I388" t="n">
-        <v>0.02014667778426165</v>
+        <v>0.2333</v>
       </c>
       <c r="J388" t="n">
-        <v>0.4835202668222796</v>
+        <v>5.5992</v>
       </c>
     </row>
     <row r="389">
@@ -19531,10 +19519,10 @@
         <v>0.91</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.1670268016616099</v>
+        <v>-0.2057</v>
       </c>
       <c r="J389" t="n">
-        <v>-4.008643239878638</v>
+        <v>-4.9368</v>
       </c>
     </row>
     <row r="390">
@@ -19571,10 +19559,10 @@
         <v>0.82</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.260496418993007</v>
+        <v>-0.3509</v>
       </c>
       <c r="J390" t="n">
-        <v>-6.251914055832168</v>
+        <v>-8.4216</v>
       </c>
     </row>
     <row r="391">
@@ -19611,10 +19599,10 @@
         <v>0.76</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.3225661739314928</v>
+        <v>-0.4369</v>
       </c>
       <c r="J391" t="n">
-        <v>-7.741588174355828</v>
+        <v>-10.4856</v>
       </c>
     </row>
     <row r="392">
@@ -19651,10 +19639,10 @@
         <v>1.93</v>
       </c>
       <c r="I392" t="n">
-        <v>0.7855474392164314</v>
+        <v>1.9895</v>
       </c>
       <c r="J392" t="n">
-        <v>18.85313854119435</v>
+        <v>47.748</v>
       </c>
     </row>
     <row r="393">
@@ -19691,10 +19679,10 @@
         <v>1.36</v>
       </c>
       <c r="I393" t="n">
-        <v>0.3032684812648577</v>
+        <v>0.9627</v>
       </c>
       <c r="J393" t="n">
-        <v>7.278443550356585</v>
+        <v>23.1048</v>
       </c>
     </row>
     <row r="394">
@@ -19731,10 +19719,10 @@
         <v>1.01</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.02485930012004503</v>
+        <v>-0.0379</v>
       </c>
       <c r="J394" t="n">
-        <v>-0.5966232028810808</v>
+        <v>-0.9096</v>
       </c>
     </row>
     <row r="395">
@@ -19771,10 +19759,10 @@
         <v>0.83</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.2437664568294176</v>
+        <v>-0.6398</v>
       </c>
       <c r="J395" t="n">
-        <v>-5.850394963906023</v>
+        <v>-15.3552</v>
       </c>
     </row>
     <row r="396">
@@ -19811,10 +19799,10 @@
         <v>0.55</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.5762835498459291</v>
+        <v>-1.2537</v>
       </c>
       <c r="J396" t="n">
-        <v>-13.8308051963023</v>
+        <v>-30.0888</v>
       </c>
     </row>
     <row r="397">
@@ -19851,10 +19839,10 @@
         <v>1.12</v>
       </c>
       <c r="I397" t="n">
-        <v>0.09090262351492034</v>
+        <v>0.2874</v>
       </c>
       <c r="J397" t="n">
-        <v>2.181662964358088</v>
+        <v>6.8976</v>
       </c>
     </row>
     <row r="398">
@@ -19891,10 +19879,10 @@
         <v>0.99</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.05095596303768368</v>
+        <v>0.0047</v>
       </c>
       <c r="J398" t="n">
-        <v>-1.222943112904408</v>
+        <v>0.1128</v>
       </c>
     </row>
     <row r="399">
@@ -19931,10 +19919,10 @@
         <v>0.95</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.09310107775220779</v>
+        <v>-0.0893</v>
       </c>
       <c r="J399" t="n">
-        <v>-2.234425866052987</v>
+        <v>-2.1432</v>
       </c>
     </row>
     <row r="400">
@@ -19971,10 +19959,10 @@
         <v>0.95</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.09310107775220779</v>
+        <v>-0.0893</v>
       </c>
       <c r="J400" t="n">
-        <v>-2.234425866052987</v>
+        <v>-2.1432</v>
       </c>
     </row>
     <row r="401">
@@ -20011,10 +19999,10 @@
         <v>0.64</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.4244296118775285</v>
+        <v>-0.5846</v>
       </c>
       <c r="J401" t="n">
-        <v>-10.18631068506068</v>
+        <v>-14.0304</v>
       </c>
     </row>
     <row r="402">
@@ -20051,10 +20039,10 @@
         <v>1.28</v>
       </c>
       <c r="I402" t="n">
-        <v>0.2323631268559457</v>
+        <v>0.7851</v>
       </c>
       <c r="J402" t="n">
-        <v>6.738530678822426</v>
+        <v>22.7679</v>
       </c>
     </row>
     <row r="403">
@@ -20091,10 +20079,10 @@
         <v>1.25</v>
       </c>
       <c r="I403" t="n">
-        <v>0.2035307461658502</v>
+        <v>0.7134</v>
       </c>
       <c r="J403" t="n">
-        <v>5.902391638809655</v>
+        <v>20.6886</v>
       </c>
     </row>
     <row r="404">
@@ -20131,10 +20119,10 @@
         <v>1.13</v>
       </c>
       <c r="I404" t="n">
-        <v>0.09443383645514229</v>
+        <v>0.3798</v>
       </c>
       <c r="J404" t="n">
-        <v>2.738581257199126</v>
+        <v>11.0142</v>
       </c>
     </row>
     <row r="405">
@@ -20171,10 +20159,10 @@
         <v>1.07</v>
       </c>
       <c r="I405" t="n">
-        <v>0.04262170111627808</v>
+        <v>0.1831</v>
       </c>
       <c r="J405" t="n">
-        <v>1.236029332372064</v>
+        <v>5.3099</v>
       </c>
     </row>
     <row r="406">
@@ -20211,10 +20199,10 @@
         <v>0.92</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.1256463643590398</v>
+        <v>-0.396</v>
       </c>
       <c r="J406" t="n">
-        <v>-3.643744566412154</v>
+        <v>-11.484</v>
       </c>
     </row>
     <row r="407">
@@ -20251,10 +20239,10 @@
         <v>1.41</v>
       </c>
       <c r="I407" t="n">
-        <v>0.3300538262838071</v>
+        <v>0.6593</v>
       </c>
       <c r="J407" t="n">
-        <v>9.571560962230405</v>
+        <v>19.1197</v>
       </c>
     </row>
     <row r="408">
@@ -20291,10 +20279,10 @@
         <v>1.14</v>
       </c>
       <c r="I408" t="n">
-        <v>0.03896755603464604</v>
+        <v>0.2949</v>
       </c>
       <c r="J408" t="n">
-        <v>1.130059125004735</v>
+        <v>8.552099999999999</v>
       </c>
     </row>
     <row r="409">
@@ -20331,10 +20319,10 @@
         <v>1.03</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.07719637044955073</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="J409" t="n">
-        <v>-2.238694743036971</v>
+        <v>2.7347</v>
       </c>
     </row>
     <row r="410">
@@ -20371,10 +20359,10 @@
         <v>0.7</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.4313612434168788</v>
+        <v>-0.5195</v>
       </c>
       <c r="J410" t="n">
-        <v>-12.50947605908949</v>
+        <v>-15.0655</v>
       </c>
     </row>
     <row r="411">
@@ -20411,10 +20399,10 @@
         <v>0.7</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.4313612434168788</v>
+        <v>-0.5195</v>
       </c>
       <c r="J411" t="n">
-        <v>-12.50947605908949</v>
+        <v>-15.0655</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7732/event_7732_evp_summary.xlsx
+++ b/database/event/7732/event_7732_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>8.172800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4.7185</v>
       </c>
       <c r="D2" t="n">
         <v>2.8803</v>
@@ -545,7 +545,7 @@
         <v>7.2042</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4.1593</v>
       </c>
       <c r="D3" t="n">
         <v>2.489</v>
@@ -591,7 +591,7 @@
         <v>6.3806</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.6838</v>
       </c>
       <c r="D4" t="n">
         <v>2.1563</v>
@@ -637,7 +637,7 @@
         <v>5.0272</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.9024</v>
       </c>
       <c r="D5" t="n">
         <v>1.6095</v>
@@ -683,7 +683,7 @@
         <v>3.6123</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.0855</v>
       </c>
       <c r="D6" t="n">
         <v>1.0379</v>
@@ -729,7 +729,7 @@
         <v>3.4178</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.9732</v>
       </c>
       <c r="D7" t="n">
         <v>0.9594</v>
@@ -775,7 +775,7 @@
         <v>3.151</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1.8192</v>
       </c>
       <c r="D8" t="n">
         <v>0.8516</v>
@@ -821,7 +821,7 @@
         <v>2.9819</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.7216</v>
       </c>
       <c r="D9" t="n">
         <v>0.7833</v>
@@ -867,7 +867,7 @@
         <v>2.9483</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.7022</v>
       </c>
       <c r="D10" t="n">
         <v>0.7697000000000001</v>
@@ -913,7 +913,7 @@
         <v>2.5673</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.4822</v>
       </c>
       <c r="D11" t="n">
         <v>0.6158</v>
@@ -959,7 +959,7 @@
         <v>2.4774</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.4303</v>
       </c>
       <c r="D12" t="n">
         <v>0.5795</v>
@@ -1005,7 +1005,7 @@
         <v>2.0799</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.2008</v>
       </c>
       <c r="D13" t="n">
         <v>0.4189</v>
@@ -1051,7 +1051,7 @@
         <v>1.966</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.135</v>
       </c>
       <c r="D14" t="n">
         <v>0.3729</v>
@@ -1097,7 +1097,7 @@
         <v>1.8706</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D15" t="n">
         <v>0.3343</v>
@@ -1143,7 +1143,7 @@
         <v>1.8334</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.0585</v>
       </c>
       <c r="D16" t="n">
         <v>0.3193</v>
@@ -1189,7 +1189,7 @@
         <v>1.806</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.0427</v>
       </c>
       <c r="D17" t="n">
         <v>0.3082</v>
@@ -1235,7 +1235,7 @@
         <v>1.6236</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.9374</v>
       </c>
       <c r="D18" t="n">
         <v>0.2345</v>
@@ -1281,7 +1281,7 @@
         <v>1.587</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.9162</v>
       </c>
       <c r="D19" t="n">
         <v>0.2198</v>
@@ -1327,7 +1327,7 @@
         <v>1.4431</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="D20" t="n">
         <v>0.1616</v>
@@ -1373,7 +1373,7 @@
         <v>1.4194</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.8195</v>
       </c>
       <c r="D21" t="n">
         <v>0.152</v>
@@ -1419,7 +1419,7 @@
         <v>1.3217</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.7631</v>
       </c>
       <c r="D22" t="n">
         <v>0.1126</v>
@@ -1465,7 +1465,7 @@
         <v>1.2217</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.7053</v>
       </c>
       <c r="D23" t="n">
         <v>0.0722</v>
@@ -1511,7 +1511,7 @@
         <v>1.1953</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.6901</v>
       </c>
       <c r="D24" t="n">
         <v>0.0615</v>
@@ -1557,7 +1557,7 @@
         <v>1.1885</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.6862</v>
       </c>
       <c r="D25" t="n">
         <v>0.0588</v>
@@ -1603,7 +1603,7 @@
         <v>1.1682</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.6744</v>
       </c>
       <c r="D26" t="n">
         <v>0.0506</v>
@@ -1649,7 +1649,7 @@
         <v>1.1273</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.6508</v>
       </c>
       <c r="D27" t="n">
         <v>0.034</v>
@@ -1695,7 +1695,7 @@
         <v>0.822</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.4746</v>
       </c>
       <c r="D28" t="n">
         <v>-0.0893</v>
@@ -1741,7 +1741,7 @@
         <v>0.79</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.4561</v>
       </c>
       <c r="D29" t="n">
         <v>-0.1022</v>
@@ -1787,7 +1787,7 @@
         <v>0.7655</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.442</v>
       </c>
       <c r="D30" t="n">
         <v>-0.1121</v>
@@ -1833,7 +1833,7 @@
         <v>0.7648</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.4415</v>
       </c>
       <c r="D31" t="n">
         <v>-0.1124</v>
@@ -1879,7 +1879,7 @@
         <v>0.748</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.4318</v>
       </c>
       <c r="D32" t="n">
         <v>-0.1192</v>
@@ -1925,7 +1925,7 @@
         <v>0.6032999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.3483</v>
       </c>
       <c r="D33" t="n">
         <v>-0.1776</v>
@@ -1971,7 +1971,7 @@
         <v>0.5646</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.326</v>
       </c>
       <c r="D34" t="n">
         <v>-0.1933</v>
@@ -2017,7 +2017,7 @@
         <v>0.5148</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.2972</v>
       </c>
       <c r="D35" t="n">
         <v>-0.2134</v>
@@ -2063,7 +2063,7 @@
         <v>0.4763</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.275</v>
       </c>
       <c r="D36" t="n">
         <v>-0.2289</v>
@@ -2109,7 +2109,7 @@
         <v>0.4402</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.2541</v>
       </c>
       <c r="D37" t="n">
         <v>-0.2435</v>
@@ -2155,7 +2155,7 @@
         <v>0.3539</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.2043</v>
       </c>
       <c r="D38" t="n">
         <v>-0.2784</v>
@@ -2201,7 +2201,7 @@
         <v>0.3128</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.1806</v>
       </c>
       <c r="D39" t="n">
         <v>-0.295</v>
@@ -2247,7 +2247,7 @@
         <v>0.3108</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.1794</v>
       </c>
       <c r="D40" t="n">
         <v>-0.2958</v>
@@ -2293,7 +2293,7 @@
         <v>0.2899</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.1674</v>
       </c>
       <c r="D41" t="n">
         <v>-0.3042</v>
@@ -2339,7 +2339,7 @@
         <v>0.1191</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.0688</v>
       </c>
       <c r="D42" t="n">
         <v>-0.3732</v>
@@ -2385,7 +2385,7 @@
         <v>0.0588</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.0339</v>
       </c>
       <c r="D43" t="n">
         <v>-0.3976</v>
@@ -2431,7 +2431,7 @@
         <v>0.0035</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="D44" t="n">
         <v>-0.4199</v>
@@ -2477,7 +2477,7 @@
         <v>-0.005</v>
       </c>
       <c r="C45" t="n">
-        <v>-0</v>
+        <v>-0.0029</v>
       </c>
       <c r="D45" t="n">
         <v>-0.4234</v>
@@ -2523,7 +2523,7 @@
         <v>-0.0101</v>
       </c>
       <c r="C46" t="n">
-        <v>-0</v>
+        <v>-0.0058</v>
       </c>
       <c r="D46" t="n">
         <v>-0.4254</v>
@@ -2569,7 +2569,7 @@
         <v>-0.0458</v>
       </c>
       <c r="C47" t="n">
-        <v>-0</v>
+        <v>-0.0264</v>
       </c>
       <c r="D47" t="n">
         <v>-0.4399</v>
@@ -2615,7 +2615,7 @@
         <v>-0.0742</v>
       </c>
       <c r="C48" t="n">
-        <v>-0</v>
+        <v>-0.0428</v>
       </c>
       <c r="D48" t="n">
         <v>-0.4513</v>
@@ -2661,7 +2661,7 @@
         <v>-0.1659</v>
       </c>
       <c r="C49" t="n">
-        <v>-0</v>
+        <v>-0.0958</v>
       </c>
       <c r="D49" t="n">
         <v>-0.4884</v>
@@ -2707,7 +2707,7 @@
         <v>-0.1669</v>
       </c>
       <c r="C50" t="n">
-        <v>-0</v>
+        <v>-0.0964</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4888</v>
@@ -2753,7 +2753,7 @@
         <v>-0.1774</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.1024</v>
       </c>
       <c r="D51" t="n">
         <v>-0.493</v>
@@ -2799,7 +2799,7 @@
         <v>-0.2568</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.1483</v>
       </c>
       <c r="D52" t="n">
         <v>-0.5251</v>
@@ -2845,7 +2845,7 @@
         <v>-0.2839</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.1639</v>
       </c>
       <c r="D53" t="n">
         <v>-0.5361</v>
@@ -2891,7 +2891,7 @@
         <v>-0.3084</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.1781</v>
       </c>
       <c r="D54" t="n">
         <v>-0.5459000000000001</v>
@@ -2937,7 +2937,7 @@
         <v>-0.3167</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.1828</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5493</v>
@@ -2983,7 +2983,7 @@
         <v>-0.5928</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.3422</v>
       </c>
       <c r="D56" t="n">
         <v>-0.6608000000000001</v>
@@ -3029,7 +3029,7 @@
         <v>-0.6064000000000001</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.3501</v>
       </c>
       <c r="D57" t="n">
         <v>-0.6663</v>
@@ -3075,7 +3075,7 @@
         <v>-0.6201</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.358</v>
       </c>
       <c r="D58" t="n">
         <v>-0.6719000000000001</v>
@@ -3121,7 +3121,7 @@
         <v>-0.6235000000000001</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.36</v>
       </c>
       <c r="D59" t="n">
         <v>-0.6732</v>
@@ -3167,7 +3167,7 @@
         <v>-0.6635</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.3831</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6894</v>
@@ -3213,7 +3213,7 @@
         <v>-0.7432</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.4291</v>
       </c>
       <c r="D61" t="n">
         <v>-0.7216</v>
@@ -3259,7 +3259,7 @@
         <v>-0.7456</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.4305</v>
       </c>
       <c r="D62" t="n">
         <v>-0.7226</v>
@@ -3305,7 +3305,7 @@
         <v>-0.7509</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.4335</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7247</v>
@@ -3351,7 +3351,7 @@
         <v>-0.8004</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.4621</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7447</v>
@@ -3397,7 +3397,7 @@
         <v>-0.8519</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.4918</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7655</v>
@@ -3443,7 +3443,7 @@
         <v>-0.8767</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.5062</v>
       </c>
       <c r="D66" t="n">
         <v>-0.7755</v>
@@ -3489,7 +3489,7 @@
         <v>-0.898</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.5184</v>
       </c>
       <c r="D67" t="n">
         <v>-0.7841</v>
@@ -3535,7 +3535,7 @@
         <v>-0.9895</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.5713</v>
       </c>
       <c r="D68" t="n">
         <v>-0.8211000000000001</v>
@@ -3581,7 +3581,7 @@
         <v>-1.1521</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.6652</v>
       </c>
       <c r="D69" t="n">
         <v>-0.8868</v>
@@ -3627,7 +3627,7 @@
         <v>-1.2351</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.7131</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9203</v>
@@ -3673,7 +3673,7 @@
         <v>-1.2374</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.7144</v>
       </c>
       <c r="D71" t="n">
         <v>-0.9212</v>
@@ -3719,7 +3719,7 @@
         <v>-1.5052</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.869</v>
       </c>
       <c r="D72" t="n">
         <v>-1.0294</v>
@@ -3765,7 +3765,7 @@
         <v>-1.6828</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.9715</v>
       </c>
       <c r="D73" t="n">
         <v>-1.1012</v>
@@ -3811,7 +3811,7 @@
         <v>-1.8246</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-1.0534</v>
       </c>
       <c r="D74" t="n">
         <v>-1.1585</v>
@@ -3857,7 +3857,7 @@
         <v>-2.1033</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.2143</v>
       </c>
       <c r="D75" t="n">
         <v>-1.271</v>
@@ -3903,7 +3903,7 @@
         <v>-2.3379</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.3498</v>
       </c>
       <c r="D76" t="n">
         <v>-1.3658</v>

--- a/database/event/7732/event_7732_evp_summary.xlsx
+++ b/database/event/7732/event_7732_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.7185</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8803</v>
+        <v>2.8121</v>
       </c>
       <c r="E2" t="n">
         <v>8.172800000000001</v>
@@ -548,7 +548,7 @@
         <v>4.1593</v>
       </c>
       <c r="D3" t="n">
-        <v>2.489</v>
+        <v>2.4262</v>
       </c>
       <c r="E3" t="n">
         <v>7.2042</v>
@@ -594,7 +594,7 @@
         <v>3.6838</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1563</v>
+        <v>2.0981</v>
       </c>
       <c r="E4" t="n">
         <v>6.3806</v>
@@ -640,7 +640,7 @@
         <v>2.9024</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6095</v>
+        <v>1.5589</v>
       </c>
       <c r="E5" t="n">
         <v>5.0272</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6123</v>
+        <v>4.5364</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0855</v>
+        <v>2.619</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0379</v>
+        <v>1.3634</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6123</v>
+        <v>4.5364</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9465</v>
+        <v>4.8706</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3342</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9465</v>
+        <v>5.3341</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9649</v>
+        <v>5.379</v>
       </c>
       <c r="J6" t="n">
         <v>-0.3342</v>
@@ -713,7 +713,7 @@
         <v>64</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6307</v>
+        <v>5.0448</v>
       </c>
       <c r="N6" t="n">
         <v>180</v>
@@ -732,7 +732,7 @@
         <v>1.9732</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9594</v>
+        <v>0.9177</v>
       </c>
       <c r="E7" t="n">
         <v>3.4178</v>
@@ -778,7 +778,7 @@
         <v>1.8192</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8516</v>
+        <v>0.8114</v>
       </c>
       <c r="E8" t="n">
         <v>3.151</v>
@@ -824,7 +824,7 @@
         <v>1.7216</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7833</v>
+        <v>0.7441</v>
       </c>
       <c r="E9" t="n">
         <v>2.9819</v>
@@ -870,7 +870,7 @@
         <v>1.7022</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.7307</v>
       </c>
       <c r="E10" t="n">
         <v>2.9483</v>
@@ -906,357 +906,357 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5673</v>
+        <v>2.8895</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4822</v>
+        <v>1.6682</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6158</v>
+        <v>0.7073</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5673</v>
+        <v>2.8895</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3419</v>
+        <v>2.8281</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2254</v>
+        <v>0.0614</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3419</v>
+        <v>2.8281</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3419</v>
+        <v>2.8519</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2254</v>
+        <v>0.0614</v>
       </c>
       <c r="K11" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="L11" t="n">
-        <v>174</v>
+        <v>64</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5673</v>
+        <v>2.9133</v>
       </c>
       <c r="N11" t="n">
-        <v>227</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4774</v>
+        <v>2.5673</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4303</v>
+        <v>1.4822</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5795</v>
+        <v>0.5789</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4774</v>
+        <v>2.5673</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1219</v>
+        <v>0.3419</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3555</v>
+        <v>2.2254</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1219</v>
+        <v>0.3419</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1219</v>
+        <v>0.3419</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3555</v>
+        <v>2.2254</v>
       </c>
       <c r="K12" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="L12" t="n">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4774</v>
+        <v>2.5673</v>
       </c>
       <c r="N12" t="n">
-        <v>156</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0799</v>
+        <v>2.4774</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2008</v>
+        <v>1.4303</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4189</v>
+        <v>0.5431</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0799</v>
+        <v>2.4774</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7447</v>
+        <v>0.1219</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3352</v>
+        <v>2.3555</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7447</v>
+        <v>0.1219</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7447</v>
+        <v>0.1219</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3352</v>
+        <v>2.3555</v>
       </c>
       <c r="K13" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L13" t="n">
         <v>117</v>
       </c>
       <c r="M13" t="n">
-        <v>2.0799</v>
+        <v>2.4774</v>
       </c>
       <c r="N13" t="n">
-        <v>179</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.966</v>
+        <v>2.1478</v>
       </c>
       <c r="C14" t="n">
-        <v>1.135</v>
+        <v>1.24</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3729</v>
+        <v>0.4118</v>
       </c>
       <c r="E14" t="n">
-        <v>1.966</v>
+        <v>2.1478</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9046</v>
+        <v>2.1478</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0614</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9046</v>
+        <v>2.1478</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9135</v>
+        <v>2.1478</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0614</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="L14" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9749</v>
+        <v>2.1478</v>
       </c>
       <c r="N14" t="n">
-        <v>180</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8706</v>
+        <v>2.0799</v>
       </c>
       <c r="C15" t="n">
-        <v>1.08</v>
+        <v>1.2008</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3343</v>
+        <v>0.3847</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8706</v>
+        <v>2.0799</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4546</v>
+        <v>1.7447</v>
       </c>
       <c r="G15" t="n">
-        <v>1.416</v>
+        <v>0.3352</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4546</v>
+        <v>1.7447</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4546</v>
+        <v>1.7447</v>
       </c>
       <c r="J15" t="n">
-        <v>1.416</v>
+        <v>0.3352</v>
       </c>
       <c r="K15" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="L15" t="n">
-        <v>172</v>
+        <v>117</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8706</v>
+        <v>2.0799</v>
       </c>
       <c r="N15" t="n">
-        <v>214</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8334</v>
+        <v>2.0244</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0585</v>
+        <v>1.1688</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3193</v>
+        <v>0.3626</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8334</v>
+        <v>2.0244</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7813</v>
+        <v>2.0244</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0521</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7813</v>
+        <v>2.0244</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7813</v>
+        <v>2.0244</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0521</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="L16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8334</v>
+        <v>2.0244</v>
       </c>
       <c r="N16" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.806</v>
+        <v>1.8706</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0427</v>
+        <v>1.08</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3082</v>
+        <v>0.3013</v>
       </c>
       <c r="E17" t="n">
-        <v>1.806</v>
+        <v>1.8706</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6244</v>
+        <v>0.4546</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1816</v>
+        <v>1.416</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6244</v>
+        <v>0.4546</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6244</v>
+        <v>0.4546</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1816</v>
+        <v>1.416</v>
       </c>
       <c r="K17" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="L17" t="n">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="M17" t="n">
-        <v>1.806</v>
+        <v>1.8706</v>
       </c>
       <c r="N17" t="n">
-        <v>179</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6236</v>
+        <v>1.8334</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9374</v>
+        <v>1.0585</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2345</v>
+        <v>0.2865</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6236</v>
+        <v>1.8334</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4034</v>
+        <v>0.7813</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2202</v>
+        <v>1.0521</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4034</v>
+        <v>0.7813</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4034</v>
+        <v>0.7813</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2202</v>
+        <v>1.0521</v>
       </c>
       <c r="K18" t="n">
         <v>33</v>
@@ -1265,7 +1265,7 @@
         <v>69</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6236</v>
+        <v>1.8334</v>
       </c>
       <c r="N18" t="n">
         <v>102</v>
@@ -1274,185 +1274,185 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.587</v>
+        <v>1.806</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9162</v>
+        <v>1.0427</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2198</v>
+        <v>0.2756</v>
       </c>
       <c r="E19" t="n">
-        <v>1.587</v>
+        <v>1.806</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7282</v>
+        <v>0.6244</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1412</v>
+        <v>1.1816</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7282</v>
+        <v>0.6244</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7282</v>
+        <v>0.6244</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1412</v>
+        <v>1.1816</v>
       </c>
       <c r="K19" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="L19" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="M19" t="n">
-        <v>1.587</v>
+        <v>1.806</v>
       </c>
       <c r="N19" t="n">
-        <v>104</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4431</v>
+        <v>1.6236</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.9374</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1616</v>
+        <v>0.2029</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4431</v>
+        <v>1.6236</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4431</v>
+        <v>1.4034</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.2202</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4431</v>
+        <v>1.4034</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4431</v>
+        <v>1.4034</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.2202</v>
       </c>
       <c r="K20" t="n">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4431</v>
+        <v>1.6236</v>
       </c>
       <c r="N20" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4194</v>
+        <v>1.587</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8195</v>
+        <v>0.9162</v>
       </c>
       <c r="D21" t="n">
-        <v>0.152</v>
+        <v>0.1884</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4194</v>
+        <v>1.587</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6194</v>
+        <v>1.7282</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8</v>
+        <v>-0.1412</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6194</v>
+        <v>1.7282</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6194</v>
+        <v>1.7282</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8</v>
+        <v>-0.1412</v>
       </c>
       <c r="K21" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="L21" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4194</v>
+        <v>1.587</v>
       </c>
       <c r="N21" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3217</v>
+        <v>1.4194</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7631</v>
+        <v>0.8195</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1126</v>
+        <v>0.1216</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3217</v>
+        <v>1.4194</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3217</v>
+        <v>0.6194</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3217</v>
+        <v>0.6194</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3217</v>
+        <v>0.6194</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3217</v>
+        <v>1.4194</v>
       </c>
       <c r="N22" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.2217</v>
+        <v>1.31</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7053</v>
+        <v>0.7563</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0722</v>
+        <v>0.078</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2217</v>
+        <v>1.31</v>
       </c>
       <c r="F23" t="n">
-        <v>1.36</v>
+        <v>1.4483</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1383</v>
       </c>
       <c r="H23" t="n">
-        <v>1.36</v>
+        <v>1.4483</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3663</v>
+        <v>1.4605</v>
       </c>
       <c r="J23" t="n">
         <v>-0.1383</v>
@@ -1495,7 +1495,7 @@
         <v>64</v>
       </c>
       <c r="M23" t="n">
-        <v>1.228</v>
+        <v>1.3222</v>
       </c>
       <c r="N23" t="n">
         <v>180</v>
@@ -1504,633 +1504,633 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>0SAMAS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1953</v>
+        <v>1.2142</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6901</v>
+        <v>0.701</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0615</v>
+        <v>0.0398</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1953</v>
+        <v>1.2142</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9677</v>
+        <v>1.2142</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2276</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9677</v>
+        <v>1.2142</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9677</v>
+        <v>1.2142</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2276</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="L24" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1953</v>
+        <v>1.2142</v>
       </c>
       <c r="N24" t="n">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kwezz</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.1885</v>
+        <v>1.1953</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6862</v>
+        <v>0.6901</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0588</v>
+        <v>0.0323</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1885</v>
+        <v>1.1953</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1885</v>
+        <v>0.9677</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1885</v>
+        <v>0.9677</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1885</v>
+        <v>0.9677</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="K25" t="n">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1885</v>
+        <v>1.1953</v>
       </c>
       <c r="N25" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>kwezz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.1682</v>
+        <v>1.1885</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6744</v>
+        <v>0.6862</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0506</v>
+        <v>0.0296</v>
       </c>
       <c r="E26" t="n">
-        <v>1.1682</v>
+        <v>1.1885</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4761</v>
+        <v>1.1885</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3079</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4761</v>
+        <v>1.1885</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4761</v>
+        <v>1.1885</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3079</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="L26" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.1682</v>
+        <v>1.1885</v>
       </c>
       <c r="N26" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1273</v>
+        <v>1.1682</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6508</v>
+        <v>0.6744</v>
       </c>
       <c r="D27" t="n">
-        <v>0.034</v>
+        <v>0.0215</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1273</v>
+        <v>1.1682</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1273</v>
+        <v>1.4761</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.3079</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1273</v>
+        <v>1.4761</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1273</v>
+        <v>1.4761</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.3079</v>
       </c>
       <c r="K27" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1273</v>
+        <v>1.1682</v>
       </c>
       <c r="N27" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0SAMAS</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.822</v>
+        <v>1.1273</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4746</v>
+        <v>0.6508</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0893</v>
+        <v>0.0052</v>
       </c>
       <c r="E28" t="n">
-        <v>0.822</v>
+        <v>1.1273</v>
       </c>
       <c r="F28" t="n">
-        <v>0.822</v>
+        <v>1.1273</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.822</v>
+        <v>1.1273</v>
       </c>
       <c r="I28" t="n">
-        <v>0.822</v>
+        <v>1.1273</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.822</v>
+        <v>1.1273</v>
       </c>
       <c r="N28" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.79</v>
+        <v>1.0498</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4561</v>
+        <v>0.6061</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1022</v>
+        <v>-0.0257</v>
       </c>
       <c r="E29" t="n">
-        <v>0.79</v>
+        <v>1.0498</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2715</v>
+        <v>1.0498</v>
       </c>
       <c r="G29" t="n">
-        <v>1.0615</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2715</v>
+        <v>1.0498</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2715</v>
+        <v>1.0498</v>
       </c>
       <c r="J29" t="n">
-        <v>1.0615</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="L29" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.79</v>
+        <v>1.0498</v>
       </c>
       <c r="N29" t="n">
-        <v>179</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7655</v>
+        <v>0.7924</v>
       </c>
       <c r="C30" t="n">
-        <v>0.442</v>
+        <v>0.4575</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1121</v>
+        <v>-0.1282</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7655</v>
+        <v>0.7924</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2497</v>
+        <v>0.7924</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5158</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2497</v>
+        <v>0.7924</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2497</v>
+        <v>0.7924</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5158</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>39</v>
+        <v>117</v>
       </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.7924</v>
+      </c>
+      <c r="N30" t="n">
         <v>117</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.7655000000000001</v>
-      </c>
-      <c r="N30" t="n">
-        <v>156</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7648</v>
+        <v>0.79</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4415</v>
+        <v>0.4561</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1124</v>
+        <v>-0.1292</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7648</v>
+        <v>0.79</v>
       </c>
       <c r="F31" t="n">
-        <v>1.7648</v>
+        <v>-0.2715</v>
       </c>
       <c r="G31" t="n">
-        <v>-1</v>
+        <v>1.0615</v>
       </c>
       <c r="H31" t="n">
-        <v>1.7648</v>
+        <v>-0.2715</v>
       </c>
       <c r="I31" t="n">
-        <v>1.7648</v>
+        <v>-0.2715</v>
       </c>
       <c r="J31" t="n">
-        <v>-1</v>
+        <v>1.0615</v>
       </c>
       <c r="K31" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="L31" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7647999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="N31" t="n">
-        <v>102</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.748</v>
+        <v>0.7655</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4318</v>
+        <v>0.442</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1192</v>
+        <v>-0.1389</v>
       </c>
       <c r="E32" t="n">
-        <v>0.748</v>
+        <v>0.7655</v>
       </c>
       <c r="F32" t="n">
-        <v>1.748</v>
+        <v>0.2497</v>
       </c>
       <c r="G32" t="n">
-        <v>-1</v>
+        <v>0.5158</v>
       </c>
       <c r="H32" t="n">
-        <v>1.748</v>
+        <v>0.2497</v>
       </c>
       <c r="I32" t="n">
-        <v>1.748</v>
+        <v>0.2497</v>
       </c>
       <c r="J32" t="n">
-        <v>-1</v>
+        <v>0.5158</v>
       </c>
       <c r="K32" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L32" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="M32" t="n">
-        <v>0.748</v>
+        <v>0.7655000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>102</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.7648</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3483</v>
+        <v>0.4415</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1776</v>
+        <v>-0.1392</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.7648</v>
       </c>
       <c r="F33" t="n">
-        <v>1.7636</v>
+        <v>1.7648</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.1603</v>
+        <v>-1</v>
       </c>
       <c r="H33" t="n">
-        <v>1.7636</v>
+        <v>1.7648</v>
       </c>
       <c r="I33" t="n">
-        <v>1.7636</v>
+        <v>1.7648</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.1603</v>
+        <v>-1</v>
       </c>
       <c r="K33" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L33" t="n">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.7647999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>156</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5646</v>
+        <v>0.748</v>
       </c>
       <c r="C34" t="n">
-        <v>0.326</v>
+        <v>0.4318</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1933</v>
+        <v>-0.1459</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5646</v>
+        <v>0.748</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5646</v>
+        <v>1.748</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5646</v>
+        <v>1.748</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5646</v>
+        <v>1.748</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K34" t="n">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5646</v>
+        <v>0.748</v>
       </c>
       <c r="N34" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5148</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2972</v>
+        <v>0.3483</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2134</v>
+        <v>-0.2036</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5148</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5148</v>
+        <v>1.7636</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-1.1603</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5148</v>
+        <v>1.7636</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5148</v>
+        <v>1.7636</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-1.1603</v>
       </c>
       <c r="K35" t="n">
+        <v>39</v>
+      </c>
+      <c r="L35" t="n">
         <v>117</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
-        <v>0.5148</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>117</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4763</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>0.275</v>
+        <v>0.3355</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2289</v>
+        <v>-0.2124</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4763</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4347</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0416</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4347</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4347</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0416</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="L36" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.4762999999999999</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>122</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4402</v>
+        <v>0.4763</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2541</v>
+        <v>0.275</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2435</v>
+        <v>-0.2542</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4402</v>
+        <v>0.4763</v>
       </c>
       <c r="F37" t="n">
-        <v>1.154</v>
+        <v>0.4347</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.7138</v>
+        <v>0.0416</v>
       </c>
       <c r="H37" t="n">
-        <v>1.154</v>
+        <v>0.4347</v>
       </c>
       <c r="I37" t="n">
-        <v>1.154</v>
+        <v>0.4347</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7138</v>
+        <v>0.0416</v>
       </c>
       <c r="K37" t="n">
         <v>42</v>
@@ -2139,7 +2139,7 @@
         <v>80</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4401999999999999</v>
+        <v>0.4762999999999999</v>
       </c>
       <c r="N37" t="n">
         <v>122</v>
@@ -2148,78 +2148,78 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.3539</v>
+        <v>0.4402</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2043</v>
+        <v>0.2541</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2784</v>
+        <v>-0.2685</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3539</v>
+        <v>0.4402</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3539</v>
+        <v>1.154</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.7138</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3539</v>
+        <v>1.154</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3539</v>
+        <v>1.154</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.7138</v>
       </c>
       <c r="K38" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3539</v>
+        <v>0.4401999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>71</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.3128</v>
+        <v>0.3539</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1806</v>
+        <v>0.2043</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.295</v>
+        <v>-0.3029</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3128</v>
+        <v>0.3539</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3128</v>
+        <v>0.3539</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3128</v>
+        <v>0.3539</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3128</v>
+        <v>0.3539</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3128</v>
+        <v>0.3539</v>
       </c>
       <c r="N39" t="n">
         <v>71</v>
@@ -2240,507 +2240,507 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3108</v>
+        <v>0.3128</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1794</v>
+        <v>0.1806</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2958</v>
+        <v>-0.3193</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3108</v>
+        <v>0.3128</v>
       </c>
       <c r="F40" t="n">
-        <v>1.3108</v>
+        <v>0.3128</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.3108</v>
+        <v>0.3128</v>
       </c>
       <c r="I40" t="n">
-        <v>1.3108</v>
+        <v>0.3128</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="L40" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3108</v>
+        <v>0.3128</v>
       </c>
       <c r="N40" t="n">
-        <v>122</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.2899</v>
+        <v>0.3108</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1674</v>
+        <v>0.1794</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3042</v>
+        <v>-0.3201</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2899</v>
+        <v>0.3108</v>
       </c>
       <c r="F41" t="n">
-        <v>1.1828</v>
+        <v>1.3108</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.8929</v>
+        <v>-1</v>
       </c>
       <c r="H41" t="n">
-        <v>1.1828</v>
+        <v>1.3108</v>
       </c>
       <c r="I41" t="n">
-        <v>1.1828</v>
+        <v>1.3108</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8929</v>
+        <v>-1</v>
       </c>
       <c r="K41" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L41" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2899</v>
+        <v>0.3108</v>
       </c>
       <c r="N41" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.1191</v>
+        <v>0.2899</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0688</v>
+        <v>0.1674</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3732</v>
+        <v>-0.3284</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1191</v>
+        <v>0.2899</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1191</v>
+        <v>1.1828</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-0.8929</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1191</v>
+        <v>1.1828</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1191</v>
+        <v>1.1828</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-0.8929</v>
       </c>
       <c r="K42" t="n">
-        <v>111</v>
+        <v>39</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1191</v>
+        <v>0.2899</v>
       </c>
       <c r="N42" t="n">
-        <v>111</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>m1N1</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.0588</v>
+        <v>0.2891</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0339</v>
+        <v>0.1669</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3976</v>
+        <v>-0.3287</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0588</v>
+        <v>0.2891</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0588</v>
+        <v>0.2891</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0588</v>
+        <v>0.2891</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0588</v>
+        <v>0.2891</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.0588</v>
+        <v>0.2891</v>
       </c>
       <c r="N43" t="n">
-        <v>21</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>m1N1</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0035</v>
+        <v>0.0588</v>
       </c>
       <c r="C44" t="n">
-        <v>0.002</v>
+        <v>0.0339</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4199</v>
+        <v>-0.4205</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0035</v>
+        <v>0.0588</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9324</v>
+        <v>0.0588</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.9288999999999999</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9324</v>
+        <v>0.0588</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9324</v>
+        <v>0.0588</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.9288999999999999</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="L44" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.003500000000000059</v>
+        <v>0.0588</v>
       </c>
       <c r="N44" t="n">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.005</v>
+        <v>0.0035</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.0029</v>
+        <v>0.002</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4234</v>
+        <v>-0.4425</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.005</v>
+        <v>0.0035</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.4567</v>
+        <v>0.9324</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4517</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4567</v>
+        <v>0.9324</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4567</v>
+        <v>0.9324</v>
       </c>
       <c r="J45" t="n">
-        <v>0.4517</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="K45" t="n">
         <v>53</v>
       </c>
       <c r="L45" t="n">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.005000000000000004</v>
+        <v>0.003500000000000059</v>
       </c>
       <c r="N45" t="n">
-        <v>227</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.0101</v>
+        <v>-0.005</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0058</v>
+        <v>-0.0029</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4254</v>
+        <v>-0.4459</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.0101</v>
+        <v>-0.005</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.0101</v>
+        <v>-0.4567</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.4517</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.0101</v>
+        <v>-0.4567</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0101</v>
+        <v>-0.4567</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.4517</v>
       </c>
       <c r="K46" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.0101</v>
+        <v>-0.005000000000000004</v>
       </c>
       <c r="N46" t="n">
-        <v>21</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0458</v>
+        <v>-0.0101</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0264</v>
+        <v>-0.0058</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4399</v>
+        <v>-0.4479</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0458</v>
+        <v>-0.0101</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.3497</v>
+        <v>-0.0101</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3039</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.3497</v>
+        <v>-0.0101</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.3513</v>
+        <v>-0.0101</v>
       </c>
       <c r="J47" t="n">
-        <v>0.3039</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="L47" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0474</v>
+        <v>-0.0101</v>
       </c>
       <c r="N47" t="n">
-        <v>180</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cabbi</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0742</v>
+        <v>-0.0327</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0428</v>
+        <v>-0.0189</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4513</v>
+        <v>-0.4569</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0742</v>
+        <v>-0.0327</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0742</v>
+        <v>-0.3366</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.3039</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0742</v>
+        <v>-0.3366</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0742</v>
+        <v>-0.3394</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>0.3039</v>
       </c>
       <c r="K48" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0742</v>
+        <v>-0.03549999999999998</v>
       </c>
       <c r="N48" t="n">
-        <v>117</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>dennyslaw</t>
+          <t>Cabbi</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.1659</v>
+        <v>-0.0742</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0958</v>
+        <v>-0.0428</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4884</v>
+        <v>-0.4735</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1659</v>
+        <v>-0.0742</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1659</v>
+        <v>-0.0742</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1659</v>
+        <v>-0.0742</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1659</v>
+        <v>-0.0742</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.1659</v>
+        <v>-0.0742</v>
       </c>
       <c r="N49" t="n">
-        <v>21</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>dennyslaw</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1669</v>
+        <v>-0.1659</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0964</v>
+        <v>-0.0958</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4888</v>
+        <v>-0.51</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1669</v>
+        <v>-0.1659</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1669</v>
+        <v>-0.1659</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1669</v>
+        <v>-0.1659</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1669</v>
+        <v>-0.1659</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1669</v>
+        <v>-0.1659</v>
       </c>
       <c r="N50" t="n">
-        <v>111</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51">
@@ -2756,7 +2756,7 @@
         <v>-0.1024</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.493</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="E51" t="n">
         <v>-0.1774</v>
@@ -2802,7 +2802,7 @@
         <v>-0.1483</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5251</v>
+        <v>-0.5462</v>
       </c>
       <c r="E52" t="n">
         <v>-0.2568</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1639</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5361</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="E53" t="n">
         <v>-0.2839</v>
@@ -2894,7 +2894,7 @@
         <v>-0.1781</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.5668</v>
       </c>
       <c r="E54" t="n">
         <v>-0.3084</v>
@@ -2930,323 +2930,323 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.3167</v>
+        <v>-0.3166</v>
       </c>
       <c r="C55" t="n">
         <v>-0.1828</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5493</v>
+        <v>-0.57</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3167</v>
+        <v>-0.3166</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3167</v>
+        <v>-0.3166</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3167</v>
+        <v>-0.3166</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3167</v>
+        <v>-0.3166</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.3167</v>
+        <v>-0.3166</v>
       </c>
       <c r="N55" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.5928</v>
+        <v>-0.3167</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.3422</v>
+        <v>-0.1828</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.5928</v>
+        <v>-0.3167</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.5928</v>
+        <v>-0.3167</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.5928</v>
+        <v>-0.3167</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5928</v>
+        <v>-0.3167</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.5928</v>
+        <v>-0.3167</v>
       </c>
       <c r="N56" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>IceBerg</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.3501</v>
+        <v>-0.3413</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6663</v>
+        <v>-0.6794</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>48</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.6201</v>
+        <v>-0.5928</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.358</v>
+        <v>-0.3422</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.6801</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.6201</v>
+        <v>-0.5928</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7229</v>
+        <v>-0.5928</v>
       </c>
       <c r="G58" t="n">
-        <v>-1.343</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.7229</v>
+        <v>-0.5928</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7229</v>
+        <v>-0.5928</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.343</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="L58" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.6201</v>
+        <v>-0.5928</v>
       </c>
       <c r="N58" t="n">
-        <v>179</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.36</v>
+        <v>-0.3501</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6732</v>
+        <v>-0.6855</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="N59" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.6635</v>
+        <v>-0.6201</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3831</v>
+        <v>-0.358</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6894</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.6635</v>
+        <v>-0.6201</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.6635</v>
+        <v>0.7229</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>-1.343</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.6635</v>
+        <v>0.7229</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.6635</v>
+        <v>0.7229</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>-1.343</v>
       </c>
       <c r="K60" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.6635</v>
+        <v>-0.6201</v>
       </c>
       <c r="N60" t="n">
-        <v>93</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>IceBerg</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.7432</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.4291</v>
+        <v>-0.36</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7216</v>
+        <v>-0.6923</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.7432</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.7432</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.7432</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7432</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.7432</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="N61" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62">
@@ -3262,7 +3262,7 @@
         <v>-0.4305</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7226</v>
+        <v>-0.741</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7456</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4335</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7247</v>
+        <v>-0.7431</v>
       </c>
       <c r="E63" t="n">
         <v>-0.7509</v>
@@ -3354,7 +3354,7 @@
         <v>-0.4621</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7447</v>
+        <v>-0.7628</v>
       </c>
       <c r="E64" t="n">
         <v>-0.8004</v>
@@ -3400,7 +3400,7 @@
         <v>-0.4918</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7655</v>
+        <v>-0.7833</v>
       </c>
       <c r="E65" t="n">
         <v>-0.8519</v>
@@ -3446,7 +3446,7 @@
         <v>-0.5062</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7755</v>
+        <v>-0.7932</v>
       </c>
       <c r="E66" t="n">
         <v>-0.8767</v>
@@ -3492,7 +3492,7 @@
         <v>-0.5184</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7841</v>
+        <v>-0.8017</v>
       </c>
       <c r="E67" t="n">
         <v>-0.898</v>
@@ -3538,7 +3538,7 @@
         <v>-0.5713</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.8381</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9895</v>
@@ -3584,7 +3584,7 @@
         <v>-0.6652</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8868</v>
+        <v>-0.9029</v>
       </c>
       <c r="E69" t="n">
         <v>-1.1521</v>
@@ -3630,7 +3630,7 @@
         <v>-0.7131</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9203</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="E70" t="n">
         <v>-1.2351</v>
@@ -3676,7 +3676,7 @@
         <v>-0.7144</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9212</v>
+        <v>-0.9369</v>
       </c>
       <c r="E71" t="n">
         <v>-1.2374</v>
@@ -3722,7 +3722,7 @@
         <v>-0.869</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0294</v>
+        <v>-1.0436</v>
       </c>
       <c r="E72" t="n">
         <v>-1.5052</v>
@@ -3768,7 +3768,7 @@
         <v>-0.9715</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1012</v>
+        <v>-1.1143</v>
       </c>
       <c r="E73" t="n">
         <v>-1.6828</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.8246</v>
+        <v>-1.8206</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.0534</v>
+        <v>-1.0511</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1585</v>
+        <v>-1.1692</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.8246</v>
+        <v>-1.8206</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.0609</v>
+        <v>-1.0569</v>
       </c>
       <c r="G74" t="n">
         <v>-0.7637</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.0609</v>
+        <v>-1.0569</v>
       </c>
       <c r="I74" t="n">
         <v>-1.0658</v>
@@ -3860,7 +3860,7 @@
         <v>-1.2143</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.271</v>
+        <v>-1.2819</v>
       </c>
       <c r="E75" t="n">
         <v>-2.1033</v>
@@ -3906,7 +3906,7 @@
         <v>-1.3498</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.3658</v>
+        <v>-1.3753</v>
       </c>
       <c r="E76" t="n">
         <v>-2.3379</v>

--- a/database/event/7732/event_7732_evp_summary.xlsx
+++ b/database/event/7732/event_7732_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.172800000000001</v>
+        <v>7.8399</v>
       </c>
       <c r="C2" t="n">
-        <v>4.7185</v>
+        <v>4.5263</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8121</v>
+        <v>2.9013</v>
       </c>
       <c r="E2" t="n">
-        <v>8.172800000000001</v>
+        <v>7.8399</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6481</v>
+        <v>1.7186</v>
       </c>
       <c r="G2" t="n">
-        <v>6.5247</v>
+        <v>6.1213</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6481</v>
+        <v>1.7186</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6481</v>
+        <v>1.7186</v>
       </c>
       <c r="J2" t="n">
-        <v>6.8953</v>
+        <v>6.1213</v>
       </c>
       <c r="K2" t="n">
         <v>53</v>
@@ -529,7 +529,7 @@
         <v>174</v>
       </c>
       <c r="M2" t="n">
-        <v>8.5434</v>
+        <v>7.8399</v>
       </c>
       <c r="N2" t="n">
         <v>227</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.2042</v>
+        <v>7.2237</v>
       </c>
       <c r="C3" t="n">
-        <v>4.1593</v>
+        <v>4.1705</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4262</v>
+        <v>2.6231</v>
       </c>
       <c r="E3" t="n">
-        <v>7.2042</v>
+        <v>7.2237</v>
       </c>
       <c r="F3" t="n">
-        <v>1.762</v>
+        <v>2.7558</v>
       </c>
       <c r="G3" t="n">
-        <v>5.4422</v>
+        <v>4.4679</v>
       </c>
       <c r="H3" t="n">
-        <v>1.762</v>
+        <v>2.7558</v>
       </c>
       <c r="I3" t="n">
-        <v>1.762</v>
+        <v>2.7558</v>
       </c>
       <c r="J3" t="n">
-        <v>5.4422</v>
+        <v>4.4679</v>
       </c>
       <c r="K3" t="n">
         <v>42</v>
@@ -575,7 +575,7 @@
         <v>172</v>
       </c>
       <c r="M3" t="n">
-        <v>7.2042</v>
+        <v>7.2237</v>
       </c>
       <c r="N3" t="n">
         <v>214</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3806</v>
+        <v>6.4369</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6838</v>
+        <v>3.7163</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0981</v>
+        <v>2.2679</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3806</v>
+        <v>6.4369</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7614</v>
+        <v>2.7487</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6192</v>
+        <v>3.6882</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7614</v>
+        <v>2.7487</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7614</v>
+        <v>2.7487</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6192</v>
+        <v>3.6882</v>
       </c>
       <c r="K4" t="n">
         <v>62</v>
@@ -621,7 +621,7 @@
         <v>117</v>
       </c>
       <c r="M4" t="n">
-        <v>6.3806</v>
+        <v>6.4369</v>
       </c>
       <c r="N4" t="n">
         <v>179</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0272</v>
+        <v>4.7452</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9024</v>
+        <v>2.7396</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5589</v>
+        <v>1.5042</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0272</v>
+        <v>4.7452</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7194</v>
+        <v>2.0751</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3077</v>
+        <v>2.6701</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7194</v>
+        <v>2.0751</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7194</v>
+        <v>2.0751</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3077</v>
+        <v>2.6701</v>
       </c>
       <c r="K5" t="n">
         <v>42</v>
@@ -667,7 +667,7 @@
         <v>172</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0271</v>
+        <v>4.745200000000001</v>
       </c>
       <c r="N5" t="n">
         <v>214</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5364</v>
+        <v>4.0063</v>
       </c>
       <c r="C6" t="n">
-        <v>2.619</v>
+        <v>2.313</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3634</v>
+        <v>1.1706</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5364</v>
+        <v>4.0063</v>
       </c>
       <c r="F6" t="n">
-        <v>4.8706</v>
+        <v>2.4978</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3342</v>
+        <v>1.5085</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3341</v>
+        <v>2.4978</v>
       </c>
       <c r="I6" t="n">
-        <v>5.379</v>
+        <v>2.4978</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3342</v>
+        <v>1.5085</v>
       </c>
       <c r="K6" t="n">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="L6" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="M6" t="n">
-        <v>5.0448</v>
+        <v>4.0063</v>
       </c>
       <c r="N6" t="n">
-        <v>180</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4178</v>
+        <v>3.717</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9732</v>
+        <v>2.146</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9177</v>
+        <v>1.04</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4178</v>
+        <v>3.717</v>
       </c>
       <c r="F7" t="n">
-        <v>1.76</v>
+        <v>3.9139</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6578</v>
+        <v>-0.1969</v>
       </c>
       <c r="H7" t="n">
-        <v>1.76</v>
+        <v>5.2345</v>
       </c>
       <c r="I7" t="n">
-        <v>1.76</v>
+        <v>5.4498</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6578</v>
+        <v>-0.1969</v>
       </c>
       <c r="K7" t="n">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="L7" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4178</v>
+        <v>5.252899999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>122</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.151</v>
+        <v>3.5963</v>
       </c>
       <c r="C8" t="n">
-        <v>1.8192</v>
+        <v>2.0763</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8114</v>
+        <v>0.9855</v>
       </c>
       <c r="E8" t="n">
-        <v>3.151</v>
+        <v>3.5963</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7591</v>
+        <v>2.3954</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3919</v>
+        <v>1.2009</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7591</v>
+        <v>2.3954</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7591</v>
+        <v>2.3954</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3919</v>
+        <v>1.2009</v>
       </c>
       <c r="K8" t="n">
         <v>53</v>
@@ -805,7 +805,7 @@
         <v>174</v>
       </c>
       <c r="M8" t="n">
-        <v>3.151</v>
+        <v>3.5963</v>
       </c>
       <c r="N8" t="n">
         <v>227</v>
@@ -814,185 +814,185 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9819</v>
+        <v>3.2572</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7216</v>
+        <v>1.8805</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7441</v>
+        <v>0.8324</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9819</v>
+        <v>3.2572</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5735</v>
+        <v>0.4358</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4084</v>
+        <v>2.8214</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5735</v>
+        <v>0.4358</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5735</v>
+        <v>0.4358</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4084</v>
+        <v>2.8214</v>
       </c>
       <c r="K9" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L9" t="n">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9819</v>
+        <v>3.2572</v>
       </c>
       <c r="N9" t="n">
-        <v>156</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9483</v>
+        <v>2.7994</v>
       </c>
       <c r="C10" t="n">
-        <v>1.7022</v>
+        <v>1.6162</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7307</v>
+        <v>0.6258</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9483</v>
+        <v>2.7994</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2593</v>
+        <v>2.6941</v>
       </c>
       <c r="G10" t="n">
-        <v>2.689</v>
+        <v>0.1053</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2593</v>
+        <v>2.6941</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2593</v>
+        <v>2.8049</v>
       </c>
       <c r="J10" t="n">
-        <v>2.689</v>
+        <v>0.1053</v>
       </c>
       <c r="K10" t="n">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="L10" t="n">
-        <v>172</v>
+        <v>64</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9483</v>
+        <v>2.9102</v>
       </c>
       <c r="N10" t="n">
-        <v>214</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8895</v>
+        <v>2.7646</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6682</v>
+        <v>1.5961</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7073</v>
+        <v>0.6101</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8895</v>
+        <v>2.7646</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8281</v>
+        <v>1.615</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0614</v>
+        <v>1.1496</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8281</v>
+        <v>1.615</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8519</v>
+        <v>1.615</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0614</v>
+        <v>1.1496</v>
       </c>
       <c r="K11" t="n">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="L11" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9133</v>
+        <v>2.7646</v>
       </c>
       <c r="N11" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5673</v>
+        <v>2.5181</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4822</v>
+        <v>1.4538</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5789</v>
+        <v>0.4988</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5673</v>
+        <v>2.5181</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3419</v>
+        <v>2.1299</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2254</v>
+        <v>0.3882</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3419</v>
+        <v>2.1299</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3419</v>
+        <v>2.1299</v>
       </c>
       <c r="J12" t="n">
-        <v>2.2254</v>
+        <v>0.3882</v>
       </c>
       <c r="K12" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="L12" t="n">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5673</v>
+        <v>2.5181</v>
       </c>
       <c r="N12" t="n">
-        <v>227</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4774</v>
+        <v>2.4296</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4303</v>
+        <v>1.4027</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5431</v>
+        <v>0.4588</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4774</v>
+        <v>2.4296</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1219</v>
+        <v>0.3077</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3555</v>
+        <v>2.1219</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1219</v>
+        <v>0.3077</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1219</v>
+        <v>0.3077</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3555</v>
+        <v>2.1219</v>
       </c>
       <c r="K13" t="n">
         <v>39</v>
@@ -1035,7 +1035,7 @@
         <v>117</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4774</v>
+        <v>2.4296</v>
       </c>
       <c r="N13" t="n">
         <v>156</v>
@@ -1044,219 +1044,219 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1478</v>
+        <v>2.4064</v>
       </c>
       <c r="C14" t="n">
-        <v>1.24</v>
+        <v>1.3893</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4118</v>
+        <v>0.4484</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1478</v>
+        <v>2.4064</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1478</v>
+        <v>0.4205</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.9859</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1478</v>
+        <v>0.4205</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1478</v>
+        <v>0.4205</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.9859</v>
       </c>
       <c r="K14" t="n">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1478</v>
+        <v>2.4064</v>
       </c>
       <c r="N14" t="n">
-        <v>111</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0799</v>
+        <v>2.1541</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2008</v>
+        <v>1.2436</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3847</v>
+        <v>0.3345</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0799</v>
+        <v>2.1541</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7447</v>
+        <v>2.1541</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3352</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7447</v>
+        <v>2.1541</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7447</v>
+        <v>2.1541</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3352</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="L15" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.0799</v>
+        <v>2.1541</v>
       </c>
       <c r="N15" t="n">
-        <v>179</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0244</v>
+        <v>2.0779</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1688</v>
+        <v>1.1997</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3626</v>
+        <v>0.3001</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0244</v>
+        <v>2.0779</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0244</v>
+        <v>3.0779</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0244</v>
+        <v>3.3988</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0244</v>
+        <v>3.3988</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K16" t="n">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0244</v>
+        <v>2.3988</v>
       </c>
       <c r="N16" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8706</v>
+        <v>1.9566</v>
       </c>
       <c r="C17" t="n">
-        <v>1.08</v>
+        <v>1.1296</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3013</v>
+        <v>0.2453</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8706</v>
+        <v>1.9566</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4546</v>
+        <v>1.9566</v>
       </c>
       <c r="G17" t="n">
-        <v>1.416</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4546</v>
+        <v>1.9566</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4546</v>
+        <v>1.9566</v>
       </c>
       <c r="J17" t="n">
-        <v>1.416</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="L17" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8706</v>
+        <v>1.9566</v>
       </c>
       <c r="N17" t="n">
-        <v>214</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8334</v>
+        <v>1.9207</v>
       </c>
       <c r="C18" t="n">
-        <v>1.0585</v>
+        <v>1.1089</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2865</v>
+        <v>0.2291</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8334</v>
+        <v>1.9207</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7813</v>
+        <v>1.5942</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0521</v>
+        <v>0.3265</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7813</v>
+        <v>1.5942</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7813</v>
+        <v>1.5942</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0521</v>
+        <v>0.3265</v>
       </c>
       <c r="K18" t="n">
         <v>33</v>
@@ -1265,7 +1265,7 @@
         <v>69</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8334</v>
+        <v>1.9207</v>
       </c>
       <c r="N18" t="n">
         <v>102</v>
@@ -1274,173 +1274,173 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.806</v>
+        <v>1.8944</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0427</v>
+        <v>1.0937</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2756</v>
+        <v>0.2172</v>
       </c>
       <c r="E19" t="n">
-        <v>1.806</v>
+        <v>1.8944</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6244</v>
+        <v>2.0034</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1816</v>
+        <v>-0.109</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6244</v>
+        <v>2.0034</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6244</v>
+        <v>2.0034</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1816</v>
+        <v>-0.109</v>
       </c>
       <c r="K19" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="L19" t="n">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="M19" t="n">
-        <v>1.806</v>
+        <v>1.8944</v>
       </c>
       <c r="N19" t="n">
-        <v>179</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6236</v>
+        <v>1.8632</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9374</v>
+        <v>1.0757</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2029</v>
+        <v>0.2031</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6236</v>
+        <v>1.8632</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4034</v>
+        <v>2.8572</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2202</v>
+        <v>-0.994</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4034</v>
+        <v>2.9141</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4034</v>
+        <v>2.9141</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2202</v>
+        <v>-0.994</v>
       </c>
       <c r="K20" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L20" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6236</v>
+        <v>1.9201</v>
       </c>
       <c r="N20" t="n">
-        <v>102</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.587</v>
+        <v>1.8309</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9162</v>
+        <v>1.057</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1884</v>
+        <v>0.1885</v>
       </c>
       <c r="E21" t="n">
-        <v>1.587</v>
+        <v>1.8309</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7282</v>
+        <v>0.6885</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1412</v>
+        <v>1.1424</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7282</v>
+        <v>0.6885</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7282</v>
+        <v>0.6885</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1412</v>
+        <v>1.1424</v>
       </c>
       <c r="K21" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="L21" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="M21" t="n">
-        <v>1.587</v>
+        <v>1.8309</v>
       </c>
       <c r="N21" t="n">
-        <v>104</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4194</v>
+        <v>1.7801</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8195</v>
+        <v>1.0277</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1216</v>
+        <v>0.1656</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4194</v>
+        <v>1.7801</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6194</v>
+        <v>0.7753</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8</v>
+        <v>1.0048</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6194</v>
+        <v>0.7753</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6194</v>
+        <v>0.7753</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>1.0048</v>
       </c>
       <c r="K22" t="n">
         <v>33</v>
@@ -1449,7 +1449,7 @@
         <v>69</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4194</v>
+        <v>1.7801</v>
       </c>
       <c r="N22" t="n">
         <v>102</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.31</v>
+        <v>1.6796</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7563</v>
+        <v>0.9697</v>
       </c>
       <c r="D23" t="n">
-        <v>0.078</v>
+        <v>0.1202</v>
       </c>
       <c r="E23" t="n">
-        <v>1.31</v>
+        <v>1.6796</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4483</v>
+        <v>1.7198</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1383</v>
+        <v>-0.0402</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4483</v>
+        <v>1.7198</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4605</v>
+        <v>1.7905</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1383</v>
+        <v>-0.0402</v>
       </c>
       <c r="K23" t="n">
         <v>116</v>
@@ -1495,7 +1495,7 @@
         <v>64</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3222</v>
+        <v>1.7503</v>
       </c>
       <c r="N23" t="n">
         <v>180</v>
@@ -1504,541 +1504,541 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0SAMAS</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.2142</v>
+        <v>1.6635</v>
       </c>
       <c r="C24" t="n">
-        <v>0.701</v>
+        <v>0.9604</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0398</v>
+        <v>0.113</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2142</v>
+        <v>1.6635</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2142</v>
+        <v>0.2207</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1.4428</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2142</v>
+        <v>0.2207</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2142</v>
+        <v>0.2207</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1.4428</v>
       </c>
       <c r="K24" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="M24" t="n">
-        <v>1.2142</v>
+        <v>1.6635</v>
       </c>
       <c r="N24" t="n">
-        <v>21</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.1953</v>
+        <v>1.5819</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6901</v>
+        <v>0.9133</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0323</v>
+        <v>0.0761</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1953</v>
+        <v>1.5819</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9677</v>
+        <v>0.8315</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2276</v>
+        <v>0.7504</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9677</v>
+        <v>0.8315</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9677</v>
+        <v>0.8315</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2276</v>
+        <v>0.7504</v>
       </c>
       <c r="K25" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="L25" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1953</v>
+        <v>1.5819</v>
       </c>
       <c r="N25" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kwezz</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.1885</v>
+        <v>1.3819</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6862</v>
+        <v>0.7978</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0296</v>
+        <v>-0.0142</v>
       </c>
       <c r="E26" t="n">
-        <v>1.1885</v>
+        <v>1.3819</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1885</v>
+        <v>2.2939</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.912</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1885</v>
+        <v>2.2939</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1885</v>
+        <v>2.2939</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.912</v>
       </c>
       <c r="K26" t="n">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M26" t="n">
-        <v>1.1885</v>
+        <v>1.3819</v>
       </c>
       <c r="N26" t="n">
-        <v>117</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>0SAMAS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1682</v>
+        <v>1.36</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6744</v>
+        <v>0.7852</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0215</v>
+        <v>-0.024</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1682</v>
+        <v>1.36</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4761</v>
+        <v>1.36</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.3079</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4761</v>
+        <v>1.36</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4761</v>
+        <v>1.36</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3079</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="L27" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1682</v>
+        <v>1.36</v>
       </c>
       <c r="N27" t="n">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1273</v>
+        <v>1.3471</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6508</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0052</v>
+        <v>-0.0299</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1273</v>
+        <v>1.3471</v>
       </c>
       <c r="F28" t="n">
-        <v>1.1273</v>
+        <v>0.9946</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.3525</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1273</v>
+        <v>0.9946</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1273</v>
+        <v>0.9946</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.3525</v>
       </c>
       <c r="K28" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1273</v>
+        <v>1.3471</v>
       </c>
       <c r="N28" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.0498</v>
+        <v>1.2928</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6061</v>
+        <v>0.7464</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0257</v>
+        <v>-0.0544</v>
       </c>
       <c r="E29" t="n">
-        <v>1.0498</v>
+        <v>1.2928</v>
       </c>
       <c r="F29" t="n">
-        <v>1.0498</v>
+        <v>1.2928</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.0498</v>
+        <v>1.2928</v>
       </c>
       <c r="I29" t="n">
-        <v>1.0498</v>
+        <v>1.2928</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.0498</v>
+        <v>1.2928</v>
       </c>
       <c r="N29" t="n">
-        <v>111</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7924</v>
+        <v>1.263</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4575</v>
+        <v>0.7292</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1282</v>
+        <v>-0.0678</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7924</v>
+        <v>1.263</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7924</v>
+        <v>1.4622</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.1992</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7924</v>
+        <v>1.4622</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7924</v>
+        <v>1.4622</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.1992</v>
       </c>
       <c r="K30" t="n">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7924</v>
+        <v>1.263</v>
       </c>
       <c r="N30" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.79</v>
+        <v>1.2275</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4561</v>
+        <v>0.7087</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1292</v>
+        <v>-0.0839</v>
       </c>
       <c r="E31" t="n">
-        <v>0.79</v>
+        <v>1.2275</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2715</v>
+        <v>1.2275</v>
       </c>
       <c r="G31" t="n">
-        <v>1.0615</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2715</v>
+        <v>1.2275</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2715</v>
+        <v>1.2275</v>
       </c>
       <c r="J31" t="n">
-        <v>1.0615</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="L31" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.79</v>
+        <v>1.2275</v>
       </c>
       <c r="N31" t="n">
-        <v>179</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>kwezz</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7655</v>
+        <v>1.1658</v>
       </c>
       <c r="C32" t="n">
-        <v>0.442</v>
+        <v>0.6731</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1389</v>
+        <v>-0.1117</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7655</v>
+        <v>1.1658</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2497</v>
+        <v>1.1658</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5158</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2497</v>
+        <v>1.1658</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2497</v>
+        <v>1.1658</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5158</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>39</v>
+        <v>117</v>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.1658</v>
+      </c>
+      <c r="N32" t="n">
         <v>117</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.7655000000000001</v>
-      </c>
-      <c r="N32" t="n">
-        <v>156</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7648</v>
+        <v>1.0783</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4415</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1392</v>
+        <v>-0.1512</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7648</v>
+        <v>1.0783</v>
       </c>
       <c r="F33" t="n">
-        <v>1.7648</v>
+        <v>1.0783</v>
       </c>
       <c r="G33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.7648</v>
+        <v>1.0783</v>
       </c>
       <c r="I33" t="n">
-        <v>1.7648</v>
+        <v>1.0783</v>
       </c>
       <c r="J33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>33</v>
+        <v>117</v>
       </c>
       <c r="L33" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7647999999999999</v>
+        <v>1.0783</v>
       </c>
       <c r="N33" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.748</v>
+        <v>1.0024</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4318</v>
+        <v>0.5787</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1459</v>
+        <v>-0.1855</v>
       </c>
       <c r="E34" t="n">
-        <v>0.748</v>
+        <v>1.0024</v>
       </c>
       <c r="F34" t="n">
-        <v>1.748</v>
+        <v>0.0264</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>0.976</v>
       </c>
       <c r="H34" t="n">
-        <v>1.748</v>
+        <v>0.0264</v>
       </c>
       <c r="I34" t="n">
-        <v>1.748</v>
+        <v>0.0264</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>0.976</v>
       </c>
       <c r="K34" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="L34" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="M34" t="n">
-        <v>0.748</v>
+        <v>1.0024</v>
       </c>
       <c r="N34" t="n">
-        <v>102</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.9166</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3483</v>
+        <v>0.5292</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2036</v>
+        <v>-0.2242</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.9166</v>
       </c>
       <c r="F35" t="n">
-        <v>1.7636</v>
+        <v>0.4091</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.1603</v>
+        <v>0.5075</v>
       </c>
       <c r="H35" t="n">
-        <v>1.7636</v>
+        <v>0.4091</v>
       </c>
       <c r="I35" t="n">
-        <v>1.7636</v>
+        <v>0.4091</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.1603</v>
+        <v>0.5075</v>
       </c>
       <c r="K35" t="n">
         <v>39</v>
@@ -2047,7 +2047,7 @@
         <v>117</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.9166</v>
       </c>
       <c r="N35" t="n">
         <v>156</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.8857</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3355</v>
+        <v>0.5113</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2124</v>
+        <v>-0.2382</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.8857</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.8857</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.8857</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.8857</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.8857</v>
       </c>
       <c r="N36" t="n">
         <v>93</v>
@@ -2102,35 +2102,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4763</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>0.275</v>
+        <v>0.4426</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2542</v>
+        <v>-0.2919</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4763</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4347</v>
+        <v>1.1999</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0416</v>
+        <v>-0.4333</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4347</v>
+        <v>1.1999</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4347</v>
+        <v>1.1999</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0416</v>
+        <v>-0.4333</v>
       </c>
       <c r="K37" t="n">
         <v>42</v>
@@ -2139,7 +2139,7 @@
         <v>80</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4762999999999999</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="N37" t="n">
         <v>122</v>
@@ -2148,47 +2148,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4402</v>
+        <v>0.6808</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2541</v>
+        <v>0.3931</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2685</v>
+        <v>-0.3307</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4402</v>
+        <v>0.6808</v>
       </c>
       <c r="F38" t="n">
-        <v>1.154</v>
+        <v>1.2863</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.7138</v>
+        <v>-0.6055</v>
       </c>
       <c r="H38" t="n">
-        <v>1.154</v>
+        <v>1.2863</v>
       </c>
       <c r="I38" t="n">
-        <v>1.154</v>
+        <v>1.2863</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7138</v>
+        <v>-0.6055</v>
       </c>
       <c r="K38" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L38" t="n">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4401999999999999</v>
+        <v>0.6808</v>
       </c>
       <c r="N38" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.3539</v>
+        <v>0.5259</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2043</v>
+        <v>0.3036</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3029</v>
+        <v>-0.4006</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3539</v>
+        <v>0.5259</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3539</v>
+        <v>0.5259</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3539</v>
+        <v>0.5259</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3539</v>
+        <v>0.5259</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3539</v>
+        <v>0.5259</v>
       </c>
       <c r="N39" t="n">
         <v>71</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3128</v>
+        <v>0.5208</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1806</v>
+        <v>0.3007</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3193</v>
+        <v>-0.4029</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3128</v>
+        <v>0.5208</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3128</v>
+        <v>0.5208</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3128</v>
+        <v>0.5208</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3128</v>
+        <v>0.5208</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3128</v>
+        <v>0.5208</v>
       </c>
       <c r="N40" t="n">
         <v>71</v>
@@ -2286,35 +2286,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3108</v>
+        <v>0.517</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1794</v>
+        <v>0.2985</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3201</v>
+        <v>-0.4046</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3108</v>
+        <v>0.517</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3108</v>
+        <v>0.4957</v>
       </c>
       <c r="G41" t="n">
-        <v>-1</v>
+        <v>0.0213</v>
       </c>
       <c r="H41" t="n">
-        <v>1.3108</v>
+        <v>0.4957</v>
       </c>
       <c r="I41" t="n">
-        <v>1.3108</v>
+        <v>0.4957</v>
       </c>
       <c r="J41" t="n">
-        <v>-1</v>
+        <v>0.0213</v>
       </c>
       <c r="K41" t="n">
         <v>42</v>
@@ -2323,7 +2323,7 @@
         <v>80</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3108</v>
+        <v>0.517</v>
       </c>
       <c r="N41" t="n">
         <v>122</v>
@@ -2332,630 +2332,630 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2899</v>
+        <v>0.4848</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1674</v>
+        <v>0.2799</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3284</v>
+        <v>-0.4192</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2899</v>
+        <v>0.4848</v>
       </c>
       <c r="F42" t="n">
-        <v>1.1828</v>
+        <v>0.4848</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.8929</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.1828</v>
+        <v>0.4848</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1828</v>
+        <v>0.4848</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.8929</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="L42" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2899</v>
+        <v>0.4848</v>
       </c>
       <c r="N42" t="n">
-        <v>156</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2891</v>
+        <v>0.4756</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1669</v>
+        <v>0.2746</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3287</v>
+        <v>-0.4233</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2891</v>
+        <v>0.4756</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2891</v>
+        <v>0.1166</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.359</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2891</v>
+        <v>0.1166</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2891</v>
+        <v>0.1214</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.359</v>
       </c>
       <c r="K43" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2891</v>
+        <v>0.4804</v>
       </c>
       <c r="N43" t="n">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>m1N1</t>
+          <t>Cabbi</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0588</v>
+        <v>0.3593</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0339</v>
+        <v>0.2074</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4205</v>
+        <v>-0.4758</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0588</v>
+        <v>0.3593</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0588</v>
+        <v>0.3593</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0588</v>
+        <v>0.3593</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0588</v>
+        <v>0.3593</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0588</v>
+        <v>0.3593</v>
       </c>
       <c r="N44" t="n">
-        <v>21</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0035</v>
+        <v>0.3173</v>
       </c>
       <c r="C45" t="n">
-        <v>0.002</v>
+        <v>0.1832</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4425</v>
+        <v>-0.4948</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0035</v>
+        <v>0.3173</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9324</v>
+        <v>1.3168</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9324</v>
+        <v>1.3168</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9324</v>
+        <v>1.3168</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="L45" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="M45" t="n">
-        <v>0.003500000000000059</v>
+        <v>0.3172999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.005</v>
+        <v>0.2607</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0029</v>
+        <v>0.1505</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4459</v>
+        <v>-0.5203</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.005</v>
+        <v>0.2607</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.4567</v>
+        <v>0.2607</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4517</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.4567</v>
+        <v>0.2607</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4567</v>
+        <v>0.2607</v>
       </c>
       <c r="J46" t="n">
-        <v>0.4517</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="L46" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.005000000000000004</v>
+        <v>0.2607</v>
       </c>
       <c r="N46" t="n">
-        <v>227</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0101</v>
+        <v>0.1591</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0058</v>
+        <v>0.0919</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4479</v>
+        <v>-0.5662</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0101</v>
+        <v>0.1591</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0101</v>
+        <v>0.1591</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0101</v>
+        <v>0.1591</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0101</v>
+        <v>0.1591</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0101</v>
+        <v>0.1591</v>
       </c>
       <c r="N47" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0327</v>
+        <v>0.1359</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0189</v>
+        <v>0.0785</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4569</v>
+        <v>-0.5767</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0327</v>
+        <v>0.1359</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.3366</v>
+        <v>0.7343</v>
       </c>
       <c r="G48" t="n">
-        <v>0.3039</v>
+        <v>-0.5984</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.3366</v>
+        <v>0.7343</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.3394</v>
+        <v>0.7343</v>
       </c>
       <c r="J48" t="n">
-        <v>0.3039</v>
+        <v>-0.5984</v>
       </c>
       <c r="K48" t="n">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="L48" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.03549999999999998</v>
+        <v>0.1358999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>180</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cabbi</t>
+          <t>m1N1</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0742</v>
+        <v>0.1023</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0428</v>
+        <v>0.0591</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4735</v>
+        <v>-0.5918</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0742</v>
+        <v>0.1023</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.0742</v>
+        <v>0.1023</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.0742</v>
+        <v>0.1023</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0742</v>
+        <v>0.1023</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0742</v>
+        <v>0.1023</v>
       </c>
       <c r="N49" t="n">
-        <v>117</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>dennyslaw</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1659</v>
+        <v>0.0345</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0958</v>
+        <v>0.0199</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.51</v>
+        <v>-0.6224</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1659</v>
+        <v>0.0345</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1659</v>
+        <v>0.0345</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1659</v>
+        <v>0.0345</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1659</v>
+        <v>0.0345</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1659</v>
+        <v>0.0345</v>
       </c>
       <c r="N50" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1774</v>
+        <v>0.0232</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1024</v>
+        <v>0.0134</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1774</v>
+        <v>0.0232</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1774</v>
+        <v>0.0232</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1774</v>
+        <v>0.0232</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1774</v>
+        <v>0.0232</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1774</v>
+        <v>0.0232</v>
       </c>
       <c r="N51" t="n">
-        <v>69</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2568</v>
+        <v>-0.0548</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1483</v>
+        <v>-0.0316</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5462</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2568</v>
+        <v>-0.0548</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.2568</v>
+        <v>0.9882</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-1.043</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2568</v>
+        <v>0.9882</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2568</v>
+        <v>0.9882</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-1.043</v>
       </c>
       <c r="K52" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.2568</v>
+        <v>-0.05479999999999996</v>
       </c>
       <c r="N52" t="n">
-        <v>71</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.2839</v>
+        <v>-0.0626</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1639</v>
+        <v>-0.0361</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.6663</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.2839</v>
+        <v>-0.0626</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.7194</v>
+        <v>-0.0626</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4355</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.7194</v>
+        <v>-0.0626</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.7194</v>
+        <v>-0.0626</v>
       </c>
       <c r="J53" t="n">
-        <v>0.4355</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="L53" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.2839</v>
+        <v>-0.0626</v>
       </c>
       <c r="N53" t="n">
-        <v>214</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>dennyslaw</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3084</v>
+        <v>-0.0859</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1781</v>
+        <v>-0.0496</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5668</v>
+        <v>-0.6768</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.3084</v>
+        <v>-0.0859</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3084</v>
+        <v>-0.0859</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.3084</v>
+        <v>-0.0859</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3084</v>
+        <v>-0.0859</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.3084</v>
+        <v>-0.0859</v>
       </c>
       <c r="N54" t="n">
-        <v>93</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.3166</v>
+        <v>-0.126</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1828</v>
+        <v>-0.0727</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.57</v>
+        <v>-0.6949</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3166</v>
+        <v>-0.126</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3166</v>
+        <v>-0.126</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3166</v>
+        <v>-0.126</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3166</v>
+        <v>-0.126</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.3166</v>
+        <v>-0.126</v>
       </c>
       <c r="N55" t="n">
         <v>93</v>
@@ -2976,599 +2976,599 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>IceBerg</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.3167</v>
+        <v>-0.173</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1828</v>
+        <v>-0.0999</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.7161</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3167</v>
+        <v>-0.173</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.3167</v>
+        <v>-0.173</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.3167</v>
+        <v>-0.173</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3167</v>
+        <v>-0.173</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.3167</v>
+        <v>-0.173</v>
       </c>
       <c r="N56" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IceBerg</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.3413</v>
+        <v>-0.1443</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6794</v>
+        <v>-0.7509</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.5911999999999999</v>
+        <v>0.3254</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-0.5754</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.5911999999999999</v>
+        <v>0.3254</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.5911999999999999</v>
+        <v>0.3254</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>-0.5754</v>
       </c>
       <c r="K57" t="n">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="N57" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.5928</v>
+        <v>-0.2875</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.3422</v>
+        <v>-0.166</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6801</v>
+        <v>-0.7678</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5928</v>
+        <v>-0.2875</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.5928</v>
+        <v>-0.6201</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>0.3326</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.5928</v>
+        <v>-0.6201</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.5928</v>
+        <v>-0.6201</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>0.3326</v>
       </c>
       <c r="K58" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.5928</v>
+        <v>-0.2875</v>
       </c>
       <c r="N58" t="n">
-        <v>48</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.3084</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3501</v>
+        <v>-0.1781</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6855</v>
+        <v>-0.7772</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.3084</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.3084</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.3084</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.3084</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.3084</v>
       </c>
       <c r="N59" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.6201</v>
+        <v>-0.3447</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.358</v>
+        <v>-0.199</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.7936</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.6201</v>
+        <v>-0.3447</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7229</v>
+        <v>-0.3447</v>
       </c>
       <c r="G60" t="n">
-        <v>-1.343</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.7229</v>
+        <v>-0.3447</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7229</v>
+        <v>-0.3447</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.343</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="L60" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.6201</v>
+        <v>-0.3447</v>
       </c>
       <c r="N60" t="n">
-        <v>179</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.3988</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.36</v>
+        <v>-0.2302</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6923</v>
+        <v>-0.8181</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.3988</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.3988</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.3988</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.3988</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.3988</v>
       </c>
       <c r="N61" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>aliStair</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.7456</v>
+        <v>-0.4802</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.4305</v>
+        <v>-0.2772</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.741</v>
+        <v>-0.8548</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.7456</v>
+        <v>-0.4802</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.7456</v>
+        <v>-0.4802</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.7456</v>
+        <v>-0.4802</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.7456</v>
+        <v>-0.4802</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.7456</v>
+        <v>-0.4802</v>
       </c>
       <c r="N62" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>aliStair</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.7509</v>
+        <v>-0.4968</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4335</v>
+        <v>-0.2868</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7431</v>
+        <v>-0.8623</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.7509</v>
+        <v>-0.4968</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.7509</v>
+        <v>-0.4968</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.7509</v>
+        <v>-0.4968</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.7509</v>
+        <v>-0.4968</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.7509</v>
+        <v>-0.4968</v>
       </c>
       <c r="N63" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.8004</v>
+        <v>-0.5029</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4621</v>
+        <v>-0.2903</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7628</v>
+        <v>-0.865</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.8004</v>
+        <v>-0.5029</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1469</v>
+        <v>-0.349</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.9473</v>
+        <v>-0.1539</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1469</v>
+        <v>-0.349</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1469</v>
+        <v>-0.349</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.9473</v>
+        <v>-0.1539</v>
       </c>
       <c r="K64" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L64" t="n">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.8004</v>
+        <v>-0.5029</v>
       </c>
       <c r="N64" t="n">
-        <v>122</v>
+        <v>227</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8519</v>
+        <v>-0.5098</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4918</v>
+        <v>-0.2943</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7833</v>
+        <v>-0.8682</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8519</v>
+        <v>-0.5098</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8519</v>
+        <v>-0.5098</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8519</v>
+        <v>-0.5098</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8519</v>
+        <v>-0.5098</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.8519</v>
+        <v>-0.5098</v>
       </c>
       <c r="N65" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8767</v>
+        <v>-0.6385</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5062</v>
+        <v>-0.3686</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7932</v>
+        <v>-0.9263</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8767</v>
+        <v>-0.6385</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.8767</v>
+        <v>-0.6385</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.8767</v>
+        <v>-0.6385</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8767</v>
+        <v>-0.6385</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.8767</v>
+        <v>-0.6385</v>
       </c>
       <c r="N66" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.898</v>
+        <v>-0.7252</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5184</v>
+        <v>-0.4187</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8017</v>
+        <v>-0.9654</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.898</v>
+        <v>-0.7252</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.898</v>
+        <v>-0.7252</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.898</v>
+        <v>-0.7252</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.898</v>
+        <v>-0.7252</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.898</v>
+        <v>-0.7252</v>
       </c>
       <c r="N67" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.9895</v>
+        <v>-0.7655</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5713</v>
+        <v>-0.442</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8381</v>
+        <v>-0.9836</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.9895</v>
+        <v>-0.7655</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.9895</v>
+        <v>-0.7655</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.9895</v>
+        <v>-0.7655</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.9895</v>
+        <v>-0.7655</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.9895</v>
+        <v>-0.7655</v>
       </c>
       <c r="N68" t="n">
-        <v>48</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69">
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1521</v>
+        <v>-0.8487</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.6652</v>
+        <v>-0.49</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9029</v>
+        <v>-1.0212</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.1521</v>
+        <v>-0.8487</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.1521</v>
+        <v>-0.8487</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.1521</v>
+        <v>-0.8487</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1521</v>
+        <v>-0.8487</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.1521</v>
+        <v>-0.8487</v>
       </c>
       <c r="N69" t="n">
         <v>117</v>
@@ -3620,32 +3620,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.2351</v>
+        <v>-0.851</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.7131</v>
+        <v>-0.4913</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-1.0222</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.2351</v>
+        <v>-0.851</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.2351</v>
+        <v>-0.851</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.2351</v>
+        <v>-0.851</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2351</v>
+        <v>-0.851</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.2351</v>
+        <v>-0.851</v>
       </c>
       <c r="N70" t="n">
         <v>69</v>
@@ -3666,47 +3666,47 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.2374</v>
+        <v>-0.8851</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.7144</v>
+        <v>-0.511</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9369</v>
+        <v>-1.0376</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.2374</v>
+        <v>-0.8851</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.2374</v>
+        <v>-0.8851</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.2374</v>
+        <v>-0.8851</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2374</v>
+        <v>-0.8851</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.2374</v>
+        <v>-0.8851</v>
       </c>
       <c r="N71" t="n">
-        <v>111</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72">
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.5052</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.869</v>
+        <v>-0.5706</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0436</v>
+        <v>-1.0842</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.5052</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.5052</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.5052</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.5052</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.5052</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="N72" t="n">
         <v>71</v>
@@ -3758,185 +3758,185 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.6828</v>
+        <v>-1.1297</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.9715</v>
+        <v>-0.6522</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1143</v>
+        <v>-1.148</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.6828</v>
+        <v>-1.1297</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.6828</v>
+        <v>-0.6711</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>-0.4586</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.6828</v>
+        <v>-0.6711</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.6828</v>
+        <v>-0.6987</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>-0.4586</v>
       </c>
       <c r="K73" t="n">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.6828</v>
+        <v>-1.1573</v>
       </c>
       <c r="N73" t="n">
-        <v>48</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.8206</v>
+        <v>-1.2939</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.0511</v>
+        <v>-0.747</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1692</v>
+        <v>-1.2221</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.8206</v>
+        <v>-1.2939</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.0569</v>
+        <v>-1.2939</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.7637</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.0569</v>
+        <v>-1.2939</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.0658</v>
+        <v>-1.2939</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.7637</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="L74" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.8295</v>
+        <v>-1.2939</v>
       </c>
       <c r="N74" t="n">
-        <v>180</v>
+        <v>48</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-2.1033</v>
+        <v>-2.1756</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.2143</v>
+        <v>-1.2561</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2819</v>
+        <v>-1.6202</v>
       </c>
       <c r="E75" t="n">
-        <v>-2.1033</v>
+        <v>-2.1756</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.6497</v>
+        <v>-2.3353</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.4536</v>
+        <v>0.1597</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.6497</v>
+        <v>-2.3353</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.6497</v>
+        <v>-2.3353</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.4536</v>
+        <v>0.1597</v>
       </c>
       <c r="K75" t="n">
         <v>53</v>
       </c>
       <c r="L75" t="n">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="M75" t="n">
-        <v>-2.1033</v>
+        <v>-2.1756</v>
       </c>
       <c r="N75" t="n">
-        <v>227</v>
+        <v>104</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-2.3379</v>
+        <v>-2.2588</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.3498</v>
+        <v>-1.3041</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.3753</v>
+        <v>-1.6577</v>
       </c>
       <c r="E76" t="n">
-        <v>-2.3379</v>
+        <v>-2.2588</v>
       </c>
       <c r="F76" t="n">
-        <v>-2.3333</v>
+        <v>-1.5905</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.0046</v>
+        <v>-0.6683</v>
       </c>
       <c r="H76" t="n">
-        <v>-2.3333</v>
+        <v>-1.5905</v>
       </c>
       <c r="I76" t="n">
-        <v>-2.3333</v>
+        <v>-1.5905</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.0046</v>
+        <v>-0.6683</v>
       </c>
       <c r="K76" t="n">
         <v>53</v>
       </c>
       <c r="L76" t="n">
-        <v>51</v>
+        <v>174</v>
       </c>
       <c r="M76" t="n">
-        <v>-2.3379</v>
+        <v>-2.2588</v>
       </c>
       <c r="N76" t="n">
-        <v>104</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -4039,10 +4039,10 @@
         <v>1.33</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5258</v>
+        <v>0.4513</v>
       </c>
       <c r="J2" t="n">
-        <v>15.774</v>
+        <v>13.539</v>
       </c>
     </row>
     <row r="3">
@@ -4079,10 +4079,10 @@
         <v>1.29</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4737</v>
+        <v>0.4036</v>
       </c>
       <c r="J3" t="n">
-        <v>14.211</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="4">
@@ -4119,10 +4119,10 @@
         <v>1.08</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1355</v>
+        <v>0.1343</v>
       </c>
       <c r="J4" t="n">
-        <v>4.065</v>
+        <v>4.029</v>
       </c>
     </row>
     <row r="5">
@@ -4159,10 +4159,10 @@
         <v>1.07</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1162</v>
+        <v>0.1196</v>
       </c>
       <c r="J5" t="n">
-        <v>3.486</v>
+        <v>3.588</v>
       </c>
     </row>
     <row r="6">
@@ -4199,10 +4199,10 @@
         <v>0.74</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4851</v>
+        <v>-0.3089</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.553</v>
+        <v>-9.266999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -4239,10 +4239,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1072</v>
+        <v>0.0751</v>
       </c>
       <c r="J7" t="n">
-        <v>3.216</v>
+        <v>2.253</v>
       </c>
     </row>
     <row r="8">
@@ -4279,10 +4279,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0551</v>
       </c>
       <c r="J8" t="n">
-        <v>2.52</v>
+        <v>1.653</v>
       </c>
     </row>
     <row r="9">
@@ -4319,10 +4319,10 @@
         <v>0.99</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0142</v>
+        <v>-0.0184</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.426</v>
+        <v>-0.552</v>
       </c>
     </row>
     <row r="10">
@@ -4359,10 +4359,10 @@
         <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0973</v>
+        <v>-0.0605</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.919</v>
+        <v>-1.815</v>
       </c>
     </row>
     <row r="11">
@@ -4399,10 +4399,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3156</v>
+        <v>-0.1946</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.468</v>
+        <v>-5.838</v>
       </c>
     </row>
     <row r="12">
@@ -4439,10 +4439,10 @@
         <v>1.36</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6555</v>
+        <v>0.806</v>
       </c>
       <c r="J12" t="n">
-        <v>12.4545</v>
+        <v>15.314</v>
       </c>
     </row>
     <row r="13">
@@ -4479,10 +4479,10 @@
         <v>0.95</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.046</v>
+        <v>-0.0578</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.874</v>
+        <v>-1.0982</v>
       </c>
     </row>
     <row r="14">
@@ -4519,10 +4519,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.497</v>
+        <v>-0.3257</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.443</v>
+        <v>-6.1883</v>
       </c>
     </row>
     <row r="15">
@@ -4559,10 +4559,10 @@
         <v>0.61</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.401</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.4817</v>
+        <v>-7.619</v>
       </c>
     </row>
     <row r="16">
@@ -4599,10 +4599,10 @@
         <v>0.59</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6301</v>
+        <v>-0.4196</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.9719</v>
+        <v>-7.9724</v>
       </c>
     </row>
     <row r="17">
@@ -4639,10 +4639,10 @@
         <v>1.71</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5652</v>
+        <v>1.3711</v>
       </c>
       <c r="J17" t="n">
-        <v>29.7388</v>
+        <v>26.0509</v>
       </c>
     </row>
     <row r="18">
@@ -4679,10 +4679,10 @@
         <v>1.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.36</v>
+        <v>1.2386</v>
       </c>
       <c r="J18" t="n">
-        <v>25.84</v>
+        <v>23.5334</v>
       </c>
     </row>
     <row r="19">
@@ -4719,10 +4719,10 @@
         <v>1.49</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1425</v>
+        <v>1.1036</v>
       </c>
       <c r="J19" t="n">
-        <v>21.7075</v>
+        <v>20.9684</v>
       </c>
     </row>
     <row r="20">
@@ -4759,10 +4759,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3313</v>
+        <v>-0.2461</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.2947</v>
+        <v>-4.6759</v>
       </c>
     </row>
     <row r="21">
@@ -4799,10 +4799,10 @@
         <v>0.85</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6367</v>
+        <v>-0.5709</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.0973</v>
+        <v>-10.8471</v>
       </c>
     </row>
     <row r="22">
@@ -4839,10 +4839,10 @@
         <v>1.19</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4322</v>
+        <v>0.4924</v>
       </c>
       <c r="J22" t="n">
-        <v>8.2118</v>
+        <v>9.355600000000001</v>
       </c>
     </row>
     <row r="23">
@@ -4879,10 +4879,10 @@
         <v>1.08</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2594</v>
+        <v>0.2627</v>
       </c>
       <c r="J23" t="n">
-        <v>4.9286</v>
+        <v>4.9913</v>
       </c>
     </row>
     <row r="24">
@@ -4919,10 +4919,10 @@
         <v>0.7</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4799</v>
+        <v>-0.3148</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.1181</v>
+        <v>-5.9812</v>
       </c>
     </row>
     <row r="25">
@@ -4959,10 +4959,10 @@
         <v>0.66</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5354</v>
+        <v>-0.3527</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.1726</v>
+        <v>-6.7013</v>
       </c>
     </row>
     <row r="26">
@@ -4999,10 +4999,10 @@
         <v>0.52</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7156</v>
+        <v>-0.4829</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.5964</v>
+        <v>-9.1751</v>
       </c>
     </row>
     <row r="27">
@@ -5039,10 +5039,10 @@
         <v>1.73</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6059</v>
+        <v>1.3974</v>
       </c>
       <c r="J27" t="n">
-        <v>30.5121</v>
+        <v>26.5506</v>
       </c>
     </row>
     <row r="28">
@@ -5079,10 +5079,10 @@
         <v>1.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1677</v>
+        <v>1.1177</v>
       </c>
       <c r="J28" t="n">
-        <v>22.1863</v>
+        <v>21.2363</v>
       </c>
     </row>
     <row r="29">
@@ -5119,10 +5119,10 @@
         <v>1.32</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7645</v>
+        <v>0.8144</v>
       </c>
       <c r="J29" t="n">
-        <v>14.5255</v>
+        <v>15.4736</v>
       </c>
     </row>
     <row r="30">
@@ -5159,10 +5159,10 @@
         <v>1.17</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3753</v>
+        <v>0.4639</v>
       </c>
       <c r="J30" t="n">
-        <v>7.1307</v>
+        <v>8.8141</v>
       </c>
     </row>
     <row r="31">
@@ -5199,10 +5199,10 @@
         <v>0.84</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6592</v>
+        <v>-0.5956</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.5248</v>
+        <v>-11.3164</v>
       </c>
     </row>
     <row r="32">
@@ -5239,10 +5239,10 @@
         <v>2.21</v>
       </c>
       <c r="I32" t="n">
-        <v>1.322</v>
+        <v>0.8728</v>
       </c>
       <c r="J32" t="n">
-        <v>18.508</v>
+        <v>12.2192</v>
       </c>
     </row>
     <row r="33">
@@ -5279,10 +5279,10 @@
         <v>1.73</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8573</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>12.0022</v>
+        <v>8.5176</v>
       </c>
     </row>
     <row r="34">
@@ -5319,10 +5319,10 @@
         <v>1.5</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5775</v>
+        <v>0.4775</v>
       </c>
       <c r="J34" t="n">
-        <v>8.085000000000001</v>
+        <v>6.685</v>
       </c>
     </row>
     <row r="35">
@@ -5359,10 +5359,10 @@
         <v>1.27</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3007</v>
+        <v>0.3254</v>
       </c>
       <c r="J35" t="n">
-        <v>4.2098</v>
+        <v>4.5556</v>
       </c>
     </row>
     <row r="36">
@@ -5399,10 +5399,10 @@
         <v>1.19</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1972</v>
+        <v>0.2307</v>
       </c>
       <c r="J36" t="n">
-        <v>2.7608</v>
+        <v>3.2298</v>
       </c>
     </row>
     <row r="37">
@@ -5439,10 +5439,10 @@
         <v>1.08</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3495</v>
+        <v>0.3016</v>
       </c>
       <c r="J37" t="n">
-        <v>4.893</v>
+        <v>4.2224</v>
       </c>
     </row>
     <row r="38">
@@ -5479,10 +5479,10 @@
         <v>0.7</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3628</v>
+        <v>-0.2874</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.0792</v>
+        <v>-4.0236</v>
       </c>
     </row>
     <row r="39">
@@ -5519,10 +5519,10 @@
         <v>0.59</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5614</v>
+        <v>-0.3878</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.8596</v>
+        <v>-5.4292</v>
       </c>
     </row>
     <row r="40">
@@ -5559,10 +5559,10 @@
         <v>0.44</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7725</v>
+        <v>-0.5284</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.815</v>
+        <v>-7.3976</v>
       </c>
     </row>
     <row r="41">
@@ -5599,10 +5599,10 @@
         <v>0.37</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8616</v>
+        <v>-0.5947</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.0624</v>
+        <v>-8.325799999999999</v>
       </c>
     </row>
     <row r="42">
@@ -5639,10 +5639,10 @@
         <v>1.13</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3146</v>
+        <v>0.3348</v>
       </c>
       <c r="J42" t="n">
-        <v>6.6066</v>
+        <v>7.0308</v>
       </c>
     </row>
     <row r="43">
@@ -5679,10 +5679,10 @@
         <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1566</v>
+        <v>0.1417</v>
       </c>
       <c r="J43" t="n">
-        <v>3.2886</v>
+        <v>2.9757</v>
       </c>
     </row>
     <row r="44">
@@ -5719,10 +5719,10 @@
         <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1566</v>
+        <v>0.1417</v>
       </c>
       <c r="J44" t="n">
-        <v>3.2886</v>
+        <v>2.9757</v>
       </c>
     </row>
     <row r="45">
@@ -5759,10 +5759,10 @@
         <v>0.76</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4152</v>
+        <v>-0.2663</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.719200000000001</v>
+        <v>-5.5923</v>
       </c>
     </row>
     <row r="46">
@@ -5799,10 +5799,10 @@
         <v>0.53</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7153</v>
+        <v>-0.4822</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.0213</v>
+        <v>-10.1262</v>
       </c>
     </row>
     <row r="47">
@@ -5839,10 +5839,10 @@
         <v>1.56</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3106</v>
+        <v>0.9288</v>
       </c>
       <c r="J47" t="n">
-        <v>27.5226</v>
+        <v>19.5048</v>
       </c>
     </row>
     <row r="48">
@@ -5879,10 +5879,10 @@
         <v>1.47</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1309</v>
+        <v>0.8158</v>
       </c>
       <c r="J48" t="n">
-        <v>23.7489</v>
+        <v>17.1318</v>
       </c>
     </row>
     <row r="49">
@@ -5919,10 +5919,10 @@
         <v>1.2</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4757</v>
+        <v>0.461</v>
       </c>
       <c r="J49" t="n">
-        <v>9.989699999999999</v>
+        <v>9.680999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -5959,10 +5959,10 @@
         <v>1.17</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3976</v>
+        <v>0.4171</v>
       </c>
       <c r="J50" t="n">
-        <v>8.349600000000001</v>
+        <v>8.7591</v>
       </c>
     </row>
     <row r="51">
@@ -5999,10 +5999,10 @@
         <v>0.91</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4658</v>
+        <v>-0.3893</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.7818</v>
+        <v>-8.1753</v>
       </c>
     </row>
     <row r="52">
@@ -6039,10 +6039,10 @@
         <v>1.36</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.5971</v>
       </c>
       <c r="J52" t="n">
-        <v>11.5128</v>
+        <v>10.7478</v>
       </c>
     </row>
     <row r="53">
@@ -6079,10 +6079,10 @@
         <v>0.82</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3168</v>
+        <v>-0.2044</v>
       </c>
       <c r="J53" t="n">
-        <v>-5.7024</v>
+        <v>-3.6792</v>
       </c>
     </row>
     <row r="54">
@@ -6119,10 +6119,10 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3794</v>
+        <v>-0.2441</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.8292</v>
+        <v>-4.3938</v>
       </c>
     </row>
     <row r="55">
@@ -6159,10 +6159,10 @@
         <v>0.73</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4524</v>
+        <v>-0.2928</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.1432</v>
+        <v>-5.2704</v>
       </c>
     </row>
     <row r="56">
@@ -6199,10 +6199,10 @@
         <v>0.71</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4804</v>
+        <v>-0.312</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.6472</v>
+        <v>-5.616</v>
       </c>
     </row>
     <row r="57">
@@ -6239,10 +6239,10 @@
         <v>2.12</v>
       </c>
       <c r="I57" t="n">
-        <v>2.0168</v>
+        <v>1.5711</v>
       </c>
       <c r="J57" t="n">
-        <v>36.3024</v>
+        <v>28.2798</v>
       </c>
     </row>
     <row r="58">
@@ -6279,10 +6279,10 @@
         <v>1.53</v>
       </c>
       <c r="I58" t="n">
-        <v>1.2186</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>21.9348</v>
+        <v>15.795</v>
       </c>
     </row>
     <row r="59">
@@ -6319,10 +6319,10 @@
         <v>1.24</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5397</v>
+        <v>0.5091</v>
       </c>
       <c r="J59" t="n">
-        <v>9.714600000000001</v>
+        <v>9.1638</v>
       </c>
     </row>
     <row r="60">
@@ -6359,10 +6359,10 @@
         <v>0.93</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4263</v>
+        <v>-0.345</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.6734</v>
+        <v>-6.21</v>
       </c>
     </row>
     <row r="61">
@@ -6399,10 +6399,10 @@
         <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6633</v>
+        <v>-0.5998</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.9394</v>
+        <v>-10.7964</v>
       </c>
     </row>
     <row r="62">
@@ -6439,10 +6439,10 @@
         <v>2.88</v>
       </c>
       <c r="I62" t="n">
-        <v>2.5208</v>
+        <v>2.2937</v>
       </c>
       <c r="J62" t="n">
-        <v>42.8536</v>
+        <v>38.9929</v>
       </c>
     </row>
     <row r="63">
@@ -6479,10 +6479,10 @@
         <v>1.89</v>
       </c>
       <c r="I63" t="n">
-        <v>1.7456</v>
+        <v>1.2491</v>
       </c>
       <c r="J63" t="n">
-        <v>29.6752</v>
+        <v>21.2347</v>
       </c>
     </row>
     <row r="64">
@@ -6519,10 +6519,10 @@
         <v>1.58</v>
       </c>
       <c r="I64" t="n">
-        <v>1.1656</v>
+        <v>0.9048</v>
       </c>
       <c r="J64" t="n">
-        <v>19.8152</v>
+        <v>15.3816</v>
       </c>
     </row>
     <row r="65">
@@ -6559,10 +6559,10 @@
         <v>0.91</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5312</v>
+        <v>-0.455</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.0304</v>
+        <v>-7.735</v>
       </c>
     </row>
     <row r="66">
@@ -6599,10 +6599,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9503</v>
+        <v>-0.9216</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.1551</v>
+        <v>-15.6672</v>
       </c>
     </row>
     <row r="67">
@@ -6639,10 +6639,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0017</v>
+        <v>-0.0345</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0289</v>
+        <v>-0.5865</v>
       </c>
     </row>
     <row r="68">
@@ -6679,10 +6679,10 @@
         <v>0.75</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3155</v>
+        <v>-0.2494</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.3635</v>
+        <v>-4.2398</v>
       </c>
     </row>
     <row r="69">
@@ -6719,10 +6719,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4263</v>
+        <v>-0.3054</v>
       </c>
       <c r="J69" t="n">
-        <v>-7.2471</v>
+        <v>-5.1918</v>
       </c>
     </row>
     <row r="70">
@@ -6759,10 +6759,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6294</v>
+        <v>-0.4253</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.6998</v>
+        <v>-7.2301</v>
       </c>
     </row>
     <row r="71">
@@ -6799,10 +6799,10 @@
         <v>0.52</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6835</v>
+        <v>-0.4627</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.6195</v>
+        <v>-7.8659</v>
       </c>
     </row>
     <row r="72">
@@ -6839,10 +6839,10 @@
         <v>1.61</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4209</v>
+        <v>0.9982</v>
       </c>
       <c r="J72" t="n">
-        <v>28.418</v>
+        <v>19.964</v>
       </c>
     </row>
     <row r="73">
@@ -6879,10 +6879,10 @@
         <v>1.57</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3443</v>
+        <v>0.9484</v>
       </c>
       <c r="J73" t="n">
-        <v>26.886</v>
+        <v>18.968</v>
       </c>
     </row>
     <row r="74">
@@ -6919,10 +6919,10 @@
         <v>1.35</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8889</v>
+        <v>0.6663</v>
       </c>
       <c r="J74" t="n">
-        <v>17.778</v>
+        <v>13.326</v>
       </c>
     </row>
     <row r="75">
@@ -6959,10 +6959,10 @@
         <v>1.1</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2214</v>
+        <v>0.295</v>
       </c>
       <c r="J75" t="n">
-        <v>4.428</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="76">
@@ -6999,10 +6999,10 @@
         <v>0.53</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.3072</v>
+        <v>-1.3276</v>
       </c>
       <c r="J76" t="n">
-        <v>-26.144</v>
+        <v>-26.552</v>
       </c>
     </row>
     <row r="77">
@@ -7039,10 +7039,10 @@
         <v>1.35</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6373</v>
+        <v>0.596</v>
       </c>
       <c r="J77" t="n">
-        <v>12.746</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="78">
@@ -7079,10 +7079,10 @@
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0722</v>
+        <v>0.0354</v>
       </c>
       <c r="J78" t="n">
-        <v>1.444</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="79">
@@ -7119,10 +7119,10 @@
         <v>0.71</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4731</v>
+        <v>-0.3085</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.462</v>
+        <v>-6.17</v>
       </c>
     </row>
     <row r="80">
@@ -7159,10 +7159,10 @@
         <v>0.64</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5684</v>
+        <v>-0.3748</v>
       </c>
       <c r="J80" t="n">
-        <v>-11.368</v>
+        <v>-7.496</v>
       </c>
     </row>
     <row r="81">
@@ -7199,10 +7199,10 @@
         <v>0.57</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6583</v>
+        <v>-0.44</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.166</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -7239,10 +7239,10 @@
         <v>1.35</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9268</v>
+        <v>0.6795</v>
       </c>
       <c r="J82" t="n">
-        <v>21.3164</v>
+        <v>15.6285</v>
       </c>
     </row>
     <row r="83">
@@ -7279,10 +7279,10 @@
         <v>1.2</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5651</v>
+        <v>0.4711</v>
       </c>
       <c r="J83" t="n">
-        <v>12.9973</v>
+        <v>10.8353</v>
       </c>
     </row>
     <row r="84">
@@ -7319,10 +7319,10 @@
         <v>1.15</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4067</v>
+        <v>0.399</v>
       </c>
       <c r="J84" t="n">
-        <v>9.354100000000001</v>
+        <v>9.177</v>
       </c>
     </row>
     <row r="85">
@@ -7359,10 +7359,10 @@
         <v>1.07</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1651</v>
+        <v>0.2241</v>
       </c>
       <c r="J85" t="n">
-        <v>3.7973</v>
+        <v>5.1543</v>
       </c>
     </row>
     <row r="86">
@@ -7399,10 +7399,10 @@
         <v>1.04</v>
       </c>
       <c r="I86" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.1287</v>
       </c>
       <c r="J86" t="n">
-        <v>1.5318</v>
+        <v>2.9601</v>
       </c>
     </row>
     <row r="87">
@@ -7439,10 +7439,10 @@
         <v>1.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5425</v>
+        <v>0.5168</v>
       </c>
       <c r="J87" t="n">
-        <v>12.4775</v>
+        <v>11.8864</v>
       </c>
     </row>
     <row r="88">
@@ -7479,10 +7479,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>0.002</v>
+        <v>-0.015</v>
       </c>
       <c r="J88" t="n">
-        <v>0.046</v>
+        <v>-0.345</v>
       </c>
     </row>
     <row r="89">
@@ -7519,10 +7519,10 @@
         <v>0.93</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1432</v>
+        <v>-0.094</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.2936</v>
+        <v>-2.162</v>
       </c>
     </row>
     <row r="90">
@@ -7559,10 +7559,10 @@
         <v>0.79</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3818</v>
+        <v>-0.2413</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.7814</v>
+        <v>-5.5499</v>
       </c>
     </row>
     <row r="91">
@@ -7599,10 +7599,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5471</v>
+        <v>-0.3571</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.5833</v>
+        <v>-8.2133</v>
       </c>
     </row>
     <row r="92">
@@ -7639,10 +7639,10 @@
         <v>1.81</v>
       </c>
       <c r="I92" t="n">
-        <v>1.769</v>
+        <v>1.2592</v>
       </c>
       <c r="J92" t="n">
-        <v>49.532</v>
+        <v>35.2576</v>
       </c>
     </row>
     <row r="93">
@@ -7679,10 +7679,10 @@
         <v>1.34</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8927</v>
+        <v>0.6616</v>
       </c>
       <c r="J93" t="n">
-        <v>24.9956</v>
+        <v>18.5248</v>
       </c>
     </row>
     <row r="94">
@@ -7719,10 +7719,10 @@
         <v>1.17</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4473</v>
+        <v>0.4263</v>
       </c>
       <c r="J94" t="n">
-        <v>12.5244</v>
+        <v>11.9364</v>
       </c>
     </row>
     <row r="95">
@@ -7759,10 +7759,10 @@
         <v>0.98</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2179</v>
+        <v>-0.1407</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.1012</v>
+        <v>-3.9396</v>
       </c>
     </row>
     <row r="96">
@@ -7799,10 +7799,10 @@
         <v>0.62</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.1206</v>
+        <v>-1.1116</v>
       </c>
       <c r="J96" t="n">
-        <v>-31.3768</v>
+        <v>-31.1248</v>
       </c>
     </row>
     <row r="97">
@@ -7839,10 +7839,10 @@
         <v>1.49</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.7096</v>
       </c>
       <c r="J97" t="n">
-        <v>21.6916</v>
+        <v>19.8688</v>
       </c>
     </row>
     <row r="98">
@@ -7879,10 +7879,10 @@
         <v>0.93</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1432</v>
+        <v>-0.094</v>
       </c>
       <c r="J98" t="n">
-        <v>-4.0096</v>
+        <v>-2.632</v>
       </c>
     </row>
     <row r="99">
@@ -7919,10 +7919,10 @@
         <v>0.92</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1647</v>
+        <v>-0.1052</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.6116</v>
+        <v>-2.9456</v>
       </c>
     </row>
     <row r="100">
@@ -7959,10 +7959,10 @@
         <v>0.67</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5471</v>
+        <v>-0.3571</v>
       </c>
       <c r="J100" t="n">
-        <v>-15.3188</v>
+        <v>-9.998799999999999</v>
       </c>
     </row>
     <row r="101">
@@ -7999,10 +7999,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5471</v>
+        <v>-0.3571</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.3188</v>
+        <v>-9.998799999999999</v>
       </c>
     </row>
     <row r="102">
@@ -8039,10 +8039,10 @@
         <v>1.88</v>
       </c>
       <c r="I102" t="n">
-        <v>1.8234</v>
+        <v>1.3266</v>
       </c>
       <c r="J102" t="n">
-        <v>36.468</v>
+        <v>26.532</v>
       </c>
     </row>
     <row r="103">
@@ -8079,10 +8079,10 @@
         <v>1.43</v>
       </c>
       <c r="I103" t="n">
-        <v>1.0628</v>
+        <v>0.7706</v>
       </c>
       <c r="J103" t="n">
-        <v>21.256</v>
+        <v>15.412</v>
       </c>
     </row>
     <row r="104">
@@ -8119,10 +8119,10 @@
         <v>1.39</v>
       </c>
       <c r="I104" t="n">
-        <v>0.9774</v>
+        <v>0.7187</v>
       </c>
       <c r="J104" t="n">
-        <v>19.548</v>
+        <v>14.374</v>
       </c>
     </row>
     <row r="105">
@@ -8159,10 +8159,10 @@
         <v>0.83</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.6656</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="J105" t="n">
-        <v>-13.312</v>
+        <v>-12.086</v>
       </c>
     </row>
     <row r="106">
@@ -8199,10 +8199,10 @@
         <v>0.63</v>
       </c>
       <c r="I106" t="n">
-        <v>-1.1082</v>
+        <v>-1.0978</v>
       </c>
       <c r="J106" t="n">
-        <v>-22.164</v>
+        <v>-21.956</v>
       </c>
     </row>
     <row r="107">
@@ -8239,10 +8239,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5347</v>
+        <v>0.5109</v>
       </c>
       <c r="J107" t="n">
-        <v>10.694</v>
+        <v>10.218</v>
       </c>
     </row>
     <row r="108">
@@ -8279,10 +8279,10 @@
         <v>1.06</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1726</v>
+        <v>0.1718</v>
       </c>
       <c r="J108" t="n">
-        <v>3.452</v>
+        <v>3.436</v>
       </c>
     </row>
     <row r="109">
@@ -8319,10 +8319,10 @@
         <v>1.01</v>
       </c>
       <c r="I109" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0452</v>
       </c>
       <c r="J109" t="n">
-        <v>1.254</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="110">
@@ -8359,10 +8359,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4445</v>
+        <v>-0.2833</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.890000000000001</v>
+        <v>-5.666</v>
       </c>
     </row>
     <row r="111">
@@ -8399,10 +8399,10 @@
         <v>0.67</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5514</v>
+        <v>-0.3597</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.028</v>
+        <v>-7.194</v>
       </c>
     </row>
     <row r="112">
@@ -8439,10 +8439,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6302</v>
+        <v>0.4825</v>
       </c>
       <c r="J112" t="n">
-        <v>15.1248</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="113">
@@ -8479,10 +8479,10 @@
         <v>1.29</v>
       </c>
       <c r="I113" t="n">
-        <v>0.516</v>
+        <v>0.4122</v>
       </c>
       <c r="J113" t="n">
-        <v>12.384</v>
+        <v>9.892799999999999</v>
       </c>
     </row>
     <row r="114">
@@ -8519,10 +8519,10 @@
         <v>1.04</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1262</v>
+        <v>0.0929</v>
       </c>
       <c r="J114" t="n">
-        <v>3.0288</v>
+        <v>2.2296</v>
       </c>
     </row>
     <row r="115">
@@ -8559,10 +8559,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3626</v>
+        <v>-0.2259</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.702400000000001</v>
+        <v>-5.4216</v>
       </c>
     </row>
     <row r="116">
@@ -8599,10 +8599,10 @@
         <v>0.35</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.9283</v>
+        <v>-0.6491</v>
       </c>
       <c r="J116" t="n">
-        <v>-22.2792</v>
+        <v>-15.5784</v>
       </c>
     </row>
     <row r="117">
@@ -8639,10 +8639,10 @@
         <v>1.3</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4914</v>
+        <v>0.3838</v>
       </c>
       <c r="J117" t="n">
-        <v>11.7936</v>
+        <v>9.2112</v>
       </c>
     </row>
     <row r="118">
@@ -8679,10 +8679,10 @@
         <v>1.12</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2257</v>
+        <v>0.1906</v>
       </c>
       <c r="J118" t="n">
-        <v>5.4168</v>
+        <v>4.5744</v>
       </c>
     </row>
     <row r="119">
@@ -8719,10 +8719,10 @@
         <v>1.11</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2078</v>
+        <v>0.177</v>
       </c>
       <c r="J119" t="n">
-        <v>4.9872</v>
+        <v>4.248</v>
       </c>
     </row>
     <row r="120">
@@ -8759,10 +8759,10 @@
         <v>1.01</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0076</v>
+        <v>0.0175</v>
       </c>
       <c r="J120" t="n">
-        <v>-0.1824</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="121">
@@ -8799,10 +8799,10 @@
         <v>0.9</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2515</v>
+        <v>-0.1439</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.036</v>
+        <v>-3.4536</v>
       </c>
     </row>
     <row r="122">
@@ -8839,10 +8839,10 @@
         <v>1.57</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3405</v>
+        <v>0.9464</v>
       </c>
       <c r="J122" t="n">
-        <v>26.81</v>
+        <v>18.928</v>
       </c>
     </row>
     <row r="123">
@@ -8879,10 +8879,10 @@
         <v>1.4</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9948</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="J123" t="n">
-        <v>19.896</v>
+        <v>14.606</v>
       </c>
     </row>
     <row r="124">
@@ -8919,10 +8919,10 @@
         <v>1.15</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3556</v>
+        <v>0.3897</v>
       </c>
       <c r="J124" t="n">
-        <v>7.112</v>
+        <v>7.794</v>
       </c>
     </row>
     <row r="125">
@@ -8959,10 +8959,10 @@
         <v>1.07</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1301</v>
+        <v>0.2052</v>
       </c>
       <c r="J125" t="n">
-        <v>2.602</v>
+        <v>4.104</v>
       </c>
     </row>
     <row r="126">
@@ -8999,10 +8999,10 @@
         <v>1.01</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.0791</v>
+        <v>-0.0036</v>
       </c>
       <c r="J126" t="n">
-        <v>-1.582</v>
+        <v>-0.07199999999999999</v>
       </c>
     </row>
     <row r="127">
@@ -9039,10 +9039,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.0594</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J127" t="n">
-        <v>-1.188</v>
+        <v>-1.362</v>
       </c>
     </row>
     <row r="128">
@@ -9079,10 +9079,10 @@
         <v>0.91</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1154</v>
+        <v>-0.1042</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.308</v>
+        <v>-2.084</v>
       </c>
     </row>
     <row r="129">
@@ -9119,10 +9119,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2232</v>
+        <v>-0.1694</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.464</v>
+        <v>-3.388</v>
       </c>
     </row>
     <row r="130">
@@ -9159,10 +9159,10 @@
         <v>0.74</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4201</v>
+        <v>-0.2759</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.401999999999999</v>
+        <v>-5.518</v>
       </c>
     </row>
     <row r="131">
@@ -9199,10 +9199,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4927</v>
+        <v>-0.3237</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.853999999999999</v>
+        <v>-6.474</v>
       </c>
     </row>
     <row r="132">
@@ -9239,10 +9239,10 @@
         <v>1.26</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4339</v>
+        <v>0.3538</v>
       </c>
       <c r="J132" t="n">
-        <v>18.2238</v>
+        <v>14.8596</v>
       </c>
     </row>
     <row r="133">
@@ -9279,10 +9279,10 @@
         <v>1.19</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3337</v>
+        <v>0.2806</v>
       </c>
       <c r="J133" t="n">
-        <v>14.0154</v>
+        <v>11.7852</v>
       </c>
     </row>
     <row r="134">
@@ -9319,10 +9319,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2546</v>
+        <v>0.2159</v>
       </c>
       <c r="J134" t="n">
-        <v>10.6932</v>
+        <v>9.0678</v>
       </c>
     </row>
     <row r="135">
@@ -9359,10 +9359,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.1046</v>
       </c>
       <c r="J135" t="n">
-        <v>4.0992</v>
+        <v>4.3932</v>
       </c>
     </row>
     <row r="136">
@@ -9399,10 +9399,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3319</v>
+        <v>-0.199</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.9398</v>
+        <v>-8.358000000000001</v>
       </c>
     </row>
     <row r="137">
@@ -9439,10 +9439,10 @@
         <v>1.13</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2671</v>
+        <v>0.2288</v>
       </c>
       <c r="J137" t="n">
-        <v>11.2182</v>
+        <v>9.6096</v>
       </c>
     </row>
     <row r="138">
@@ -9479,10 +9479,10 @@
         <v>1.09</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1992</v>
+        <v>0.168</v>
       </c>
       <c r="J138" t="n">
-        <v>8.366400000000001</v>
+        <v>7.056</v>
       </c>
     </row>
     <row r="139">
@@ -9519,10 +9519,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.0853</v>
       </c>
       <c r="J139" t="n">
-        <v>4.1832</v>
+        <v>3.5826</v>
       </c>
     </row>
     <row r="140">
@@ -9559,10 +9559,10 @@
         <v>1.01</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0171</v>
+        <v>0.0265</v>
       </c>
       <c r="J140" t="n">
-        <v>0.7181999999999999</v>
+        <v>1.113</v>
       </c>
     </row>
     <row r="141">
@@ -9599,10 +9599,10 @@
         <v>0.87</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2851</v>
+        <v>-0.17</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.9742</v>
+        <v>-7.14</v>
       </c>
     </row>
     <row r="142">
@@ -9639,10 +9639,10 @@
         <v>1.61</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9307</v>
+        <v>0.8496</v>
       </c>
       <c r="J142" t="n">
-        <v>18.614</v>
+        <v>16.992</v>
       </c>
     </row>
     <row r="143">
@@ -9679,10 +9679,10 @@
         <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0605</v>
+        <v>0.0261</v>
       </c>
       <c r="J143" t="n">
-        <v>1.21</v>
+        <v>0.522</v>
       </c>
     </row>
     <row r="144">
@@ -9719,10 +9719,10 @@
         <v>0.63</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.5877</v>
+        <v>-0.3879</v>
       </c>
       <c r="J144" t="n">
-        <v>-11.754</v>
+        <v>-7.758</v>
       </c>
     </row>
     <row r="145">
@@ -9759,10 +9759,10 @@
         <v>0.61</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-0.4065</v>
       </c>
       <c r="J145" t="n">
-        <v>-12.268</v>
+        <v>-8.130000000000001</v>
       </c>
     </row>
     <row r="146">
@@ -9799,10 +9799,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.4527</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.518</v>
+        <v>-9.054</v>
       </c>
     </row>
     <row r="147">
@@ -9839,10 +9839,10 @@
         <v>1.95</v>
       </c>
       <c r="I147" t="n">
-        <v>1.8904</v>
+        <v>1.412</v>
       </c>
       <c r="J147" t="n">
-        <v>37.808</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="148">
@@ -9879,10 +9879,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8922</v>
+        <v>0.6673</v>
       </c>
       <c r="J148" t="n">
-        <v>17.844</v>
+        <v>13.346</v>
       </c>
     </row>
     <row r="149">
@@ -9919,10 +9919,10 @@
         <v>1.2</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4989</v>
+        <v>0.4651</v>
       </c>
       <c r="J149" t="n">
-        <v>9.978</v>
+        <v>9.302</v>
       </c>
     </row>
     <row r="150">
@@ -9959,10 +9959,10 @@
         <v>0.91</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4559</v>
+        <v>-0.3807</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.118</v>
+        <v>-7.614</v>
       </c>
     </row>
     <row r="151">
@@ -9999,10 +9999,10 @@
         <v>0.72</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.9171</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="J151" t="n">
-        <v>-18.342</v>
+        <v>-17.632</v>
       </c>
     </row>
     <row r="152">
@@ -10039,10 +10039,10 @@
         <v>1.09</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2932</v>
+        <v>0.3051</v>
       </c>
       <c r="J152" t="n">
-        <v>5.2776</v>
+        <v>5.4918</v>
       </c>
     </row>
     <row r="153">
@@ -10079,10 +10079,10 @@
         <v>0.9</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1165</v>
+        <v>-0.1094</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.097</v>
+        <v>-1.9692</v>
       </c>
     </row>
     <row r="154">
@@ -10119,10 +10119,10 @@
         <v>0.77</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.355</v>
+        <v>-0.2427</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.39</v>
+        <v>-4.3686</v>
       </c>
     </row>
     <row r="155">
@@ -10159,10 +10159,10 @@
         <v>0.6</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.6051</v>
+        <v>-0.4033</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.8918</v>
+        <v>-7.2594</v>
       </c>
     </row>
     <row r="156">
@@ -10199,10 +10199,10 @@
         <v>0.59</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6182</v>
+        <v>-0.4126</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.1276</v>
+        <v>-7.4268</v>
       </c>
     </row>
     <row r="157">
@@ -10239,10 +10239,10 @@
         <v>1.51</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2091</v>
+        <v>0.865</v>
       </c>
       <c r="J157" t="n">
-        <v>21.7638</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="158">
@@ -10279,10 +10279,10 @@
         <v>1.33</v>
       </c>
       <c r="I158" t="n">
-        <v>0.8219</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>14.7942</v>
+        <v>11.4228</v>
       </c>
     </row>
     <row r="159">
@@ -10319,10 +10319,10 @@
         <v>1.27</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6662</v>
+        <v>0.5562</v>
       </c>
       <c r="J159" t="n">
-        <v>11.9916</v>
+        <v>10.0116</v>
       </c>
     </row>
     <row r="160">
@@ -10359,10 +10359,10 @@
         <v>1.22</v>
       </c>
       <c r="I160" t="n">
-        <v>0.524</v>
+        <v>0.4887</v>
       </c>
       <c r="J160" t="n">
-        <v>9.432</v>
+        <v>8.7966</v>
       </c>
     </row>
     <row r="161">
@@ -10399,10 +10399,10 @@
         <v>1.01</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.0883</v>
+        <v>-0.0104</v>
       </c>
       <c r="J161" t="n">
-        <v>-1.5894</v>
+        <v>-0.1872</v>
       </c>
     </row>
     <row r="162">
@@ -10439,10 +10439,10 @@
         <v>1.45</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7016</v>
+        <v>0.6471</v>
       </c>
       <c r="J162" t="n">
-        <v>14.7336</v>
+        <v>13.5891</v>
       </c>
     </row>
     <row r="163">
@@ -10479,10 +10479,10 @@
         <v>1.15</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3047</v>
+        <v>0.3365</v>
       </c>
       <c r="J163" t="n">
-        <v>6.3987</v>
+        <v>7.0665</v>
       </c>
     </row>
     <row r="164">
@@ -10519,10 +10519,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2232</v>
+        <v>0.2435</v>
       </c>
       <c r="J164" t="n">
-        <v>4.6872</v>
+        <v>5.1135</v>
       </c>
     </row>
     <row r="165">
@@ -10559,10 +10559,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2809</v>
+        <v>-0.1682</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.8989</v>
+        <v>-3.5322</v>
       </c>
     </row>
     <row r="166">
@@ -10599,10 +10599,10 @@
         <v>0.49</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7765</v>
+        <v>-0.5293</v>
       </c>
       <c r="J166" t="n">
-        <v>-16.3065</v>
+        <v>-11.1153</v>
       </c>
     </row>
     <row r="167">
@@ -10639,10 +10639,10 @@
         <v>1.68</v>
       </c>
       <c r="I167" t="n">
-        <v>1.5857</v>
+        <v>1.1063</v>
       </c>
       <c r="J167" t="n">
-        <v>33.2997</v>
+        <v>23.2323</v>
       </c>
     </row>
     <row r="168">
@@ -10679,10 +10679,10 @@
         <v>1.67</v>
       </c>
       <c r="I168" t="n">
-        <v>1.5672</v>
+        <v>1.0938</v>
       </c>
       <c r="J168" t="n">
-        <v>32.9112</v>
+        <v>22.9698</v>
       </c>
     </row>
     <row r="169">
@@ -10719,10 +10719,10 @@
         <v>1.05</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1006</v>
+        <v>0.1617</v>
       </c>
       <c r="J169" t="n">
-        <v>2.1126</v>
+        <v>3.3957</v>
       </c>
     </row>
     <row r="170">
@@ -10759,10 +10759,10 @@
         <v>0.78</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.7675</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>-16.1175</v>
+        <v>-15.0612</v>
       </c>
     </row>
     <row r="171">
@@ -10799,10 +10799,10 @@
         <v>0.63</v>
       </c>
       <c r="I171" t="n">
-        <v>-1.096</v>
+        <v>-1.0834</v>
       </c>
       <c r="J171" t="n">
-        <v>-23.016</v>
+        <v>-22.7514</v>
       </c>
     </row>
     <row r="172">
@@ -10839,10 +10839,10 @@
         <v>1.34</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5436</v>
+        <v>0.4121</v>
       </c>
       <c r="J172" t="n">
-        <v>16.308</v>
+        <v>12.363</v>
       </c>
     </row>
     <row r="173">
@@ -10879,10 +10879,10 @@
         <v>1.29</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4788</v>
+        <v>0.3769</v>
       </c>
       <c r="J173" t="n">
-        <v>14.364</v>
+        <v>11.307</v>
       </c>
     </row>
     <row r="174">
@@ -10919,10 +10919,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3826</v>
+        <v>0.3194</v>
       </c>
       <c r="J174" t="n">
-        <v>11.478</v>
+        <v>9.582000000000001</v>
       </c>
     </row>
     <row r="175">
@@ -10959,10 +10959,10 @@
         <v>0.82</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.373</v>
+        <v>-0.2284</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.19</v>
+        <v>-6.852</v>
       </c>
     </row>
     <row r="176">
@@ -10999,10 +10999,10 @@
         <v>0.76</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.456</v>
+        <v>-0.288</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.68</v>
+        <v>-8.640000000000001</v>
       </c>
     </row>
     <row r="177">
@@ -11039,10 +11039,10 @@
         <v>1.29</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4965</v>
+        <v>0.4024</v>
       </c>
       <c r="J177" t="n">
-        <v>14.895</v>
+        <v>12.072</v>
       </c>
     </row>
     <row r="178">
@@ -11079,10 +11079,10 @@
         <v>1.07</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1603</v>
+        <v>0.1356</v>
       </c>
       <c r="J178" t="n">
-        <v>4.809</v>
+        <v>4.068</v>
       </c>
     </row>
     <row r="179">
@@ -11119,10 +11119,10 @@
         <v>1.05</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1196</v>
+        <v>0.1023</v>
       </c>
       <c r="J179" t="n">
-        <v>3.588</v>
+        <v>3.069</v>
       </c>
     </row>
     <row r="180">
@@ -11159,10 +11159,10 @@
         <v>1</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0211</v>
+        <v>-0.0023</v>
       </c>
       <c r="J180" t="n">
-        <v>-0.633</v>
+        <v>-0.06900000000000001</v>
       </c>
     </row>
     <row r="181">
@@ -11199,10 +11199,10 @@
         <v>0.75</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4599</v>
+        <v>-0.2919</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.797</v>
+        <v>-8.757</v>
       </c>
     </row>
     <row r="182">
@@ -11239,10 +11239,10 @@
         <v>1.17</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4463</v>
+        <v>0.4419</v>
       </c>
       <c r="J182" t="n">
-        <v>8.0334</v>
+        <v>7.9542</v>
       </c>
     </row>
     <row r="183">
@@ -11279,10 +11279,10 @@
         <v>0.73</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.3804</v>
+        <v>-0.2736</v>
       </c>
       <c r="J183" t="n">
-        <v>-6.8472</v>
+        <v>-4.9248</v>
       </c>
     </row>
     <row r="184">
@@ -11319,10 +11319,10 @@
         <v>0.71</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.4209</v>
+        <v>-0.2915</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.5762</v>
+        <v>-5.247</v>
       </c>
     </row>
     <row r="185">
@@ -11359,10 +11359,10 @@
         <v>0.57</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.6281</v>
+        <v>-0.4221</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.3058</v>
+        <v>-7.5978</v>
       </c>
     </row>
     <row r="186">
@@ -11399,10 +11399,10 @@
         <v>0.47</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7575</v>
+        <v>-0.5154</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.635</v>
+        <v>-9.277200000000001</v>
       </c>
     </row>
     <row r="187">
@@ -11439,10 +11439,10 @@
         <v>1.47</v>
       </c>
       <c r="I187" t="n">
-        <v>1.0891</v>
+        <v>0.8013</v>
       </c>
       <c r="J187" t="n">
-        <v>19.6038</v>
+        <v>14.4234</v>
       </c>
     </row>
     <row r="188">
@@ -11479,10 +11479,10 @@
         <v>1.46</v>
       </c>
       <c r="I188" t="n">
-        <v>1.068</v>
+        <v>0.7889</v>
       </c>
       <c r="J188" t="n">
-        <v>19.224</v>
+        <v>14.2002</v>
       </c>
     </row>
     <row r="189">
@@ -11519,10 +11519,10 @@
         <v>1.34</v>
       </c>
       <c r="I189" t="n">
-        <v>0.7794</v>
+        <v>0.6399</v>
       </c>
       <c r="J189" t="n">
-        <v>14.0292</v>
+        <v>11.5182</v>
       </c>
     </row>
     <row r="190">
@@ -11559,10 +11559,10 @@
         <v>1.33</v>
       </c>
       <c r="I190" t="n">
-        <v>0.7524</v>
+        <v>0.6273</v>
       </c>
       <c r="J190" t="n">
-        <v>13.5432</v>
+        <v>11.2914</v>
       </c>
     </row>
     <row r="191">
@@ -11599,10 +11599,10 @@
         <v>1.13</v>
       </c>
       <c r="I191" t="n">
-        <v>0.2598</v>
+        <v>0.3435</v>
       </c>
       <c r="J191" t="n">
-        <v>4.6764</v>
+        <v>6.183</v>
       </c>
     </row>
     <row r="192">
@@ -11639,10 +11639,10 @@
         <v>1.69</v>
       </c>
       <c r="I192" t="n">
-        <v>1.5737</v>
+        <v>1.373</v>
       </c>
       <c r="J192" t="n">
-        <v>34.6214</v>
+        <v>30.206</v>
       </c>
     </row>
     <row r="193">
@@ -11679,10 +11679,10 @@
         <v>1.2</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5004</v>
+        <v>0.5568</v>
       </c>
       <c r="J193" t="n">
-        <v>11.0088</v>
+        <v>12.2496</v>
       </c>
     </row>
     <row r="194">
@@ -11719,10 +11719,10 @@
         <v>1.08</v>
       </c>
       <c r="I194" t="n">
-        <v>0.1666</v>
+        <v>0.2391</v>
       </c>
       <c r="J194" t="n">
-        <v>3.6652</v>
+        <v>5.2602</v>
       </c>
     </row>
     <row r="195">
@@ -11759,10 +11759,10 @@
         <v>1.08</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1666</v>
+        <v>0.2391</v>
       </c>
       <c r="J195" t="n">
-        <v>3.6652</v>
+        <v>5.2602</v>
       </c>
     </row>
     <row r="196">
@@ -11799,10 +11799,10 @@
         <v>1.07</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1365</v>
+        <v>0.2091</v>
       </c>
       <c r="J196" t="n">
-        <v>3.003</v>
+        <v>4.6002</v>
       </c>
     </row>
     <row r="197">
@@ -11839,10 +11839,10 @@
         <v>0.97</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.0226</v>
+        <v>-0.0379</v>
       </c>
       <c r="J197" t="n">
-        <v>-0.4972</v>
+        <v>-0.8338</v>
       </c>
     </row>
     <row r="198">
@@ -11879,10 +11879,10 @@
         <v>0.97</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.0226</v>
+        <v>-0.0379</v>
       </c>
       <c r="J198" t="n">
-        <v>-0.4972</v>
+        <v>-0.8338</v>
       </c>
     </row>
     <row r="199">
@@ -11919,10 +11919,10 @@
         <v>0.87</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2299</v>
+        <v>-0.1539</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.0578</v>
+        <v>-3.3858</v>
       </c>
     </row>
     <row r="200">
@@ -11959,10 +11959,10 @@
         <v>0.86</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.249</v>
+        <v>-0.1642</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.478</v>
+        <v>-3.6124</v>
       </c>
     </row>
     <row r="201">
@@ -11999,10 +11999,10 @@
         <v>0.74</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4388</v>
+        <v>-0.2834</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.653600000000001</v>
+        <v>-6.2348</v>
       </c>
     </row>
     <row r="202">
@@ -12039,10 +12039,10 @@
         <v>1.66</v>
       </c>
       <c r="I202" t="n">
-        <v>1.5548</v>
+        <v>1.359</v>
       </c>
       <c r="J202" t="n">
-        <v>32.6508</v>
+        <v>28.539</v>
       </c>
     </row>
     <row r="203">
@@ -12079,10 +12079,10 @@
         <v>1.27</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7499</v>
+        <v>0.7381</v>
       </c>
       <c r="J203" t="n">
-        <v>15.7479</v>
+        <v>15.5001</v>
       </c>
     </row>
     <row r="204">
@@ -12119,10 +12119,10 @@
         <v>1.15</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4234</v>
+        <v>0.4458</v>
       </c>
       <c r="J204" t="n">
-        <v>8.891400000000001</v>
+        <v>9.361800000000001</v>
       </c>
     </row>
     <row r="205">
@@ -12159,10 +12159,10 @@
         <v>0.89</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.488</v>
+        <v>-0.4194</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.248</v>
+        <v>-8.807399999999999</v>
       </c>
     </row>
     <row r="206">
@@ -12199,10 +12199,10 @@
         <v>0.78</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7644</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>-16.0524</v>
+        <v>-14.9982</v>
       </c>
     </row>
     <row r="207">
@@ -12239,10 +12239,10 @@
         <v>1.42</v>
       </c>
       <c r="I207" t="n">
-        <v>0.6966</v>
+        <v>0.8598</v>
       </c>
       <c r="J207" t="n">
-        <v>14.6286</v>
+        <v>18.0558</v>
       </c>
     </row>
     <row r="208">
@@ -12279,10 +12279,10 @@
         <v>0.87</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2516</v>
+        <v>-0.1582</v>
       </c>
       <c r="J208" t="n">
-        <v>-5.2836</v>
+        <v>-3.3222</v>
       </c>
     </row>
     <row r="209">
@@ -12319,10 +12319,10 @@
         <v>0.84</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3014</v>
+        <v>-0.1894</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.3294</v>
+        <v>-3.9774</v>
       </c>
     </row>
     <row r="210">
@@ -12359,10 +12359,10 @@
         <v>0.77</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4076</v>
+        <v>-0.2596</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.5596</v>
+        <v>-5.4516</v>
       </c>
     </row>
     <row r="211">
@@ -12399,10 +12399,10 @@
         <v>0.72</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4778</v>
+        <v>-0.3081</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.0338</v>
+        <v>-6.4701</v>
       </c>
     </row>
     <row r="212">
@@ -12439,10 +12439,10 @@
         <v>1.04</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1638</v>
+        <v>0.1478</v>
       </c>
       <c r="J212" t="n">
-        <v>5.5692</v>
+        <v>5.0252</v>
       </c>
     </row>
     <row r="213">
@@ -12479,10 +12479,10 @@
         <v>0.9</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1632</v>
+        <v>-0.1229</v>
       </c>
       <c r="J213" t="n">
-        <v>-5.5488</v>
+        <v>-4.1786</v>
       </c>
     </row>
     <row r="214">
@@ -12519,10 +12519,10 @@
         <v>0.9</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1632</v>
+        <v>-0.1229</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.5488</v>
+        <v>-4.1786</v>
       </c>
     </row>
     <row r="215">
@@ -12559,10 +12559,10 @@
         <v>0.87</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2299</v>
+        <v>-0.1539</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.8166</v>
+        <v>-5.2326</v>
       </c>
     </row>
     <row r="216">
@@ -12599,10 +12599,10 @@
         <v>0.7</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4947</v>
+        <v>-0.3218</v>
       </c>
       <c r="J216" t="n">
-        <v>-16.8198</v>
+        <v>-10.9412</v>
       </c>
     </row>
     <row r="217">
@@ -12639,10 +12639,10 @@
         <v>1.44</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1212</v>
+        <v>1.074</v>
       </c>
       <c r="J217" t="n">
-        <v>38.1208</v>
+        <v>36.516</v>
       </c>
     </row>
     <row r="218">
@@ -12679,10 +12679,10 @@
         <v>1.32</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8618</v>
+        <v>0.8527</v>
       </c>
       <c r="J218" t="n">
-        <v>29.3012</v>
+        <v>28.9918</v>
       </c>
     </row>
     <row r="219">
@@ -12719,10 +12719,10 @@
         <v>1.3</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8159</v>
+        <v>0.8062</v>
       </c>
       <c r="J219" t="n">
-        <v>27.7406</v>
+        <v>27.4108</v>
       </c>
     </row>
     <row r="220">
@@ -12759,10 +12759,10 @@
         <v>0.89</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4907</v>
+        <v>-0.4215</v>
       </c>
       <c r="J220" t="n">
-        <v>-16.6838</v>
+        <v>-14.331</v>
       </c>
     </row>
     <row r="221">
@@ -12799,10 +12799,10 @@
         <v>0.84</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6213</v>
+        <v>-0.5596</v>
       </c>
       <c r="J221" t="n">
-        <v>-21.1242</v>
+        <v>-19.0264</v>
       </c>
     </row>
     <row r="222">
@@ -12839,10 +12839,10 @@
         <v>1.44</v>
       </c>
       <c r="I222" t="n">
-        <v>1.1612</v>
+        <v>1.0952</v>
       </c>
       <c r="J222" t="n">
-        <v>34.836</v>
+        <v>32.856</v>
       </c>
     </row>
     <row r="223">
@@ -12879,10 +12879,10 @@
         <v>1.09</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3003</v>
+        <v>0.2982</v>
       </c>
       <c r="J223" t="n">
-        <v>9.009</v>
+        <v>8.946</v>
       </c>
     </row>
     <row r="224">
@@ -12919,10 +12919,10 @@
         <v>0.97</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2121</v>
+        <v>-0.1511</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.363</v>
+        <v>-4.533</v>
       </c>
     </row>
     <row r="225">
@@ -12959,10 +12959,10 @@
         <v>0.96</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2482</v>
+        <v>-0.186</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.446</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="226">
@@ -12999,10 +12999,10 @@
         <v>0.95</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2822</v>
+        <v>-0.2193</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.465999999999999</v>
+        <v>-6.579</v>
       </c>
     </row>
     <row r="227">
@@ -13039,10 +13039,10 @@
         <v>1.14</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2846</v>
+        <v>0.3193</v>
       </c>
       <c r="J227" t="n">
-        <v>8.538</v>
+        <v>9.579000000000001</v>
       </c>
     </row>
     <row r="228">
@@ -13079,10 +13079,10 @@
         <v>1.04</v>
       </c>
       <c r="I228" t="n">
-        <v>0.102</v>
+        <v>0.112</v>
       </c>
       <c r="J228" t="n">
-        <v>3.06</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="229">
@@ -13119,10 +13119,10 @@
         <v>1.02</v>
       </c>
       <c r="I229" t="n">
-        <v>0.0479</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="J229" t="n">
-        <v>1.437</v>
+        <v>1.896</v>
       </c>
     </row>
     <row r="230">
@@ -13159,10 +13159,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>0.0479</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="J230" t="n">
-        <v>1.437</v>
+        <v>1.896</v>
       </c>
     </row>
     <row r="231">
@@ -13199,10 +13199,10 @@
         <v>0.9</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2351</v>
+        <v>-0.1369</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.053</v>
+        <v>-4.107</v>
       </c>
     </row>
     <row r="232">
@@ -13239,10 +13239,10 @@
         <v>2.47</v>
       </c>
       <c r="I232" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J232" t="n">
-        <v>30.8895</v>
+        <v>27.507</v>
       </c>
     </row>
     <row r="233">
@@ -13279,10 +13279,10 @@
         <v>1.73</v>
       </c>
       <c r="I233" t="n">
-        <v>1.4994</v>
+        <v>1.3501</v>
       </c>
       <c r="J233" t="n">
-        <v>22.491</v>
+        <v>20.2515</v>
       </c>
     </row>
     <row r="234">
@@ -13319,10 +13319,10 @@
         <v>1.62</v>
       </c>
       <c r="I234" t="n">
-        <v>1.2867</v>
+        <v>1.2258</v>
       </c>
       <c r="J234" t="n">
-        <v>19.3005</v>
+        <v>18.387</v>
       </c>
     </row>
     <row r="235">
@@ -13359,10 +13359,10 @@
         <v>1.04</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0484</v>
+        <v>0.0408</v>
       </c>
       <c r="J235" t="n">
-        <v>-0.726</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="236">
@@ -13399,10 +13399,10 @@
         <v>0.95</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4118</v>
+        <v>-0.3268</v>
       </c>
       <c r="J236" t="n">
-        <v>-6.177</v>
+        <v>-4.902</v>
       </c>
     </row>
     <row r="237">
@@ -13439,10 +13439,10 @@
         <v>1.01</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2003</v>
+        <v>0.1907</v>
       </c>
       <c r="J237" t="n">
-        <v>3.0045</v>
+        <v>2.8605</v>
       </c>
     </row>
     <row r="238">
@@ -13479,10 +13479,10 @@
         <v>0.67</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.4205</v>
+        <v>-0.3182</v>
       </c>
       <c r="J238" t="n">
-        <v>-6.3075</v>
+        <v>-4.773</v>
       </c>
     </row>
     <row r="239">
@@ -13519,10 +13519,10 @@
         <v>0.55</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.6269</v>
+        <v>-0.427</v>
       </c>
       <c r="J239" t="n">
-        <v>-9.403499999999999</v>
+        <v>-6.405</v>
       </c>
     </row>
     <row r="240">
@@ -13559,10 +13559,10 @@
         <v>0.51</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.6828</v>
+        <v>-0.4645</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.242</v>
+        <v>-6.9675</v>
       </c>
     </row>
     <row r="241">
@@ -13599,10 +13599,10 @@
         <v>0.5</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6965</v>
+        <v>-0.4739</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.4475</v>
+        <v>-7.1085</v>
       </c>
     </row>
     <row r="242">
@@ -13639,10 +13639,10 @@
         <v>0.95</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.0044</v>
+        <v>-0.0371</v>
       </c>
       <c r="J242" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.6677999999999999</v>
       </c>
     </row>
     <row r="243">
@@ -13679,10 +13679,10 @@
         <v>0.9</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0961</v>
+        <v>-0.0999</v>
       </c>
       <c r="J243" t="n">
-        <v>-1.7298</v>
+        <v>-1.7982</v>
       </c>
     </row>
     <row r="244">
@@ -13719,10 +13719,10 @@
         <v>0.74</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3776</v>
+        <v>-0.2659</v>
       </c>
       <c r="J244" t="n">
-        <v>-6.7968</v>
+        <v>-4.7862</v>
       </c>
     </row>
     <row r="245">
@@ -13759,10 +13759,10 @@
         <v>0.63</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5507</v>
+        <v>-0.3685</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.912599999999999</v>
+        <v>-6.633</v>
       </c>
     </row>
     <row r="246">
@@ -13799,10 +13799,10 @@
         <v>0.51</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7107</v>
+        <v>-0.4806</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.7926</v>
+        <v>-8.6508</v>
       </c>
     </row>
     <row r="247">
@@ -13839,10 +13839,10 @@
         <v>1.8</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6852</v>
+        <v>1.455</v>
       </c>
       <c r="J247" t="n">
-        <v>30.3336</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="248">
@@ -13879,10 +13879,10 @@
         <v>1.54</v>
       </c>
       <c r="I248" t="n">
-        <v>1.1974</v>
+        <v>1.1497</v>
       </c>
       <c r="J248" t="n">
-        <v>21.5532</v>
+        <v>20.6946</v>
       </c>
     </row>
     <row r="249">
@@ -13919,10 +13919,10 @@
         <v>1.32</v>
       </c>
       <c r="I249" t="n">
-        <v>0.6876</v>
+        <v>0.7973</v>
       </c>
       <c r="J249" t="n">
-        <v>12.3768</v>
+        <v>14.3514</v>
       </c>
     </row>
     <row r="250">
@@ -13959,10 +13959,10 @@
         <v>1.28</v>
       </c>
       <c r="I250" t="n">
-        <v>0.5966</v>
+        <v>0.7068</v>
       </c>
       <c r="J250" t="n">
-        <v>10.7388</v>
+        <v>12.7224</v>
       </c>
     </row>
     <row r="251">
@@ -13999,10 +13999,10 @@
         <v>1.15</v>
       </c>
       <c r="I251" t="n">
-        <v>0.2884</v>
+        <v>0.389</v>
       </c>
       <c r="J251" t="n">
-        <v>5.1912</v>
+        <v>7.002</v>
       </c>
     </row>
     <row r="252">
@@ -14039,10 +14039,10 @@
         <v>1.96</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2142</v>
+        <v>1.36</v>
       </c>
       <c r="J252" t="n">
-        <v>25.4982</v>
+        <v>28.56</v>
       </c>
     </row>
     <row r="253">
@@ -14079,10 +14079,10 @@
         <v>1.04</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0588</v>
+        <v>0.1023</v>
       </c>
       <c r="J253" t="n">
-        <v>1.2348</v>
+        <v>2.1483</v>
       </c>
     </row>
     <row r="254">
@@ -14119,10 +14119,10 @@
         <v>1.01</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0101</v>
+        <v>0.0232</v>
       </c>
       <c r="J254" t="n">
-        <v>-0.2121</v>
+        <v>0.4872</v>
       </c>
     </row>
     <row r="255">
@@ -14159,10 +14159,10 @@
         <v>0.95</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1659</v>
+        <v>-0.0859</v>
       </c>
       <c r="J255" t="n">
-        <v>-3.4839</v>
+        <v>-1.8039</v>
       </c>
     </row>
     <row r="256">
@@ -14199,10 +14199,10 @@
         <v>0.52</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.7509</v>
+        <v>-0.5098</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.7689</v>
+        <v>-10.7058</v>
       </c>
     </row>
     <row r="257">
@@ -14239,10 +14239,10 @@
         <v>1.42</v>
       </c>
       <c r="I257" t="n">
-        <v>1.0765</v>
+        <v>1.0454</v>
       </c>
       <c r="J257" t="n">
-        <v>22.6065</v>
+        <v>21.9534</v>
       </c>
     </row>
     <row r="258">
@@ -14279,10 +14279,10 @@
         <v>1.34</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9035</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="J258" t="n">
-        <v>18.9735</v>
+        <v>18.8307</v>
       </c>
     </row>
     <row r="259">
@@ -14319,10 +14319,10 @@
         <v>1.16</v>
       </c>
       <c r="I259" t="n">
-        <v>0.4371</v>
+        <v>0.4688</v>
       </c>
       <c r="J259" t="n">
-        <v>9.1791</v>
+        <v>9.844799999999999</v>
       </c>
     </row>
     <row r="260">
@@ -14359,10 +14359,10 @@
         <v>1.06</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1323</v>
+        <v>0.1929</v>
       </c>
       <c r="J260" t="n">
-        <v>2.7783</v>
+        <v>4.0509</v>
       </c>
     </row>
     <row r="261">
@@ -14399,10 +14399,10 @@
         <v>0.84</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.623</v>
+        <v>-0.5611</v>
       </c>
       <c r="J261" t="n">
-        <v>-13.083</v>
+        <v>-11.7831</v>
       </c>
     </row>
     <row r="262">
@@ -14439,10 +14439,10 @@
         <v>1.45</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1276</v>
+        <v>1.0803</v>
       </c>
       <c r="J262" t="n">
-        <v>24.8072</v>
+        <v>23.7666</v>
       </c>
     </row>
     <row r="263">
@@ -14479,10 +14479,10 @@
         <v>1.3</v>
       </c>
       <c r="I263" t="n">
-        <v>0.8</v>
+        <v>0.7975</v>
       </c>
       <c r="J263" t="n">
-        <v>17.6</v>
+        <v>17.545</v>
       </c>
     </row>
     <row r="264">
@@ -14519,10 +14519,10 @@
         <v>1.18</v>
       </c>
       <c r="I264" t="n">
-        <v>0.4763</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="J264" t="n">
-        <v>10.4786</v>
+        <v>11.3212</v>
       </c>
     </row>
     <row r="265">
@@ -14559,10 +14559,10 @@
         <v>1.06</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1218</v>
+        <v>0.1875</v>
       </c>
       <c r="J265" t="n">
-        <v>2.6796</v>
+        <v>4.125</v>
       </c>
     </row>
     <row r="266">
@@ -14599,10 +14599,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3553</v>
+        <v>-0.2791</v>
       </c>
       <c r="J266" t="n">
-        <v>-7.8166</v>
+        <v>-6.1402</v>
       </c>
     </row>
     <row r="267">
@@ -14639,10 +14639,10 @@
         <v>1.83</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1411</v>
+        <v>1.3081</v>
       </c>
       <c r="J267" t="n">
-        <v>25.1042</v>
+        <v>28.7782</v>
       </c>
     </row>
     <row r="268">
@@ -14679,10 +14679,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5022</v>
+        <v>0.5896</v>
       </c>
       <c r="J268" t="n">
-        <v>11.0484</v>
+        <v>12.9712</v>
       </c>
     </row>
     <row r="269">
@@ -14719,10 +14719,10 @@
         <v>0.63</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.5987</v>
+        <v>-0.3947</v>
       </c>
       <c r="J269" t="n">
-        <v>-13.1714</v>
+        <v>-8.683400000000001</v>
       </c>
     </row>
     <row r="270">
@@ -14759,10 +14759,10 @@
         <v>0.63</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5987</v>
+        <v>-0.3947</v>
       </c>
       <c r="J270" t="n">
-        <v>-13.1714</v>
+        <v>-8.683400000000001</v>
       </c>
     </row>
     <row r="271">
@@ -14799,10 +14799,10 @@
         <v>0.33</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.9472</v>
+        <v>-0.6639</v>
       </c>
       <c r="J271" t="n">
-        <v>-20.8384</v>
+        <v>-14.6058</v>
       </c>
     </row>
     <row r="272">
@@ -14839,10 +14839,10 @@
         <v>2.14</v>
       </c>
       <c r="I272" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J272" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="273">
@@ -14879,10 +14879,10 @@
         <v>1.5</v>
       </c>
       <c r="I273" t="n">
-        <v>1.1082</v>
+        <v>1.1004</v>
       </c>
       <c r="J273" t="n">
-        <v>18.8394</v>
+        <v>18.7068</v>
       </c>
     </row>
     <row r="274">
@@ -14919,10 +14919,10 @@
         <v>1.23</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4772</v>
+        <v>0.5868</v>
       </c>
       <c r="J274" t="n">
-        <v>8.112399999999999</v>
+        <v>9.9756</v>
       </c>
     </row>
     <row r="275">
@@ -14959,10 +14959,10 @@
         <v>1.19</v>
       </c>
       <c r="I275" t="n">
-        <v>0.3828</v>
+        <v>0.4888</v>
       </c>
       <c r="J275" t="n">
-        <v>6.5076</v>
+        <v>8.3096</v>
       </c>
     </row>
     <row r="276">
@@ -14999,10 +14999,10 @@
         <v>1.09</v>
       </c>
       <c r="I276" t="n">
-        <v>0.1279</v>
+        <v>0.2216</v>
       </c>
       <c r="J276" t="n">
-        <v>2.1743</v>
+        <v>3.7672</v>
       </c>
     </row>
     <row r="277">
@@ -15039,10 +15039,10 @@
         <v>1.1</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3459</v>
+        <v>0.3791</v>
       </c>
       <c r="J277" t="n">
-        <v>5.8803</v>
+        <v>6.4447</v>
       </c>
     </row>
     <row r="278">
@@ -15079,10 +15079,10 @@
         <v>0.91</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0617</v>
+        <v>-0.0785</v>
       </c>
       <c r="J278" t="n">
-        <v>-1.0489</v>
+        <v>-1.3345</v>
       </c>
     </row>
     <row r="279">
@@ -15119,10 +15119,10 @@
         <v>0.64</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.5219</v>
+        <v>-0.3535</v>
       </c>
       <c r="J279" t="n">
-        <v>-8.872299999999999</v>
+        <v>-6.0095</v>
       </c>
     </row>
     <row r="280">
@@ -15159,10 +15159,10 @@
         <v>0.49</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.7275</v>
+        <v>-0.4937</v>
       </c>
       <c r="J280" t="n">
-        <v>-12.3675</v>
+        <v>-8.392899999999999</v>
       </c>
     </row>
     <row r="281">
@@ -15199,10 +15199,10 @@
         <v>0.41</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.8274</v>
+        <v>-0.5683</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.0658</v>
+        <v>-9.661099999999999</v>
       </c>
     </row>
     <row r="282">
@@ -15239,10 +15239,10 @@
         <v>2.16</v>
       </c>
       <c r="I282" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J282" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="283">
@@ -15279,10 +15279,10 @@
         <v>1.76</v>
       </c>
       <c r="I283" t="n">
-        <v>1.604</v>
+        <v>1.404</v>
       </c>
       <c r="J283" t="n">
-        <v>27.268</v>
+        <v>23.868</v>
       </c>
     </row>
     <row r="284">
@@ -15319,10 +15319,10 @@
         <v>1.21</v>
       </c>
       <c r="I284" t="n">
-        <v>0.4265</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="J284" t="n">
-        <v>7.2505</v>
+        <v>9.108599999999999</v>
       </c>
     </row>
     <row r="285">
@@ -15359,10 +15359,10 @@
         <v>1.18</v>
       </c>
       <c r="I285" t="n">
-        <v>0.3551</v>
+        <v>0.4611</v>
       </c>
       <c r="J285" t="n">
-        <v>6.0367</v>
+        <v>7.8387</v>
       </c>
     </row>
     <row r="286">
@@ -15399,10 +15399,10 @@
         <v>0.9</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5325</v>
+        <v>-0.4565</v>
       </c>
       <c r="J286" t="n">
-        <v>-9.0525</v>
+        <v>-7.7605</v>
       </c>
     </row>
     <row r="287">
@@ -15439,10 +15439,10 @@
         <v>1.04</v>
       </c>
       <c r="I287" t="n">
-        <v>0.1873</v>
+        <v>0.1705</v>
       </c>
       <c r="J287" t="n">
-        <v>3.1841</v>
+        <v>2.8985</v>
       </c>
     </row>
     <row r="288">
@@ -15479,10 +15479,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0585</v>
+        <v>-0.0677</v>
       </c>
       <c r="J288" t="n">
-        <v>-0.9945000000000001</v>
+        <v>-1.1509</v>
       </c>
     </row>
     <row r="289">
@@ -15519,10 +15519,10 @@
         <v>0.82</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2851</v>
+        <v>-0.1985</v>
       </c>
       <c r="J289" t="n">
-        <v>-4.8467</v>
+        <v>-3.3745</v>
       </c>
     </row>
     <row r="290">
@@ -15559,10 +15559,10 @@
         <v>0.74</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4194</v>
+        <v>-0.2757</v>
       </c>
       <c r="J290" t="n">
-        <v>-7.1298</v>
+        <v>-4.6869</v>
       </c>
     </row>
     <row r="291">
@@ -15599,10 +15599,10 @@
         <v>0.58</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6393</v>
+        <v>-0.4267</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.8681</v>
+        <v>-7.2539</v>
       </c>
     </row>
     <row r="292">
@@ -15639,10 +15639,10 @@
         <v>1.93</v>
       </c>
       <c r="I292" t="n">
-        <v>1.87</v>
+        <v>1.5835</v>
       </c>
       <c r="J292" t="n">
-        <v>29.92</v>
+        <v>25.336</v>
       </c>
     </row>
     <row r="293">
@@ -15679,10 +15679,10 @@
         <v>1.62</v>
       </c>
       <c r="I293" t="n">
-        <v>1.3138</v>
+        <v>1.2318</v>
       </c>
       <c r="J293" t="n">
-        <v>21.0208</v>
+        <v>19.7088</v>
       </c>
     </row>
     <row r="294">
@@ -15719,10 +15719,10 @@
         <v>1.47</v>
       </c>
       <c r="I294" t="n">
-        <v>0.9769</v>
+        <v>1.0584</v>
       </c>
       <c r="J294" t="n">
-        <v>15.6304</v>
+        <v>16.9344</v>
       </c>
     </row>
     <row r="295">
@@ -15759,10 +15759,10 @@
         <v>1.37</v>
       </c>
       <c r="I295" t="n">
-        <v>0.7608</v>
+        <v>0.8899</v>
       </c>
       <c r="J295" t="n">
-        <v>12.1728</v>
+        <v>14.2384</v>
       </c>
     </row>
     <row r="296">
@@ -15799,10 +15799,10 @@
         <v>1.15</v>
       </c>
       <c r="I296" t="n">
-        <v>0.2643</v>
+        <v>0.3704</v>
       </c>
       <c r="J296" t="n">
-        <v>4.2288</v>
+        <v>5.9264</v>
       </c>
     </row>
     <row r="297">
@@ -15879,10 +15879,10 @@
         <v>0.88</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1496</v>
+        <v>-0.1313</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.3936</v>
+        <v>-2.1008</v>
       </c>
     </row>
     <row r="299">
@@ -15919,10 +15919,10 @@
         <v>0.87</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1668</v>
+        <v>-0.1423</v>
       </c>
       <c r="J299" t="n">
-        <v>-2.6688</v>
+        <v>-2.2768</v>
       </c>
     </row>
     <row r="300">
@@ -15959,10 +15959,10 @@
         <v>0.67</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.508</v>
+        <v>-0.3369</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.128</v>
+        <v>-5.3904</v>
       </c>
     </row>
     <row r="301">
@@ -15999,10 +15999,10 @@
         <v>0.6</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.604</v>
+        <v>-0.4027</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.664</v>
+        <v>-6.4432</v>
       </c>
     </row>
     <row r="302">
@@ -16039,10 +16039,10 @@
         <v>1.99</v>
       </c>
       <c r="I302" t="n">
-        <v>2.058</v>
+        <v>1.7926</v>
       </c>
       <c r="J302" t="n">
-        <v>49.392</v>
+        <v>43.0224</v>
       </c>
     </row>
     <row r="303">
@@ -16079,10 +16079,10 @@
         <v>1.43</v>
       </c>
       <c r="I303" t="n">
-        <v>1.1341</v>
+        <v>1.0782</v>
       </c>
       <c r="J303" t="n">
-        <v>27.2184</v>
+        <v>25.8768</v>
       </c>
     </row>
     <row r="304">
@@ -16119,10 +16119,10 @@
         <v>0.95</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2878</v>
+        <v>-0.2226</v>
       </c>
       <c r="J304" t="n">
-        <v>-6.9072</v>
+        <v>-5.3424</v>
       </c>
     </row>
     <row r="305">
@@ -16159,10 +16159,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I305" t="n">
-        <v>-1.2264</v>
+        <v>-1.2322</v>
       </c>
       <c r="J305" t="n">
-        <v>-29.4336</v>
+        <v>-29.5728</v>
       </c>
     </row>
     <row r="306">
@@ -16199,10 +16199,10 @@
         <v>0.54</v>
       </c>
       <c r="I306" t="n">
-        <v>-1.2665</v>
+        <v>-1.2785</v>
       </c>
       <c r="J306" t="n">
-        <v>-30.396</v>
+        <v>-30.684</v>
       </c>
     </row>
     <row r="307">
@@ -16239,10 +16239,10 @@
         <v>1.48</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7211</v>
+        <v>0.8934</v>
       </c>
       <c r="J307" t="n">
-        <v>17.3064</v>
+        <v>21.4416</v>
       </c>
     </row>
     <row r="308">
@@ -16279,10 +16279,10 @@
         <v>1.19</v>
       </c>
       <c r="I308" t="n">
-        <v>0.3481</v>
+        <v>0.4033</v>
       </c>
       <c r="J308" t="n">
-        <v>8.3544</v>
+        <v>9.6792</v>
       </c>
     </row>
     <row r="309">
@@ -16319,10 +16319,10 @@
         <v>0.99</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0675</v>
+        <v>-0.0259</v>
       </c>
       <c r="J309" t="n">
-        <v>-1.62</v>
+        <v>-0.6216</v>
       </c>
     </row>
     <row r="310">
@@ -16359,10 +16359,10 @@
         <v>0.93</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1932</v>
+        <v>-0.1064</v>
       </c>
       <c r="J310" t="n">
-        <v>-4.6368</v>
+        <v>-2.5536</v>
       </c>
     </row>
     <row r="311">
@@ -16399,10 +16399,10 @@
         <v>0.71</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5175</v>
+        <v>-0.3332</v>
       </c>
       <c r="J311" t="n">
-        <v>-12.42</v>
+        <v>-7.9968</v>
       </c>
     </row>
     <row r="312">
@@ -16439,10 +16439,10 @@
         <v>1.8</v>
       </c>
       <c r="I312" t="n">
-        <v>1.681</v>
+        <v>1.4529</v>
       </c>
       <c r="J312" t="n">
-        <v>30.258</v>
+        <v>26.1522</v>
       </c>
     </row>
     <row r="313">
@@ -16479,10 +16479,10 @@
         <v>1.42</v>
       </c>
       <c r="I313" t="n">
-        <v>0.9152</v>
+        <v>0.9969</v>
       </c>
       <c r="J313" t="n">
-        <v>16.4736</v>
+        <v>17.9442</v>
       </c>
     </row>
     <row r="314">
@@ -16519,10 +16519,10 @@
         <v>1.4</v>
       </c>
       <c r="I314" t="n">
-        <v>0.8658</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="J314" t="n">
-        <v>15.5844</v>
+        <v>17.3376</v>
       </c>
     </row>
     <row r="315">
@@ -16559,10 +16559,10 @@
         <v>1.26</v>
       </c>
       <c r="I315" t="n">
-        <v>0.5471</v>
+        <v>0.6584</v>
       </c>
       <c r="J315" t="n">
-        <v>9.847799999999999</v>
+        <v>11.8512</v>
       </c>
     </row>
     <row r="316">
@@ -16599,10 +16599,10 @@
         <v>1.26</v>
       </c>
       <c r="I316" t="n">
-        <v>0.5471</v>
+        <v>0.6584</v>
       </c>
       <c r="J316" t="n">
-        <v>9.847799999999999</v>
+        <v>11.8512</v>
       </c>
     </row>
     <row r="317">
@@ -16639,10 +16639,10 @@
         <v>1.46</v>
       </c>
       <c r="I317" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.9597</v>
       </c>
       <c r="J317" t="n">
-        <v>13.7808</v>
+        <v>17.2746</v>
       </c>
     </row>
     <row r="318">
@@ -16679,10 +16679,10 @@
         <v>0.88</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1936</v>
+        <v>-0.1428</v>
       </c>
       <c r="J318" t="n">
-        <v>-3.4848</v>
+        <v>-2.5704</v>
       </c>
     </row>
     <row r="319">
@@ -16719,10 +16719,10 @@
         <v>0.85</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2592</v>
+        <v>-0.1729</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.6656</v>
+        <v>-3.1122</v>
       </c>
     </row>
     <row r="320">
@@ -16759,10 +16759,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5048</v>
+        <v>-0.3295</v>
       </c>
       <c r="J320" t="n">
-        <v>-9.086399999999999</v>
+        <v>-5.931</v>
       </c>
     </row>
     <row r="321">
@@ -16799,10 +16799,10 @@
         <v>0.46</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.7936</v>
+        <v>-0.5421</v>
       </c>
       <c r="J321" t="n">
-        <v>-14.2848</v>
+        <v>-9.7578</v>
       </c>
     </row>
     <row r="322">
@@ -16839,10 +16839,10 @@
         <v>1.51</v>
       </c>
       <c r="I322" t="n">
-        <v>1.2693</v>
+        <v>1.1687</v>
       </c>
       <c r="J322" t="n">
-        <v>30.4632</v>
+        <v>28.0488</v>
       </c>
     </row>
     <row r="323">
@@ -16879,10 +16879,10 @@
         <v>1.43</v>
       </c>
       <c r="I323" t="n">
-        <v>1.1067</v>
+        <v>1.0638</v>
       </c>
       <c r="J323" t="n">
-        <v>26.5608</v>
+        <v>25.5312</v>
       </c>
     </row>
     <row r="324">
@@ -16919,10 +16919,10 @@
         <v>1.05</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1085</v>
+        <v>0.1656</v>
       </c>
       <c r="J324" t="n">
-        <v>2.604</v>
+        <v>3.9744</v>
       </c>
     </row>
     <row r="325">
@@ -16959,10 +16959,10 @@
         <v>0.91</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.4308</v>
+        <v>-0.3604</v>
       </c>
       <c r="J325" t="n">
-        <v>-10.3392</v>
+        <v>-8.6496</v>
       </c>
     </row>
     <row r="326">
@@ -16999,10 +16999,10 @@
         <v>0.83</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.6428</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="J326" t="n">
-        <v>-15.4272</v>
+        <v>-13.9968</v>
       </c>
     </row>
     <row r="327">
@@ -17039,10 +17039,10 @@
         <v>1.11</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2802</v>
+        <v>0.296</v>
       </c>
       <c r="J327" t="n">
-        <v>6.7248</v>
+        <v>7.104</v>
       </c>
     </row>
     <row r="328">
@@ -17079,10 +17079,10 @@
         <v>1.11</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2802</v>
+        <v>0.296</v>
       </c>
       <c r="J328" t="n">
-        <v>6.7248</v>
+        <v>7.104</v>
       </c>
     </row>
     <row r="329">
@@ -17119,10 +17119,10 @@
         <v>1.01</v>
       </c>
       <c r="I329" t="n">
-        <v>0.0853</v>
+        <v>0.0583</v>
       </c>
       <c r="J329" t="n">
-        <v>2.0472</v>
+        <v>1.3992</v>
       </c>
     </row>
     <row r="330">
@@ -17159,10 +17159,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3424</v>
+        <v>-0.2176</v>
       </c>
       <c r="J330" t="n">
-        <v>-8.217599999999999</v>
+        <v>-5.2224</v>
       </c>
     </row>
     <row r="331">
@@ -17199,10 +17199,10 @@
         <v>0.49</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.7637</v>
+        <v>-0.5191</v>
       </c>
       <c r="J331" t="n">
-        <v>-18.3288</v>
+        <v>-12.4584</v>
       </c>
     </row>
     <row r="332">
@@ -17239,10 +17239,10 @@
         <v>1.69</v>
       </c>
       <c r="I332" t="n">
-        <v>1.491</v>
+        <v>1.3291</v>
       </c>
       <c r="J332" t="n">
-        <v>26.838</v>
+        <v>23.9238</v>
       </c>
     </row>
     <row r="333">
@@ -17279,10 +17279,10 @@
         <v>1.54</v>
       </c>
       <c r="I333" t="n">
-        <v>1.2023</v>
+        <v>1.1512</v>
       </c>
       <c r="J333" t="n">
-        <v>21.6414</v>
+        <v>20.7216</v>
       </c>
     </row>
     <row r="334">
@@ -17319,10 +17319,10 @@
         <v>1.48</v>
       </c>
       <c r="I334" t="n">
-        <v>1.0775</v>
+        <v>1.0789</v>
       </c>
       <c r="J334" t="n">
-        <v>19.395</v>
+        <v>19.4202</v>
       </c>
     </row>
     <row r="335">
@@ -17359,10 +17359,10 @@
         <v>1.27</v>
       </c>
       <c r="I335" t="n">
-        <v>0.5777</v>
+        <v>0.6858</v>
       </c>
       <c r="J335" t="n">
-        <v>10.3986</v>
+        <v>12.3444</v>
       </c>
     </row>
     <row r="336">
@@ -17399,10 +17399,10 @@
         <v>1.06</v>
       </c>
       <c r="I336" t="n">
-        <v>0.0473</v>
+        <v>0.1361</v>
       </c>
       <c r="J336" t="n">
-        <v>0.8514</v>
+        <v>2.4498</v>
       </c>
     </row>
     <row r="337">
@@ -17439,10 +17439,10 @@
         <v>1.1</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3025</v>
+        <v>0.3179</v>
       </c>
       <c r="J337" t="n">
-        <v>5.445</v>
+        <v>5.7222</v>
       </c>
     </row>
     <row r="338">
@@ -17479,10 +17479,10 @@
         <v>0.9</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1249</v>
+        <v>-0.1127</v>
       </c>
       <c r="J338" t="n">
-        <v>-2.2482</v>
+        <v>-2.0286</v>
       </c>
     </row>
     <row r="339">
@@ -17519,10 +17519,10 @@
         <v>0.68</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.5011</v>
+        <v>-0.3306</v>
       </c>
       <c r="J339" t="n">
-        <v>-9.0198</v>
+        <v>-5.9508</v>
       </c>
     </row>
     <row r="340">
@@ -17559,10 +17559,10 @@
         <v>0.68</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.5011</v>
+        <v>-0.3306</v>
       </c>
       <c r="J340" t="n">
-        <v>-9.0198</v>
+        <v>-5.9508</v>
       </c>
     </row>
     <row r="341">
@@ -17599,10 +17599,10 @@
         <v>0.68</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5011</v>
+        <v>-0.3306</v>
       </c>
       <c r="J341" t="n">
-        <v>-9.0198</v>
+        <v>-5.9508</v>
       </c>
     </row>
     <row r="342">
@@ -17639,10 +17639,10 @@
         <v>1.38</v>
       </c>
       <c r="I342" t="n">
-        <v>0.6095</v>
+        <v>0.5658</v>
       </c>
       <c r="J342" t="n">
-        <v>14.628</v>
+        <v>13.5792</v>
       </c>
     </row>
     <row r="343">
@@ -17679,10 +17679,10 @@
         <v>1.06</v>
       </c>
       <c r="I343" t="n">
-        <v>0.1384</v>
+        <v>0.1186</v>
       </c>
       <c r="J343" t="n">
-        <v>3.3216</v>
+        <v>2.8464</v>
       </c>
     </row>
     <row r="344">
@@ -17719,10 +17719,10 @@
         <v>1.01</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0129</v>
+        <v>0.0255</v>
       </c>
       <c r="J344" t="n">
-        <v>0.3096</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="345">
@@ -17759,10 +17759,10 @@
         <v>0.89</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.2551</v>
+        <v>-0.1493</v>
       </c>
       <c r="J345" t="n">
-        <v>-6.1224</v>
+        <v>-3.5832</v>
       </c>
     </row>
     <row r="346">
@@ -17799,10 +17799,10 @@
         <v>0.84</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3332</v>
+        <v>-0.2025</v>
       </c>
       <c r="J346" t="n">
-        <v>-7.9968</v>
+        <v>-4.86</v>
       </c>
     </row>
     <row r="347">
@@ -17839,10 +17839,10 @@
         <v>1.78</v>
       </c>
       <c r="I347" t="n">
-        <v>1.0401</v>
+        <v>0.958</v>
       </c>
       <c r="J347" t="n">
-        <v>24.9624</v>
+        <v>22.992</v>
       </c>
     </row>
     <row r="348">
@@ -17879,10 +17879,10 @@
         <v>1.17</v>
       </c>
       <c r="I348" t="n">
-        <v>0.3107</v>
+        <v>0.2579</v>
       </c>
       <c r="J348" t="n">
-        <v>7.4568</v>
+        <v>6.1896</v>
       </c>
     </row>
     <row r="349">
@@ -17919,10 +17919,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.1804</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="J349" t="n">
-        <v>-4.3296</v>
+        <v>-2.3184</v>
       </c>
     </row>
     <row r="350">
@@ -17959,10 +17959,10 @@
         <v>0.82</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3718</v>
+        <v>-0.2278</v>
       </c>
       <c r="J350" t="n">
-        <v>-8.9232</v>
+        <v>-5.4672</v>
       </c>
     </row>
     <row r="351">
@@ -17999,10 +17999,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5461</v>
+        <v>-0.3541</v>
       </c>
       <c r="J351" t="n">
-        <v>-13.1064</v>
+        <v>-8.4984</v>
       </c>
     </row>
     <row r="352">
@@ -18039,10 +18039,10 @@
         <v>1.78</v>
       </c>
       <c r="I352" t="n">
-        <v>1.7226</v>
+        <v>1.474</v>
       </c>
       <c r="J352" t="n">
-        <v>34.452</v>
+        <v>29.48</v>
       </c>
     </row>
     <row r="353">
@@ -18079,10 +18079,10 @@
         <v>1.46</v>
       </c>
       <c r="I353" t="n">
-        <v>1.1152</v>
+        <v>1.0789</v>
       </c>
       <c r="J353" t="n">
-        <v>22.304</v>
+        <v>21.578</v>
       </c>
     </row>
     <row r="354">
@@ -18119,10 +18119,10 @@
         <v>1.2</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4815</v>
+        <v>0.5515</v>
       </c>
       <c r="J354" t="n">
-        <v>9.630000000000001</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="355">
@@ -18159,10 +18159,10 @@
         <v>0.92</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.4348</v>
+        <v>-0.3571</v>
       </c>
       <c r="J355" t="n">
-        <v>-8.696</v>
+        <v>-7.142</v>
       </c>
     </row>
     <row r="356">
@@ -18199,10 +18199,10 @@
         <v>0.9</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.4907</v>
+        <v>-0.4161</v>
       </c>
       <c r="J356" t="n">
-        <v>-9.814</v>
+        <v>-8.321999999999999</v>
       </c>
     </row>
     <row r="357">
@@ -18239,10 +18239,10 @@
         <v>1.05</v>
       </c>
       <c r="I357" t="n">
-        <v>0.1804</v>
+        <v>0.1693</v>
       </c>
       <c r="J357" t="n">
-        <v>3.608</v>
+        <v>3.386</v>
       </c>
     </row>
     <row r="358">
@@ -18279,10 +18279,10 @@
         <v>0.93</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.1087</v>
+        <v>-0.09</v>
       </c>
       <c r="J358" t="n">
-        <v>-2.174</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="359">
@@ -18319,10 +18319,10 @@
         <v>0.87</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.235</v>
+        <v>-0.1547</v>
       </c>
       <c r="J359" t="n">
-        <v>-4.7</v>
+        <v>-3.094</v>
       </c>
     </row>
     <row r="360">
@@ -18359,10 +18359,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.3367</v>
+        <v>-0.2157</v>
       </c>
       <c r="J360" t="n">
-        <v>-6.734</v>
+        <v>-4.314</v>
       </c>
     </row>
     <row r="361">
@@ -18399,10 +18399,10 @@
         <v>0.79</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3676</v>
+        <v>-0.2355</v>
       </c>
       <c r="J361" t="n">
-        <v>-7.352</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="362">
@@ -18439,10 +18439,10 @@
         <v>1.49</v>
       </c>
       <c r="I362" t="n">
-        <v>1.1435</v>
+        <v>1.104</v>
       </c>
       <c r="J362" t="n">
-        <v>20.583</v>
+        <v>19.872</v>
       </c>
     </row>
     <row r="363">
@@ -18479,10 +18479,10 @@
         <v>1.47</v>
       </c>
       <c r="I363" t="n">
-        <v>1.1022</v>
+        <v>1.0791</v>
       </c>
       <c r="J363" t="n">
-        <v>19.8396</v>
+        <v>19.4238</v>
       </c>
     </row>
     <row r="364">
@@ -18519,10 +18519,10 @@
         <v>1.22</v>
       </c>
       <c r="I364" t="n">
-        <v>0.4965</v>
+        <v>0.586</v>
       </c>
       <c r="J364" t="n">
-        <v>8.936999999999999</v>
+        <v>10.548</v>
       </c>
     </row>
     <row r="365">
@@ -18559,10 +18559,10 @@
         <v>1.22</v>
       </c>
       <c r="I365" t="n">
-        <v>0.4965</v>
+        <v>0.586</v>
       </c>
       <c r="J365" t="n">
-        <v>8.936999999999999</v>
+        <v>10.548</v>
       </c>
     </row>
     <row r="366">
@@ -18599,10 +18599,10 @@
         <v>1.2</v>
       </c>
       <c r="I366" t="n">
-        <v>0.4471</v>
+        <v>0.5373</v>
       </c>
       <c r="J366" t="n">
-        <v>8.047800000000001</v>
+        <v>9.6714</v>
       </c>
     </row>
     <row r="367">
@@ -18639,10 +18639,10 @@
         <v>1.21</v>
       </c>
       <c r="I367" t="n">
-        <v>0.4271</v>
+        <v>0.4879</v>
       </c>
       <c r="J367" t="n">
-        <v>7.6878</v>
+        <v>8.7822</v>
       </c>
     </row>
     <row r="368">
@@ -18679,10 +18679,10 @@
         <v>1.21</v>
       </c>
       <c r="I368" t="n">
-        <v>0.4271</v>
+        <v>0.4879</v>
       </c>
       <c r="J368" t="n">
-        <v>7.6878</v>
+        <v>8.7822</v>
       </c>
     </row>
     <row r="369">
@@ -18719,10 +18719,10 @@
         <v>0.97</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.039</v>
+        <v>-0.0429</v>
       </c>
       <c r="J369" t="n">
-        <v>-0.702</v>
+        <v>-0.7722</v>
       </c>
     </row>
     <row r="370">
@@ -18759,10 +18759,10 @@
         <v>0.79</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.3766</v>
+        <v>-0.2391</v>
       </c>
       <c r="J370" t="n">
-        <v>-6.7788</v>
+        <v>-4.3038</v>
       </c>
     </row>
     <row r="371">
@@ -18799,10 +18799,10 @@
         <v>0.41</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.857</v>
+        <v>-0.5919</v>
       </c>
       <c r="J371" t="n">
-        <v>-15.426</v>
+        <v>-10.6542</v>
       </c>
     </row>
     <row r="372">
@@ -18839,10 +18839,10 @@
         <v>1.51</v>
       </c>
       <c r="I372" t="n">
-        <v>1.2795</v>
+        <v>1.1746</v>
       </c>
       <c r="J372" t="n">
-        <v>37.1055</v>
+        <v>34.0634</v>
       </c>
     </row>
     <row r="373">
@@ -18879,10 +18879,10 @@
         <v>1.45</v>
       </c>
       <c r="I373" t="n">
-        <v>1.1584</v>
+        <v>1.0957</v>
       </c>
       <c r="J373" t="n">
-        <v>33.5936</v>
+        <v>31.7753</v>
       </c>
     </row>
     <row r="374">
@@ -18919,10 +18919,10 @@
         <v>1.2</v>
       </c>
       <c r="I374" t="n">
-        <v>0.59</v>
+        <v>0.5755</v>
       </c>
       <c r="J374" t="n">
-        <v>17.11</v>
+        <v>16.6895</v>
       </c>
     </row>
     <row r="375">
@@ -18959,10 +18959,10 @@
         <v>0.77</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.7814</v>
+        <v>-0.7336</v>
       </c>
       <c r="J375" t="n">
-        <v>-22.6606</v>
+        <v>-21.2744</v>
       </c>
     </row>
     <row r="376">
@@ -18999,10 +18999,10 @@
         <v>0.7</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.9394</v>
+        <v>-0.9074</v>
       </c>
       <c r="J376" t="n">
-        <v>-27.2426</v>
+        <v>-26.3146</v>
       </c>
     </row>
     <row r="377">
@@ -19039,10 +19039,10 @@
         <v>1.48</v>
       </c>
       <c r="I377" t="n">
-        <v>0.7308</v>
+        <v>0.9061</v>
       </c>
       <c r="J377" t="n">
-        <v>21.1932</v>
+        <v>26.2769</v>
       </c>
     </row>
     <row r="378">
@@ -19079,10 +19079,10 @@
         <v>1.26</v>
       </c>
       <c r="I378" t="n">
-        <v>0.4571</v>
+        <v>0.5367</v>
       </c>
       <c r="J378" t="n">
-        <v>13.2559</v>
+        <v>15.5643</v>
       </c>
     </row>
     <row r="379">
@@ -19119,10 +19119,10 @@
         <v>0.96</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.1263</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="J379" t="n">
-        <v>-3.6627</v>
+        <v>-1.9198</v>
       </c>
     </row>
     <row r="380">
@@ -19159,10 +19159,10 @@
         <v>0.8</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.3903</v>
+        <v>-0.2425</v>
       </c>
       <c r="J380" t="n">
-        <v>-11.3187</v>
+        <v>-7.0325</v>
       </c>
     </row>
     <row r="381">
@@ -19199,10 +19199,10 @@
         <v>0.65</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.5888</v>
+        <v>-0.3863</v>
       </c>
       <c r="J381" t="n">
-        <v>-17.0752</v>
+        <v>-11.2027</v>
       </c>
     </row>
     <row r="382">
@@ -19239,10 +19239,10 @@
         <v>1.75</v>
       </c>
       <c r="I382" t="n">
-        <v>1.7138</v>
+        <v>1.4679</v>
       </c>
       <c r="J382" t="n">
-        <v>41.1312</v>
+        <v>35.2296</v>
       </c>
     </row>
     <row r="383">
@@ -19279,10 +19279,10 @@
         <v>1.31</v>
       </c>
       <c r="I383" t="n">
-        <v>0.8378</v>
+        <v>0.8288</v>
       </c>
       <c r="J383" t="n">
-        <v>20.1072</v>
+        <v>19.8912</v>
       </c>
     </row>
     <row r="384">
@@ -19319,10 +19319,10 @@
         <v>1.14</v>
       </c>
       <c r="I384" t="n">
-        <v>0.3777</v>
+        <v>0.4191</v>
       </c>
       <c r="J384" t="n">
-        <v>9.0648</v>
+        <v>10.0584</v>
       </c>
     </row>
     <row r="385">
@@ -19359,10 +19359,10 @@
         <v>1.12</v>
       </c>
       <c r="I385" t="n">
-        <v>0.3177</v>
+        <v>0.3665</v>
       </c>
       <c r="J385" t="n">
-        <v>7.6248</v>
+        <v>8.795999999999999</v>
       </c>
     </row>
     <row r="386">
@@ -19399,10 +19399,10 @@
         <v>0.48</v>
       </c>
       <c r="I386" t="n">
-        <v>-1.3939</v>
+        <v>-1.4279</v>
       </c>
       <c r="J386" t="n">
-        <v>-33.4536</v>
+        <v>-34.2696</v>
       </c>
     </row>
     <row r="387">
@@ -19439,10 +19439,10 @@
         <v>1.34</v>
       </c>
       <c r="I387" t="n">
-        <v>0.5763</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J387" t="n">
-        <v>13.8312</v>
+        <v>16.608</v>
       </c>
     </row>
     <row r="388">
@@ -19479,10 +19479,10 @@
         <v>1.1</v>
       </c>
       <c r="I388" t="n">
-        <v>0.2333</v>
+        <v>0.25</v>
       </c>
       <c r="J388" t="n">
-        <v>5.5992</v>
+        <v>6</v>
       </c>
     </row>
     <row r="389">
@@ -19519,10 +19519,10 @@
         <v>0.91</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.2057</v>
+        <v>-0.1215</v>
       </c>
       <c r="J389" t="n">
-        <v>-4.9368</v>
+        <v>-2.916</v>
       </c>
     </row>
     <row r="390">
@@ -19559,10 +19559,10 @@
         <v>0.82</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.3509</v>
+        <v>-0.2172</v>
       </c>
       <c r="J390" t="n">
-        <v>-8.4216</v>
+        <v>-5.2128</v>
       </c>
     </row>
     <row r="391">
@@ -19599,10 +19599,10 @@
         <v>0.76</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4369</v>
+        <v>-0.2769</v>
       </c>
       <c r="J391" t="n">
-        <v>-10.4856</v>
+        <v>-6.6456</v>
       </c>
     </row>
     <row r="392">
@@ -19639,10 +19639,10 @@
         <v>1.93</v>
       </c>
       <c r="I392" t="n">
-        <v>1.9895</v>
+        <v>1.6988</v>
       </c>
       <c r="J392" t="n">
-        <v>47.748</v>
+        <v>40.7712</v>
       </c>
     </row>
     <row r="393">
@@ -19679,10 +19679,10 @@
         <v>1.36</v>
       </c>
       <c r="I393" t="n">
-        <v>0.9627</v>
+        <v>0.9502</v>
       </c>
       <c r="J393" t="n">
-        <v>23.1048</v>
+        <v>22.8048</v>
       </c>
     </row>
     <row r="394">
@@ -19719,10 +19719,10 @@
         <v>1.01</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.0379</v>
+        <v>0.0226</v>
       </c>
       <c r="J394" t="n">
-        <v>-0.9096</v>
+        <v>0.5424</v>
       </c>
     </row>
     <row r="395">
@@ -19759,10 +19759,10 @@
         <v>0.83</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.6398</v>
+        <v>-0.5806</v>
       </c>
       <c r="J395" t="n">
-        <v>-15.3552</v>
+        <v>-13.9344</v>
       </c>
     </row>
     <row r="396">
@@ -19799,10 +19799,10 @@
         <v>0.55</v>
       </c>
       <c r="I396" t="n">
-        <v>-1.2537</v>
+        <v>-1.2642</v>
       </c>
       <c r="J396" t="n">
-        <v>-30.0888</v>
+        <v>-30.3408</v>
       </c>
     </row>
     <row r="397">
@@ -19839,10 +19839,10 @@
         <v>1.12</v>
       </c>
       <c r="I397" t="n">
-        <v>0.2874</v>
+        <v>0.3079</v>
       </c>
       <c r="J397" t="n">
-        <v>6.8976</v>
+        <v>7.3896</v>
       </c>
     </row>
     <row r="398">
@@ -19879,10 +19879,10 @@
         <v>0.99</v>
       </c>
       <c r="I398" t="n">
-        <v>0.0047</v>
+        <v>-0.0142</v>
       </c>
       <c r="J398" t="n">
-        <v>0.1128</v>
+        <v>-0.3408</v>
       </c>
     </row>
     <row r="399">
@@ -19919,10 +19919,10 @@
         <v>0.95</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.0893</v>
+        <v>-0.0702</v>
       </c>
       <c r="J399" t="n">
-        <v>-2.1432</v>
+        <v>-1.6848</v>
       </c>
     </row>
     <row r="400">
@@ -19959,10 +19959,10 @@
         <v>0.95</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.0893</v>
+        <v>-0.0702</v>
       </c>
       <c r="J400" t="n">
-        <v>-2.1432</v>
+        <v>-1.6848</v>
       </c>
     </row>
     <row r="401">
@@ -19999,10 +19999,10 @@
         <v>0.64</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.5846</v>
+        <v>-0.3845</v>
       </c>
       <c r="J401" t="n">
-        <v>-14.0304</v>
+        <v>-9.228</v>
       </c>
     </row>
     <row r="402">
@@ -20039,10 +20039,10 @@
         <v>1.28</v>
       </c>
       <c r="I402" t="n">
-        <v>0.7851</v>
+        <v>0.7684</v>
       </c>
       <c r="J402" t="n">
-        <v>22.7679</v>
+        <v>22.2836</v>
       </c>
     </row>
     <row r="403">
@@ -20079,10 +20079,10 @@
         <v>1.25</v>
       </c>
       <c r="I403" t="n">
-        <v>0.7134</v>
+        <v>0.6966</v>
       </c>
       <c r="J403" t="n">
-        <v>20.6886</v>
+        <v>20.2014</v>
       </c>
     </row>
     <row r="404">
@@ -20119,10 +20119,10 @@
         <v>1.13</v>
       </c>
       <c r="I404" t="n">
-        <v>0.3798</v>
+        <v>0.3979</v>
       </c>
       <c r="J404" t="n">
-        <v>11.0142</v>
+        <v>11.5391</v>
       </c>
     </row>
     <row r="405">
@@ -20159,10 +20159,10 @@
         <v>1.07</v>
       </c>
       <c r="I405" t="n">
-        <v>0.1831</v>
+        <v>0.2316</v>
       </c>
       <c r="J405" t="n">
-        <v>5.3099</v>
+        <v>6.7164</v>
       </c>
     </row>
     <row r="406">
@@ -20199,10 +20199,10 @@
         <v>0.92</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.396</v>
+        <v>-0.3263</v>
       </c>
       <c r="J406" t="n">
-        <v>-11.484</v>
+        <v>-9.4627</v>
       </c>
     </row>
     <row r="407">
@@ -20239,10 +20239,10 @@
         <v>1.41</v>
       </c>
       <c r="I407" t="n">
-        <v>0.6593</v>
+        <v>0.8064</v>
       </c>
       <c r="J407" t="n">
-        <v>19.1197</v>
+        <v>23.3856</v>
       </c>
     </row>
     <row r="408">
@@ -20279,10 +20279,10 @@
         <v>1.14</v>
       </c>
       <c r="I408" t="n">
-        <v>0.2949</v>
+        <v>0.3268</v>
       </c>
       <c r="J408" t="n">
-        <v>8.552099999999999</v>
+        <v>9.4772</v>
       </c>
     </row>
     <row r="409">
@@ -20319,10 +20319,10 @@
         <v>1.03</v>
       </c>
       <c r="I409" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0925</v>
       </c>
       <c r="J409" t="n">
-        <v>2.7347</v>
+        <v>2.6825</v>
       </c>
     </row>
     <row r="410">
@@ -20359,10 +20359,10 @@
         <v>0.7</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.5195</v>
+        <v>-0.3358</v>
       </c>
       <c r="J410" t="n">
-        <v>-15.0655</v>
+        <v>-9.738200000000001</v>
       </c>
     </row>
     <row r="411">
@@ -20399,10 +20399,10 @@
         <v>0.7</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.5195</v>
+        <v>-0.3358</v>
       </c>
       <c r="J411" t="n">
-        <v>-15.0655</v>
+        <v>-9.738200000000001</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7732/event_7732_evp_summary.xlsx
+++ b/database/event/7732/event_7732_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.8399</v>
+        <v>7.8063</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5263</v>
+        <v>4.5069</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9013</v>
+        <v>2.9294</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8399</v>
+        <v>7.8063</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7186</v>
+        <v>1.6155</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1213</v>
+        <v>6.1908</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7186</v>
+        <v>1.6155</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7186</v>
+        <v>1.6155</v>
       </c>
       <c r="J2" t="n">
-        <v>6.1213</v>
+        <v>6.6595</v>
       </c>
       <c r="K2" t="n">
         <v>53</v>
@@ -529,7 +529,7 @@
         <v>174</v>
       </c>
       <c r="M2" t="n">
-        <v>7.8399</v>
+        <v>8.275</v>
       </c>
       <c r="N2" t="n">
         <v>227</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.2237</v>
+        <v>7.4711</v>
       </c>
       <c r="C3" t="n">
-        <v>4.1705</v>
+        <v>4.3134</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6231</v>
+        <v>2.7768</v>
       </c>
       <c r="E3" t="n">
-        <v>7.2237</v>
+        <v>7.4711</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7558</v>
+        <v>2.4769</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4679</v>
+        <v>4.9942</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7558</v>
+        <v>2.6963</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7558</v>
+        <v>2.6963</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4679</v>
+        <v>4.9942</v>
       </c>
       <c r="K3" t="n">
         <v>42</v>
@@ -575,7 +575,7 @@
         <v>172</v>
       </c>
       <c r="M3" t="n">
-        <v>7.2237</v>
+        <v>7.6905</v>
       </c>
       <c r="N3" t="n">
         <v>214</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4369</v>
+        <v>6.6551</v>
       </c>
       <c r="C4" t="n">
-        <v>3.7163</v>
+        <v>3.8422</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2679</v>
+        <v>2.4053</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4369</v>
+        <v>6.6551</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7487</v>
+        <v>2.4614</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6882</v>
+        <v>4.1938</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7487</v>
+        <v>2.6622</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7487</v>
+        <v>2.6622</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6882</v>
+        <v>4.1938</v>
       </c>
       <c r="K4" t="n">
         <v>62</v>
@@ -621,7 +621,7 @@
         <v>117</v>
       </c>
       <c r="M4" t="n">
-        <v>6.4369</v>
+        <v>6.856</v>
       </c>
       <c r="N4" t="n">
         <v>179</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7452</v>
+        <v>5.0955</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7396</v>
+        <v>2.9418</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5042</v>
+        <v>1.6954</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7452</v>
+        <v>5.0955</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0751</v>
+        <v>1.977</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6701</v>
+        <v>3.1185</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0751</v>
+        <v>1.977</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0751</v>
+        <v>1.977</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6701</v>
+        <v>3.1185</v>
       </c>
       <c r="K5" t="n">
         <v>42</v>
@@ -667,7 +667,7 @@
         <v>172</v>
       </c>
       <c r="M5" t="n">
-        <v>4.745200000000001</v>
+        <v>5.0955</v>
       </c>
       <c r="N5" t="n">
         <v>214</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0063</v>
+        <v>3.9698</v>
       </c>
       <c r="C6" t="n">
-        <v>2.313</v>
+        <v>2.2919</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1706</v>
+        <v>1.1829</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0063</v>
+        <v>3.9698</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4978</v>
+        <v>2.3616</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5085</v>
+        <v>1.6082</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4978</v>
+        <v>2.4438</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4978</v>
+        <v>2.4438</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5085</v>
+        <v>1.6082</v>
       </c>
       <c r="K6" t="n">
         <v>42</v>
@@ -713,7 +713,7 @@
         <v>80</v>
       </c>
       <c r="M6" t="n">
-        <v>4.0063</v>
+        <v>4.052</v>
       </c>
       <c r="N6" t="n">
         <v>122</v>
@@ -722,369 +722,369 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.717</v>
+        <v>3.7778</v>
       </c>
       <c r="C7" t="n">
-        <v>2.146</v>
+        <v>2.1811</v>
       </c>
       <c r="D7" t="n">
-        <v>1.04</v>
+        <v>1.0955</v>
       </c>
       <c r="E7" t="n">
-        <v>3.717</v>
+        <v>3.7778</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9139</v>
+        <v>2.3193</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1969</v>
+        <v>1.4584</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2345</v>
+        <v>2.3514</v>
       </c>
       <c r="I7" t="n">
-        <v>5.4498</v>
+        <v>2.3514</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1969</v>
+        <v>1.4584</v>
       </c>
       <c r="K7" t="n">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="L7" t="n">
-        <v>64</v>
+        <v>174</v>
       </c>
       <c r="M7" t="n">
-        <v>5.252899999999999</v>
+        <v>3.8098</v>
       </c>
       <c r="N7" t="n">
-        <v>180</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5963</v>
+        <v>3.4399</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0763</v>
+        <v>1.986</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9855</v>
+        <v>0.9417</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5963</v>
+        <v>3.4399</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3954</v>
+        <v>0.4243</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2009</v>
+        <v>3.0156</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3954</v>
+        <v>0.4243</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3954</v>
+        <v>0.4243</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2009</v>
+        <v>3.0156</v>
       </c>
       <c r="K8" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5963</v>
+        <v>3.4399</v>
       </c>
       <c r="N8" t="n">
-        <v>227</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2572</v>
+        <v>3.3698</v>
       </c>
       <c r="C9" t="n">
-        <v>1.8805</v>
+        <v>1.9455</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8324</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2572</v>
+        <v>3.3698</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4358</v>
+        <v>3.5819</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8214</v>
+        <v>-0.2121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4358</v>
+        <v>5.1147</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4358</v>
+        <v>5.2465</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8214</v>
+        <v>-0.2121</v>
       </c>
       <c r="K9" t="n">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="L9" t="n">
-        <v>172</v>
+        <v>64</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2572</v>
+        <v>5.0344</v>
       </c>
       <c r="N9" t="n">
-        <v>214</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7994</v>
+        <v>2.837</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6162</v>
+        <v>1.6379</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6258</v>
+        <v>0.6673</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7994</v>
+        <v>2.837</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6941</v>
+        <v>1.5714</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1053</v>
+        <v>1.2656</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6941</v>
+        <v>1.5714</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8049</v>
+        <v>1.5714</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1053</v>
+        <v>1.2656</v>
       </c>
       <c r="K10" t="n">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="L10" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9102</v>
+        <v>2.837</v>
       </c>
       <c r="N10" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7646</v>
+        <v>2.668</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5961</v>
+        <v>1.5403</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6101</v>
+        <v>0.5903</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7646</v>
+        <v>2.668</v>
       </c>
       <c r="F11" t="n">
-        <v>1.615</v>
+        <v>2.1187</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1496</v>
+        <v>0.5493</v>
       </c>
       <c r="H11" t="n">
-        <v>1.615</v>
+        <v>2.1187</v>
       </c>
       <c r="I11" t="n">
-        <v>1.615</v>
+        <v>2.1187</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1496</v>
+        <v>0.5493</v>
       </c>
       <c r="K11" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="L11" t="n">
         <v>117</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7646</v>
+        <v>2.668</v>
       </c>
       <c r="N11" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5181</v>
+        <v>2.665</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4538</v>
+        <v>1.5386</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4988</v>
+        <v>0.589</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5181</v>
+        <v>2.665</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1299</v>
+        <v>0.3132</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3882</v>
+        <v>2.3518</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1299</v>
+        <v>0.3132</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1299</v>
+        <v>0.3132</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3882</v>
+        <v>2.3518</v>
       </c>
       <c r="K12" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L12" t="n">
         <v>117</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5181</v>
+        <v>2.665</v>
       </c>
       <c r="N12" t="n">
-        <v>179</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4296</v>
+        <v>2.6259</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4027</v>
+        <v>1.516</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4588</v>
+        <v>0.5712</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4296</v>
+        <v>2.6259</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3077</v>
+        <v>0.4324</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1219</v>
+        <v>2.1935</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3077</v>
+        <v>0.4324</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3077</v>
+        <v>0.4324</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1219</v>
+        <v>2.1935</v>
       </c>
       <c r="K13" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="L13" t="n">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4296</v>
+        <v>2.6259</v>
       </c>
       <c r="N13" t="n">
-        <v>156</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4064</v>
+        <v>2.6039</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3893</v>
+        <v>1.5033</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4484</v>
+        <v>0.5611</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4064</v>
+        <v>2.6039</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4205</v>
+        <v>2.4686</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9859</v>
+        <v>0.1353</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4205</v>
+        <v>2.6781</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4205</v>
+        <v>2.7471</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9859</v>
+        <v>0.1353</v>
       </c>
       <c r="K14" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="L14" t="n">
-        <v>174</v>
+        <v>64</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4064</v>
+        <v>2.8824</v>
       </c>
       <c r="N14" t="n">
-        <v>227</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1541</v>
+        <v>2.1143</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2436</v>
+        <v>1.2207</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3345</v>
+        <v>0.3383</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1541</v>
+        <v>2.1143</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1541</v>
+        <v>2.1143</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1541</v>
+        <v>2.1143</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1541</v>
+        <v>2.1143</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1541</v>
+        <v>2.1143</v>
       </c>
       <c r="N15" t="n">
         <v>111</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0779</v>
+        <v>2.0295</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1997</v>
+        <v>1.1717</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3001</v>
+        <v>0.2997</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0779</v>
+        <v>2.0295</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0779</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-1</v>
+        <v>1.3465</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3988</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3988</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-1</v>
+        <v>1.3465</v>
       </c>
       <c r="K16" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="L16" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3988</v>
+        <v>2.0295</v>
       </c>
       <c r="N16" t="n">
-        <v>102</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9566</v>
+        <v>1.9346</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1296</v>
+        <v>1.1169</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2453</v>
+        <v>0.2565</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9566</v>
+        <v>1.9346</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9566</v>
+        <v>0.3309</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.6037</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9566</v>
+        <v>0.3309</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9566</v>
+        <v>0.3309</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.6037</v>
       </c>
       <c r="K17" t="n">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9566</v>
+        <v>1.9346</v>
       </c>
       <c r="N17" t="n">
-        <v>111</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9207</v>
+        <v>1.9259</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1089</v>
+        <v>1.1119</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2291</v>
+        <v>0.2525</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9207</v>
+        <v>1.9259</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5942</v>
+        <v>1.5543</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3265</v>
+        <v>0.3716</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5942</v>
+        <v>1.5543</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5942</v>
+        <v>1.5543</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3265</v>
+        <v>0.3716</v>
       </c>
       <c r="K18" t="n">
         <v>33</v>
@@ -1265,7 +1265,7 @@
         <v>69</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9207</v>
+        <v>1.9259</v>
       </c>
       <c r="N18" t="n">
         <v>102</v>
@@ -1274,599 +1274,599 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8944</v>
+        <v>1.8899</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0937</v>
+        <v>1.0911</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2172</v>
+        <v>0.2361</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8944</v>
+        <v>1.8899</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0034</v>
+        <v>1.8899</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.109</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0034</v>
+        <v>1.8899</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0034</v>
+        <v>1.8899</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.109</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="L19" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8944</v>
+        <v>1.8899</v>
       </c>
       <c r="N19" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8632</v>
+        <v>1.8487</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0757</v>
+        <v>1.0673</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2031</v>
+        <v>0.2174</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8632</v>
+        <v>1.8487</v>
       </c>
       <c r="F20" t="n">
-        <v>2.8572</v>
+        <v>0.7947</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.994</v>
+        <v>1.054</v>
       </c>
       <c r="H20" t="n">
-        <v>2.9141</v>
+        <v>0.7947</v>
       </c>
       <c r="I20" t="n">
-        <v>2.9141</v>
+        <v>0.7947</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.994</v>
+        <v>1.054</v>
       </c>
       <c r="K20" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L20" t="n">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="M20" t="n">
-        <v>1.9201</v>
+        <v>1.8487</v>
       </c>
       <c r="N20" t="n">
-        <v>156</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.8309</v>
+        <v>1.8217</v>
       </c>
       <c r="C21" t="n">
-        <v>1.057</v>
+        <v>1.0517</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1885</v>
+        <v>0.2051</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8309</v>
+        <v>1.8217</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6885</v>
+        <v>2.8217</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1424</v>
+        <v>-1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6885</v>
+        <v>3.4509</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6885</v>
+        <v>3.4509</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1424</v>
+        <v>-1</v>
       </c>
       <c r="K21" t="n">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="L21" t="n">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="M21" t="n">
-        <v>1.8309</v>
+        <v>2.4509</v>
       </c>
       <c r="N21" t="n">
-        <v>179</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.7801</v>
+        <v>1.7897</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0277</v>
+        <v>1.0333</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1656</v>
+        <v>0.1905</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7801</v>
+        <v>1.7897</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7753</v>
+        <v>1.9176</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0048</v>
+        <v>-0.1279</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7753</v>
+        <v>1.9176</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7753</v>
+        <v>1.9176</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0048</v>
+        <v>-0.1279</v>
       </c>
       <c r="K22" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="L22" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="M22" t="n">
-        <v>1.7801</v>
+        <v>1.7897</v>
       </c>
       <c r="N22" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.6796</v>
+        <v>1.6977</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9697</v>
+        <v>0.9801</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1202</v>
+        <v>0.1486</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6796</v>
+        <v>1.6977</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7198</v>
+        <v>0.8535</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0402</v>
+        <v>0.8442</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7198</v>
+        <v>0.8535</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7905</v>
+        <v>0.8535</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0402</v>
+        <v>0.8442</v>
       </c>
       <c r="K23" t="n">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="L23" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M23" t="n">
-        <v>1.7503</v>
+        <v>1.6977</v>
       </c>
       <c r="N23" t="n">
-        <v>180</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6635</v>
+        <v>1.6486</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9604</v>
+        <v>0.9518</v>
       </c>
       <c r="D24" t="n">
-        <v>0.113</v>
+        <v>0.1263</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6635</v>
+        <v>1.6486</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2207</v>
+        <v>2.5616</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4428</v>
+        <v>-0.913</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2207</v>
+        <v>2.8816</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2207</v>
+        <v>2.8816</v>
       </c>
       <c r="J24" t="n">
-        <v>1.4428</v>
+        <v>-0.913</v>
       </c>
       <c r="K24" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L24" t="n">
-        <v>172</v>
+        <v>117</v>
       </c>
       <c r="M24" t="n">
-        <v>1.6635</v>
+        <v>1.9686</v>
       </c>
       <c r="N24" t="n">
-        <v>214</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.5819</v>
+        <v>1.58</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9133</v>
+        <v>0.9122</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0761</v>
+        <v>0.095</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5819</v>
+        <v>1.58</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8315</v>
+        <v>1.6406</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7504</v>
+        <v>-0.0606</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8315</v>
+        <v>1.6406</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8315</v>
+        <v>1.6829</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7504</v>
+        <v>-0.0606</v>
       </c>
       <c r="K25" t="n">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="L25" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="M25" t="n">
-        <v>1.5819</v>
+        <v>1.6223</v>
       </c>
       <c r="N25" t="n">
-        <v>102</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3819</v>
+        <v>1.4496</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7978</v>
+        <v>0.8369</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0142</v>
+        <v>0.0357</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3819</v>
+        <v>1.4496</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2939</v>
+        <v>1.4496</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.912</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.2939</v>
+        <v>1.4496</v>
       </c>
       <c r="I26" t="n">
-        <v>2.2939</v>
+        <v>1.4496</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.912</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="L26" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3819</v>
+        <v>1.4496</v>
       </c>
       <c r="N26" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0SAMAS</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.36</v>
+        <v>1.3889</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7852</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.024</v>
+        <v>0.0081</v>
       </c>
       <c r="E27" t="n">
-        <v>1.36</v>
+        <v>1.3889</v>
       </c>
       <c r="F27" t="n">
-        <v>1.36</v>
+        <v>0.9711</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.4178</v>
       </c>
       <c r="H27" t="n">
-        <v>1.36</v>
+        <v>0.9711</v>
       </c>
       <c r="I27" t="n">
-        <v>1.36</v>
+        <v>0.9711</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.4178</v>
       </c>
       <c r="K27" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M27" t="n">
-        <v>1.36</v>
+        <v>1.3889</v>
       </c>
       <c r="N27" t="n">
-        <v>21</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>0SAMAS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3471</v>
+        <v>1.3554</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.7825</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0299</v>
+        <v>-0.0072</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3471</v>
+        <v>1.3554</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9946</v>
+        <v>1.3554</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3525</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9946</v>
+        <v>1.3554</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9946</v>
+        <v>1.3554</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3525</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="L28" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3471</v>
+        <v>1.3554</v>
       </c>
       <c r="N28" t="n">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.2928</v>
+        <v>1.2975</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7464</v>
+        <v>0.7491</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0544</v>
+        <v>-0.0336</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2928</v>
+        <v>1.2975</v>
       </c>
       <c r="F29" t="n">
-        <v>1.2928</v>
+        <v>2.2426</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>1.2928</v>
+        <v>2.2426</v>
       </c>
       <c r="I29" t="n">
-        <v>1.2928</v>
+        <v>2.2426</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="K29" t="n">
+        <v>33</v>
+      </c>
+      <c r="L29" t="n">
         <v>69</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
-        <v>1.2928</v>
+        <v>1.2975</v>
       </c>
       <c r="N29" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.263</v>
+        <v>1.2604</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7292</v>
+        <v>0.7277</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0678</v>
+        <v>-0.0504</v>
       </c>
       <c r="E30" t="n">
-        <v>1.263</v>
+        <v>1.2604</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4622</v>
+        <v>1.2604</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1992</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4622</v>
+        <v>1.2604</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4622</v>
+        <v>1.2604</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1992</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="L30" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.263</v>
+        <v>1.2604</v>
       </c>
       <c r="N30" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2275</v>
+        <v>1.1919</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7087</v>
+        <v>0.6881</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0839</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2275</v>
+        <v>1.1919</v>
       </c>
       <c r="F31" t="n">
-        <v>1.2275</v>
+        <v>1.4175</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.2256</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2275</v>
+        <v>1.4175</v>
       </c>
       <c r="I31" t="n">
-        <v>1.2275</v>
+        <v>1.4175</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.2256</v>
       </c>
       <c r="K31" t="n">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M31" t="n">
-        <v>1.2275</v>
+        <v>1.1919</v>
       </c>
       <c r="N31" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1658</v>
+        <v>1.1271</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6731</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1117</v>
+        <v>-0.1111</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1658</v>
+        <v>1.1271</v>
       </c>
       <c r="F32" t="n">
-        <v>1.1658</v>
+        <v>1.1271</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.1658</v>
+        <v>1.1271</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1658</v>
+        <v>1.1271</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1658</v>
+        <v>1.1271</v>
       </c>
       <c r="N32" t="n">
         <v>117</v>
@@ -1918,139 +1918,139 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.0783</v>
+        <v>1.1204</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6469</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1512</v>
+        <v>-0.1142</v>
       </c>
       <c r="E33" t="n">
-        <v>1.0783</v>
+        <v>1.1204</v>
       </c>
       <c r="F33" t="n">
-        <v>1.0783</v>
+        <v>0.0235</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1.0969</v>
       </c>
       <c r="H33" t="n">
-        <v>1.0783</v>
+        <v>0.0235</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0783</v>
+        <v>0.0235</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1.0969</v>
       </c>
       <c r="K33" t="n">
+        <v>62</v>
+      </c>
+      <c r="L33" t="n">
         <v>117</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
-        <v>1.0783</v>
+        <v>1.1204</v>
       </c>
       <c r="N33" t="n">
-        <v>117</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0024</v>
+        <v>1.0642</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5787</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1855</v>
+        <v>-0.1398</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0024</v>
+        <v>1.0642</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0264</v>
+        <v>0.4493</v>
       </c>
       <c r="G34" t="n">
-        <v>0.976</v>
+        <v>0.6149</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0264</v>
+        <v>0.4493</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0264</v>
+        <v>0.4493</v>
       </c>
       <c r="J34" t="n">
-        <v>0.976</v>
+        <v>0.6149</v>
       </c>
       <c r="K34" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L34" t="n">
         <v>117</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0024</v>
+        <v>1.0642</v>
       </c>
       <c r="N34" t="n">
-        <v>179</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9166</v>
+        <v>0.9705</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5292</v>
+        <v>0.5603</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2242</v>
+        <v>-0.1824</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9166</v>
+        <v>0.9705</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4091</v>
+        <v>0.9705</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5075</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4091</v>
+        <v>0.9705</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4091</v>
+        <v>0.9705</v>
       </c>
       <c r="J35" t="n">
-        <v>0.5075</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>39</v>
+        <v>117</v>
       </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.9705</v>
+      </c>
+      <c r="N35" t="n">
         <v>117</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.9166</v>
-      </c>
-      <c r="N35" t="n">
-        <v>156</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8857</v>
+        <v>0.8213</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5113</v>
+        <v>0.4742</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2382</v>
+        <v>-0.2503</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8857</v>
+        <v>0.8213</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8857</v>
+        <v>0.8213</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8857</v>
+        <v>0.8213</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8857</v>
+        <v>0.8213</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8857</v>
+        <v>0.8213</v>
       </c>
       <c r="N36" t="n">
         <v>93</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.7325</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4426</v>
+        <v>0.4229</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2919</v>
+        <v>-0.2908</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.7325</v>
       </c>
       <c r="F37" t="n">
-        <v>1.1999</v>
+        <v>1.18</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.4333</v>
+        <v>-0.4475</v>
       </c>
       <c r="H37" t="n">
-        <v>1.1999</v>
+        <v>1.18</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1999</v>
+        <v>1.18</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.4333</v>
+        <v>-0.4475</v>
       </c>
       <c r="K37" t="n">
         <v>42</v>
@@ -2139,7 +2139,7 @@
         <v>80</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.7324999999999999</v>
       </c>
       <c r="N37" t="n">
         <v>122</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6808</v>
+        <v>0.6915</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3931</v>
+        <v>0.3992</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3307</v>
+        <v>-0.3094</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6808</v>
+        <v>0.6915</v>
       </c>
       <c r="F38" t="n">
-        <v>1.2863</v>
+        <v>1.2465</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.6055</v>
+        <v>-0.555</v>
       </c>
       <c r="H38" t="n">
-        <v>1.2863</v>
+        <v>1.2465</v>
       </c>
       <c r="I38" t="n">
-        <v>1.2863</v>
+        <v>1.2465</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.6055</v>
+        <v>-0.555</v>
       </c>
       <c r="K38" t="n">
         <v>39</v>
@@ -2185,7 +2185,7 @@
         <v>117</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6808</v>
+        <v>0.6914999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>156</v>
@@ -2194,139 +2194,139 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5259</v>
+        <v>0.5201</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3036</v>
+        <v>0.3003</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4006</v>
+        <v>-0.3874</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5259</v>
+        <v>0.5201</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5259</v>
+        <v>0.1166</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.4035</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5259</v>
+        <v>0.1166</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5259</v>
+        <v>0.1196</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.4035</v>
       </c>
       <c r="K39" t="n">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5259</v>
+        <v>0.5231</v>
       </c>
       <c r="N39" t="n">
-        <v>71</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5208</v>
+        <v>0.5068</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3007</v>
+        <v>0.2926</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4029</v>
+        <v>-0.3935</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5208</v>
+        <v>0.5068</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5208</v>
+        <v>0.4972</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5208</v>
+        <v>0.4972</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5208</v>
+        <v>0.4972</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5208</v>
+        <v>0.5068</v>
       </c>
       <c r="N40" t="n">
-        <v>71</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.517</v>
+        <v>0.4954</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2985</v>
+        <v>0.286</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4046</v>
+        <v>-0.3987</v>
       </c>
       <c r="E41" t="n">
-        <v>0.517</v>
+        <v>0.4954</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4957</v>
+        <v>0.4954</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0213</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4957</v>
+        <v>0.4954</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4957</v>
+        <v>0.4954</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0213</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="L41" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.517</v>
+        <v>0.4954</v>
       </c>
       <c r="N41" t="n">
-        <v>122</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42">
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4848</v>
+        <v>0.4927</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2799</v>
+        <v>0.2845</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4192</v>
+        <v>-0.3999</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4848</v>
+        <v>0.4927</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4848</v>
+        <v>0.4927</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4848</v>
+        <v>0.4927</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4848</v>
+        <v>0.4927</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4848</v>
+        <v>0.4927</v>
       </c>
       <c r="N42" t="n">
         <v>111</v>
@@ -2378,139 +2378,139 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4756</v>
+        <v>0.4689</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2746</v>
+        <v>0.2707</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4233</v>
+        <v>-0.4108</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4756</v>
+        <v>0.4689</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1166</v>
+        <v>0.4689</v>
       </c>
       <c r="G43" t="n">
-        <v>0.359</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1166</v>
+        <v>0.4689</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1214</v>
+        <v>0.4689</v>
       </c>
       <c r="J43" t="n">
-        <v>0.359</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="L43" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4804</v>
+        <v>0.4689</v>
       </c>
       <c r="N43" t="n">
-        <v>180</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cabbi</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3593</v>
+        <v>0.3013</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2074</v>
+        <v>0.174</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4758</v>
+        <v>-0.487</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3593</v>
+        <v>0.3013</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3593</v>
+        <v>1.3013</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3593</v>
+        <v>1.3013</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3593</v>
+        <v>1.3013</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K44" t="n">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3593</v>
+        <v>0.3012999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Cabbi</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3173</v>
+        <v>0.2925</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1832</v>
+        <v>0.1689</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4948</v>
+        <v>-0.4911</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3173</v>
+        <v>0.2925</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3168</v>
+        <v>0.2925</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.9995000000000001</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.3168</v>
+        <v>0.2925</v>
       </c>
       <c r="I45" t="n">
-        <v>1.3168</v>
+        <v>0.2925</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.9995000000000001</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="L45" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3172999999999999</v>
+        <v>0.2925</v>
       </c>
       <c r="N45" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46">
@@ -2520,28 +2520,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2607</v>
+        <v>0.1842</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1505</v>
+        <v>0.1063</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5203</v>
+        <v>-0.5404</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2607</v>
+        <v>0.1842</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2607</v>
+        <v>0.1842</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2607</v>
+        <v>0.1842</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2607</v>
+        <v>0.1842</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2607</v>
+        <v>0.1842</v>
       </c>
       <c r="N46" t="n">
         <v>71</v>
@@ -2562,93 +2562,93 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1591</v>
+        <v>0.1424</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0919</v>
+        <v>0.0822</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5662</v>
+        <v>-0.5594</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1591</v>
+        <v>0.1424</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1591</v>
+        <v>0.7679</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1591</v>
+        <v>0.7679</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1591</v>
+        <v>0.7679</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1591</v>
+        <v>0.1424000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1359</v>
+        <v>0.1353</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0785</v>
+        <v>0.0781</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5767</v>
+        <v>-0.5626</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1359</v>
+        <v>0.1353</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7343</v>
+        <v>0.1353</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.5984</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.7343</v>
+        <v>0.1353</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7343</v>
+        <v>0.1353</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.5984</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="L48" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1358999999999999</v>
+        <v>0.1353</v>
       </c>
       <c r="N48" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1023</v>
+        <v>0.1149</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0591</v>
+        <v>0.0663</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5918</v>
+        <v>-0.5719</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1023</v>
+        <v>0.1149</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1023</v>
+        <v>0.1149</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1023</v>
+        <v>0.1149</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1023</v>
+        <v>0.1149</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1023</v>
+        <v>0.1149</v>
       </c>
       <c r="N49" t="n">
         <v>21</v>
@@ -2700,47 +2700,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0345</v>
+        <v>0.0815</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0199</v>
+        <v>0.0471</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.6224</v>
+        <v>-0.5871</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0345</v>
+        <v>0.0815</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0345</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-0.8696</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0345</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0345</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-0.8696</v>
       </c>
       <c r="K50" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0345</v>
+        <v>0.08149999999999991</v>
       </c>
       <c r="N50" t="n">
-        <v>69</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0232</v>
+        <v>0.033</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0134</v>
+        <v>0.0191</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.6092</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0232</v>
+        <v>0.033</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0232</v>
+        <v>0.033</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0232</v>
+        <v>0.033</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0232</v>
+        <v>0.033</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0232</v>
+        <v>0.033</v>
       </c>
       <c r="N51" t="n">
         <v>21</v>
@@ -2792,93 +2792,93 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0548</v>
+        <v>0.0144</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0316</v>
+        <v>0.0083</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.6176</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0548</v>
+        <v>0.0144</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9882</v>
+        <v>0.0144</v>
       </c>
       <c r="G52" t="n">
-        <v>-1.043</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.9882</v>
+        <v>0.0144</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9882</v>
+        <v>0.0144</v>
       </c>
       <c r="J52" t="n">
-        <v>-1.043</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="L52" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.05479999999999996</v>
+        <v>0.0144</v>
       </c>
       <c r="N52" t="n">
-        <v>179</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0626</v>
+        <v>-0.0702</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0361</v>
+        <v>-0.0405</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6663</v>
+        <v>-0.6562</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0626</v>
+        <v>-0.0702</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.0626</v>
+        <v>-0.5113</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.4411</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.0626</v>
+        <v>-0.5113</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0626</v>
+        <v>-0.5113</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>0.4411</v>
       </c>
       <c r="K53" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.0626</v>
+        <v>-0.07019999999999998</v>
       </c>
       <c r="N53" t="n">
-        <v>93</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.0859</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0496</v>
+        <v>-0.0542</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6768</v>
+        <v>-0.6669</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.0859</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.0859</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.0859</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0859</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.0859</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="N54" t="n">
         <v>21</v>
@@ -2930,308 +2930,308 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.126</v>
+        <v>-0.0959</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0727</v>
+        <v>-0.0554</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6949</v>
+        <v>-0.6679</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.126</v>
+        <v>-0.0959</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.126</v>
+        <v>-0.3038</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>0.2079</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.126</v>
+        <v>-0.3038</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.126</v>
+        <v>-0.3038</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>0.2079</v>
       </c>
       <c r="K55" t="n">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.126</v>
+        <v>-0.09590000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>93</v>
+        <v>227</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IceBerg</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.173</v>
+        <v>-0.1456</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0999</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7161</v>
+        <v>-0.6905</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.173</v>
+        <v>-0.1456</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.173</v>
+        <v>-0.1456</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.173</v>
+        <v>-0.1456</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.173</v>
+        <v>-0.1456</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.173</v>
+        <v>-0.1456</v>
       </c>
       <c r="N56" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.25</v>
+        <v>-0.1606</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1443</v>
+        <v>-0.0927</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7509</v>
+        <v>-0.6973</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.25</v>
+        <v>-0.1606</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3254</v>
+        <v>-0.1606</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.5754</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.3254</v>
+        <v>-0.1606</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3254</v>
+        <v>-0.1606</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.5754</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="L57" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.25</v>
+        <v>-0.1606</v>
       </c>
       <c r="N57" t="n">
-        <v>122</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.2875</v>
+        <v>-0.2609</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.166</v>
+        <v>-0.1506</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7678</v>
+        <v>-0.743</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.2875</v>
+        <v>-0.2609</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.6201</v>
+        <v>0.3222</v>
       </c>
       <c r="G58" t="n">
-        <v>0.3326</v>
+        <v>-0.5831</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.6201</v>
+        <v>0.3222</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.6201</v>
+        <v>0.3222</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3326</v>
+        <v>-0.5831</v>
       </c>
       <c r="K58" t="n">
         <v>42</v>
       </c>
       <c r="L58" t="n">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.2875</v>
+        <v>-0.2609</v>
       </c>
       <c r="N58" t="n">
-        <v>214</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>IceBerg</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.3084</v>
+        <v>-0.2839</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1781</v>
+        <v>-0.1639</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7772</v>
+        <v>-0.7534</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.3084</v>
+        <v>-0.2839</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.3084</v>
+        <v>-0.2839</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.3084</v>
+        <v>-0.2839</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3084</v>
+        <v>-0.2839</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.3084</v>
+        <v>-0.2839</v>
       </c>
       <c r="N59" t="n">
-        <v>93</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3447</v>
+        <v>-0.3492</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.199</v>
+        <v>-0.2016</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7936</v>
+        <v>-0.7832</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3447</v>
+        <v>-0.3492</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3447</v>
+        <v>-0.3492</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.3447</v>
+        <v>-0.3492</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3447</v>
+        <v>-0.3492</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.3447</v>
+        <v>-0.3492</v>
       </c>
       <c r="N60" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3988</v>
+        <v>-0.4144</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2302</v>
+        <v>-0.2392</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.8181</v>
+        <v>-0.8128</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3988</v>
+        <v>-0.4144</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.3988</v>
+        <v>-0.4144</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.3988</v>
+        <v>-0.4144</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3988</v>
+        <v>-0.4144</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.3988</v>
+        <v>-0.4144</v>
       </c>
       <c r="N61" t="n">
         <v>48</v>
@@ -3252,185 +3252,185 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.4802</v>
+        <v>-0.4403</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2772</v>
+        <v>-0.2542</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8548</v>
+        <v>-0.8246</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.4802</v>
+        <v>-0.4403</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.4802</v>
+        <v>-0.4403</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.4802</v>
+        <v>-0.4403</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.4802</v>
+        <v>-0.4403</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.4802</v>
+        <v>-0.4403</v>
       </c>
       <c r="N62" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>aliStair</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.4968</v>
+        <v>-0.5118</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2868</v>
+        <v>-0.2955</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8623</v>
+        <v>-0.8572</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4968</v>
+        <v>-0.5118</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.4968</v>
+        <v>-0.5118</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.4968</v>
+        <v>-0.5118</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4968</v>
+        <v>-0.5118</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.4968</v>
+        <v>-0.5118</v>
       </c>
       <c r="N63" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.5029</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2903</v>
+        <v>-0.2959</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.865</v>
+        <v>-0.8575</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.5029</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.349</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.1539</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.349</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.349</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.1539</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="L64" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.5029</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="N64" t="n">
-        <v>227</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>aliStair</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.5098</v>
+        <v>-0.5422</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2943</v>
+        <v>-0.313</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8682</v>
+        <v>-0.871</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.5098</v>
+        <v>-0.5422</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.5098</v>
+        <v>-0.5422</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.5098</v>
+        <v>-0.5422</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5098</v>
+        <v>-0.5422</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.5098</v>
+        <v>-0.5422</v>
       </c>
       <c r="N65" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66">
@@ -3440,28 +3440,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.6385</v>
+        <v>-0.6857</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3686</v>
+        <v>-0.3959</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9263</v>
+        <v>-0.9363</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6385</v>
+        <v>-0.6857</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.6385</v>
+        <v>-0.6857</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.6385</v>
+        <v>-0.6857</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6385</v>
+        <v>-0.6857</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.6385</v>
+        <v>-0.6857</v>
       </c>
       <c r="N66" t="n">
         <v>48</v>
@@ -3482,93 +3482,93 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.7252</v>
+        <v>-0.7752</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4187</v>
+        <v>-0.4476</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9654</v>
+        <v>-0.9771</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7252</v>
+        <v>-0.7752</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.7252</v>
+        <v>-0.7752</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.7252</v>
+        <v>-0.7752</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.7252</v>
+        <v>-0.7752</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.7252</v>
+        <v>-0.7752</v>
       </c>
       <c r="N67" t="n">
-        <v>48</v>
+        <v>111</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.7655</v>
+        <v>-0.7823</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.442</v>
+        <v>-0.4517</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9836</v>
+        <v>-0.9802999999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.7655</v>
+        <v>-0.7823</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.7655</v>
+        <v>-0.7823</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.7655</v>
+        <v>-0.7823</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.7655</v>
+        <v>-0.7823</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.7655</v>
+        <v>-0.7823</v>
       </c>
       <c r="N68" t="n">
-        <v>111</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69">
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.8487</v>
+        <v>-0.8135</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.49</v>
+        <v>-0.4697</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0212</v>
+        <v>-0.9945000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.8487</v>
+        <v>-0.8135</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.8487</v>
+        <v>-0.8135</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.8487</v>
+        <v>-0.8135</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.8487</v>
+        <v>-0.8135</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.8487</v>
+        <v>-0.8135</v>
       </c>
       <c r="N69" t="n">
         <v>117</v>
@@ -3624,28 +3624,28 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.851</v>
+        <v>-0.8572</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4913</v>
+        <v>-0.4949</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0222</v>
+        <v>-1.0144</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.851</v>
+        <v>-0.8572</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.851</v>
+        <v>-0.8572</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.851</v>
+        <v>-0.8572</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.851</v>
+        <v>-0.8572</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.851</v>
+        <v>-0.8572</v>
       </c>
       <c r="N70" t="n">
         <v>69</v>
@@ -3670,28 +3670,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.8851</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.511</v>
+        <v>-0.5346</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0376</v>
+        <v>-1.0457</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.8851</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.8851</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.8851</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8851</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.8851</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="N71" t="n">
         <v>69</v>
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-1.0206</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5706</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0842</v>
+        <v>-1.0888</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-1.0206</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-1.0206</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-1.0206</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-1.0206</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-1.0206</v>
       </c>
       <c r="N72" t="n">
         <v>71</v>
@@ -3762,31 +3762,31 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.1297</v>
+        <v>-1.1195</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.6522</v>
+        <v>-0.6463</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.148</v>
+        <v>-1.1338</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1297</v>
+        <v>-1.1195</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.6711</v>
+        <v>-0.6474</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.4586</v>
+        <v>-0.4721</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.6711</v>
+        <v>-0.6474</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.6987</v>
+        <v>-0.6641</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.4586</v>
+        <v>-0.4721</v>
       </c>
       <c r="K73" t="n">
         <v>116</v>
@@ -3795,7 +3795,7 @@
         <v>64</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.1573</v>
+        <v>-1.1362</v>
       </c>
       <c r="N73" t="n">
         <v>180</v>
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.2939</v>
+        <v>-1.3329</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.747</v>
+        <v>-0.7695</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2221</v>
+        <v>-1.231</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.2939</v>
+        <v>-1.3329</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.2939</v>
+        <v>-1.3329</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.2939</v>
+        <v>-1.3329</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2939</v>
+        <v>-1.3329</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.2939</v>
+        <v>-1.3329</v>
       </c>
       <c r="N74" t="n">
         <v>48</v>
@@ -3850,93 +3850,93 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-2.1756</v>
+        <v>-1.7431</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.2561</v>
+        <v>-1.0064</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.6202</v>
+        <v>-1.4177</v>
       </c>
       <c r="E75" t="n">
-        <v>-2.1756</v>
+        <v>-1.7431</v>
       </c>
       <c r="F75" t="n">
-        <v>-2.3353</v>
+        <v>-1.4528</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1597</v>
+        <v>-0.2903</v>
       </c>
       <c r="H75" t="n">
-        <v>-2.3353</v>
+        <v>-1.4528</v>
       </c>
       <c r="I75" t="n">
-        <v>-2.3353</v>
+        <v>-1.4528</v>
       </c>
       <c r="J75" t="n">
-        <v>0.1597</v>
+        <v>-0.2903</v>
       </c>
       <c r="K75" t="n">
         <v>53</v>
       </c>
       <c r="L75" t="n">
-        <v>51</v>
+        <v>174</v>
       </c>
       <c r="M75" t="n">
-        <v>-2.1756</v>
+        <v>-1.7431</v>
       </c>
       <c r="N75" t="n">
-        <v>104</v>
+        <v>227</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-2.2588</v>
+        <v>-1.91</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.3041</v>
+        <v>-1.1027</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.6577</v>
+        <v>-1.4937</v>
       </c>
       <c r="E76" t="n">
-        <v>-2.2588</v>
+        <v>-1.91</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.5905</v>
+        <v>-2.1116</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.6683</v>
+        <v>0.2016</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.5905</v>
+        <v>-2.1116</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.5905</v>
+        <v>-2.1116</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.6683</v>
+        <v>0.2016</v>
       </c>
       <c r="K76" t="n">
         <v>53</v>
       </c>
       <c r="L76" t="n">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="M76" t="n">
-        <v>-2.2588</v>
+        <v>-1.91</v>
       </c>
       <c r="N76" t="n">
-        <v>227</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -4039,10 +4039,10 @@
         <v>1.33</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4513</v>
+        <v>0.4595</v>
       </c>
       <c r="J2" t="n">
-        <v>13.539</v>
+        <v>13.785</v>
       </c>
     </row>
     <row r="3">
@@ -4079,10 +4079,10 @@
         <v>1.29</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4036</v>
+        <v>0.4142</v>
       </c>
       <c r="J3" t="n">
-        <v>12.108</v>
+        <v>12.426</v>
       </c>
     </row>
     <row r="4">
@@ -4119,10 +4119,10 @@
         <v>1.08</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1343</v>
+        <v>0.1492</v>
       </c>
       <c r="J4" t="n">
-        <v>4.029</v>
+        <v>4.476</v>
       </c>
     </row>
     <row r="5">
@@ -4159,10 +4159,10 @@
         <v>1.07</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1196</v>
+        <v>0.1341</v>
       </c>
       <c r="J5" t="n">
-        <v>3.588</v>
+        <v>4.023</v>
       </c>
     </row>
     <row r="6">
@@ -4199,10 +4199,10 @@
         <v>0.74</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3089</v>
+        <v>-0.319</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.266999999999999</v>
+        <v>-9.57</v>
       </c>
     </row>
     <row r="7">
@@ -4239,10 +4239,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0751</v>
+        <v>0.0819</v>
       </c>
       <c r="J7" t="n">
-        <v>2.253</v>
+        <v>2.457</v>
       </c>
     </row>
     <row r="8">
@@ -4279,10 +4279,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0551</v>
+        <v>0.0608</v>
       </c>
       <c r="J8" t="n">
-        <v>1.653</v>
+        <v>1.824</v>
       </c>
     </row>
     <row r="9">
@@ -4319,10 +4319,10 @@
         <v>0.99</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0184</v>
+        <v>-0.0236</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.552</v>
+        <v>-0.708</v>
       </c>
     </row>
     <row r="10">
@@ -4359,10 +4359,10 @@
         <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0605</v>
+        <v>-0.0704</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.815</v>
+        <v>-2.112</v>
       </c>
     </row>
     <row r="11">
@@ -4399,10 +4399,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1946</v>
+        <v>-0.209</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.838</v>
+        <v>-6.27</v>
       </c>
     </row>
     <row r="12">
@@ -4439,10 +4439,10 @@
         <v>1.36</v>
       </c>
       <c r="I12" t="n">
-        <v>0.806</v>
+        <v>0.7542</v>
       </c>
       <c r="J12" t="n">
-        <v>15.314</v>
+        <v>14.3298</v>
       </c>
     </row>
     <row r="13">
@@ -4479,10 +4479,10 @@
         <v>0.95</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0578</v>
+        <v>-0.0722</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0982</v>
+        <v>-1.3718</v>
       </c>
     </row>
     <row r="14">
@@ -4519,10 +4519,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3257</v>
+        <v>-0.3411</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.1883</v>
+        <v>-6.4809</v>
       </c>
     </row>
     <row r="15">
@@ -4559,10 +4559,10 @@
         <v>0.61</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.401</v>
+        <v>-0.4134</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.619</v>
+        <v>-7.8546</v>
       </c>
     </row>
     <row r="16">
@@ -4599,10 +4599,10 @@
         <v>0.59</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4196</v>
+        <v>-0.4312</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.9724</v>
+        <v>-8.1928</v>
       </c>
     </row>
     <row r="17">
@@ -4639,10 +4639,10 @@
         <v>1.71</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3711</v>
+        <v>1.4743</v>
       </c>
       <c r="J17" t="n">
-        <v>26.0509</v>
+        <v>28.0117</v>
       </c>
     </row>
     <row r="18">
@@ -4679,10 +4679,10 @@
         <v>1.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2386</v>
+        <v>1.2873</v>
       </c>
       <c r="J18" t="n">
-        <v>23.5334</v>
+        <v>24.4587</v>
       </c>
     </row>
     <row r="19">
@@ -4719,10 +4719,10 @@
         <v>1.49</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1036</v>
+        <v>1.0912</v>
       </c>
       <c r="J19" t="n">
-        <v>20.9684</v>
+        <v>20.7328</v>
       </c>
     </row>
     <row r="20">
@@ -4759,10 +4759,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2461</v>
+        <v>-0.2258</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.6759</v>
+        <v>-4.2902</v>
       </c>
     </row>
     <row r="21">
@@ -4799,10 +4799,10 @@
         <v>0.85</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5709</v>
+        <v>-0.5268</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.8471</v>
+        <v>-10.0092</v>
       </c>
     </row>
     <row r="22">
@@ -4839,10 +4839,10 @@
         <v>1.19</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4924</v>
+        <v>0.4697</v>
       </c>
       <c r="J22" t="n">
-        <v>9.355600000000001</v>
+        <v>8.924300000000001</v>
       </c>
     </row>
     <row r="23">
@@ -4879,10 +4879,10 @@
         <v>1.08</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2627</v>
+        <v>0.2546</v>
       </c>
       <c r="J23" t="n">
-        <v>4.9913</v>
+        <v>4.8374</v>
       </c>
     </row>
     <row r="24">
@@ -4919,10 +4919,10 @@
         <v>0.7</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3148</v>
+        <v>-0.3309</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.9812</v>
+        <v>-6.2871</v>
       </c>
     </row>
     <row r="25">
@@ -4959,10 +4959,10 @@
         <v>0.66</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3527</v>
+        <v>-0.3674</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.7013</v>
+        <v>-6.9806</v>
       </c>
     </row>
     <row r="26">
@@ -4999,10 +4999,10 @@
         <v>0.52</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4829</v>
+        <v>-0.4913</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.1751</v>
+        <v>-9.3347</v>
       </c>
     </row>
     <row r="27">
@@ -5039,10 +5039,10 @@
         <v>1.73</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3974</v>
+        <v>1.5082</v>
       </c>
       <c r="J27" t="n">
-        <v>26.5506</v>
+        <v>28.6558</v>
       </c>
     </row>
     <row r="28">
@@ -5079,10 +5079,10 @@
         <v>1.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1177</v>
+        <v>1.1114</v>
       </c>
       <c r="J28" t="n">
-        <v>21.2363</v>
+        <v>21.1166</v>
       </c>
     </row>
     <row r="29">
@@ -5119,10 +5119,10 @@
         <v>1.32</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8144</v>
+        <v>0.7761</v>
       </c>
       <c r="J29" t="n">
-        <v>15.4736</v>
+        <v>14.7459</v>
       </c>
     </row>
     <row r="30">
@@ -5159,10 +5159,10 @@
         <v>1.17</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4639</v>
+        <v>0.4632</v>
       </c>
       <c r="J30" t="n">
-        <v>8.8141</v>
+        <v>8.800800000000001</v>
       </c>
     </row>
     <row r="31">
@@ -5199,10 +5199,10 @@
         <v>0.84</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5956</v>
+        <v>-0.5494</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.3164</v>
+        <v>-10.4386</v>
       </c>
     </row>
     <row r="32">
@@ -5239,10 +5239,10 @@
         <v>2.21</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8728</v>
+        <v>1.0077</v>
       </c>
       <c r="J32" t="n">
-        <v>12.2192</v>
+        <v>14.1078</v>
       </c>
     </row>
     <row r="33">
@@ -5279,10 +5279,10 @@
         <v>1.73</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.7048</v>
       </c>
       <c r="J33" t="n">
-        <v>8.5176</v>
+        <v>9.8672</v>
       </c>
     </row>
     <row r="34">
@@ -5319,10 +5319,10 @@
         <v>1.5</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4775</v>
+        <v>0.5508</v>
       </c>
       <c r="J34" t="n">
-        <v>6.685</v>
+        <v>7.7112</v>
       </c>
     </row>
     <row r="35">
@@ -5359,10 +5359,10 @@
         <v>1.27</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3254</v>
+        <v>0.352</v>
       </c>
       <c r="J35" t="n">
-        <v>4.5556</v>
+        <v>4.928</v>
       </c>
     </row>
     <row r="36">
@@ -5399,10 +5399,10 @@
         <v>1.19</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2307</v>
+        <v>0.2577</v>
       </c>
       <c r="J36" t="n">
-        <v>3.2298</v>
+        <v>3.6078</v>
       </c>
     </row>
     <row r="37">
@@ -5439,10 +5439,10 @@
         <v>1.08</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3016</v>
+        <v>0.2759</v>
       </c>
       <c r="J37" t="n">
-        <v>4.2224</v>
+        <v>3.8626</v>
       </c>
     </row>
     <row r="38">
@@ -5479,10 +5479,10 @@
         <v>0.7</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2874</v>
+        <v>-0.3099</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.0236</v>
+        <v>-4.3386</v>
       </c>
     </row>
     <row r="39">
@@ -5519,10 +5519,10 @@
         <v>0.59</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3878</v>
+        <v>-0.4063</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.4292</v>
+        <v>-5.6882</v>
       </c>
     </row>
     <row r="40">
@@ -5559,10 +5559,10 @@
         <v>0.44</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5284</v>
+        <v>-0.5381</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.3976</v>
+        <v>-7.5334</v>
       </c>
     </row>
     <row r="41">
@@ -5599,10 +5599,10 @@
         <v>0.37</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5947</v>
+        <v>-0.5995</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.325799999999999</v>
+        <v>-8.393000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -5639,10 +5639,10 @@
         <v>1.13</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3348</v>
+        <v>0.3339</v>
       </c>
       <c r="J42" t="n">
-        <v>7.0308</v>
+        <v>7.0119</v>
       </c>
     </row>
     <row r="43">
@@ -5679,10 +5679,10 @@
         <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1417</v>
+        <v>0.1432</v>
       </c>
       <c r="J43" t="n">
-        <v>2.9757</v>
+        <v>3.0072</v>
       </c>
     </row>
     <row r="44">
@@ -5719,10 +5719,10 @@
         <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1417</v>
+        <v>0.1432</v>
       </c>
       <c r="J44" t="n">
-        <v>2.9757</v>
+        <v>3.0072</v>
       </c>
     </row>
     <row r="45">
@@ -5759,10 +5759,10 @@
         <v>0.76</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2663</v>
+        <v>-0.2818</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.5923</v>
+        <v>-5.9178</v>
       </c>
     </row>
     <row r="46">
@@ -5799,10 +5799,10 @@
         <v>0.53</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4822</v>
+        <v>-0.4893</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.1262</v>
+        <v>-10.2753</v>
       </c>
     </row>
     <row r="47">
@@ -5839,10 +5839,10 @@
         <v>1.56</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9288</v>
+        <v>1.0251</v>
       </c>
       <c r="J47" t="n">
-        <v>19.5048</v>
+        <v>21.5271</v>
       </c>
     </row>
     <row r="48">
@@ -5879,10 +5879,10 @@
         <v>1.47</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8158</v>
+        <v>0.9038</v>
       </c>
       <c r="J48" t="n">
-        <v>17.1318</v>
+        <v>18.9798</v>
       </c>
     </row>
     <row r="49">
@@ -5919,10 +5919,10 @@
         <v>1.2</v>
       </c>
       <c r="I49" t="n">
-        <v>0.461</v>
+        <v>0.5121</v>
       </c>
       <c r="J49" t="n">
-        <v>9.680999999999999</v>
+        <v>10.7541</v>
       </c>
     </row>
     <row r="50">
@@ -5959,10 +5959,10 @@
         <v>1.17</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4171</v>
+        <v>0.4621</v>
       </c>
       <c r="J50" t="n">
-        <v>8.7591</v>
+        <v>9.7041</v>
       </c>
     </row>
     <row r="51">
@@ -5999,10 +5999,10 @@
         <v>0.91</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3893</v>
+        <v>-0.3637</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.1753</v>
+        <v>-7.6377</v>
       </c>
     </row>
     <row r="52">
@@ -6039,10 +6039,10 @@
         <v>1.36</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5971</v>
+        <v>0.658</v>
       </c>
       <c r="J52" t="n">
-        <v>10.7478</v>
+        <v>11.844</v>
       </c>
     </row>
     <row r="53">
@@ -6079,10 +6079,10 @@
         <v>0.82</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2044</v>
+        <v>-0.2212</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.6792</v>
+        <v>-3.9816</v>
       </c>
     </row>
     <row r="54">
@@ -6119,10 +6119,10 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2441</v>
+        <v>-0.2606</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.3938</v>
+        <v>-4.6908</v>
       </c>
     </row>
     <row r="55">
@@ -6159,10 +6159,10 @@
         <v>0.73</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2928</v>
+        <v>-0.3082</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.2704</v>
+        <v>-5.5476</v>
       </c>
     </row>
     <row r="56">
@@ -6199,10 +6199,10 @@
         <v>0.71</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.312</v>
+        <v>-0.3269</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.616</v>
+        <v>-5.8842</v>
       </c>
     </row>
     <row r="57">
@@ -6239,10 +6239,10 @@
         <v>2.12</v>
       </c>
       <c r="I57" t="n">
-        <v>1.5711</v>
+        <v>1.703</v>
       </c>
       <c r="J57" t="n">
-        <v>28.2798</v>
+        <v>30.654</v>
       </c>
     </row>
     <row r="58">
@@ -6279,10 +6279,10 @@
         <v>1.53</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.9729</v>
       </c>
       <c r="J58" t="n">
-        <v>15.795</v>
+        <v>17.5122</v>
       </c>
     </row>
     <row r="59">
@@ -6319,10 +6319,10 @@
         <v>1.24</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5091</v>
+        <v>0.5683</v>
       </c>
       <c r="J59" t="n">
-        <v>9.1638</v>
+        <v>10.2294</v>
       </c>
     </row>
     <row r="60">
@@ -6359,10 +6359,10 @@
         <v>0.93</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.345</v>
+        <v>-0.3189</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.21</v>
+        <v>-5.7402</v>
       </c>
     </row>
     <row r="61">
@@ -6399,10 +6399,10 @@
         <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5998</v>
+        <v>-0.5524</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.7964</v>
+        <v>-9.943199999999999</v>
       </c>
     </row>
     <row r="62">
@@ -6439,10 +6439,10 @@
         <v>2.88</v>
       </c>
       <c r="I62" t="n">
-        <v>2.2937</v>
+        <v>2.4557</v>
       </c>
       <c r="J62" t="n">
-        <v>38.9929</v>
+        <v>41.7469</v>
       </c>
     </row>
     <row r="63">
@@ -6479,10 +6479,10 @@
         <v>1.89</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2491</v>
+        <v>1.3768</v>
       </c>
       <c r="J63" t="n">
-        <v>21.2347</v>
+        <v>23.4056</v>
       </c>
     </row>
     <row r="64">
@@ -6519,10 +6519,10 @@
         <v>1.58</v>
       </c>
       <c r="I64" t="n">
-        <v>0.9048</v>
+        <v>1.0091</v>
       </c>
       <c r="J64" t="n">
-        <v>15.3816</v>
+        <v>17.1547</v>
       </c>
     </row>
     <row r="65">
@@ -6559,10 +6559,10 @@
         <v>0.91</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.455</v>
+        <v>-0.4101</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.735</v>
+        <v>-6.9717</v>
       </c>
     </row>
     <row r="66">
@@ -6599,10 +6599,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9216</v>
+        <v>-0.8307</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.6672</v>
+        <v>-14.1219</v>
       </c>
     </row>
     <row r="67">
@@ -6639,10 +6639,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.0345</v>
+        <v>-0.0573</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.5865</v>
+        <v>-0.9741</v>
       </c>
     </row>
     <row r="68">
@@ -6679,10 +6679,10 @@
         <v>0.75</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2494</v>
+        <v>-0.2709</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.2398</v>
+        <v>-4.6053</v>
       </c>
     </row>
     <row r="69">
@@ -6719,10 +6719,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3054</v>
+        <v>-0.3255</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.1918</v>
+        <v>-5.5335</v>
       </c>
     </row>
     <row r="70">
@@ -6759,10 +6759,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4253</v>
+        <v>-0.4402</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.2301</v>
+        <v>-7.4834</v>
       </c>
     </row>
     <row r="71">
@@ -6799,10 +6799,10 @@
         <v>0.52</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4627</v>
+        <v>-0.4754</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.8659</v>
+        <v>-8.081799999999999</v>
       </c>
     </row>
     <row r="72">
@@ -6839,10 +6839,10 @@
         <v>1.61</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9982</v>
+        <v>1.0979</v>
       </c>
       <c r="J72" t="n">
-        <v>19.964</v>
+        <v>21.958</v>
       </c>
     </row>
     <row r="73">
@@ -6879,10 +6879,10 @@
         <v>1.57</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9484</v>
+        <v>1.0448</v>
       </c>
       <c r="J73" t="n">
-        <v>18.968</v>
+        <v>20.896</v>
       </c>
     </row>
     <row r="74">
@@ -6919,10 +6919,10 @@
         <v>1.35</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6663</v>
+        <v>0.74</v>
       </c>
       <c r="J74" t="n">
-        <v>13.326</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="75">
@@ -6959,10 +6959,10 @@
         <v>1.1</v>
       </c>
       <c r="I75" t="n">
-        <v>0.295</v>
+        <v>0.305</v>
       </c>
       <c r="J75" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="76">
@@ -6999,10 +6999,10 @@
         <v>0.53</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.3276</v>
+        <v>-1.1916</v>
       </c>
       <c r="J76" t="n">
-        <v>-26.552</v>
+        <v>-23.832</v>
       </c>
     </row>
     <row r="77">
@@ -7039,10 +7039,10 @@
         <v>1.35</v>
       </c>
       <c r="I77" t="n">
-        <v>0.596</v>
+        <v>0.6549</v>
       </c>
       <c r="J77" t="n">
-        <v>11.92</v>
+        <v>13.098</v>
       </c>
     </row>
     <row r="78">
@@ -7079,10 +7079,10 @@
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0354</v>
+        <v>0.0256</v>
       </c>
       <c r="J78" t="n">
-        <v>0.708</v>
+        <v>0.512</v>
       </c>
     </row>
     <row r="79">
@@ -7119,10 +7119,10 @@
         <v>0.71</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3085</v>
+        <v>-0.3242</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.17</v>
+        <v>-6.484</v>
       </c>
     </row>
     <row r="80">
@@ -7159,10 +7159,10 @@
         <v>0.64</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3748</v>
+        <v>-0.3881</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.496</v>
+        <v>-7.762</v>
       </c>
     </row>
     <row r="81">
@@ -7199,10 +7199,10 @@
         <v>0.57</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.44</v>
+        <v>-0.4502</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.004</v>
       </c>
     </row>
     <row r="82">
@@ -7239,10 +7239,10 @@
         <v>1.35</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6795</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="J82" t="n">
-        <v>15.6285</v>
+        <v>17.2845</v>
       </c>
     </row>
     <row r="83">
@@ -7279,10 +7279,10 @@
         <v>1.2</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4711</v>
+        <v>0.5206</v>
       </c>
       <c r="J83" t="n">
-        <v>10.8353</v>
+        <v>11.9738</v>
       </c>
     </row>
     <row r="84">
@@ -7319,10 +7319,10 @@
         <v>1.15</v>
       </c>
       <c r="I84" t="n">
-        <v>0.399</v>
+        <v>0.4357</v>
       </c>
       <c r="J84" t="n">
-        <v>9.177</v>
+        <v>10.0211</v>
       </c>
     </row>
     <row r="85">
@@ -7359,10 +7359,10 @@
         <v>1.07</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2241</v>
+        <v>0.235</v>
       </c>
       <c r="J85" t="n">
-        <v>5.1543</v>
+        <v>5.405</v>
       </c>
     </row>
     <row r="86">
@@ -7399,10 +7399,10 @@
         <v>1.04</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1287</v>
+        <v>0.1444</v>
       </c>
       <c r="J86" t="n">
-        <v>2.9601</v>
+        <v>3.3212</v>
       </c>
     </row>
     <row r="87">
@@ -7439,10 +7439,10 @@
         <v>1.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5168</v>
+        <v>0.5708</v>
       </c>
       <c r="J87" t="n">
-        <v>11.8864</v>
+        <v>13.1284</v>
       </c>
     </row>
     <row r="88">
@@ -7479,10 +7479,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.015</v>
+        <v>-0.021</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.345</v>
+        <v>-0.483</v>
       </c>
     </row>
     <row r="89">
@@ -7519,10 +7519,10 @@
         <v>0.93</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.094</v>
+        <v>-0.1069</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.162</v>
+        <v>-2.4587</v>
       </c>
     </row>
     <row r="90">
@@ -7559,10 +7559,10 @@
         <v>0.79</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2413</v>
+        <v>-0.2563</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.5499</v>
+        <v>-5.8949</v>
       </c>
     </row>
     <row r="91">
@@ -7599,10 +7599,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3571</v>
+        <v>-0.3692</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.2133</v>
+        <v>-8.4916</v>
       </c>
     </row>
     <row r="92">
@@ -7639,10 +7639,10 @@
         <v>1.81</v>
       </c>
       <c r="I92" t="n">
-        <v>1.2592</v>
+        <v>1.3706</v>
       </c>
       <c r="J92" t="n">
-        <v>35.2576</v>
+        <v>38.3768</v>
       </c>
     </row>
     <row r="93">
@@ -7679,10 +7679,10 @@
         <v>1.34</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6616</v>
+        <v>0.7329</v>
       </c>
       <c r="J93" t="n">
-        <v>18.5248</v>
+        <v>20.5212</v>
       </c>
     </row>
     <row r="94">
@@ -7719,10 +7719,10 @@
         <v>1.17</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4263</v>
+        <v>0.4702</v>
       </c>
       <c r="J94" t="n">
-        <v>11.9364</v>
+        <v>13.1656</v>
       </c>
     </row>
     <row r="95">
@@ -7759,10 +7759,10 @@
         <v>0.98</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1407</v>
+        <v>-0.132</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.9396</v>
+        <v>-3.696</v>
       </c>
     </row>
     <row r="96">
@@ -7799,10 +7799,10 @@
         <v>0.62</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.1116</v>
+        <v>-1.0076</v>
       </c>
       <c r="J96" t="n">
-        <v>-31.1248</v>
+        <v>-28.2128</v>
       </c>
     </row>
     <row r="97">
@@ -7839,10 +7839,10 @@
         <v>1.49</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7096</v>
+        <v>0.787</v>
       </c>
       <c r="J97" t="n">
-        <v>19.8688</v>
+        <v>22.036</v>
       </c>
     </row>
     <row r="98">
@@ -7879,10 +7879,10 @@
         <v>0.93</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.094</v>
+        <v>-0.1069</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.632</v>
+        <v>-2.9932</v>
       </c>
     </row>
     <row r="99">
@@ -7919,10 +7919,10 @@
         <v>0.92</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1052</v>
+        <v>-0.1187</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.9456</v>
+        <v>-3.3236</v>
       </c>
     </row>
     <row r="100">
@@ -7959,10 +7959,10 @@
         <v>0.67</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3571</v>
+        <v>-0.3692</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.998799999999999</v>
+        <v>-10.3376</v>
       </c>
     </row>
     <row r="101">
@@ -7999,10 +7999,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3571</v>
+        <v>-0.3692</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.998799999999999</v>
+        <v>-10.3376</v>
       </c>
     </row>
     <row r="102">
@@ -8039,10 +8039,10 @@
         <v>1.88</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3266</v>
+        <v>1.4436</v>
       </c>
       <c r="J102" t="n">
-        <v>26.532</v>
+        <v>28.872</v>
       </c>
     </row>
     <row r="103">
@@ -8079,10 +8079,10 @@
         <v>1.43</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7706</v>
+        <v>0.8537</v>
       </c>
       <c r="J103" t="n">
-        <v>15.412</v>
+        <v>17.074</v>
       </c>
     </row>
     <row r="104">
@@ -8119,10 +8119,10 @@
         <v>1.39</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7187</v>
+        <v>0.7973</v>
       </c>
       <c r="J104" t="n">
-        <v>14.374</v>
+        <v>15.946</v>
       </c>
     </row>
     <row r="105">
@@ -8159,10 +8159,10 @@
         <v>0.83</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.5607</v>
       </c>
       <c r="J105" t="n">
-        <v>-12.086</v>
+        <v>-11.214</v>
       </c>
     </row>
     <row r="106">
@@ -8199,10 +8199,10 @@
         <v>0.63</v>
       </c>
       <c r="I106" t="n">
-        <v>-1.0978</v>
+        <v>-0.9942</v>
       </c>
       <c r="J106" t="n">
-        <v>-21.956</v>
+        <v>-19.884</v>
       </c>
     </row>
     <row r="107">
@@ -8239,10 +8239,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5109</v>
+        <v>0.5654</v>
       </c>
       <c r="J107" t="n">
-        <v>10.218</v>
+        <v>11.308</v>
       </c>
     </row>
     <row r="108">
@@ -8279,10 +8279,10 @@
         <v>1.06</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1718</v>
+        <v>0.1774</v>
       </c>
       <c r="J108" t="n">
-        <v>3.436</v>
+        <v>3.548</v>
       </c>
     </row>
     <row r="109">
@@ -8319,10 +8319,10 @@
         <v>1.01</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0452</v>
+        <v>0.0487</v>
       </c>
       <c r="J109" t="n">
-        <v>0.904</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="110">
@@ -8359,10 +8359,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2833</v>
+        <v>-0.2971</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.666</v>
+        <v>-5.942</v>
       </c>
     </row>
     <row r="111">
@@ -8399,10 +8399,10 @@
         <v>0.67</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3597</v>
+        <v>-0.3713</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.194</v>
+        <v>-7.426</v>
       </c>
     </row>
     <row r="112">
@@ -8439,10 +8439,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4825</v>
+        <v>0.5369</v>
       </c>
       <c r="J112" t="n">
-        <v>11.58</v>
+        <v>12.8856</v>
       </c>
     </row>
     <row r="113">
@@ -8479,10 +8479,10 @@
         <v>1.29</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4122</v>
+        <v>0.4547</v>
       </c>
       <c r="J113" t="n">
-        <v>9.892799999999999</v>
+        <v>10.9128</v>
       </c>
     </row>
     <row r="114">
@@ -8519,10 +8519,10 @@
         <v>1.04</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0929</v>
+        <v>0.1006</v>
       </c>
       <c r="J114" t="n">
-        <v>2.2296</v>
+        <v>2.4144</v>
       </c>
     </row>
     <row r="115">
@@ -8559,10 +8559,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2259</v>
+        <v>-0.2401</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.4216</v>
+        <v>-5.7624</v>
       </c>
     </row>
     <row r="116">
@@ -8599,10 +8599,10 @@
         <v>0.35</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6491</v>
+        <v>-0.6451</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.5784</v>
+        <v>-15.4824</v>
       </c>
     </row>
     <row r="117">
@@ -8639,10 +8639,10 @@
         <v>1.3</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3838</v>
+        <v>0.4262</v>
       </c>
       <c r="J117" t="n">
-        <v>9.2112</v>
+        <v>10.2288</v>
       </c>
     </row>
     <row r="118">
@@ -8679,10 +8679,10 @@
         <v>1.12</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1906</v>
+        <v>0.206</v>
       </c>
       <c r="J118" t="n">
-        <v>4.5744</v>
+        <v>4.944</v>
       </c>
     </row>
     <row r="119">
@@ -8719,10 +8719,10 @@
         <v>1.11</v>
       </c>
       <c r="I119" t="n">
-        <v>0.177</v>
+        <v>0.1924</v>
       </c>
       <c r="J119" t="n">
-        <v>4.248</v>
+        <v>4.6176</v>
       </c>
     </row>
     <row r="120">
@@ -8759,10 +8759,10 @@
         <v>1.01</v>
       </c>
       <c r="I120" t="n">
-        <v>0.0175</v>
+        <v>0.0253</v>
       </c>
       <c r="J120" t="n">
-        <v>0.42</v>
+        <v>0.6072</v>
       </c>
     </row>
     <row r="121">
@@ -8799,10 +8799,10 @@
         <v>0.9</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1439</v>
+        <v>-0.1544</v>
       </c>
       <c r="J121" t="n">
-        <v>-3.4536</v>
+        <v>-3.7056</v>
       </c>
     </row>
     <row r="122">
@@ -8839,10 +8839,10 @@
         <v>1.57</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9464</v>
+        <v>1.043</v>
       </c>
       <c r="J122" t="n">
-        <v>18.928</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="123">
@@ -8879,10 +8879,10 @@
         <v>1.4</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.8102</v>
       </c>
       <c r="J123" t="n">
-        <v>14.606</v>
+        <v>16.204</v>
       </c>
     </row>
     <row r="124">
@@ -8919,10 +8919,10 @@
         <v>1.15</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3897</v>
+        <v>0.4261</v>
       </c>
       <c r="J124" t="n">
-        <v>7.794</v>
+        <v>8.522</v>
       </c>
     </row>
     <row r="125">
@@ -8959,10 +8959,10 @@
         <v>1.07</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2052</v>
+        <v>0.2219</v>
       </c>
       <c r="J125" t="n">
-        <v>4.104</v>
+        <v>4.438</v>
       </c>
     </row>
     <row r="126">
@@ -8999,10 +8999,10 @@
         <v>1.01</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.0036</v>
+        <v>0.0193</v>
       </c>
       <c r="J126" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="127">
@@ -9039,10 +9039,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="J127" t="n">
-        <v>-1.362</v>
+        <v>-1.672</v>
       </c>
     </row>
     <row r="128">
@@ -9079,10 +9079,10 @@
         <v>0.91</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1042</v>
+        <v>-0.121</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.084</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="129">
@@ -9119,10 +9119,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1694</v>
+        <v>-0.1872</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.388</v>
+        <v>-3.744</v>
       </c>
     </row>
     <row r="130">
@@ -9159,10 +9159,10 @@
         <v>0.74</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2759</v>
+        <v>-0.2932</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.518</v>
+        <v>-5.864</v>
       </c>
     </row>
     <row r="131">
@@ -9199,10 +9199,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3237</v>
+        <v>-0.3396</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.474</v>
+        <v>-6.792</v>
       </c>
     </row>
     <row r="132">
@@ -9239,10 +9239,10 @@
         <v>1.26</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3538</v>
+        <v>0.3797</v>
       </c>
       <c r="J132" t="n">
-        <v>14.8596</v>
+        <v>15.9474</v>
       </c>
     </row>
     <row r="133">
@@ -9279,10 +9279,10 @@
         <v>1.19</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2806</v>
+        <v>0.2954</v>
       </c>
       <c r="J133" t="n">
-        <v>11.7852</v>
+        <v>12.4068</v>
       </c>
     </row>
     <row r="134">
@@ -9319,10 +9319,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2159</v>
+        <v>0.2317</v>
       </c>
       <c r="J134" t="n">
-        <v>9.0678</v>
+        <v>9.731400000000001</v>
       </c>
     </row>
     <row r="135">
@@ -9359,10 +9359,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1046</v>
+        <v>0.1186</v>
       </c>
       <c r="J135" t="n">
-        <v>4.3932</v>
+        <v>4.9812</v>
       </c>
     </row>
     <row r="136">
@@ -9399,10 +9399,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.199</v>
+        <v>-0.2101</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.358000000000001</v>
+        <v>-8.824199999999999</v>
       </c>
     </row>
     <row r="137">
@@ -9439,10 +9439,10 @@
         <v>1.13</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2288</v>
+        <v>0.2384</v>
       </c>
       <c r="J137" t="n">
-        <v>9.6096</v>
+        <v>10.0128</v>
       </c>
     </row>
     <row r="138">
@@ -9479,10 +9479,10 @@
         <v>1.09</v>
       </c>
       <c r="I138" t="n">
-        <v>0.168</v>
+        <v>0.1787</v>
       </c>
       <c r="J138" t="n">
-        <v>7.056</v>
+        <v>7.5054</v>
       </c>
     </row>
     <row r="139">
@@ -9519,10 +9519,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0853</v>
+        <v>0.095</v>
       </c>
       <c r="J139" t="n">
-        <v>3.5826</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="140">
@@ -9559,10 +9559,10 @@
         <v>1.01</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0265</v>
+        <v>0.0322</v>
       </c>
       <c r="J140" t="n">
-        <v>1.113</v>
+        <v>1.3524</v>
       </c>
     </row>
     <row r="141">
@@ -9599,10 +9599,10 @@
         <v>0.87</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.17</v>
+        <v>-0.1827</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.14</v>
+        <v>-7.6734</v>
       </c>
     </row>
     <row r="142">
@@ -9639,10 +9639,10 @@
         <v>1.61</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8496</v>
+        <v>0.9376</v>
       </c>
       <c r="J142" t="n">
-        <v>16.992</v>
+        <v>18.752</v>
       </c>
     </row>
     <row r="143">
@@ -9679,10 +9679,10 @@
         <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0261</v>
+        <v>0.0188</v>
       </c>
       <c r="J143" t="n">
-        <v>0.522</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="144">
@@ -9719,10 +9719,10 @@
         <v>0.63</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3879</v>
+        <v>-0.3999</v>
       </c>
       <c r="J144" t="n">
-        <v>-7.758</v>
+        <v>-7.998</v>
       </c>
     </row>
     <row r="145">
@@ -9759,10 +9759,10 @@
         <v>0.61</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4065</v>
+        <v>-0.4177</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.130000000000001</v>
+        <v>-8.353999999999999</v>
       </c>
     </row>
     <row r="146">
@@ -9799,10 +9799,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4527</v>
+        <v>-0.4617</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.054</v>
+        <v>-9.234</v>
       </c>
     </row>
     <row r="147">
@@ -9839,10 +9839,10 @@
         <v>1.95</v>
       </c>
       <c r="I147" t="n">
-        <v>1.412</v>
+        <v>1.5324</v>
       </c>
       <c r="J147" t="n">
-        <v>28.24</v>
+        <v>30.648</v>
       </c>
     </row>
     <row r="148">
@@ -9879,10 +9879,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6673</v>
+        <v>0.7409</v>
       </c>
       <c r="J148" t="n">
-        <v>13.346</v>
+        <v>14.818</v>
       </c>
     </row>
     <row r="149">
@@ -9919,10 +9919,10 @@
         <v>1.2</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4651</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="J149" t="n">
-        <v>9.302</v>
+        <v>10.312</v>
       </c>
     </row>
     <row r="150">
@@ -9959,10 +9959,10 @@
         <v>0.91</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3807</v>
+        <v>-0.3577</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.614</v>
+        <v>-7.154</v>
       </c>
     </row>
     <row r="151">
@@ -9999,10 +9999,10 @@
         <v>0.72</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.8064</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.632</v>
+        <v>-16.128</v>
       </c>
     </row>
     <row r="152">
@@ -10039,10 +10039,10 @@
         <v>1.09</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3051</v>
+        <v>0.2909</v>
       </c>
       <c r="J152" t="n">
-        <v>5.4918</v>
+        <v>5.2362</v>
       </c>
     </row>
     <row r="153">
@@ -10079,10 +10079,10 @@
         <v>0.9</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1094</v>
+        <v>-0.1278</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.9692</v>
+        <v>-2.3004</v>
       </c>
     </row>
     <row r="154">
@@ -10119,10 +10119,10 @@
         <v>0.77</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2427</v>
+        <v>-0.2615</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.3686</v>
+        <v>-4.707</v>
       </c>
     </row>
     <row r="155">
@@ -10159,10 +10159,10 @@
         <v>0.6</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4033</v>
+        <v>-0.4168</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.2594</v>
+        <v>-7.5024</v>
       </c>
     </row>
     <row r="156">
@@ -10199,10 +10199,10 @@
         <v>0.59</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4126</v>
+        <v>-0.4257</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.4268</v>
+        <v>-7.6626</v>
       </c>
     </row>
     <row r="157">
@@ -10239,10 +10239,10 @@
         <v>1.51</v>
       </c>
       <c r="I157" t="n">
-        <v>0.865</v>
+        <v>0.957</v>
       </c>
       <c r="J157" t="n">
-        <v>15.57</v>
+        <v>17.226</v>
       </c>
     </row>
     <row r="158">
@@ -10279,10 +10279,10 @@
         <v>1.33</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.7065</v>
       </c>
       <c r="J158" t="n">
-        <v>11.4228</v>
+        <v>12.717</v>
       </c>
     </row>
     <row r="159">
@@ -10319,10 +10319,10 @@
         <v>1.27</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5562</v>
+        <v>0.6192</v>
       </c>
       <c r="J159" t="n">
-        <v>10.0116</v>
+        <v>11.1456</v>
       </c>
     </row>
     <row r="160">
@@ -10359,10 +10359,10 @@
         <v>1.22</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4887</v>
+        <v>0.5434</v>
       </c>
       <c r="J160" t="n">
-        <v>8.7966</v>
+        <v>9.7812</v>
       </c>
     </row>
     <row r="161">
@@ -10399,10 +10399,10 @@
         <v>1.01</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.0104</v>
+        <v>0.0146</v>
       </c>
       <c r="J161" t="n">
-        <v>-0.1872</v>
+        <v>0.2628</v>
       </c>
     </row>
     <row r="162">
@@ -10439,10 +10439,10 @@
         <v>1.45</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6471</v>
+        <v>0.7217</v>
       </c>
       <c r="J162" t="n">
-        <v>13.5891</v>
+        <v>15.1557</v>
       </c>
     </row>
     <row r="163">
@@ -10479,10 +10479,10 @@
         <v>1.15</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3365</v>
+        <v>0.3437</v>
       </c>
       <c r="J163" t="n">
-        <v>7.0665</v>
+        <v>7.2177</v>
       </c>
     </row>
     <row r="164">
@@ -10519,10 +10519,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2435</v>
+        <v>0.2504</v>
       </c>
       <c r="J164" t="n">
-        <v>5.1135</v>
+        <v>5.2584</v>
       </c>
     </row>
     <row r="165">
@@ -10559,10 +10559,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1682</v>
+        <v>-0.1813</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.5322</v>
+        <v>-3.8073</v>
       </c>
     </row>
     <row r="166">
@@ -10599,10 +10599,10 @@
         <v>0.49</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5293</v>
+        <v>-0.5322</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.1153</v>
+        <v>-11.1762</v>
       </c>
     </row>
     <row r="167">
@@ -10639,10 +10639,10 @@
         <v>1.68</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1063</v>
+        <v>1.2088</v>
       </c>
       <c r="J167" t="n">
-        <v>23.2323</v>
+        <v>25.3848</v>
       </c>
     </row>
     <row r="168">
@@ -10679,10 +10679,10 @@
         <v>1.67</v>
       </c>
       <c r="I168" t="n">
-        <v>1.0938</v>
+        <v>1.1955</v>
       </c>
       <c r="J168" t="n">
-        <v>22.9698</v>
+        <v>25.1055</v>
       </c>
     </row>
     <row r="169">
@@ -10719,10 +10719,10 @@
         <v>1.05</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1617</v>
+        <v>0.176</v>
       </c>
       <c r="J169" t="n">
-        <v>3.3957</v>
+        <v>3.696</v>
       </c>
     </row>
     <row r="170">
@@ -10759,10 +10759,10 @@
         <v>0.78</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.6644</v>
       </c>
       <c r="J170" t="n">
-        <v>-15.0612</v>
+        <v>-13.9524</v>
       </c>
     </row>
     <row r="171">
@@ -10799,10 +10799,10 @@
         <v>0.63</v>
       </c>
       <c r="I171" t="n">
-        <v>-1.0834</v>
+        <v>-0.984</v>
       </c>
       <c r="J171" t="n">
-        <v>-22.7514</v>
+        <v>-20.664</v>
       </c>
     </row>
     <row r="172">
@@ -10839,10 +10839,10 @@
         <v>1.34</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4121</v>
+        <v>0.4641</v>
       </c>
       <c r="J172" t="n">
-        <v>12.363</v>
+        <v>13.923</v>
       </c>
     </row>
     <row r="173">
@@ -10879,10 +10879,10 @@
         <v>1.29</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3769</v>
+        <v>0.4159</v>
       </c>
       <c r="J173" t="n">
-        <v>11.307</v>
+        <v>12.477</v>
       </c>
     </row>
     <row r="174">
@@ -10919,10 +10919,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3194</v>
+        <v>0.3339</v>
       </c>
       <c r="J174" t="n">
-        <v>9.582000000000001</v>
+        <v>10.017</v>
       </c>
     </row>
     <row r="175">
@@ -10959,10 +10959,10 @@
         <v>0.82</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2284</v>
+        <v>-0.2399</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.852</v>
+        <v>-7.197</v>
       </c>
     </row>
     <row r="176">
@@ -10999,10 +10999,10 @@
         <v>0.76</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.288</v>
+        <v>-0.2988</v>
       </c>
       <c r="J176" t="n">
-        <v>-8.640000000000001</v>
+        <v>-8.964</v>
       </c>
     </row>
     <row r="177">
@@ -11039,10 +11039,10 @@
         <v>1.29</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4024</v>
+        <v>0.4446</v>
       </c>
       <c r="J177" t="n">
-        <v>12.072</v>
+        <v>13.338</v>
       </c>
     </row>
     <row r="178">
@@ -11079,10 +11079,10 @@
         <v>1.07</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1356</v>
+        <v>0.1465</v>
       </c>
       <c r="J178" t="n">
-        <v>4.068</v>
+        <v>4.395</v>
       </c>
     </row>
     <row r="179">
@@ -11119,10 +11119,10 @@
         <v>1.05</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1023</v>
+        <v>0.1127</v>
       </c>
       <c r="J179" t="n">
-        <v>3.069</v>
+        <v>3.381</v>
       </c>
     </row>
     <row r="180">
@@ -11159,10 +11159,10 @@
         <v>1</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0023</v>
+        <v>-0.0017</v>
       </c>
       <c r="J180" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.051</v>
       </c>
     </row>
     <row r="181">
@@ -11199,10 +11199,10 @@
         <v>0.75</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2919</v>
+        <v>-0.3038</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.757</v>
+        <v>-9.114000000000001</v>
       </c>
     </row>
     <row r="182">
@@ -11239,10 +11239,10 @@
         <v>1.17</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4419</v>
+        <v>0.4697</v>
       </c>
       <c r="J182" t="n">
-        <v>7.9542</v>
+        <v>8.454599999999999</v>
       </c>
     </row>
     <row r="183">
@@ -11279,10 +11279,10 @@
         <v>0.73</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2736</v>
+        <v>-0.2934</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.9248</v>
+        <v>-5.2812</v>
       </c>
     </row>
     <row r="184">
@@ -11319,10 +11319,10 @@
         <v>0.71</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2915</v>
+        <v>-0.311</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.247</v>
+        <v>-5.598</v>
       </c>
     </row>
     <row r="185">
@@ -11359,10 +11359,10 @@
         <v>0.57</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4221</v>
+        <v>-0.4362</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.5978</v>
+        <v>-7.8516</v>
       </c>
     </row>
     <row r="186">
@@ -11399,10 +11399,10 @@
         <v>0.47</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5154</v>
+        <v>-0.5239</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.277200000000001</v>
+        <v>-9.430199999999999</v>
       </c>
     </row>
     <row r="187">
@@ -11439,10 +11439,10 @@
         <v>1.47</v>
       </c>
       <c r="I187" t="n">
-        <v>0.8013</v>
+        <v>0.8911</v>
       </c>
       <c r="J187" t="n">
-        <v>14.4234</v>
+        <v>16.0398</v>
       </c>
     </row>
     <row r="188">
@@ -11479,10 +11479,10 @@
         <v>1.46</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7889</v>
+        <v>0.8777</v>
       </c>
       <c r="J188" t="n">
-        <v>14.2002</v>
+        <v>15.7986</v>
       </c>
     </row>
     <row r="189">
@@ -11519,10 +11519,10 @@
         <v>1.34</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6399</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="J189" t="n">
-        <v>11.5182</v>
+        <v>12.8556</v>
       </c>
     </row>
     <row r="190">
@@ -11559,10 +11559,10 @@
         <v>1.33</v>
       </c>
       <c r="I190" t="n">
-        <v>0.6273</v>
+        <v>0.7002</v>
       </c>
       <c r="J190" t="n">
-        <v>11.2914</v>
+        <v>12.6036</v>
       </c>
     </row>
     <row r="191">
@@ -11599,10 +11599,10 @@
         <v>1.13</v>
       </c>
       <c r="I191" t="n">
-        <v>0.3435</v>
+        <v>0.3628</v>
       </c>
       <c r="J191" t="n">
-        <v>6.183</v>
+        <v>6.5304</v>
       </c>
     </row>
     <row r="192">
@@ -11639,10 +11639,10 @@
         <v>1.69</v>
       </c>
       <c r="I192" t="n">
-        <v>1.373</v>
+        <v>1.3518</v>
       </c>
       <c r="J192" t="n">
-        <v>30.206</v>
+        <v>29.7396</v>
       </c>
     </row>
     <row r="193">
@@ -11679,10 +11679,10 @@
         <v>1.2</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5568</v>
+        <v>0.543</v>
       </c>
       <c r="J193" t="n">
-        <v>12.2496</v>
+        <v>11.946</v>
       </c>
     </row>
     <row r="194">
@@ -11719,10 +11719,10 @@
         <v>1.08</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2391</v>
+        <v>0.2527</v>
       </c>
       <c r="J194" t="n">
-        <v>5.2602</v>
+        <v>5.5594</v>
       </c>
     </row>
     <row r="195">
@@ -11759,10 +11759,10 @@
         <v>1.08</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2391</v>
+        <v>0.2527</v>
       </c>
       <c r="J195" t="n">
-        <v>5.2602</v>
+        <v>5.5594</v>
       </c>
     </row>
     <row r="196">
@@ -11799,10 +11799,10 @@
         <v>1.07</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2091</v>
+        <v>0.2246</v>
       </c>
       <c r="J196" t="n">
-        <v>4.6002</v>
+        <v>4.9412</v>
       </c>
     </row>
     <row r="197">
@@ -11839,10 +11839,10 @@
         <v>0.97</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.0379</v>
+        <v>-0.0489</v>
       </c>
       <c r="J197" t="n">
-        <v>-0.8338</v>
+        <v>-1.0758</v>
       </c>
     </row>
     <row r="198">
@@ -11879,10 +11879,10 @@
         <v>0.97</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.0379</v>
+        <v>-0.0489</v>
       </c>
       <c r="J198" t="n">
-        <v>-0.8338</v>
+        <v>-1.0758</v>
       </c>
     </row>
     <row r="199">
@@ -11919,10 +11919,10 @@
         <v>0.87</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1539</v>
+        <v>-0.1703</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.3858</v>
+        <v>-3.7466</v>
       </c>
     </row>
     <row r="200">
@@ -11959,10 +11959,10 @@
         <v>0.86</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1642</v>
+        <v>-0.1807</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.6124</v>
+        <v>-3.9754</v>
       </c>
     </row>
     <row r="201">
@@ -11999,10 +11999,10 @@
         <v>0.74</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2834</v>
+        <v>-0.299</v>
       </c>
       <c r="J201" t="n">
-        <v>-6.2348</v>
+        <v>-6.578</v>
       </c>
     </row>
     <row r="202">
@@ -12039,10 +12039,10 @@
         <v>1.66</v>
       </c>
       <c r="I202" t="n">
-        <v>1.359</v>
+        <v>1.3332</v>
       </c>
       <c r="J202" t="n">
-        <v>28.539</v>
+        <v>27.9972</v>
       </c>
     </row>
     <row r="203">
@@ -12079,10 +12079,10 @@
         <v>1.27</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7381</v>
+        <v>0.7014</v>
       </c>
       <c r="J203" t="n">
-        <v>15.5001</v>
+        <v>14.7294</v>
       </c>
     </row>
     <row r="204">
@@ -12119,10 +12119,10 @@
         <v>1.15</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4458</v>
+        <v>0.4395</v>
       </c>
       <c r="J204" t="n">
-        <v>9.361800000000001</v>
+        <v>9.2295</v>
       </c>
     </row>
     <row r="205">
@@ -12159,10 +12159,10 @@
         <v>0.89</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4194</v>
+        <v>-0.3975</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.807399999999999</v>
+        <v>-8.3475</v>
       </c>
     </row>
     <row r="206">
@@ -12199,10 +12199,10 @@
         <v>0.78</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.6623</v>
       </c>
       <c r="J206" t="n">
-        <v>-14.9982</v>
+        <v>-13.9083</v>
       </c>
     </row>
     <row r="207">
@@ -12239,10 +12239,10 @@
         <v>1.42</v>
       </c>
       <c r="I207" t="n">
-        <v>0.8598</v>
+        <v>0.8097</v>
       </c>
       <c r="J207" t="n">
-        <v>18.0558</v>
+        <v>17.0037</v>
       </c>
     </row>
     <row r="208">
@@ -12279,10 +12279,10 @@
         <v>0.87</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1582</v>
+        <v>-0.1735</v>
       </c>
       <c r="J208" t="n">
-        <v>-3.3222</v>
+        <v>-3.6435</v>
       </c>
     </row>
     <row r="209">
@@ -12319,10 +12319,10 @@
         <v>0.84</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1894</v>
+        <v>-0.2049</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.9774</v>
+        <v>-4.3029</v>
       </c>
     </row>
     <row r="210">
@@ -12359,10 +12359,10 @@
         <v>0.77</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2596</v>
+        <v>-0.2746</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.4516</v>
+        <v>-5.7666</v>
       </c>
     </row>
     <row r="211">
@@ -12399,10 +12399,10 @@
         <v>0.72</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3081</v>
+        <v>-0.322</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.4701</v>
+        <v>-6.762</v>
       </c>
     </row>
     <row r="212">
@@ -12439,10 +12439,10 @@
         <v>1.04</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1478</v>
+        <v>0.1476</v>
       </c>
       <c r="J212" t="n">
-        <v>5.0252</v>
+        <v>5.0184</v>
       </c>
     </row>
     <row r="213">
@@ -12479,10 +12479,10 @@
         <v>0.9</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1229</v>
+        <v>-0.1383</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.1786</v>
+        <v>-4.7022</v>
       </c>
     </row>
     <row r="214">
@@ -12519,10 +12519,10 @@
         <v>0.9</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1229</v>
+        <v>-0.1383</v>
       </c>
       <c r="J214" t="n">
-        <v>-4.1786</v>
+        <v>-4.7022</v>
       </c>
     </row>
     <row r="215">
@@ -12559,10 +12559,10 @@
         <v>0.87</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1539</v>
+        <v>-0.1703</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.2326</v>
+        <v>-5.7902</v>
       </c>
     </row>
     <row r="216">
@@ -12599,10 +12599,10 @@
         <v>0.7</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3218</v>
+        <v>-0.3364</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.9412</v>
+        <v>-11.4376</v>
       </c>
     </row>
     <row r="217">
@@ -12639,10 +12639,10 @@
         <v>1.44</v>
       </c>
       <c r="I217" t="n">
-        <v>1.074</v>
+        <v>1.0269</v>
       </c>
       <c r="J217" t="n">
-        <v>36.516</v>
+        <v>34.9146</v>
       </c>
     </row>
     <row r="218">
@@ -12679,10 +12679,10 @@
         <v>1.32</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8527</v>
+        <v>0.8025</v>
       </c>
       <c r="J218" t="n">
-        <v>28.9918</v>
+        <v>27.285</v>
       </c>
     </row>
     <row r="219">
@@ -12719,10 +12719,10 @@
         <v>1.3</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8062</v>
+        <v>0.7617</v>
       </c>
       <c r="J219" t="n">
-        <v>27.4108</v>
+        <v>25.8978</v>
       </c>
     </row>
     <row r="220">
@@ -12759,10 +12759,10 @@
         <v>0.89</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4215</v>
+        <v>-0.399</v>
       </c>
       <c r="J220" t="n">
-        <v>-14.331</v>
+        <v>-13.566</v>
       </c>
     </row>
     <row r="221">
@@ -12799,10 +12799,10 @@
         <v>0.84</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5596</v>
+        <v>-0.5241</v>
       </c>
       <c r="J221" t="n">
-        <v>-19.0264</v>
+        <v>-17.8194</v>
       </c>
     </row>
     <row r="222">
@@ -12839,10 +12839,10 @@
         <v>1.44</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0952</v>
+        <v>1.0473</v>
       </c>
       <c r="J222" t="n">
-        <v>32.856</v>
+        <v>31.419</v>
       </c>
     </row>
     <row r="223">
@@ -12879,10 +12879,10 @@
         <v>1.09</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2982</v>
+        <v>0.3003</v>
       </c>
       <c r="J223" t="n">
-        <v>8.946</v>
+        <v>9.009</v>
       </c>
     </row>
     <row r="224">
@@ -12919,10 +12919,10 @@
         <v>0.97</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1511</v>
+        <v>-0.15</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.533</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="225">
@@ -12959,10 +12959,10 @@
         <v>0.96</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.186</v>
+        <v>-0.1837</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.58</v>
+        <v>-5.511</v>
       </c>
     </row>
     <row r="226">
@@ -12999,10 +12999,10 @@
         <v>0.95</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2193</v>
+        <v>-0.2156</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.579</v>
+        <v>-6.468</v>
       </c>
     </row>
     <row r="227">
@@ -13039,10 +13039,10 @@
         <v>1.14</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3193</v>
+        <v>0.3234</v>
       </c>
       <c r="J227" t="n">
-        <v>9.579000000000001</v>
+        <v>9.702</v>
       </c>
     </row>
     <row r="228">
@@ -13079,10 +13079,10 @@
         <v>1.04</v>
       </c>
       <c r="I228" t="n">
-        <v>0.112</v>
+        <v>0.1217</v>
       </c>
       <c r="J228" t="n">
-        <v>3.36</v>
+        <v>3.651</v>
       </c>
     </row>
     <row r="229">
@@ -13119,10 +13119,10 @@
         <v>1.02</v>
       </c>
       <c r="I229" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J229" t="n">
-        <v>1.896</v>
+        <v>2.142</v>
       </c>
     </row>
     <row r="230">
@@ -13159,10 +13159,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J230" t="n">
-        <v>1.896</v>
+        <v>2.142</v>
       </c>
     </row>
     <row r="231">
@@ -13199,10 +13199,10 @@
         <v>0.9</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1369</v>
+        <v>-0.149</v>
       </c>
       <c r="J231" t="n">
-        <v>-4.107</v>
+        <v>-4.47</v>
       </c>
     </row>
     <row r="232">
@@ -13239,10 +13239,10 @@
         <v>2.47</v>
       </c>
       <c r="I232" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J232" t="n">
-        <v>27.507</v>
+        <v>29.058</v>
       </c>
     </row>
     <row r="233">
@@ -13279,10 +13279,10 @@
         <v>1.73</v>
       </c>
       <c r="I233" t="n">
-        <v>1.3501</v>
+        <v>1.3401</v>
       </c>
       <c r="J233" t="n">
-        <v>20.2515</v>
+        <v>20.1015</v>
       </c>
     </row>
     <row r="234">
@@ -13319,10 +13319,10 @@
         <v>1.62</v>
       </c>
       <c r="I234" t="n">
-        <v>1.2258</v>
+        <v>1.2069</v>
       </c>
       <c r="J234" t="n">
-        <v>18.387</v>
+        <v>18.1035</v>
       </c>
     </row>
     <row r="235">
@@ -13359,10 +13359,10 @@
         <v>1.04</v>
       </c>
       <c r="I235" t="n">
-        <v>0.0408</v>
+        <v>0.0828</v>
       </c>
       <c r="J235" t="n">
-        <v>0.612</v>
+        <v>1.242</v>
       </c>
     </row>
     <row r="236">
@@ -13399,10 +13399,10 @@
         <v>0.95</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3268</v>
+        <v>-0.291</v>
       </c>
       <c r="J236" t="n">
-        <v>-4.902</v>
+        <v>-4.365</v>
       </c>
     </row>
     <row r="237">
@@ -13439,10 +13439,10 @@
         <v>1.01</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1907</v>
+        <v>0.1557</v>
       </c>
       <c r="J237" t="n">
-        <v>2.8605</v>
+        <v>2.3355</v>
       </c>
     </row>
     <row r="238">
@@ -13479,10 +13479,10 @@
         <v>0.67</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3182</v>
+        <v>-0.3391</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.773</v>
+        <v>-5.0865</v>
       </c>
     </row>
     <row r="239">
@@ -13519,10 +13519,10 @@
         <v>0.55</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.427</v>
+        <v>-0.4431</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.405</v>
+        <v>-6.6465</v>
       </c>
     </row>
     <row r="240">
@@ -13559,10 +13559,10 @@
         <v>0.51</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4645</v>
+        <v>-0.4783</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.9675</v>
+        <v>-7.1745</v>
       </c>
     </row>
     <row r="241">
@@ -13599,10 +13599,10 @@
         <v>0.5</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4739</v>
+        <v>-0.4871</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.1085</v>
+        <v>-7.3065</v>
       </c>
     </row>
     <row r="242">
@@ -13639,10 +13639,10 @@
         <v>0.95</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.0371</v>
+        <v>-0.056</v>
       </c>
       <c r="J242" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-1.008</v>
       </c>
     </row>
     <row r="243">
@@ -13679,10 +13679,10 @@
         <v>0.9</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0999</v>
+        <v>-0.1205</v>
       </c>
       <c r="J243" t="n">
-        <v>-1.7982</v>
+        <v>-2.169</v>
       </c>
     </row>
     <row r="244">
@@ -13719,10 +13719,10 @@
         <v>0.74</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2659</v>
+        <v>-0.2855</v>
       </c>
       <c r="J244" t="n">
-        <v>-4.7862</v>
+        <v>-5.139</v>
       </c>
     </row>
     <row r="245">
@@ -13759,10 +13759,10 @@
         <v>0.63</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3685</v>
+        <v>-0.3848</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.633</v>
+        <v>-6.9264</v>
       </c>
     </row>
     <row r="246">
@@ -13799,10 +13799,10 @@
         <v>0.51</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4806</v>
+        <v>-0.4909</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.6508</v>
+        <v>-8.8362</v>
       </c>
     </row>
     <row r="247">
@@ -13839,10 +13839,10 @@
         <v>1.8</v>
       </c>
       <c r="I247" t="n">
-        <v>1.455</v>
+        <v>1.4468</v>
       </c>
       <c r="J247" t="n">
-        <v>26.19</v>
+        <v>26.0424</v>
       </c>
     </row>
     <row r="248">
@@ -13879,10 +13879,10 @@
         <v>1.54</v>
       </c>
       <c r="I248" t="n">
-        <v>1.1497</v>
+        <v>1.1214</v>
       </c>
       <c r="J248" t="n">
-        <v>20.6946</v>
+        <v>20.1852</v>
       </c>
     </row>
     <row r="249">
@@ -13919,10 +13919,10 @@
         <v>1.32</v>
       </c>
       <c r="I249" t="n">
-        <v>0.7973</v>
+        <v>0.7644</v>
       </c>
       <c r="J249" t="n">
-        <v>14.3514</v>
+        <v>13.7592</v>
       </c>
     </row>
     <row r="250">
@@ -13959,10 +13959,10 @@
         <v>1.28</v>
       </c>
       <c r="I250" t="n">
-        <v>0.7068</v>
+        <v>0.6846</v>
       </c>
       <c r="J250" t="n">
-        <v>12.7224</v>
+        <v>12.3228</v>
       </c>
     </row>
     <row r="251">
@@ -13999,10 +13999,10 @@
         <v>1.15</v>
       </c>
       <c r="I251" t="n">
-        <v>0.389</v>
+        <v>0.4002</v>
       </c>
       <c r="J251" t="n">
-        <v>7.002</v>
+        <v>7.2036</v>
       </c>
     </row>
     <row r="252">
@@ -14039,10 +14039,10 @@
         <v>1.96</v>
       </c>
       <c r="I252" t="n">
-        <v>1.36</v>
+        <v>1.3554</v>
       </c>
       <c r="J252" t="n">
-        <v>28.56</v>
+        <v>28.4634</v>
       </c>
     </row>
     <row r="253">
@@ -14079,10 +14079,10 @@
         <v>1.04</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1023</v>
+        <v>0.1149</v>
       </c>
       <c r="J253" t="n">
-        <v>2.1483</v>
+        <v>2.4129</v>
       </c>
     </row>
     <row r="254">
@@ -14119,10 +14119,10 @@
         <v>1.01</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0232</v>
+        <v>0.033</v>
       </c>
       <c r="J254" t="n">
-        <v>0.4872</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="255">
@@ -14159,10 +14159,10 @@
         <v>0.95</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0859</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J255" t="n">
-        <v>-1.8039</v>
+        <v>-1.9698</v>
       </c>
     </row>
     <row r="256">
@@ -14199,10 +14199,10 @@
         <v>0.52</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5098</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.7058</v>
+        <v>-10.7646</v>
       </c>
     </row>
     <row r="257">
@@ -14239,10 +14239,10 @@
         <v>1.42</v>
       </c>
       <c r="I257" t="n">
-        <v>1.0454</v>
+        <v>0.9928</v>
       </c>
       <c r="J257" t="n">
-        <v>21.9534</v>
+        <v>20.8488</v>
       </c>
     </row>
     <row r="258">
@@ -14279,10 +14279,10 @@
         <v>1.34</v>
       </c>
       <c r="I258" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.8413</v>
       </c>
       <c r="J258" t="n">
-        <v>18.8307</v>
+        <v>17.6673</v>
       </c>
     </row>
     <row r="259">
@@ -14319,10 +14319,10 @@
         <v>1.16</v>
       </c>
       <c r="I259" t="n">
-        <v>0.4688</v>
+        <v>0.461</v>
       </c>
       <c r="J259" t="n">
-        <v>9.844799999999999</v>
+        <v>9.680999999999999</v>
       </c>
     </row>
     <row r="260">
@@ -14359,10 +14359,10 @@
         <v>1.06</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1929</v>
+        <v>0.2058</v>
       </c>
       <c r="J260" t="n">
-        <v>4.0509</v>
+        <v>4.3218</v>
       </c>
     </row>
     <row r="261">
@@ -14399,10 +14399,10 @@
         <v>0.84</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5611</v>
+        <v>-0.5252</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.7831</v>
+        <v>-11.0292</v>
       </c>
     </row>
     <row r="262">
@@ -14439,10 +14439,10 @@
         <v>1.45</v>
       </c>
       <c r="I262" t="n">
-        <v>1.0803</v>
+        <v>1.0358</v>
       </c>
       <c r="J262" t="n">
-        <v>23.7666</v>
+        <v>22.7876</v>
       </c>
     </row>
     <row r="263">
@@ -14479,10 +14479,10 @@
         <v>1.3</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7975</v>
+        <v>0.7557</v>
       </c>
       <c r="J263" t="n">
-        <v>17.545</v>
+        <v>16.6254</v>
       </c>
     </row>
     <row r="264">
@@ -14519,10 +14519,10 @@
         <v>1.18</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5034</v>
       </c>
       <c r="J264" t="n">
-        <v>11.3212</v>
+        <v>11.0748</v>
       </c>
     </row>
     <row r="265">
@@ -14559,10 +14559,10 @@
         <v>1.06</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1875</v>
+        <v>0.2021</v>
       </c>
       <c r="J265" t="n">
-        <v>4.125</v>
+        <v>4.4462</v>
       </c>
     </row>
     <row r="266">
@@ -14599,10 +14599,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2791</v>
+        <v>-0.2653</v>
       </c>
       <c r="J266" t="n">
-        <v>-6.1402</v>
+        <v>-5.8366</v>
       </c>
     </row>
     <row r="267">
@@ -14639,10 +14639,10 @@
         <v>1.83</v>
       </c>
       <c r="I267" t="n">
-        <v>1.3081</v>
+        <v>1.2899</v>
       </c>
       <c r="J267" t="n">
-        <v>28.7782</v>
+        <v>28.3778</v>
       </c>
     </row>
     <row r="268">
@@ -14679,10 +14679,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5896</v>
+        <v>0.5679</v>
       </c>
       <c r="J268" t="n">
-        <v>12.9712</v>
+        <v>12.4938</v>
       </c>
     </row>
     <row r="269">
@@ -14719,10 +14719,10 @@
         <v>0.63</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3947</v>
+        <v>-0.4054</v>
       </c>
       <c r="J269" t="n">
-        <v>-8.683400000000001</v>
+        <v>-8.918799999999999</v>
       </c>
     </row>
     <row r="270">
@@ -14759,10 +14759,10 @@
         <v>0.63</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3947</v>
+        <v>-0.4054</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.683400000000001</v>
+        <v>-8.918799999999999</v>
       </c>
     </row>
     <row r="271">
@@ -14799,10 +14799,10 @@
         <v>0.33</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6639</v>
+        <v>-0.6592</v>
       </c>
       <c r="J271" t="n">
-        <v>-14.6058</v>
+        <v>-14.5024</v>
       </c>
     </row>
     <row r="272">
@@ -14839,10 +14839,10 @@
         <v>2.14</v>
       </c>
       <c r="I272" t="n">
-        <v>1.8338</v>
+        <v>1.8458</v>
       </c>
       <c r="J272" t="n">
-        <v>31.1746</v>
+        <v>31.3786</v>
       </c>
     </row>
     <row r="273">
@@ -14879,10 +14879,10 @@
         <v>1.5</v>
       </c>
       <c r="I273" t="n">
-        <v>1.1004</v>
+        <v>1.068</v>
       </c>
       <c r="J273" t="n">
-        <v>18.7068</v>
+        <v>18.156</v>
       </c>
     </row>
     <row r="274">
@@ -14919,10 +14919,10 @@
         <v>1.23</v>
       </c>
       <c r="I274" t="n">
-        <v>0.5868</v>
+        <v>0.5785</v>
       </c>
       <c r="J274" t="n">
-        <v>9.9756</v>
+        <v>9.8345</v>
       </c>
     </row>
     <row r="275">
@@ -14959,10 +14959,10 @@
         <v>1.19</v>
       </c>
       <c r="I275" t="n">
-        <v>0.4888</v>
+        <v>0.4908</v>
       </c>
       <c r="J275" t="n">
-        <v>8.3096</v>
+        <v>8.3436</v>
       </c>
     </row>
     <row r="276">
@@ -14999,10 +14999,10 @@
         <v>1.09</v>
       </c>
       <c r="I276" t="n">
-        <v>0.2216</v>
+        <v>0.2472</v>
       </c>
       <c r="J276" t="n">
-        <v>3.7672</v>
+        <v>4.2024</v>
       </c>
     </row>
     <row r="277">
@@ -15039,10 +15039,10 @@
         <v>1.1</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3791</v>
+        <v>0.3502</v>
       </c>
       <c r="J277" t="n">
-        <v>6.4447</v>
+        <v>5.9534</v>
       </c>
     </row>
     <row r="278">
@@ -15079,10 +15079,10 @@
         <v>0.91</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0785</v>
+        <v>-0.1009</v>
       </c>
       <c r="J278" t="n">
-        <v>-1.3345</v>
+        <v>-1.7153</v>
       </c>
     </row>
     <row r="279">
@@ -15119,10 +15119,10 @@
         <v>0.64</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3535</v>
+        <v>-0.3715</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.0095</v>
+        <v>-6.3155</v>
       </c>
     </row>
     <row r="280">
@@ -15159,10 +15159,10 @@
         <v>0.49</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4937</v>
+        <v>-0.504</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.392899999999999</v>
+        <v>-8.568</v>
       </c>
     </row>
     <row r="281">
@@ -15199,10 +15199,10 @@
         <v>0.41</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5683</v>
+        <v>-0.5735</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.661099999999999</v>
+        <v>-9.749499999999999</v>
       </c>
     </row>
     <row r="282">
@@ -15239,10 +15239,10 @@
         <v>2.16</v>
       </c>
       <c r="I282" t="n">
-        <v>1.8338</v>
+        <v>1.8657</v>
       </c>
       <c r="J282" t="n">
-        <v>31.1746</v>
+        <v>31.7169</v>
       </c>
     </row>
     <row r="283">
@@ -15279,10 +15279,10 @@
         <v>1.76</v>
       </c>
       <c r="I283" t="n">
-        <v>1.404</v>
+        <v>1.3937</v>
       </c>
       <c r="J283" t="n">
-        <v>23.868</v>
+        <v>23.6929</v>
       </c>
     </row>
     <row r="284">
@@ -15319,10 +15319,10 @@
         <v>1.21</v>
       </c>
       <c r="I284" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.5334</v>
       </c>
       <c r="J284" t="n">
-        <v>9.108599999999999</v>
+        <v>9.0678</v>
       </c>
     </row>
     <row r="285">
@@ -15359,10 +15359,10 @@
         <v>1.18</v>
       </c>
       <c r="I285" t="n">
-        <v>0.4611</v>
+        <v>0.4664</v>
       </c>
       <c r="J285" t="n">
-        <v>7.8387</v>
+        <v>7.9288</v>
       </c>
     </row>
     <row r="286">
@@ -15399,10 +15399,10 @@
         <v>0.9</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4565</v>
+        <v>-0.4175</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.7605</v>
+        <v>-7.0975</v>
       </c>
     </row>
     <row r="287">
@@ -15439,10 +15439,10 @@
         <v>1.04</v>
       </c>
       <c r="I287" t="n">
-        <v>0.1705</v>
+        <v>0.1642</v>
       </c>
       <c r="J287" t="n">
-        <v>2.8985</v>
+        <v>2.7914</v>
       </c>
     </row>
     <row r="288">
@@ -15479,10 +15479,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0677</v>
+        <v>-0.0833</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.1509</v>
+        <v>-1.4161</v>
       </c>
     </row>
     <row r="289">
@@ -15519,10 +15519,10 @@
         <v>0.82</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1985</v>
+        <v>-0.2167</v>
       </c>
       <c r="J289" t="n">
-        <v>-3.3745</v>
+        <v>-3.6839</v>
       </c>
     </row>
     <row r="290">
@@ -15559,10 +15559,10 @@
         <v>0.74</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2757</v>
+        <v>-0.293</v>
       </c>
       <c r="J290" t="n">
-        <v>-4.6869</v>
+        <v>-4.981</v>
       </c>
     </row>
     <row r="291">
@@ -15599,10 +15599,10 @@
         <v>0.58</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4267</v>
+        <v>-0.4383</v>
       </c>
       <c r="J291" t="n">
-        <v>-7.2539</v>
+        <v>-7.4511</v>
       </c>
     </row>
     <row r="292">
@@ -15639,10 +15639,10 @@
         <v>1.93</v>
       </c>
       <c r="I292" t="n">
-        <v>1.5835</v>
+        <v>1.5852</v>
       </c>
       <c r="J292" t="n">
-        <v>25.336</v>
+        <v>25.3632</v>
       </c>
     </row>
     <row r="293">
@@ -15679,10 +15679,10 @@
         <v>1.62</v>
       </c>
       <c r="I293" t="n">
-        <v>1.2318</v>
+        <v>1.2122</v>
       </c>
       <c r="J293" t="n">
-        <v>19.7088</v>
+        <v>19.3952</v>
       </c>
     </row>
     <row r="294">
@@ -15719,10 +15719,10 @@
         <v>1.47</v>
       </c>
       <c r="I294" t="n">
-        <v>1.0584</v>
+        <v>1.0209</v>
       </c>
       <c r="J294" t="n">
-        <v>16.9344</v>
+        <v>16.3344</v>
       </c>
     </row>
     <row r="295">
@@ -15759,10 +15759,10 @@
         <v>1.37</v>
       </c>
       <c r="I295" t="n">
-        <v>0.8899</v>
+        <v>0.8489</v>
       </c>
       <c r="J295" t="n">
-        <v>14.2384</v>
+        <v>13.5824</v>
       </c>
     </row>
     <row r="296">
@@ -15799,10 +15799,10 @@
         <v>1.15</v>
       </c>
       <c r="I296" t="n">
-        <v>0.3704</v>
+        <v>0.3871</v>
       </c>
       <c r="J296" t="n">
-        <v>5.9264</v>
+        <v>6.1936</v>
       </c>
     </row>
     <row r="297">
@@ -15839,10 +15839,10 @@
         <v>0.91</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.0969</v>
+        <v>-0.1153</v>
       </c>
       <c r="J297" t="n">
-        <v>-1.5504</v>
+        <v>-1.8448</v>
       </c>
     </row>
     <row r="298">
@@ -15879,10 +15879,10 @@
         <v>0.88</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1313</v>
+        <v>-0.1502</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.1008</v>
+        <v>-2.4032</v>
       </c>
     </row>
     <row r="299">
@@ -15919,10 +15919,10 @@
         <v>0.87</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1423</v>
+        <v>-0.1614</v>
       </c>
       <c r="J299" t="n">
-        <v>-2.2768</v>
+        <v>-2.5824</v>
       </c>
     </row>
     <row r="300">
@@ -15959,10 +15959,10 @@
         <v>0.67</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3369</v>
+        <v>-0.3534</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.3904</v>
+        <v>-5.6544</v>
       </c>
     </row>
     <row r="301">
@@ -15999,10 +15999,10 @@
         <v>0.6</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4027</v>
+        <v>-0.4163</v>
       </c>
       <c r="J301" t="n">
-        <v>-6.4432</v>
+        <v>-6.6608</v>
       </c>
     </row>
     <row r="302">
@@ -16039,10 +16039,10 @@
         <v>1.99</v>
       </c>
       <c r="I302" t="n">
-        <v>1.7926</v>
+        <v>1.7821</v>
       </c>
       <c r="J302" t="n">
-        <v>43.0224</v>
+        <v>42.7704</v>
       </c>
     </row>
     <row r="303">
@@ -16079,10 +16079,10 @@
         <v>1.43</v>
       </c>
       <c r="I303" t="n">
-        <v>1.0782</v>
+        <v>1.0281</v>
       </c>
       <c r="J303" t="n">
-        <v>25.8768</v>
+        <v>24.6744</v>
       </c>
     </row>
     <row r="304">
@@ -16119,10 +16119,10 @@
         <v>0.95</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2226</v>
+        <v>-0.2178</v>
       </c>
       <c r="J304" t="n">
-        <v>-5.3424</v>
+        <v>-5.2272</v>
       </c>
     </row>
     <row r="305">
@@ -16159,10 +16159,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I305" t="n">
-        <v>-1.2322</v>
+        <v>-1.114</v>
       </c>
       <c r="J305" t="n">
-        <v>-29.5728</v>
+        <v>-26.736</v>
       </c>
     </row>
     <row r="306">
@@ -16199,10 +16199,10 @@
         <v>0.54</v>
       </c>
       <c r="I306" t="n">
-        <v>-1.2785</v>
+        <v>-1.1534</v>
       </c>
       <c r="J306" t="n">
-        <v>-30.684</v>
+        <v>-27.6816</v>
       </c>
     </row>
     <row r="307">
@@ -16239,10 +16239,10 @@
         <v>1.48</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8934</v>
+        <v>0.8495</v>
       </c>
       <c r="J307" t="n">
-        <v>21.4416</v>
+        <v>20.388</v>
       </c>
     </row>
     <row r="308">
@@ -16279,10 +16279,10 @@
         <v>1.19</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4033</v>
+        <v>0.4042</v>
       </c>
       <c r="J308" t="n">
-        <v>9.6792</v>
+        <v>9.700799999999999</v>
       </c>
     </row>
     <row r="309">
@@ -16319,10 +16319,10 @@
         <v>0.99</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0259</v>
+        <v>-0.0293</v>
       </c>
       <c r="J309" t="n">
-        <v>-0.6216</v>
+        <v>-0.7032</v>
       </c>
     </row>
     <row r="310">
@@ -16359,10 +16359,10 @@
         <v>0.93</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1064</v>
+        <v>-0.1165</v>
       </c>
       <c r="J310" t="n">
-        <v>-2.5536</v>
+        <v>-2.796</v>
       </c>
     </row>
     <row r="311">
@@ -16399,10 +16399,10 @@
         <v>0.71</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3332</v>
+        <v>-0.3436</v>
       </c>
       <c r="J311" t="n">
-        <v>-7.9968</v>
+        <v>-8.2464</v>
       </c>
     </row>
     <row r="312">
@@ -16439,10 +16439,10 @@
         <v>1.8</v>
       </c>
       <c r="I312" t="n">
-        <v>1.4529</v>
+        <v>1.4449</v>
       </c>
       <c r="J312" t="n">
-        <v>26.1522</v>
+        <v>26.0082</v>
       </c>
     </row>
     <row r="313">
@@ -16479,10 +16479,10 @@
         <v>1.42</v>
       </c>
       <c r="I313" t="n">
-        <v>0.9969</v>
+        <v>0.9489</v>
       </c>
       <c r="J313" t="n">
-        <v>17.9442</v>
+        <v>17.0802</v>
       </c>
     </row>
     <row r="314">
@@ -16519,10 +16519,10 @@
         <v>1.4</v>
       </c>
       <c r="I314" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9142</v>
       </c>
       <c r="J314" t="n">
-        <v>17.3376</v>
+        <v>16.4556</v>
       </c>
     </row>
     <row r="315">
@@ -16559,10 +16559,10 @@
         <v>1.26</v>
       </c>
       <c r="I315" t="n">
-        <v>0.6584</v>
+        <v>0.6421</v>
       </c>
       <c r="J315" t="n">
-        <v>11.8512</v>
+        <v>11.5578</v>
       </c>
     </row>
     <row r="316">
@@ -16599,10 +16599,10 @@
         <v>1.26</v>
       </c>
       <c r="I316" t="n">
-        <v>0.6584</v>
+        <v>0.6421</v>
       </c>
       <c r="J316" t="n">
-        <v>11.8512</v>
+        <v>11.5578</v>
       </c>
     </row>
     <row r="317">
@@ -16639,10 +16639,10 @@
         <v>1.46</v>
       </c>
       <c r="I317" t="n">
-        <v>0.9597</v>
+        <v>0.8969</v>
       </c>
       <c r="J317" t="n">
-        <v>17.2746</v>
+        <v>16.1442</v>
       </c>
     </row>
     <row r="318">
@@ -16679,10 +16679,10 @@
         <v>0.88</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1428</v>
+        <v>-0.1591</v>
       </c>
       <c r="J318" t="n">
-        <v>-2.5704</v>
+        <v>-2.8638</v>
       </c>
     </row>
     <row r="319">
@@ -16719,10 +16719,10 @@
         <v>0.85</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1729</v>
+        <v>-0.1899</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.1122</v>
+        <v>-3.4182</v>
       </c>
     </row>
     <row r="320">
@@ -16759,10 +16759,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3295</v>
+        <v>-0.3441</v>
       </c>
       <c r="J320" t="n">
-        <v>-5.931</v>
+        <v>-6.1938</v>
       </c>
     </row>
     <row r="321">
@@ -16799,10 +16799,10 @@
         <v>0.46</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5421</v>
+        <v>-0.5463</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.7578</v>
+        <v>-9.833399999999999</v>
       </c>
     </row>
     <row r="322">
@@ -16839,10 +16839,10 @@
         <v>1.51</v>
       </c>
       <c r="I322" t="n">
-        <v>1.1687</v>
+        <v>1.1307</v>
       </c>
       <c r="J322" t="n">
-        <v>28.0488</v>
+        <v>27.1368</v>
       </c>
     </row>
     <row r="323">
@@ -16879,10 +16879,10 @@
         <v>1.43</v>
       </c>
       <c r="I323" t="n">
-        <v>1.0638</v>
+        <v>1.0139</v>
       </c>
       <c r="J323" t="n">
-        <v>25.5312</v>
+        <v>24.3336</v>
       </c>
     </row>
     <row r="324">
@@ -16919,10 +16919,10 @@
         <v>1.05</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1656</v>
+        <v>0.1787</v>
       </c>
       <c r="J324" t="n">
-        <v>3.9744</v>
+        <v>4.2888</v>
       </c>
     </row>
     <row r="325">
@@ -16959,10 +16959,10 @@
         <v>0.91</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3604</v>
+        <v>-0.3434</v>
       </c>
       <c r="J325" t="n">
-        <v>-8.6496</v>
+        <v>-8.2416</v>
       </c>
     </row>
     <row r="326">
@@ -16999,10 +16999,10 @@
         <v>0.83</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5832000000000001</v>
+        <v>-0.5458</v>
       </c>
       <c r="J326" t="n">
-        <v>-13.9968</v>
+        <v>-13.0992</v>
       </c>
     </row>
     <row r="327">
@@ -17039,10 +17039,10 @@
         <v>1.11</v>
       </c>
       <c r="I327" t="n">
-        <v>0.296</v>
+        <v>0.2933</v>
       </c>
       <c r="J327" t="n">
-        <v>7.104</v>
+        <v>7.0392</v>
       </c>
     </row>
     <row r="328">
@@ -17079,10 +17079,10 @@
         <v>1.11</v>
       </c>
       <c r="I328" t="n">
-        <v>0.296</v>
+        <v>0.2933</v>
       </c>
       <c r="J328" t="n">
-        <v>7.104</v>
+        <v>7.0392</v>
       </c>
     </row>
     <row r="329">
@@ -17119,10 +17119,10 @@
         <v>1.01</v>
       </c>
       <c r="I329" t="n">
-        <v>0.0583</v>
+        <v>0.0581</v>
       </c>
       <c r="J329" t="n">
-        <v>1.3992</v>
+        <v>1.3944</v>
       </c>
     </row>
     <row r="330">
@@ -17159,10 +17159,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2176</v>
+        <v>-0.2336</v>
       </c>
       <c r="J330" t="n">
-        <v>-5.2224</v>
+        <v>-5.6064</v>
       </c>
     </row>
     <row r="331">
@@ -17199,10 +17199,10 @@
         <v>0.49</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5191</v>
+        <v>-0.5241</v>
       </c>
       <c r="J331" t="n">
-        <v>-12.4584</v>
+        <v>-12.5784</v>
       </c>
     </row>
     <row r="332">
@@ -17239,10 +17239,10 @@
         <v>1.69</v>
       </c>
       <c r="I332" t="n">
-        <v>1.3291</v>
+        <v>1.3131</v>
       </c>
       <c r="J332" t="n">
-        <v>23.9238</v>
+        <v>23.6358</v>
       </c>
     </row>
     <row r="333">
@@ -17279,10 +17279,10 @@
         <v>1.54</v>
       </c>
       <c r="I333" t="n">
-        <v>1.1512</v>
+        <v>1.1226</v>
       </c>
       <c r="J333" t="n">
-        <v>20.7216</v>
+        <v>20.2068</v>
       </c>
     </row>
     <row r="334">
@@ -17319,10 +17319,10 @@
         <v>1.48</v>
       </c>
       <c r="I334" t="n">
-        <v>1.0789</v>
+        <v>1.043</v>
       </c>
       <c r="J334" t="n">
-        <v>19.4202</v>
+        <v>18.774</v>
       </c>
     </row>
     <row r="335">
@@ -17359,10 +17359,10 @@
         <v>1.27</v>
       </c>
       <c r="I335" t="n">
-        <v>0.6858</v>
+        <v>0.6656</v>
       </c>
       <c r="J335" t="n">
-        <v>12.3444</v>
+        <v>11.9808</v>
       </c>
     </row>
     <row r="336">
@@ -17399,10 +17399,10 @@
         <v>1.06</v>
       </c>
       <c r="I336" t="n">
-        <v>0.1361</v>
+        <v>0.1661</v>
       </c>
       <c r="J336" t="n">
-        <v>2.4498</v>
+        <v>2.9898</v>
       </c>
     </row>
     <row r="337">
@@ -17439,10 +17439,10 @@
         <v>1.1</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3179</v>
+        <v>0.3049</v>
       </c>
       <c r="J337" t="n">
-        <v>5.7222</v>
+        <v>5.4882</v>
       </c>
     </row>
     <row r="338">
@@ -17479,10 +17479,10 @@
         <v>0.9</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1127</v>
+        <v>-0.1304</v>
       </c>
       <c r="J338" t="n">
-        <v>-2.0286</v>
+        <v>-2.3472</v>
       </c>
     </row>
     <row r="339">
@@ -17519,10 +17519,10 @@
         <v>0.68</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.3306</v>
+        <v>-0.3468</v>
       </c>
       <c r="J339" t="n">
-        <v>-5.9508</v>
+        <v>-6.2424</v>
       </c>
     </row>
     <row r="340">
@@ -17559,10 +17559,10 @@
         <v>0.68</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3306</v>
+        <v>-0.3468</v>
       </c>
       <c r="J340" t="n">
-        <v>-5.9508</v>
+        <v>-6.2424</v>
       </c>
     </row>
     <row r="341">
@@ -17599,10 +17599,10 @@
         <v>0.68</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3306</v>
+        <v>-0.3468</v>
       </c>
       <c r="J341" t="n">
-        <v>-5.9508</v>
+        <v>-6.2424</v>
       </c>
     </row>
     <row r="342">
@@ -17639,10 +17639,10 @@
         <v>1.38</v>
       </c>
       <c r="I342" t="n">
-        <v>0.5658</v>
+        <v>0.5563</v>
       </c>
       <c r="J342" t="n">
-        <v>13.5792</v>
+        <v>13.3512</v>
       </c>
     </row>
     <row r="343">
@@ -17679,10 +17679,10 @@
         <v>1.06</v>
       </c>
       <c r="I343" t="n">
-        <v>0.1186</v>
+        <v>0.1295</v>
       </c>
       <c r="J343" t="n">
-        <v>2.8464</v>
+        <v>3.108</v>
       </c>
     </row>
     <row r="344">
@@ -17719,10 +17719,10 @@
         <v>1.01</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0255</v>
+        <v>0.0316</v>
       </c>
       <c r="J344" t="n">
-        <v>0.612</v>
+        <v>0.7584</v>
       </c>
     </row>
     <row r="345">
@@ -17759,10 +17759,10 @@
         <v>0.89</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1493</v>
+        <v>-0.1614</v>
       </c>
       <c r="J345" t="n">
-        <v>-3.5832</v>
+        <v>-3.8736</v>
       </c>
     </row>
     <row r="346">
@@ -17799,10 +17799,10 @@
         <v>0.84</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2025</v>
+        <v>-0.2151</v>
       </c>
       <c r="J346" t="n">
-        <v>-4.86</v>
+        <v>-5.1624</v>
       </c>
     </row>
     <row r="347">
@@ -17839,10 +17839,10 @@
         <v>1.78</v>
       </c>
       <c r="I347" t="n">
-        <v>0.958</v>
+        <v>0.9304</v>
       </c>
       <c r="J347" t="n">
-        <v>22.992</v>
+        <v>22.3296</v>
       </c>
     </row>
     <row r="348">
@@ -17879,10 +17879,10 @@
         <v>1.17</v>
       </c>
       <c r="I348" t="n">
-        <v>0.2579</v>
+        <v>0.2725</v>
       </c>
       <c r="J348" t="n">
-        <v>6.1896</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="349">
@@ -17919,10 +17919,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.1055</v>
       </c>
       <c r="J349" t="n">
-        <v>-2.3184</v>
+        <v>-2.532</v>
       </c>
     </row>
     <row r="350">
@@ -17959,10 +17959,10 @@
         <v>0.82</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2278</v>
+        <v>-0.2394</v>
       </c>
       <c r="J350" t="n">
-        <v>-5.4672</v>
+        <v>-5.7456</v>
       </c>
     </row>
     <row r="351">
@@ -17999,10 +17999,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3541</v>
+        <v>-0.3635</v>
       </c>
       <c r="J351" t="n">
-        <v>-8.4984</v>
+        <v>-8.724</v>
       </c>
     </row>
     <row r="352">
@@ -18039,10 +18039,10 @@
         <v>1.78</v>
       </c>
       <c r="I352" t="n">
-        <v>1.474</v>
+        <v>1.4596</v>
       </c>
       <c r="J352" t="n">
-        <v>29.48</v>
+        <v>29.192</v>
       </c>
     </row>
     <row r="353">
@@ -18079,10 +18079,10 @@
         <v>1.46</v>
       </c>
       <c r="I353" t="n">
-        <v>1.0789</v>
+        <v>1.0373</v>
       </c>
       <c r="J353" t="n">
-        <v>21.578</v>
+        <v>20.746</v>
       </c>
     </row>
     <row r="354">
@@ -18119,10 +18119,10 @@
         <v>1.2</v>
       </c>
       <c r="I354" t="n">
-        <v>0.5515</v>
+        <v>0.5394</v>
       </c>
       <c r="J354" t="n">
-        <v>11.03</v>
+        <v>10.788</v>
       </c>
     </row>
     <row r="355">
@@ -18159,10 +18159,10 @@
         <v>0.92</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.3571</v>
+        <v>-0.3345</v>
       </c>
       <c r="J355" t="n">
-        <v>-7.142</v>
+        <v>-6.69</v>
       </c>
     </row>
     <row r="356">
@@ -18199,10 +18199,10 @@
         <v>0.9</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.4161</v>
+        <v>-0.389</v>
       </c>
       <c r="J356" t="n">
-        <v>-8.321999999999999</v>
+        <v>-7.78</v>
       </c>
     </row>
     <row r="357">
@@ -18239,10 +18239,10 @@
         <v>1.05</v>
       </c>
       <c r="I357" t="n">
-        <v>0.1693</v>
+        <v>0.1697</v>
       </c>
       <c r="J357" t="n">
-        <v>3.386</v>
+        <v>3.394</v>
       </c>
     </row>
     <row r="358">
@@ -18279,10 +18279,10 @@
         <v>0.93</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.09</v>
+        <v>-0.1039</v>
       </c>
       <c r="J358" t="n">
-        <v>-1.8</v>
+        <v>-2.078</v>
       </c>
     </row>
     <row r="359">
@@ -18319,10 +18319,10 @@
         <v>0.87</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.1547</v>
+        <v>-0.1708</v>
       </c>
       <c r="J359" t="n">
-        <v>-3.094</v>
+        <v>-3.416</v>
       </c>
     </row>
     <row r="360">
@@ -18359,10 +18359,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.2157</v>
+        <v>-0.2321</v>
       </c>
       <c r="J360" t="n">
-        <v>-4.314</v>
+        <v>-4.642</v>
       </c>
     </row>
     <row r="361">
@@ -18399,10 +18399,10 @@
         <v>0.79</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.2355</v>
+        <v>-0.2518</v>
       </c>
       <c r="J361" t="n">
-        <v>-4.71</v>
+        <v>-5.036</v>
       </c>
     </row>
     <row r="362">
@@ -18439,10 +18439,10 @@
         <v>1.49</v>
       </c>
       <c r="I362" t="n">
-        <v>1.104</v>
+        <v>1.0686</v>
       </c>
       <c r="J362" t="n">
-        <v>19.872</v>
+        <v>19.2348</v>
       </c>
     </row>
     <row r="363">
@@ -18479,10 +18479,10 @@
         <v>1.47</v>
       </c>
       <c r="I363" t="n">
-        <v>1.0791</v>
+        <v>1.0404</v>
       </c>
       <c r="J363" t="n">
-        <v>19.4238</v>
+        <v>18.7272</v>
       </c>
     </row>
     <row r="364">
@@ -18519,10 +18519,10 @@
         <v>1.22</v>
       </c>
       <c r="I364" t="n">
-        <v>0.586</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="J364" t="n">
-        <v>10.548</v>
+        <v>10.3158</v>
       </c>
     </row>
     <row r="365">
@@ -18559,10 +18559,10 @@
         <v>1.22</v>
       </c>
       <c r="I365" t="n">
-        <v>0.586</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="J365" t="n">
-        <v>10.548</v>
+        <v>10.3158</v>
       </c>
     </row>
     <row r="366">
@@ -18599,10 +18599,10 @@
         <v>1.2</v>
       </c>
       <c r="I366" t="n">
-        <v>0.5373</v>
+        <v>0.5296</v>
       </c>
       <c r="J366" t="n">
-        <v>9.6714</v>
+        <v>9.5328</v>
       </c>
     </row>
     <row r="367">
@@ -18639,10 +18639,10 @@
         <v>1.21</v>
       </c>
       <c r="I367" t="n">
-        <v>0.4879</v>
+        <v>0.4733</v>
       </c>
       <c r="J367" t="n">
-        <v>8.7822</v>
+        <v>8.519399999999999</v>
       </c>
     </row>
     <row r="368">
@@ -18679,10 +18679,10 @@
         <v>1.21</v>
       </c>
       <c r="I368" t="n">
-        <v>0.4879</v>
+        <v>0.4733</v>
       </c>
       <c r="J368" t="n">
-        <v>8.7822</v>
+        <v>8.519399999999999</v>
       </c>
     </row>
     <row r="369">
@@ -18719,10 +18719,10 @@
         <v>0.97</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.0429</v>
+        <v>-0.0528</v>
       </c>
       <c r="J369" t="n">
-        <v>-0.7722</v>
+        <v>-0.9504</v>
       </c>
     </row>
     <row r="370">
@@ -18759,10 +18759,10 @@
         <v>0.79</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.2391</v>
+        <v>-0.2545</v>
       </c>
       <c r="J370" t="n">
-        <v>-4.3038</v>
+        <v>-4.581</v>
       </c>
     </row>
     <row r="371">
@@ -18799,10 +18799,10 @@
         <v>0.41</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.5919</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="J371" t="n">
-        <v>-10.6542</v>
+        <v>-10.6596</v>
       </c>
     </row>
     <row r="372">
@@ -18839,10 +18839,10 @@
         <v>1.51</v>
       </c>
       <c r="I372" t="n">
-        <v>1.1746</v>
+        <v>1.1359</v>
       </c>
       <c r="J372" t="n">
-        <v>34.0634</v>
+        <v>32.9411</v>
       </c>
     </row>
     <row r="373">
@@ -18879,10 +18879,10 @@
         <v>1.45</v>
       </c>
       <c r="I373" t="n">
-        <v>1.0957</v>
+        <v>1.0504</v>
       </c>
       <c r="J373" t="n">
-        <v>31.7753</v>
+        <v>30.4616</v>
       </c>
     </row>
     <row r="374">
@@ -18919,10 +18919,10 @@
         <v>1.2</v>
       </c>
       <c r="I374" t="n">
-        <v>0.5755</v>
+        <v>0.5557</v>
       </c>
       <c r="J374" t="n">
-        <v>16.6895</v>
+        <v>16.1153</v>
       </c>
     </row>
     <row r="375">
@@ -18959,10 +18959,10 @@
         <v>0.77</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.7336</v>
+        <v>-0.6804</v>
       </c>
       <c r="J375" t="n">
-        <v>-21.2744</v>
+        <v>-19.7316</v>
       </c>
     </row>
     <row r="376">
@@ -18999,10 +18999,10 @@
         <v>0.7</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.9074</v>
+        <v>-0.8328</v>
       </c>
       <c r="J376" t="n">
-        <v>-26.3146</v>
+        <v>-24.1512</v>
       </c>
     </row>
     <row r="377">
@@ -19039,10 +19039,10 @@
         <v>1.48</v>
       </c>
       <c r="I377" t="n">
-        <v>0.9061</v>
+        <v>0.8591</v>
       </c>
       <c r="J377" t="n">
-        <v>26.2769</v>
+        <v>24.9139</v>
       </c>
     </row>
     <row r="378">
@@ -19079,10 +19079,10 @@
         <v>1.26</v>
       </c>
       <c r="I378" t="n">
-        <v>0.5367</v>
+        <v>0.5258</v>
       </c>
       <c r="J378" t="n">
-        <v>15.5643</v>
+        <v>15.2482</v>
       </c>
     </row>
     <row r="379">
@@ -19119,10 +19119,10 @@
         <v>0.96</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="J379" t="n">
-        <v>-1.9198</v>
+        <v>-2.1692</v>
       </c>
     </row>
     <row r="380">
@@ -19159,10 +19159,10 @@
         <v>0.8</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.2425</v>
+        <v>-0.2551</v>
       </c>
       <c r="J380" t="n">
-        <v>-7.0325</v>
+        <v>-7.3979</v>
       </c>
     </row>
     <row r="381">
@@ -19199,10 +19199,10 @@
         <v>0.65</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3863</v>
+        <v>-0.3955</v>
       </c>
       <c r="J381" t="n">
-        <v>-11.2027</v>
+        <v>-11.4695</v>
       </c>
     </row>
     <row r="382">
@@ -19239,10 +19239,10 @@
         <v>1.75</v>
       </c>
       <c r="I382" t="n">
-        <v>1.4679</v>
+        <v>1.4483</v>
       </c>
       <c r="J382" t="n">
-        <v>35.2296</v>
+        <v>34.7592</v>
       </c>
     </row>
     <row r="383">
@@ -19279,10 +19279,10 @@
         <v>1.31</v>
       </c>
       <c r="I383" t="n">
-        <v>0.8288</v>
+        <v>0.7817</v>
       </c>
       <c r="J383" t="n">
-        <v>19.8912</v>
+        <v>18.7608</v>
       </c>
     </row>
     <row r="384">
@@ -19319,10 +19319,10 @@
         <v>1.14</v>
       </c>
       <c r="I384" t="n">
-        <v>0.4191</v>
+        <v>0.4154</v>
       </c>
       <c r="J384" t="n">
-        <v>10.0584</v>
+        <v>9.9696</v>
       </c>
     </row>
     <row r="385">
@@ -19359,10 +19359,10 @@
         <v>1.12</v>
       </c>
       <c r="I385" t="n">
-        <v>0.3665</v>
+        <v>0.3671</v>
       </c>
       <c r="J385" t="n">
-        <v>8.795999999999999</v>
+        <v>8.8104</v>
       </c>
     </row>
     <row r="386">
@@ -19399,10 +19399,10 @@
         <v>0.48</v>
       </c>
       <c r="I386" t="n">
-        <v>-1.4279</v>
+        <v>-1.2788</v>
       </c>
       <c r="J386" t="n">
-        <v>-34.2696</v>
+        <v>-30.6912</v>
       </c>
     </row>
     <row r="387">
@@ -19439,10 +19439,10 @@
         <v>1.34</v>
       </c>
       <c r="I387" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6642</v>
       </c>
       <c r="J387" t="n">
-        <v>16.608</v>
+        <v>15.9408</v>
       </c>
     </row>
     <row r="388">
@@ -19479,10 +19479,10 @@
         <v>1.1</v>
       </c>
       <c r="I388" t="n">
-        <v>0.25</v>
+        <v>0.2551</v>
       </c>
       <c r="J388" t="n">
-        <v>6</v>
+        <v>6.1224</v>
       </c>
     </row>
     <row r="389">
@@ -19519,10 +19519,10 @@
         <v>0.91</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.1215</v>
+        <v>-0.1342</v>
       </c>
       <c r="J389" t="n">
-        <v>-2.916</v>
+        <v>-3.2208</v>
       </c>
     </row>
     <row r="390">
@@ -19559,10 +19559,10 @@
         <v>0.82</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.2172</v>
+        <v>-0.2311</v>
       </c>
       <c r="J390" t="n">
-        <v>-5.2128</v>
+        <v>-5.5464</v>
       </c>
     </row>
     <row r="391">
@@ -19599,10 +19599,10 @@
         <v>0.76</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.2769</v>
+        <v>-0.2901</v>
       </c>
       <c r="J391" t="n">
-        <v>-6.6456</v>
+        <v>-6.9624</v>
       </c>
     </row>
     <row r="392">
@@ -19639,10 +19639,10 @@
         <v>1.93</v>
       </c>
       <c r="I392" t="n">
-        <v>1.6988</v>
+        <v>1.6878</v>
       </c>
       <c r="J392" t="n">
-        <v>40.7712</v>
+        <v>40.5072</v>
       </c>
     </row>
     <row r="393">
@@ -19679,10 +19679,10 @@
         <v>1.36</v>
       </c>
       <c r="I393" t="n">
-        <v>0.9502</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="J393" t="n">
-        <v>22.8048</v>
+        <v>21.3264</v>
       </c>
     </row>
     <row r="394">
@@ -19719,10 +19719,10 @@
         <v>1.01</v>
       </c>
       <c r="I394" t="n">
-        <v>0.0226</v>
+        <v>0.0376</v>
       </c>
       <c r="J394" t="n">
-        <v>0.5424</v>
+        <v>0.9024</v>
       </c>
     </row>
     <row r="395">
@@ -19759,10 +19759,10 @@
         <v>0.83</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.5806</v>
+        <v>-0.544</v>
       </c>
       <c r="J395" t="n">
-        <v>-13.9344</v>
+        <v>-13.056</v>
       </c>
     </row>
     <row r="396">
@@ -19799,10 +19799,10 @@
         <v>0.55</v>
       </c>
       <c r="I396" t="n">
-        <v>-1.2642</v>
+        <v>-1.14</v>
       </c>
       <c r="J396" t="n">
-        <v>-30.3408</v>
+        <v>-27.36</v>
       </c>
     </row>
     <row r="397">
@@ -19839,10 +19839,10 @@
         <v>1.12</v>
       </c>
       <c r="I397" t="n">
-        <v>0.3079</v>
+        <v>0.3065</v>
       </c>
       <c r="J397" t="n">
-        <v>7.3896</v>
+        <v>7.356</v>
       </c>
     </row>
     <row r="398">
@@ -19879,10 +19879,10 @@
         <v>0.99</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.0142</v>
+        <v>-0.0204</v>
       </c>
       <c r="J398" t="n">
-        <v>-0.3408</v>
+        <v>-0.4896</v>
       </c>
     </row>
     <row r="399">
@@ -19919,10 +19919,10 @@
         <v>0.95</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.0702</v>
+        <v>-0.0818</v>
       </c>
       <c r="J399" t="n">
-        <v>-1.6848</v>
+        <v>-1.9632</v>
       </c>
     </row>
     <row r="400">
@@ -19959,10 +19959,10 @@
         <v>0.95</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.0702</v>
+        <v>-0.0818</v>
       </c>
       <c r="J400" t="n">
-        <v>-1.6848</v>
+        <v>-1.9632</v>
       </c>
     </row>
     <row r="401">
@@ -19999,10 +19999,10 @@
         <v>0.64</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.3845</v>
+        <v>-0.3957</v>
       </c>
       <c r="J401" t="n">
-        <v>-9.228</v>
+        <v>-9.4968</v>
       </c>
     </row>
     <row r="402">
@@ -20039,10 +20039,10 @@
         <v>1.28</v>
       </c>
       <c r="I402" t="n">
-        <v>0.7684</v>
+        <v>0.7269</v>
       </c>
       <c r="J402" t="n">
-        <v>22.2836</v>
+        <v>21.0801</v>
       </c>
     </row>
     <row r="403">
@@ -20079,10 +20079,10 @@
         <v>1.25</v>
       </c>
       <c r="I403" t="n">
-        <v>0.6966</v>
+        <v>0.6636</v>
       </c>
       <c r="J403" t="n">
-        <v>20.2014</v>
+        <v>19.2444</v>
       </c>
     </row>
     <row r="404">
@@ -20119,10 +20119,10 @@
         <v>1.13</v>
       </c>
       <c r="I404" t="n">
-        <v>0.3979</v>
+        <v>0.3948</v>
       </c>
       <c r="J404" t="n">
-        <v>11.5391</v>
+        <v>11.4492</v>
       </c>
     </row>
     <row r="405">
@@ -20159,10 +20159,10 @@
         <v>1.07</v>
       </c>
       <c r="I405" t="n">
-        <v>0.2316</v>
+        <v>0.2402</v>
       </c>
       <c r="J405" t="n">
-        <v>6.7164</v>
+        <v>6.9658</v>
       </c>
     </row>
     <row r="406">
@@ -20199,10 +20199,10 @@
         <v>0.92</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.3263</v>
+        <v>-0.3128</v>
       </c>
       <c r="J406" t="n">
-        <v>-9.4627</v>
+        <v>-9.071199999999999</v>
       </c>
     </row>
     <row r="407">
@@ -20239,10 +20239,10 @@
         <v>1.41</v>
       </c>
       <c r="I407" t="n">
-        <v>0.8064</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="J407" t="n">
-        <v>23.3856</v>
+        <v>22.2604</v>
       </c>
     </row>
     <row r="408">
@@ -20279,10 +20279,10 @@
         <v>1.14</v>
       </c>
       <c r="I408" t="n">
-        <v>0.3268</v>
+        <v>0.3289</v>
       </c>
       <c r="J408" t="n">
-        <v>9.4772</v>
+        <v>9.5381</v>
       </c>
     </row>
     <row r="409">
@@ -20319,10 +20319,10 @@
         <v>1.03</v>
       </c>
       <c r="I409" t="n">
-        <v>0.0925</v>
+        <v>0.1005</v>
       </c>
       <c r="J409" t="n">
-        <v>2.6825</v>
+        <v>2.9145</v>
       </c>
     </row>
     <row r="410">
@@ -20359,10 +20359,10 @@
         <v>0.7</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.3358</v>
+        <v>-0.3473</v>
       </c>
       <c r="J410" t="n">
-        <v>-9.738200000000001</v>
+        <v>-10.0717</v>
       </c>
     </row>
     <row r="411">
@@ -20399,10 +20399,10 @@
         <v>0.7</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3358</v>
+        <v>-0.3473</v>
       </c>
       <c r="J411" t="n">
-        <v>-9.738200000000001</v>
+        <v>-10.0717</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7732/event_7732_evp_summary.xlsx
+++ b/database/event/7732/event_7732_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.8063</v>
+        <v>7.9887</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5069</v>
+        <v>4.6122</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9294</v>
+        <v>2.9546</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8063</v>
+        <v>7.9887</v>
       </c>
       <c r="F2" t="n">
         <v>1.6155</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4711</v>
+        <v>7.6635</v>
       </c>
       <c r="C3" t="n">
-        <v>4.3134</v>
+        <v>4.4244</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7768</v>
+        <v>2.8093</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4711</v>
+        <v>7.6635</v>
       </c>
       <c r="F3" t="n">
         <v>2.4769</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.6551</v>
+        <v>6.9846</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8422</v>
+        <v>4.0325</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4053</v>
+        <v>2.506</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6551</v>
+        <v>6.9846</v>
       </c>
       <c r="F4" t="n">
         <v>2.4614</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0955</v>
+        <v>5.2472</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9418</v>
+        <v>3.0294</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6954</v>
+        <v>1.73</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0955</v>
+        <v>5.2472</v>
       </c>
       <c r="F5" t="n">
         <v>1.977</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9698</v>
+        <v>4.1445</v>
       </c>
       <c r="C6" t="n">
-        <v>2.2919</v>
+        <v>2.3928</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1829</v>
+        <v>1.2374</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9698</v>
+        <v>4.1445</v>
       </c>
       <c r="F6" t="n">
         <v>2.3616</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7778</v>
+        <v>3.8799</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1811</v>
+        <v>2.24</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0955</v>
+        <v>1.1192</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7778</v>
+        <v>3.8799</v>
       </c>
       <c r="F7" t="n">
         <v>2.3193</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4399</v>
+        <v>3.5248</v>
       </c>
       <c r="C8" t="n">
-        <v>1.986</v>
+        <v>2.035</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9417</v>
+        <v>0.9606</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4399</v>
+        <v>3.5248</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4243</v>
+        <v>3.5819</v>
       </c>
       <c r="G8" t="n">
-        <v>3.0156</v>
+        <v>-0.2121</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4243</v>
+        <v>5.1147</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4243</v>
+        <v>5.2465</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0156</v>
+        <v>-0.2121</v>
       </c>
       <c r="K8" t="n">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="L8" t="n">
-        <v>172</v>
+        <v>64</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4399</v>
+        <v>5.0344</v>
       </c>
       <c r="N8" t="n">
-        <v>214</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3698</v>
+        <v>3.4516</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9455</v>
+        <v>1.9927</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3698</v>
+        <v>3.4516</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5819</v>
+        <v>0.4243</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2121</v>
+        <v>3.0156</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1147</v>
+        <v>0.4243</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2465</v>
+        <v>0.4243</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2121</v>
+        <v>3.0156</v>
       </c>
       <c r="K9" t="n">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="L9" t="n">
-        <v>64</v>
+        <v>172</v>
       </c>
       <c r="M9" t="n">
-        <v>5.0344</v>
+        <v>3.4399</v>
       </c>
       <c r="N9" t="n">
-        <v>180</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.837</v>
+        <v>2.9419</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6379</v>
+        <v>1.6985</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6673</v>
+        <v>0.7003</v>
       </c>
       <c r="E10" t="n">
-        <v>2.837</v>
+        <v>2.9419</v>
       </c>
       <c r="F10" t="n">
         <v>1.5714</v>
@@ -906,185 +906,185 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.668</v>
+        <v>2.8012</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5403</v>
+        <v>1.6172</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5903</v>
+        <v>0.6374</v>
       </c>
       <c r="E11" t="n">
-        <v>2.668</v>
+        <v>2.8012</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1187</v>
+        <v>0.3132</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5493</v>
+        <v>2.3518</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1187</v>
+        <v>0.3132</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1187</v>
+        <v>0.3132</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5493</v>
+        <v>2.3518</v>
       </c>
       <c r="K11" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L11" t="n">
         <v>117</v>
       </c>
       <c r="M11" t="n">
-        <v>2.668</v>
+        <v>2.665</v>
       </c>
       <c r="N11" t="n">
-        <v>179</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.665</v>
+        <v>2.7128</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5386</v>
+        <v>1.5662</v>
       </c>
       <c r="D12" t="n">
-        <v>0.589</v>
+        <v>0.5979</v>
       </c>
       <c r="E12" t="n">
-        <v>2.665</v>
+        <v>2.7128</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3132</v>
+        <v>2.1187</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3518</v>
+        <v>0.5493</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3132</v>
+        <v>2.1187</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3132</v>
+        <v>2.1187</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3518</v>
+        <v>0.5493</v>
       </c>
       <c r="K12" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="L12" t="n">
         <v>117</v>
       </c>
       <c r="M12" t="n">
-        <v>2.665</v>
+        <v>2.668</v>
       </c>
       <c r="N12" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6259</v>
+        <v>2.7087</v>
       </c>
       <c r="C13" t="n">
-        <v>1.516</v>
+        <v>1.5638</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5712</v>
+        <v>0.5961</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6259</v>
+        <v>2.7087</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4324</v>
+        <v>2.4686</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1935</v>
+        <v>0.1353</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4324</v>
+        <v>2.6781</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4324</v>
+        <v>2.7471</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1935</v>
+        <v>0.1353</v>
       </c>
       <c r="K13" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="L13" t="n">
-        <v>174</v>
+        <v>64</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6259</v>
+        <v>2.8824</v>
       </c>
       <c r="N13" t="n">
-        <v>227</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6039</v>
+        <v>2.6833</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5033</v>
+        <v>1.5492</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5611</v>
+        <v>0.5848</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6039</v>
+        <v>2.6833</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4686</v>
+        <v>0.4324</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1353</v>
+        <v>2.1935</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6781</v>
+        <v>0.4324</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7471</v>
+        <v>0.4324</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1353</v>
+        <v>2.1935</v>
       </c>
       <c r="K14" t="n">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="L14" t="n">
-        <v>64</v>
+        <v>174</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8824</v>
+        <v>2.6259</v>
       </c>
       <c r="N14" t="n">
-        <v>180</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1143</v>
+        <v>2.1892</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2207</v>
+        <v>1.2639</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3383</v>
+        <v>0.364</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1143</v>
+        <v>2.1892</v>
       </c>
       <c r="F15" t="n">
         <v>2.1143</v>
@@ -1136,357 +1136,357 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>0SAMAS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0295</v>
+        <v>2.1738</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1717</v>
+        <v>1.255</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2997</v>
+        <v>0.3572</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0295</v>
+        <v>2.1738</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.3554</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3465</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.3554</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.3554</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3465</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="L16" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0295</v>
+        <v>1.3554</v>
       </c>
       <c r="N16" t="n">
-        <v>179</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9346</v>
+        <v>1.9942</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1169</v>
+        <v>1.1513</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2565</v>
+        <v>0.2769</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9346</v>
+        <v>1.9942</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3309</v>
+        <v>0.7947</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6037</v>
+        <v>1.054</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3309</v>
+        <v>0.7947</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3309</v>
+        <v>0.7947</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6037</v>
+        <v>1.054</v>
       </c>
       <c r="K17" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L17" t="n">
-        <v>172</v>
+        <v>69</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9346</v>
+        <v>1.8487</v>
       </c>
       <c r="N17" t="n">
-        <v>214</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9259</v>
+        <v>1.9768</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1119</v>
+        <v>1.1413</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2525</v>
+        <v>0.2692</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9259</v>
+        <v>1.9768</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5543</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3716</v>
+        <v>1.3465</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5543</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5543</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3716</v>
+        <v>1.3465</v>
       </c>
       <c r="K18" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="L18" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9259</v>
+        <v>2.0295</v>
       </c>
       <c r="N18" t="n">
-        <v>102</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8899</v>
+        <v>1.9696</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0911</v>
+        <v>1.1371</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2361</v>
+        <v>0.266</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8899</v>
+        <v>1.9696</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8899</v>
+        <v>1.5543</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.3716</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8899</v>
+        <v>1.5543</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8899</v>
+        <v>1.5543</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.3716</v>
       </c>
       <c r="K19" t="n">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8899</v>
+        <v>1.9259</v>
       </c>
       <c r="N19" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8487</v>
+        <v>1.9532</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0673</v>
+        <v>1.1277</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2174</v>
+        <v>0.2586</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8487</v>
+        <v>1.9532</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7947</v>
+        <v>1.9176</v>
       </c>
       <c r="G20" t="n">
-        <v>1.054</v>
+        <v>-0.1279</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7947</v>
+        <v>1.9176</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7947</v>
+        <v>1.9176</v>
       </c>
       <c r="J20" t="n">
-        <v>1.054</v>
+        <v>-0.1279</v>
       </c>
       <c r="K20" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="L20" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8487</v>
+        <v>1.7897</v>
       </c>
       <c r="N20" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.8217</v>
+        <v>1.8976</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0517</v>
+        <v>1.0956</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2051</v>
+        <v>0.2338</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8217</v>
+        <v>1.8976</v>
       </c>
       <c r="F21" t="n">
-        <v>2.8217</v>
+        <v>0.3309</v>
       </c>
       <c r="G21" t="n">
-        <v>-1</v>
+        <v>1.6037</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4509</v>
+        <v>0.3309</v>
       </c>
       <c r="I21" t="n">
-        <v>3.4509</v>
+        <v>0.3309</v>
       </c>
       <c r="J21" t="n">
-        <v>-1</v>
+        <v>1.6037</v>
       </c>
       <c r="K21" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L21" t="n">
-        <v>69</v>
+        <v>172</v>
       </c>
       <c r="M21" t="n">
-        <v>2.4509</v>
+        <v>1.9346</v>
       </c>
       <c r="N21" t="n">
-        <v>102</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.7897</v>
+        <v>1.8898</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0333</v>
+        <v>1.0911</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1905</v>
+        <v>0.2303</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7897</v>
+        <v>1.8898</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9176</v>
+        <v>1.8899</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1279</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9176</v>
+        <v>1.8899</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9176</v>
+        <v>1.8899</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1279</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="L22" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.7897</v>
+        <v>1.8899</v>
       </c>
       <c r="N22" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.6977</v>
+        <v>1.691</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9801</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1486</v>
+        <v>0.1415</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6977</v>
+        <v>1.691</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8535</v>
+        <v>2.8217</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8442</v>
+        <v>-1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8535</v>
+        <v>3.4509</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8535</v>
+        <v>3.4509</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8442</v>
+        <v>-1</v>
       </c>
       <c r="K23" t="n">
         <v>33</v>
@@ -1495,7 +1495,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="n">
-        <v>1.6977</v>
+        <v>2.4509</v>
       </c>
       <c r="N23" t="n">
         <v>102</v>
@@ -1504,369 +1504,369 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6486</v>
+        <v>1.6673</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9518</v>
+        <v>0.9626</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1263</v>
+        <v>0.1309</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6486</v>
+        <v>1.6673</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5616</v>
+        <v>0.8535</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.913</v>
+        <v>0.8442</v>
       </c>
       <c r="H24" t="n">
-        <v>2.8816</v>
+        <v>0.8535</v>
       </c>
       <c r="I24" t="n">
-        <v>2.8816</v>
+        <v>0.8535</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.913</v>
+        <v>0.8442</v>
       </c>
       <c r="K24" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L24" t="n">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9686</v>
+        <v>1.6977</v>
       </c>
       <c r="N24" t="n">
-        <v>156</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.58</v>
+        <v>1.6596</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9122</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.095</v>
+        <v>0.1275</v>
       </c>
       <c r="E25" t="n">
-        <v>1.58</v>
+        <v>1.6596</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6406</v>
+        <v>2.5616</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0606</v>
+        <v>-0.913</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6406</v>
+        <v>2.8816</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6829</v>
+        <v>2.8816</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0606</v>
+        <v>-0.913</v>
       </c>
       <c r="K25" t="n">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="L25" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="M25" t="n">
-        <v>1.6223</v>
+        <v>1.9686</v>
       </c>
       <c r="N25" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.4496</v>
+        <v>1.5399</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8369</v>
+        <v>0.889</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0357</v>
+        <v>0.074</v>
       </c>
       <c r="E26" t="n">
-        <v>1.4496</v>
+        <v>1.5399</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4496</v>
+        <v>1.6406</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.0606</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4496</v>
+        <v>1.6406</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4496</v>
+        <v>1.6829</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.0606</v>
       </c>
       <c r="K26" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4496</v>
+        <v>1.6223</v>
       </c>
       <c r="N26" t="n">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3889</v>
+        <v>1.5375</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.8877</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0081</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3889</v>
+        <v>1.5375</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9711</v>
+        <v>1.2604</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4178</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9711</v>
+        <v>1.2604</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9711</v>
+        <v>1.2604</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4178</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="L27" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.3889</v>
+        <v>1.2604</v>
       </c>
       <c r="N27" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0SAMAS</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3554</v>
+        <v>1.4477</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7825</v>
+        <v>0.8358</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0072</v>
+        <v>0.0328</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3554</v>
+        <v>1.4477</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3554</v>
+        <v>0.9711</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.4178</v>
       </c>
       <c r="H28" t="n">
-        <v>1.3554</v>
+        <v>0.9711</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3554</v>
+        <v>0.9711</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.4178</v>
       </c>
       <c r="K28" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3554</v>
+        <v>1.3889</v>
       </c>
       <c r="N28" t="n">
-        <v>21</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.2975</v>
+        <v>1.4288</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7491</v>
+        <v>0.8249</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0336</v>
+        <v>0.0244</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2975</v>
+        <v>1.4288</v>
       </c>
       <c r="F29" t="n">
-        <v>2.2426</v>
+        <v>1.4496</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.9451000000000001</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.2426</v>
+        <v>1.4496</v>
       </c>
       <c r="I29" t="n">
-        <v>2.2426</v>
+        <v>1.4496</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.9451000000000001</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="L29" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2975</v>
+        <v>1.4496</v>
       </c>
       <c r="N29" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.2604</v>
+        <v>1.3698</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7277</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0504</v>
+        <v>-0.002</v>
       </c>
       <c r="E30" t="n">
-        <v>1.2604</v>
+        <v>1.3698</v>
       </c>
       <c r="F30" t="n">
-        <v>1.2604</v>
+        <v>1.4175</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.2256</v>
       </c>
       <c r="H30" t="n">
-        <v>1.2604</v>
+        <v>1.4175</v>
       </c>
       <c r="I30" t="n">
-        <v>1.2604</v>
+        <v>1.4175</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.2256</v>
       </c>
       <c r="K30" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M30" t="n">
-        <v>1.2604</v>
+        <v>1.1919</v>
       </c>
       <c r="N30" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1919</v>
+        <v>1.3379</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6881</v>
+        <v>0.7724</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.0162</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1919</v>
+        <v>1.3379</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4175</v>
+        <v>2.2426</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.2256</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4175</v>
+        <v>2.2426</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4175</v>
+        <v>2.2426</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.2256</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="L31" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1919</v>
+        <v>1.2975</v>
       </c>
       <c r="N31" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32">
@@ -1876,16 +1876,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1271</v>
+        <v>1.1726</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1111</v>
+        <v>-0.09</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1271</v>
+        <v>1.1726</v>
       </c>
       <c r="F32" t="n">
         <v>1.1271</v>
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1204</v>
+        <v>1.1622</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6469</v>
+        <v>0.671</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1142</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1204</v>
+        <v>1.1622</v>
       </c>
       <c r="F33" t="n">
         <v>0.0235</v>
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0642</v>
+        <v>1.0475</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.6048</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1398</v>
+        <v>-0.1459</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0642</v>
+        <v>1.0475</v>
       </c>
       <c r="F34" t="n">
         <v>0.4493</v>
@@ -2010,599 +2010,599 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9705</v>
+        <v>0.8811</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5603</v>
+        <v>0.5087</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1824</v>
+        <v>-0.2203</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9705</v>
+        <v>0.8811</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9705</v>
+        <v>0.8213</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9705</v>
+        <v>0.8213</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9705</v>
+        <v>0.8213</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9705</v>
+        <v>0.8213</v>
       </c>
       <c r="N35" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8213</v>
+        <v>0.8626</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4742</v>
+        <v>0.498</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2503</v>
+        <v>-0.2285</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8213</v>
+        <v>0.8626</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8213</v>
+        <v>0.9705</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8213</v>
+        <v>0.9705</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8213</v>
+        <v>0.9705</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8213</v>
+        <v>0.9705</v>
       </c>
       <c r="N36" t="n">
-        <v>93</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7325</v>
+        <v>0.8137</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4229</v>
+        <v>0.4698</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2908</v>
+        <v>-0.2504</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7325</v>
+        <v>0.8137</v>
       </c>
       <c r="F37" t="n">
-        <v>1.18</v>
+        <v>0.4954</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.4475</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.18</v>
+        <v>0.4954</v>
       </c>
       <c r="I37" t="n">
-        <v>1.18</v>
+        <v>0.4954</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.4475</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="L37" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7324999999999999</v>
+        <v>0.4954</v>
       </c>
       <c r="N37" t="n">
-        <v>122</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6915</v>
+        <v>0.7268</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3992</v>
+        <v>0.4196</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3094</v>
+        <v>-0.2892</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6915</v>
+        <v>0.7268</v>
       </c>
       <c r="F38" t="n">
-        <v>1.2465</v>
+        <v>1.18</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.555</v>
+        <v>-0.4475</v>
       </c>
       <c r="H38" t="n">
-        <v>1.2465</v>
+        <v>1.18</v>
       </c>
       <c r="I38" t="n">
-        <v>1.2465</v>
+        <v>1.18</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.555</v>
+        <v>-0.4475</v>
       </c>
       <c r="K38" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L38" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6914999999999999</v>
+        <v>0.7324999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5201</v>
+        <v>0.5836</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3003</v>
+        <v>0.3369</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3874</v>
+        <v>-0.3531</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5201</v>
+        <v>0.5836</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1166</v>
+        <v>0.4927</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4035</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1166</v>
+        <v>0.4927</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1196</v>
+        <v>0.4927</v>
       </c>
       <c r="J39" t="n">
-        <v>0.4035</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="L39" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5231</v>
+        <v>0.4927</v>
       </c>
       <c r="N39" t="n">
-        <v>180</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5068</v>
+        <v>0.5432</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2926</v>
+        <v>0.3136</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3935</v>
+        <v>-0.3712</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5068</v>
+        <v>0.5432</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4972</v>
+        <v>1.2465</v>
       </c>
       <c r="G40" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.555</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4972</v>
+        <v>1.2465</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4972</v>
+        <v>1.2465</v>
       </c>
       <c r="J40" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.555</v>
       </c>
       <c r="K40" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L40" t="n">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5068</v>
+        <v>0.6914999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4954</v>
+        <v>0.4397</v>
       </c>
       <c r="C41" t="n">
-        <v>0.286</v>
+        <v>0.2539</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3987</v>
+        <v>-0.4174</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4954</v>
+        <v>0.4397</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4954</v>
+        <v>0.1166</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.4035</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4954</v>
+        <v>0.1166</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4954</v>
+        <v>0.1196</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.4035</v>
       </c>
       <c r="K41" t="n">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4954</v>
+        <v>0.5231</v>
       </c>
       <c r="N41" t="n">
-        <v>71</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4927</v>
+        <v>0.4379</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2845</v>
+        <v>0.2528</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3999</v>
+        <v>-0.4182</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4927</v>
+        <v>0.4379</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4927</v>
+        <v>0.4972</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4927</v>
+        <v>0.4972</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4927</v>
+        <v>0.4972</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4927</v>
+        <v>0.5068</v>
       </c>
       <c r="N42" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4689</v>
+        <v>0.3569</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2707</v>
+        <v>0.2061</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4108</v>
+        <v>-0.4544</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4689</v>
+        <v>0.3569</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4689</v>
+        <v>0.033</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4689</v>
+        <v>0.033</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4689</v>
+        <v>0.033</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4689</v>
+        <v>0.033</v>
       </c>
       <c r="N43" t="n">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3013</v>
+        <v>0.324</v>
       </c>
       <c r="C44" t="n">
-        <v>0.174</v>
+        <v>0.1871</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.487</v>
+        <v>-0.4691</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3013</v>
+        <v>0.324</v>
       </c>
       <c r="F44" t="n">
-        <v>1.3013</v>
+        <v>0.4689</v>
       </c>
       <c r="G44" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.3013</v>
+        <v>0.4689</v>
       </c>
       <c r="I44" t="n">
-        <v>1.3013</v>
+        <v>0.4689</v>
       </c>
       <c r="J44" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="L44" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3012999999999999</v>
+        <v>0.4689</v>
       </c>
       <c r="N44" t="n">
-        <v>122</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cabbi</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2925</v>
+        <v>0.2118</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1689</v>
+        <v>0.1223</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4911</v>
+        <v>-0.5192</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2925</v>
+        <v>0.2118</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2925</v>
+        <v>0.1842</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2925</v>
+        <v>0.1842</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2925</v>
+        <v>0.1842</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2925</v>
+        <v>0.1842</v>
       </c>
       <c r="N45" t="n">
-        <v>117</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1842</v>
+        <v>0.2021</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1063</v>
+        <v>0.1167</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5404</v>
+        <v>-0.5235</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1842</v>
+        <v>0.2021</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1842</v>
+        <v>1.3013</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1842</v>
+        <v>1.3013</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1842</v>
+        <v>1.3013</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K46" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1842</v>
+        <v>0.3012999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>71</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>Cabbi</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1424</v>
+        <v>0.187</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0822</v>
+        <v>0.108</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5594</v>
+        <v>-0.5303</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1424</v>
+        <v>0.187</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7679</v>
+        <v>0.2925</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.6254999999999999</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.7679</v>
+        <v>0.2925</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7679</v>
+        <v>0.2925</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.6254999999999999</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="L47" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1424000000000001</v>
+        <v>0.2925</v>
       </c>
       <c r="N47" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48">
@@ -2612,16 +2612,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1353</v>
+        <v>0.0823</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0781</v>
+        <v>0.0475</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5626</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1353</v>
+        <v>0.0823</v>
       </c>
       <c r="F48" t="n">
         <v>0.1353</v>
@@ -2654,32 +2654,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>m1N1</t>
+          <t>dennyslaw</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1149</v>
+        <v>0.0552</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0663</v>
+        <v>0.0319</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5719</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1149</v>
+        <v>0.0552</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1149</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1149</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1149</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1149</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="N49" t="n">
         <v>21</v>
@@ -2700,231 +2700,231 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0815</v>
+        <v>0.0226</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0471</v>
+        <v>0.013</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5871</v>
+        <v>-0.6037</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0815</v>
+        <v>0.0226</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.7679</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.8696</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.7679</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.7679</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.8696</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="L50" t="n">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="M50" t="n">
-        <v>0.08149999999999991</v>
+        <v>0.1424000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>179</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.033</v>
+        <v>-0.0194</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0191</v>
+        <v>-0.0112</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6092</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>0.033</v>
+        <v>-0.0194</v>
       </c>
       <c r="F51" t="n">
-        <v>0.033</v>
+        <v>-0.4403</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.033</v>
+        <v>-0.4403</v>
       </c>
       <c r="I51" t="n">
-        <v>0.033</v>
+        <v>-0.4403</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.033</v>
+        <v>-0.4403</v>
       </c>
       <c r="N51" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0144</v>
+        <v>-0.0457</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0083</v>
+        <v>-0.0264</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6176</v>
+        <v>-0.6342</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0144</v>
+        <v>-0.0457</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0144</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-0.8696</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0144</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0144</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-0.8696</v>
       </c>
       <c r="K52" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M52" t="n">
-        <v>0.0144</v>
+        <v>0.08149999999999991</v>
       </c>
       <c r="N52" t="n">
-        <v>69</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0702</v>
+        <v>-0.0669</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0405</v>
+        <v>-0.0386</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6562</v>
+        <v>-0.6437</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0702</v>
+        <v>-0.0669</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.5113</v>
+        <v>-0.1606</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4411</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.5113</v>
+        <v>-0.1606</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.5113</v>
+        <v>-0.1606</v>
       </c>
       <c r="J53" t="n">
-        <v>0.4411</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="L53" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.07019999999999998</v>
+        <v>-0.1606</v>
       </c>
       <c r="N53" t="n">
-        <v>214</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>dennyslaw</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.1001</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0542</v>
+        <v>-0.0578</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6669</v>
+        <v>-0.6585</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.1001</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.0144</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.0144</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.0144</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.0144</v>
       </c>
       <c r="N54" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0959</v>
+        <v>-0.1416</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0554</v>
+        <v>-0.0818</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6679</v>
+        <v>-0.6771</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0959</v>
+        <v>-0.1416</v>
       </c>
       <c r="F55" t="n">
         <v>-0.3038</v>
@@ -2980,16 +2980,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.1456</v>
+        <v>-0.1449</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0837</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6905</v>
+        <v>-0.6785</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.1456</v>
+        <v>-0.1449</v>
       </c>
       <c r="F56" t="n">
         <v>-0.1456</v>
@@ -3022,277 +3022,277 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.1606</v>
+        <v>-0.1769</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0927</v>
+        <v>-0.1021</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6973</v>
+        <v>-0.6928</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.1606</v>
+        <v>-0.1769</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.1606</v>
+        <v>-0.5113</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>0.4411</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.1606</v>
+        <v>-0.5113</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.1606</v>
+        <v>-0.5113</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>0.4411</v>
       </c>
       <c r="K57" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.1606</v>
+        <v>-0.07019999999999998</v>
       </c>
       <c r="N57" t="n">
-        <v>93</v>
+        <v>214</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>m1N1</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.2609</v>
+        <v>-0.2108</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1506</v>
+        <v>-0.1217</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.743</v>
+        <v>-0.708</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.2609</v>
+        <v>-0.2108</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3222</v>
+        <v>0.1149</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.5831</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3222</v>
+        <v>0.1149</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3222</v>
+        <v>0.1149</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.5831</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L58" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.2609</v>
+        <v>0.1149</v>
       </c>
       <c r="N58" t="n">
-        <v>122</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IceBerg</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.2839</v>
+        <v>-0.2221</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1639</v>
+        <v>-0.1282</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7534</v>
+        <v>-0.713</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2839</v>
+        <v>-0.2221</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.2839</v>
+        <v>-0.4144</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.2839</v>
+        <v>-0.4144</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2839</v>
+        <v>-0.4144</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>117</v>
+        <v>48</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.2839</v>
+        <v>-0.4144</v>
       </c>
       <c r="N59" t="n">
-        <v>117</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>IceBerg</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3492</v>
+        <v>-0.3832</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2016</v>
+        <v>-0.2212</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7832</v>
+        <v>-0.785</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3492</v>
+        <v>-0.3832</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3492</v>
+        <v>-0.2839</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.3492</v>
+        <v>-0.2839</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3492</v>
+        <v>-0.2839</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.3492</v>
+        <v>-0.2839</v>
       </c>
       <c r="N60" t="n">
-        <v>93</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.4144</v>
+        <v>-0.4244</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2392</v>
+        <v>-0.245</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.8128</v>
+        <v>-0.8034</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.4144</v>
+        <v>-0.4244</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.4144</v>
+        <v>-0.3492</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.4144</v>
+        <v>-0.3492</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4144</v>
+        <v>-0.3492</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.4144</v>
+        <v>-0.3492</v>
       </c>
       <c r="N61" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.4403</v>
+        <v>-0.4539</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2542</v>
+        <v>-0.2621</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8246</v>
+        <v>-0.8166</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.4403</v>
+        <v>-0.4539</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.4403</v>
+        <v>0.3222</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>-0.5831</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.4403</v>
+        <v>0.3222</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.4403</v>
+        <v>0.3222</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>-0.5831</v>
       </c>
       <c r="K62" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.4403</v>
+        <v>-0.2609</v>
       </c>
       <c r="N62" t="n">
-        <v>48</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63">
@@ -3302,16 +3302,16 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.5118</v>
+        <v>-0.5508</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2955</v>
+        <v>-0.318</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8572</v>
+        <v>-0.8599</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5118</v>
+        <v>-0.5508</v>
       </c>
       <c r="F63" t="n">
         <v>-0.5118</v>
@@ -3344,369 +3344,369 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>aliStair</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.7391</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2959</v>
+        <v>-0.4267</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8575</v>
+        <v>-0.944</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.7391</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.5422</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.5422</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.5422</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.5422</v>
       </c>
       <c r="N64" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>aliStair</t>
+          <t>MistR</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.5422</v>
+        <v>-0.8072</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.313</v>
+        <v>-0.466</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.871</v>
+        <v>-0.9744</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.5422</v>
+        <v>-0.8072</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.5422</v>
+        <v>-0.8135</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.5422</v>
+        <v>-0.8135</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5422</v>
+        <v>-0.8135</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.5422</v>
+        <v>-0.8135</v>
       </c>
       <c r="N65" t="n">
-        <v>71</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.6857</v>
+        <v>-0.8941</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3959</v>
+        <v>-0.5162</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9363</v>
+        <v>-1.0132</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6857</v>
+        <v>-0.8941</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.6857</v>
+        <v>-0.7752</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.6857</v>
+        <v>-0.7752</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6857</v>
+        <v>-0.7752</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.6857</v>
+        <v>-0.7752</v>
       </c>
       <c r="N66" t="n">
-        <v>48</v>
+        <v>111</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.7752</v>
+        <v>-0.9012</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4476</v>
+        <v>-0.5203</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9771</v>
+        <v>-1.0164</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7752</v>
+        <v>-0.9012</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.7752</v>
+        <v>-0.6857</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.7752</v>
+        <v>-0.6857</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.7752</v>
+        <v>-0.6857</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.7752</v>
+        <v>-0.6857</v>
       </c>
       <c r="N67" t="n">
-        <v>111</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.7823</v>
+        <v>-1.0139</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4517</v>
+        <v>-0.5854</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9802999999999999</v>
+        <v>-1.0667</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.7823</v>
+        <v>-1.0139</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.7823</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.7823</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.7823</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.7823</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="N68" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MistR</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.8135</v>
+        <v>-1.0462</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4697</v>
+        <v>-0.604</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9945000000000001</v>
+        <v>-1.0811</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.8135</v>
+        <v>-1.0462</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.8135</v>
+        <v>-0.8572</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.8135</v>
+        <v>-0.8572</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.8135</v>
+        <v>-0.8572</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.8135</v>
+        <v>-0.8572</v>
       </c>
       <c r="N69" t="n">
-        <v>117</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.8572</v>
+        <v>-1.1203</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4949</v>
+        <v>-0.6468</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0144</v>
+        <v>-1.1142</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.8572</v>
+        <v>-1.1203</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.8572</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.8572</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.8572</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.8572</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="N70" t="n">
-        <v>69</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-1.1649</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5346</v>
+        <v>-0.6725</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0457</v>
+        <v>-1.1342</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-1.1649</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.7823</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.7823</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.7823</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.7823</v>
       </c>
       <c r="N71" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72">
@@ -3716,16 +3716,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.0206</v>
+        <v>-1.2535</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5891999999999999</v>
+        <v>-0.7237</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0888</v>
+        <v>-1.1737</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.0206</v>
+        <v>-1.2535</v>
       </c>
       <c r="F72" t="n">
         <v>-1.0206</v>
@@ -3762,16 +3762,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.1195</v>
+        <v>-1.4061</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.6463</v>
+        <v>-0.8118</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1338</v>
+        <v>-1.2419</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1195</v>
+        <v>-1.4061</v>
       </c>
       <c r="F73" t="n">
         <v>-0.6474</v>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.3329</v>
+        <v>-1.6227</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.7695</v>
+        <v>-0.9368</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.231</v>
+        <v>-1.3386</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.3329</v>
+        <v>-1.6227</v>
       </c>
       <c r="F74" t="n">
         <v>-1.3329</v>
@@ -3854,16 +3854,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.7431</v>
+        <v>-1.8906</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.0064</v>
+        <v>-1.0915</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.4177</v>
+        <v>-1.4583</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.7431</v>
+        <v>-1.8906</v>
       </c>
       <c r="F75" t="n">
         <v>-1.4528</v>
@@ -3900,16 +3900,16 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.91</v>
+        <v>-2.0961</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.1027</v>
+        <v>-1.2102</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.4937</v>
+        <v>-1.5501</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.91</v>
+        <v>-2.0961</v>
       </c>
       <c r="F76" t="n">
         <v>-2.1116</v>

--- a/database/event/7732/event_7732_evp_summary.xlsx
+++ b/database/event/7732/event_7732_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.9887</v>
+        <v>7.9544</v>
       </c>
       <c r="C2" t="n">
-        <v>4.6122</v>
+        <v>4.5924</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9546</v>
+        <v>3.0178</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9887</v>
+        <v>7.9544</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6155</v>
+        <v>1.5653</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1908</v>
+        <v>6.2067</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6155</v>
+        <v>1.5653</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6155</v>
+        <v>1.5653</v>
       </c>
       <c r="J2" t="n">
-        <v>6.6595</v>
+        <v>6.5042</v>
       </c>
       <c r="K2" t="n">
         <v>53</v>
@@ -529,7 +529,7 @@
         <v>174</v>
       </c>
       <c r="M2" t="n">
-        <v>8.275</v>
+        <v>8.0695</v>
       </c>
       <c r="N2" t="n">
         <v>227</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.6635</v>
+        <v>7.753</v>
       </c>
       <c r="C3" t="n">
-        <v>4.4244</v>
+        <v>4.4761</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8093</v>
+        <v>2.9261</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6635</v>
+        <v>7.753</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4769</v>
+        <v>2.4961</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9942</v>
+        <v>5.0645</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6963</v>
+        <v>2.7701</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6963</v>
+        <v>2.7701</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9942</v>
+        <v>5.0645</v>
       </c>
       <c r="K3" t="n">
         <v>42</v>
@@ -575,7 +575,7 @@
         <v>172</v>
       </c>
       <c r="M3" t="n">
-        <v>7.6905</v>
+        <v>7.8346</v>
       </c>
       <c r="N3" t="n">
         <v>214</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.9846</v>
+        <v>6.9174</v>
       </c>
       <c r="C4" t="n">
-        <v>4.0325</v>
+        <v>3.9937</v>
       </c>
       <c r="D4" t="n">
-        <v>2.506</v>
+        <v>2.5454</v>
       </c>
       <c r="E4" t="n">
-        <v>6.9846</v>
+        <v>6.9174</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4614</v>
+        <v>2.4628</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1938</v>
+        <v>4.1252</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6622</v>
+        <v>2.6938</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6622</v>
+        <v>2.6938</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1938</v>
+        <v>4.1252</v>
       </c>
       <c r="K4" t="n">
         <v>62</v>
@@ -621,7 +621,7 @@
         <v>117</v>
       </c>
       <c r="M4" t="n">
-        <v>6.856</v>
+        <v>6.819000000000001</v>
       </c>
       <c r="N4" t="n">
         <v>179</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2472</v>
+        <v>5.2944</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0294</v>
+        <v>3.0567</v>
       </c>
       <c r="D5" t="n">
-        <v>1.73</v>
+        <v>1.8061</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2472</v>
+        <v>5.2944</v>
       </c>
       <c r="F5" t="n">
-        <v>1.977</v>
+        <v>1.9775</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1185</v>
+        <v>3.1652</v>
       </c>
       <c r="H5" t="n">
-        <v>1.977</v>
+        <v>1.9775</v>
       </c>
       <c r="I5" t="n">
-        <v>1.977</v>
+        <v>1.9775</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1185</v>
+        <v>3.1652</v>
       </c>
       <c r="K5" t="n">
         <v>42</v>
@@ -667,7 +667,7 @@
         <v>172</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0955</v>
+        <v>5.1427</v>
       </c>
       <c r="N5" t="n">
         <v>214</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1445</v>
+        <v>4.014</v>
       </c>
       <c r="C6" t="n">
-        <v>2.3928</v>
+        <v>2.3174</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2374</v>
+        <v>1.2228</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1445</v>
+        <v>4.014</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3616</v>
+        <v>2.3683</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6082</v>
+        <v>1.4711</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4438</v>
+        <v>2.4772</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4438</v>
+        <v>2.4772</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6082</v>
+        <v>1.4711</v>
       </c>
       <c r="K6" t="n">
         <v>42</v>
@@ -713,7 +713,7 @@
         <v>80</v>
       </c>
       <c r="M6" t="n">
-        <v>4.052</v>
+        <v>3.9483</v>
       </c>
       <c r="N6" t="n">
         <v>122</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8799</v>
+        <v>3.865</v>
       </c>
       <c r="C7" t="n">
-        <v>2.24</v>
+        <v>2.2314</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1192</v>
+        <v>1.1549</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8799</v>
+        <v>3.865</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3193</v>
+        <v>2.3253</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4584</v>
+        <v>1.4375</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3514</v>
+        <v>2.3788</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3514</v>
+        <v>2.3788</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4584</v>
+        <v>1.4375</v>
       </c>
       <c r="K7" t="n">
         <v>53</v>
@@ -759,7 +759,7 @@
         <v>174</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8098</v>
+        <v>3.8163</v>
       </c>
       <c r="N7" t="n">
         <v>227</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5248</v>
+        <v>3.4266</v>
       </c>
       <c r="C8" t="n">
-        <v>2.035</v>
+        <v>1.9783</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9606</v>
+        <v>0.9552</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5248</v>
+        <v>3.4266</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5819</v>
+        <v>3.4941</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2121</v>
+        <v>-0.2225</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1147</v>
+        <v>5.0574</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2465</v>
+        <v>5.1925</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2121</v>
+        <v>-0.2225</v>
       </c>
       <c r="K8" t="n">
         <v>116</v>
@@ -805,7 +805,7 @@
         <v>64</v>
       </c>
       <c r="M8" t="n">
-        <v>5.0344</v>
+        <v>4.97</v>
       </c>
       <c r="N8" t="n">
         <v>180</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4516</v>
+        <v>3.416</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9927</v>
+        <v>1.9722</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9504</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4516</v>
+        <v>3.416</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4243</v>
+        <v>0.4383</v>
       </c>
       <c r="G9" t="n">
-        <v>3.0156</v>
+        <v>2.966</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4243</v>
+        <v>0.4383</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4243</v>
+        <v>0.4383</v>
       </c>
       <c r="J9" t="n">
-        <v>3.0156</v>
+        <v>2.966</v>
       </c>
       <c r="K9" t="n">
         <v>42</v>
@@ -851,7 +851,7 @@
         <v>172</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4399</v>
+        <v>3.4043</v>
       </c>
       <c r="N9" t="n">
         <v>214</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9419</v>
+        <v>2.9104</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6985</v>
+        <v>1.6803</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7003</v>
+        <v>0.72</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9419</v>
+        <v>2.9104</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5714</v>
+        <v>1.5492</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2656</v>
+        <v>1.2563</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5714</v>
+        <v>1.5492</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5714</v>
+        <v>1.5492</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2656</v>
+        <v>1.2563</v>
       </c>
       <c r="K10" t="n">
         <v>39</v>
@@ -897,7 +897,7 @@
         <v>117</v>
       </c>
       <c r="M10" t="n">
-        <v>2.837</v>
+        <v>2.8055</v>
       </c>
       <c r="N10" t="n">
         <v>156</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8012</v>
+        <v>2.8128</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6172</v>
+        <v>1.6239</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6374</v>
+        <v>0.6756</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8012</v>
+        <v>2.8128</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3132</v>
+        <v>0.3258</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3518</v>
+        <v>2.3508</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3132</v>
+        <v>0.3258</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3132</v>
+        <v>0.3258</v>
       </c>
       <c r="J11" t="n">
-        <v>2.3518</v>
+        <v>2.3508</v>
       </c>
       <c r="K11" t="n">
         <v>39</v>
@@ -943,7 +943,7 @@
         <v>117</v>
       </c>
       <c r="M11" t="n">
-        <v>2.665</v>
+        <v>2.6766</v>
       </c>
       <c r="N11" t="n">
         <v>156</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7128</v>
+        <v>2.6696</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5662</v>
+        <v>1.5413</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5979</v>
+        <v>0.6103</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7128</v>
+        <v>2.6696</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1187</v>
+        <v>2.1045</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5493</v>
+        <v>0.5203</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1187</v>
+        <v>2.1045</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1187</v>
+        <v>2.1045</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5493</v>
+        <v>0.5203</v>
       </c>
       <c r="K12" t="n">
         <v>62</v>
@@ -989,7 +989,7 @@
         <v>117</v>
       </c>
       <c r="M12" t="n">
-        <v>2.668</v>
+        <v>2.6248</v>
       </c>
       <c r="N12" t="n">
         <v>179</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7087</v>
+        <v>2.6015</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5638</v>
+        <v>1.5019</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5961</v>
+        <v>0.5793</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7087</v>
+        <v>2.6015</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4686</v>
+        <v>2.4259</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1353</v>
+        <v>0.0708</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6781</v>
+        <v>2.6092</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7471</v>
+        <v>2.679</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1353</v>
+        <v>0.0708</v>
       </c>
       <c r="K13" t="n">
         <v>116</v>
@@ -1035,7 +1035,7 @@
         <v>64</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8824</v>
+        <v>2.7498</v>
       </c>
       <c r="N13" t="n">
         <v>180</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6833</v>
+        <v>2.5249</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5492</v>
+        <v>1.4577</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5848</v>
+        <v>0.5444</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6833</v>
+        <v>2.5249</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4324</v>
+        <v>0.3845</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1935</v>
+        <v>2.083</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4324</v>
+        <v>0.3845</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4324</v>
+        <v>0.3845</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1935</v>
+        <v>2.083</v>
       </c>
       <c r="K14" t="n">
         <v>53</v>
@@ -1081,7 +1081,7 @@
         <v>174</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6259</v>
+        <v>2.4675</v>
       </c>
       <c r="N14" t="n">
         <v>227</v>
@@ -1090,219 +1090,219 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>0SAMAS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1892</v>
+        <v>2.1623</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2639</v>
+        <v>1.2484</v>
       </c>
       <c r="D15" t="n">
-        <v>0.364</v>
+        <v>0.3792</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1892</v>
+        <v>2.1623</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1143</v>
+        <v>1.3439</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1143</v>
+        <v>1.3439</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1143</v>
+        <v>1.3439</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1143</v>
+        <v>1.3439</v>
       </c>
       <c r="N15" t="n">
-        <v>111</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0SAMAS</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1738</v>
+        <v>2.1408</v>
       </c>
       <c r="C16" t="n">
-        <v>1.255</v>
+        <v>1.236</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3572</v>
+        <v>0.3694</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1738</v>
+        <v>2.1408</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3554</v>
+        <v>2.0659</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3554</v>
+        <v>2.0659</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3554</v>
+        <v>2.0659</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3554</v>
+        <v>2.0659</v>
       </c>
       <c r="N16" t="n">
-        <v>21</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9942</v>
+        <v>1.9616</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1513</v>
+        <v>1.1325</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2769</v>
+        <v>0.2878</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9942</v>
+        <v>1.9616</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7947</v>
+        <v>1.9044</v>
       </c>
       <c r="G17" t="n">
-        <v>1.054</v>
+        <v>-0.1063</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7947</v>
+        <v>1.9044</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7947</v>
+        <v>1.9044</v>
       </c>
       <c r="J17" t="n">
-        <v>1.054</v>
+        <v>-0.1063</v>
       </c>
       <c r="K17" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="L17" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8487</v>
+        <v>1.7981</v>
       </c>
       <c r="N17" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9768</v>
+        <v>1.9451</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1413</v>
+        <v>1.123</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2692</v>
+        <v>0.2803</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9768</v>
+        <v>1.9451</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.3443</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3465</v>
+        <v>1.6378</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.3443</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.3443</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3465</v>
+        <v>1.6378</v>
       </c>
       <c r="K18" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="L18" t="n">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0295</v>
+        <v>1.9821</v>
       </c>
       <c r="N18" t="n">
-        <v>179</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9696</v>
+        <v>1.9092</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1371</v>
+        <v>1.1023</v>
       </c>
       <c r="D19" t="n">
-        <v>0.266</v>
+        <v>0.2639</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9696</v>
+        <v>1.9092</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5543</v>
+        <v>0.8477</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3716</v>
+        <v>0.916</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5543</v>
+        <v>0.8477</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5543</v>
+        <v>0.8477</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3716</v>
+        <v>0.916</v>
       </c>
       <c r="K19" t="n">
         <v>33</v>
@@ -1311,7 +1311,7 @@
         <v>69</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9259</v>
+        <v>1.7637</v>
       </c>
       <c r="N19" t="n">
         <v>102</v>
@@ -1320,139 +1320,139 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.9532</v>
+        <v>1.8888</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1277</v>
+        <v>1.0905</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2586</v>
+        <v>0.2547</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9532</v>
+        <v>1.8888</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9176</v>
+        <v>1.8889</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1279</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9176</v>
+        <v>1.8889</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9176</v>
+        <v>1.8889</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1279</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="L20" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7897</v>
+        <v>1.8889</v>
       </c>
       <c r="N20" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.8976</v>
+        <v>1.8601</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0956</v>
+        <v>1.0739</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2338</v>
+        <v>0.2416</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8976</v>
+        <v>1.8601</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3309</v>
+        <v>0.7218</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6037</v>
+        <v>1.191</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3309</v>
+        <v>0.7218</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3309</v>
+        <v>0.7218</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6037</v>
+        <v>1.191</v>
       </c>
       <c r="K21" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="L21" t="n">
-        <v>172</v>
+        <v>117</v>
       </c>
       <c r="M21" t="n">
-        <v>1.9346</v>
+        <v>1.9128</v>
       </c>
       <c r="N21" t="n">
-        <v>214</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8898</v>
+        <v>1.848</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0911</v>
+        <v>1.0669</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2303</v>
+        <v>0.2361</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8898</v>
+        <v>1.848</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8899</v>
+        <v>1.5377</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="H22" t="n">
-        <v>1.8899</v>
+        <v>1.5377</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8899</v>
+        <v>1.5377</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="K22" t="n">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M22" t="n">
-        <v>1.8899</v>
+        <v>1.8043</v>
       </c>
       <c r="N22" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.691</v>
+        <v>1.708</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9861</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1415</v>
+        <v>0.1723</v>
       </c>
       <c r="E23" t="n">
-        <v>1.691</v>
+        <v>1.708</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8217</v>
+        <v>2.8387</v>
       </c>
       <c r="G23" t="n">
         <v>-1</v>
       </c>
       <c r="H23" t="n">
-        <v>3.4509</v>
+        <v>3.5553</v>
       </c>
       <c r="I23" t="n">
-        <v>3.4509</v>
+        <v>3.5553</v>
       </c>
       <c r="J23" t="n">
         <v>-1</v>
@@ -1495,7 +1495,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="n">
-        <v>2.4509</v>
+        <v>2.5553</v>
       </c>
       <c r="N23" t="n">
         <v>102</v>
@@ -1504,277 +1504,277 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6673</v>
+        <v>1.6723</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9626</v>
+        <v>0.9655</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1309</v>
+        <v>0.156</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6673</v>
+        <v>1.6723</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8535</v>
+        <v>2.5742</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8442</v>
+        <v>-0.9129</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8535</v>
+        <v>2.9492</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8535</v>
+        <v>2.9492</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8442</v>
+        <v>-0.9129</v>
       </c>
       <c r="K24" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L24" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="M24" t="n">
-        <v>1.6977</v>
+        <v>2.0363</v>
       </c>
       <c r="N24" t="n">
-        <v>102</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6596</v>
+        <v>1.5342</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.8858</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1275</v>
+        <v>0.0931</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6596</v>
+        <v>1.5342</v>
       </c>
       <c r="F25" t="n">
-        <v>2.5616</v>
+        <v>1.2571</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.913</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.8816</v>
+        <v>1.2571</v>
       </c>
       <c r="I25" t="n">
-        <v>2.8816</v>
+        <v>1.2571</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.913</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="L25" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.9686</v>
+        <v>1.2571</v>
       </c>
       <c r="N25" t="n">
-        <v>156</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.5399</v>
+        <v>1.5174</v>
       </c>
       <c r="C26" t="n">
-        <v>0.889</v>
+        <v>0.8761</v>
       </c>
       <c r="D26" t="n">
-        <v>0.074</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>1.5399</v>
+        <v>1.5174</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6406</v>
+        <v>0.7907</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0606</v>
+        <v>0.7571</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6406</v>
+        <v>0.7907</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6829</v>
+        <v>0.7907</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0606</v>
+        <v>0.7571</v>
       </c>
       <c r="K26" t="n">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="L26" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6223</v>
+        <v>1.5478</v>
       </c>
       <c r="N26" t="n">
-        <v>180</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.5375</v>
+        <v>1.4894</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8877</v>
+        <v>0.8599</v>
       </c>
       <c r="D27" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0727</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5375</v>
+        <v>1.4894</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2604</v>
+        <v>1.5102</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2604</v>
+        <v>1.5102</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2604</v>
+        <v>1.5102</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2604</v>
+        <v>1.5102</v>
       </c>
       <c r="N27" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.4477</v>
+        <v>1.4889</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8358</v>
+        <v>0.8596</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0328</v>
+        <v>0.0725</v>
       </c>
       <c r="E28" t="n">
-        <v>1.4477</v>
+        <v>1.4889</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9711</v>
+        <v>1.5956</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4178</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9711</v>
+        <v>1.5956</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9711</v>
+        <v>1.6382</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4178</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="L28" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3889</v>
+        <v>1.5716</v>
       </c>
       <c r="N28" t="n">
-        <v>104</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4288</v>
+        <v>1.394</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8249</v>
+        <v>0.8048</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0244</v>
+        <v>0.0292</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4288</v>
+        <v>1.394</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4496</v>
+        <v>2.2597</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.9061</v>
       </c>
       <c r="H29" t="n">
-        <v>1.4496</v>
+        <v>2.2597</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4496</v>
+        <v>2.2597</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.9061</v>
       </c>
       <c r="K29" t="n">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M29" t="n">
-        <v>1.4496</v>
+        <v>1.3536</v>
       </c>
       <c r="N29" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30">
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3698</v>
+        <v>1.3734</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.7929</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.002</v>
+        <v>0.0199</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3698</v>
+        <v>1.3734</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4175</v>
+        <v>1.3878</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.2256</v>
+        <v>-0.1923</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4175</v>
+        <v>1.3878</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4175</v>
+        <v>1.3878</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2256</v>
+        <v>-0.1923</v>
       </c>
       <c r="K30" t="n">
         <v>53</v>
@@ -1817,7 +1817,7 @@
         <v>51</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1919</v>
+        <v>1.1955</v>
       </c>
       <c r="N30" t="n">
         <v>104</v>
@@ -1826,139 +1826,139 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3379</v>
+        <v>1.3539</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7724</v>
+        <v>0.7817</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0162</v>
+        <v>0.011</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3379</v>
+        <v>1.3539</v>
       </c>
       <c r="F31" t="n">
-        <v>2.2426</v>
+        <v>0.8969</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.9451000000000001</v>
+        <v>0.3982</v>
       </c>
       <c r="H31" t="n">
-        <v>2.2426</v>
+        <v>0.8969</v>
       </c>
       <c r="I31" t="n">
-        <v>2.2426</v>
+        <v>0.8969</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.9451000000000001</v>
+        <v>0.3982</v>
       </c>
       <c r="K31" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="L31" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="M31" t="n">
-        <v>1.2975</v>
+        <v>1.2951</v>
       </c>
       <c r="N31" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kwezz</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1726</v>
+        <v>1.0923</v>
       </c>
       <c r="C32" t="n">
-        <v>0.677</v>
+        <v>0.6306</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.09</v>
+        <v>-0.1082</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1726</v>
+        <v>1.0923</v>
       </c>
       <c r="F32" t="n">
-        <v>1.1271</v>
+        <v>0.055</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>1.1271</v>
+        <v>0.055</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1271</v>
+        <v>0.055</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="K32" t="n">
+        <v>62</v>
+      </c>
+      <c r="L32" t="n">
         <v>117</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
-        <v>1.1271</v>
+        <v>1.0505</v>
       </c>
       <c r="N32" t="n">
-        <v>117</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>kwezz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1622</v>
+        <v>1.0703</v>
       </c>
       <c r="C33" t="n">
-        <v>0.671</v>
+        <v>0.6179</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.1182</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1622</v>
+        <v>1.0703</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0235</v>
+        <v>1.0248</v>
       </c>
       <c r="G33" t="n">
-        <v>1.0969</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0235</v>
+        <v>1.0248</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0235</v>
+        <v>1.0248</v>
       </c>
       <c r="J33" t="n">
-        <v>1.0969</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.0248</v>
+      </c>
+      <c r="N33" t="n">
         <v>117</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.1204</v>
-      </c>
-      <c r="N33" t="n">
-        <v>179</v>
       </c>
     </row>
     <row r="34">
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0475</v>
+        <v>0.9787</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6048</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1459</v>
+        <v>-0.1599</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0475</v>
+        <v>0.9787</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4493</v>
+        <v>0.3887</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6149</v>
+        <v>0.6067</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4493</v>
+        <v>0.3887</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4493</v>
+        <v>0.3887</v>
       </c>
       <c r="J34" t="n">
-        <v>0.6149</v>
+        <v>0.6067</v>
       </c>
       <c r="K34" t="n">
         <v>39</v>
@@ -2001,7 +2001,7 @@
         <v>117</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0642</v>
+        <v>0.9954000000000001</v>
       </c>
       <c r="N34" t="n">
         <v>156</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8811</v>
+        <v>0.8547</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5087</v>
+        <v>0.4935</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2203</v>
+        <v>-0.2164</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8811</v>
+        <v>0.8547</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8213</v>
+        <v>0.9626</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8213</v>
+        <v>0.9626</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8213</v>
+        <v>0.9626</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8213</v>
+        <v>0.9626</v>
       </c>
       <c r="N35" t="n">
-        <v>93</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8626</v>
+        <v>0.7904</v>
       </c>
       <c r="C36" t="n">
-        <v>0.498</v>
+        <v>0.4563</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2285</v>
+        <v>-0.2457</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8626</v>
+        <v>0.7904</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9705</v>
+        <v>0.7306</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9705</v>
+        <v>0.7306</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9705</v>
+        <v>0.7306</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9705</v>
+        <v>0.7306</v>
       </c>
       <c r="N36" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8137</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4698</v>
+        <v>0.4146</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2504</v>
+        <v>-0.2786</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8137</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4954</v>
+        <v>0.3999</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4954</v>
+        <v>0.3999</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4954</v>
+        <v>0.3999</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4954</v>
+        <v>0.3999</v>
       </c>
       <c r="N37" t="n">
         <v>71</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7268</v>
+        <v>0.6765</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4196</v>
+        <v>0.3906</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2892</v>
+        <v>-0.2976</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7268</v>
+        <v>0.6765</v>
       </c>
       <c r="F38" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.4475</v>
+        <v>-0.4678</v>
       </c>
       <c r="H38" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="I38" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.4475</v>
+        <v>-0.4678</v>
       </c>
       <c r="K38" t="n">
         <v>42</v>
@@ -2185,7 +2185,7 @@
         <v>80</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7324999999999999</v>
+        <v>0.6821999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>122</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5836</v>
+        <v>0.6152</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3369</v>
+        <v>0.3552</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3531</v>
+        <v>-0.3255</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5836</v>
+        <v>0.6152</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4927</v>
+        <v>0.5243</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4927</v>
+        <v>0.5243</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4927</v>
+        <v>0.5243</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4927</v>
+        <v>0.5243</v>
       </c>
       <c r="N39" t="n">
         <v>111</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5432</v>
+        <v>0.5555</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3136</v>
+        <v>0.3207</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3712</v>
+        <v>-0.3527</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5432</v>
+        <v>0.5555</v>
       </c>
       <c r="F40" t="n">
-        <v>1.2465</v>
+        <v>1.1897</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.555</v>
+        <v>-0.4859</v>
       </c>
       <c r="H40" t="n">
-        <v>1.2465</v>
+        <v>1.1897</v>
       </c>
       <c r="I40" t="n">
-        <v>1.2465</v>
+        <v>1.1897</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.555</v>
+        <v>-0.4859</v>
       </c>
       <c r="K40" t="n">
         <v>39</v>
@@ -2277,7 +2277,7 @@
         <v>117</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6914999999999999</v>
+        <v>0.7038</v>
       </c>
       <c r="N40" t="n">
         <v>156</v>
@@ -2286,93 +2286,93 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4397</v>
+        <v>0.4671</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2539</v>
+        <v>0.2697</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4174</v>
+        <v>-0.393</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4397</v>
+        <v>0.4671</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1166</v>
+        <v>0.5458</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4035</v>
+        <v>-0.0098</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1166</v>
+        <v>0.5458</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1196</v>
+        <v>0.5458</v>
       </c>
       <c r="J41" t="n">
-        <v>0.4035</v>
+        <v>-0.0098</v>
       </c>
       <c r="K41" t="n">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="L41" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5231</v>
+        <v>0.5359999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>180</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4379</v>
+        <v>0.4372</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2528</v>
+        <v>0.2524</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4182</v>
+        <v>-0.4066</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4379</v>
+        <v>0.4372</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4972</v>
+        <v>0.1329</v>
       </c>
       <c r="G42" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.3846</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4972</v>
+        <v>0.1329</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4972</v>
+        <v>0.1365</v>
       </c>
       <c r="J42" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.3846</v>
       </c>
       <c r="K42" t="n">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="L42" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5068</v>
+        <v>0.5211</v>
       </c>
       <c r="N42" t="n">
-        <v>122</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3569</v>
+        <v>0.3467</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2061</v>
+        <v>0.2002</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4544</v>
+        <v>-0.4478</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3569</v>
+        <v>0.3467</v>
       </c>
       <c r="F43" t="n">
-        <v>0.033</v>
+        <v>0.0228</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.033</v>
+        <v>0.0228</v>
       </c>
       <c r="I43" t="n">
-        <v>0.033</v>
+        <v>0.0228</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.033</v>
+        <v>0.0228</v>
       </c>
       <c r="N43" t="n">
         <v>21</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.324</v>
+        <v>0.2932</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1871</v>
+        <v>0.1693</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4691</v>
+        <v>-0.4722</v>
       </c>
       <c r="E44" t="n">
-        <v>0.324</v>
+        <v>0.2932</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4689</v>
+        <v>0.4381</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4689</v>
+        <v>0.4381</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4689</v>
+        <v>0.4381</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4689</v>
+        <v>0.4381</v>
       </c>
       <c r="N44" t="n">
         <v>71</v>
@@ -2470,93 +2470,93 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2118</v>
+        <v>0.1952</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1223</v>
+        <v>0.1127</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5192</v>
+        <v>-0.5169</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2118</v>
+        <v>0.1952</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1842</v>
+        <v>1.2893</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.9949</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1842</v>
+        <v>1.2893</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1842</v>
+        <v>1.2893</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.9949</v>
       </c>
       <c r="K45" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1842</v>
+        <v>0.2943999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>71</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2021</v>
+        <v>0.1896</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1167</v>
+        <v>0.1095</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5235</v>
+        <v>-0.5194</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2021</v>
+        <v>0.1896</v>
       </c>
       <c r="F46" t="n">
-        <v>1.3013</v>
+        <v>0.162</v>
       </c>
       <c r="G46" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.3013</v>
+        <v>0.162</v>
       </c>
       <c r="I46" t="n">
-        <v>1.3013</v>
+        <v>0.162</v>
       </c>
       <c r="J46" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="L46" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3012999999999999</v>
+        <v>0.162</v>
       </c>
       <c r="N46" t="n">
-        <v>122</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47">
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.187</v>
+        <v>0.152</v>
       </c>
       <c r="C47" t="n">
-        <v>0.108</v>
+        <v>0.0878</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5303</v>
+        <v>-0.5365</v>
       </c>
       <c r="E47" t="n">
-        <v>0.187</v>
+        <v>0.152</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2925</v>
+        <v>0.2575</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2925</v>
+        <v>0.2575</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2925</v>
+        <v>0.2575</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2925</v>
+        <v>0.2575</v>
       </c>
       <c r="N47" t="n">
         <v>117</v>
@@ -2608,47 +2608,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0823</v>
+        <v>0.1213</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0475</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.5505</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0823</v>
+        <v>0.1213</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1353</v>
+        <v>0.8333</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1353</v>
+        <v>0.8333</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1353</v>
+        <v>0.8333</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1353</v>
+        <v>0.2411000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0552</v>
+        <v>0.0721</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0319</v>
+        <v>0.0416</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5891999999999999</v>
+        <v>-0.5729</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0552</v>
+        <v>0.0721</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0769</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0769</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0769</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0769</v>
       </c>
       <c r="N49" t="n">
         <v>21</v>
@@ -2700,47 +2700,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0226</v>
+        <v>0.0061</v>
       </c>
       <c r="C50" t="n">
-        <v>0.013</v>
+        <v>0.0035</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.6037</v>
+        <v>-0.603</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0226</v>
+        <v>0.0061</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7679</v>
+        <v>0.0591</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.6254999999999999</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.7679</v>
+        <v>0.0591</v>
       </c>
       <c r="I50" t="n">
-        <v>0.7679</v>
+        <v>0.0591</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.6254999999999999</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="L50" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1424000000000001</v>
+        <v>0.0591</v>
       </c>
       <c r="N50" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0194</v>
+        <v>-0.0302</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0112</v>
+        <v>-0.0174</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0194</v>
+        <v>-0.0302</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.4403</v>
+        <v>-0.4511</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.4403</v>
+        <v>-0.4511</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4403</v>
+        <v>-0.4511</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.4403</v>
+        <v>-0.4511</v>
       </c>
       <c r="N51" t="n">
         <v>48</v>
@@ -2792,78 +2792,78 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0457</v>
+        <v>-0.0517</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0264</v>
+        <v>-0.0298</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6342</v>
+        <v>-0.6293</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0457</v>
+        <v>-0.0517</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9510999999999999</v>
+        <v>-0.1454</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.8696</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.9510999999999999</v>
+        <v>-0.1454</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9510999999999999</v>
+        <v>-0.1454</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.8696</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="L52" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.08149999999999991</v>
+        <v>-0.1454</v>
       </c>
       <c r="N52" t="n">
-        <v>179</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0669</v>
+        <v>-0.1105</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0386</v>
+        <v>-0.0638</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6437</v>
+        <v>-0.6561</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0669</v>
+        <v>-0.1105</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1606</v>
+        <v>-0.1112</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1606</v>
+        <v>-0.1112</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1606</v>
+        <v>-0.1112</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.1606</v>
+        <v>-0.1112</v>
       </c>
       <c r="N53" t="n">
         <v>93</v>
@@ -2884,185 +2884,185 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1001</v>
+        <v>-0.1165</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0578</v>
+        <v>-0.0673</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6585</v>
+        <v>-0.6589</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1001</v>
+        <v>-0.1165</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0144</v>
+        <v>0.9114</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0144</v>
+        <v>0.9114</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0144</v>
+        <v>0.9114</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0144</v>
+        <v>0.01070000000000004</v>
       </c>
       <c r="N54" t="n">
-        <v>69</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1416</v>
+        <v>-0.1959</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0818</v>
+        <v>-0.1131</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6771</v>
+        <v>-0.695</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1416</v>
+        <v>-0.1959</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3038</v>
+        <v>-0.3882</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2079</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3038</v>
+        <v>-0.3882</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3038</v>
+        <v>-0.3882</v>
       </c>
       <c r="J55" t="n">
-        <v>0.2079</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="L55" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.09590000000000001</v>
+        <v>-0.3882</v>
       </c>
       <c r="N55" t="n">
-        <v>227</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.1449</v>
+        <v>-0.2072</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0837</v>
+        <v>-0.1196</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6785</v>
+        <v>-0.7002</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.1449</v>
+        <v>-0.2072</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.1456</v>
+        <v>-0.296</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.1345</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.1456</v>
+        <v>-0.296</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1456</v>
+        <v>-0.296</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>0.1345</v>
       </c>
       <c r="K56" t="n">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.1456</v>
+        <v>-0.1615</v>
       </c>
       <c r="N56" t="n">
-        <v>93</v>
+        <v>227</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.1769</v>
+        <v>-0.2163</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1021</v>
+        <v>-0.1249</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6928</v>
+        <v>-0.7043</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.1769</v>
+        <v>-0.2163</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.5113</v>
+        <v>-0.1018</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4411</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.5113</v>
+        <v>-0.1018</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.5113</v>
+        <v>-0.1018</v>
       </c>
       <c r="J57" t="n">
-        <v>0.4411</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="L57" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.07019999999999998</v>
+        <v>-0.1018</v>
       </c>
       <c r="N57" t="n">
-        <v>214</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58">
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.2108</v>
+        <v>-0.2375</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1217</v>
+        <v>-0.1371</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.708</v>
+        <v>-0.714</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.2108</v>
+        <v>-0.2375</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1149</v>
+        <v>0.0882</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1149</v>
+        <v>0.0882</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1149</v>
+        <v>0.0882</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1149</v>
+        <v>0.0882</v>
       </c>
       <c r="N58" t="n">
         <v>21</v>
@@ -3114,47 +3114,47 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.2221</v>
+        <v>-0.2621</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1282</v>
+        <v>-0.1513</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.713</v>
+        <v>-0.7252</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2221</v>
+        <v>-0.2621</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.4144</v>
+        <v>-0.5545</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>0.3991</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.4144</v>
+        <v>-0.5545</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4144</v>
+        <v>-0.5545</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>0.3991</v>
       </c>
       <c r="K59" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.4144</v>
+        <v>-0.1554</v>
       </c>
       <c r="N59" t="n">
-        <v>48</v>
+        <v>214</v>
       </c>
     </row>
     <row r="60">
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3832</v>
+        <v>-0.3387</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2212</v>
+        <v>-0.1955</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.785</v>
+        <v>-0.7601</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3832</v>
+        <v>-0.3387</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.2839</v>
+        <v>-0.2394</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.2839</v>
+        <v>-0.2394</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2839</v>
+        <v>-0.2394</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.2839</v>
+        <v>-0.2394</v>
       </c>
       <c r="N60" t="n">
         <v>117</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.4244</v>
+        <v>-0.3934</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.245</v>
+        <v>-0.2271</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.8034</v>
+        <v>-0.785</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.4244</v>
+        <v>-0.3934</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.3492</v>
+        <v>-0.3182</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.3492</v>
+        <v>-0.3182</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3492</v>
+        <v>-0.3182</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.3492</v>
+        <v>-0.3182</v>
       </c>
       <c r="N61" t="n">
         <v>93</v>
@@ -3256,31 +3256,31 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.4539</v>
+        <v>-0.4739</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2621</v>
+        <v>-0.2736</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8166</v>
+        <v>-0.8217</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.4539</v>
+        <v>-0.4739</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3222</v>
+        <v>0.3418</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.5831</v>
+        <v>-0.6227</v>
       </c>
       <c r="H62" t="n">
-        <v>0.3222</v>
+        <v>0.3418</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3222</v>
+        <v>0.3418</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.5831</v>
+        <v>-0.6227</v>
       </c>
       <c r="K62" t="n">
         <v>42</v>
@@ -3289,7 +3289,7 @@
         <v>80</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.2609</v>
+        <v>-0.2809</v>
       </c>
       <c r="N62" t="n">
         <v>122</v>
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.5508</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.318</v>
+        <v>-0.307</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8599</v>
+        <v>-0.848</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5508</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.5118</v>
+        <v>-0.4928</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.5118</v>
+        <v>-0.4928</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.5118</v>
+        <v>-0.4928</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.5118</v>
+        <v>-0.4928</v>
       </c>
       <c r="N63" t="n">
         <v>93</v>
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.7391</v>
+        <v>-0.6862</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4267</v>
+        <v>-0.3962</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.944</v>
+        <v>-0.9184</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.7391</v>
+        <v>-0.6862</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.5422</v>
+        <v>-0.4893</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.5422</v>
+        <v>-0.4893</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.5422</v>
+        <v>-0.4893</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.5422</v>
+        <v>-0.4893</v>
       </c>
       <c r="N64" t="n">
         <v>71</v>
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8072</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.466</v>
+        <v>-0.4938</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9744</v>
+        <v>-0.9954</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8072</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8135</v>
+        <v>-0.8616</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8135</v>
+        <v>-0.8616</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8135</v>
+        <v>-0.8616</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.8135</v>
+        <v>-0.8616</v>
       </c>
       <c r="N65" t="n">
         <v>117</v>
@@ -3440,28 +3440,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8941</v>
+        <v>-0.8595</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5162</v>
+        <v>-0.4962</v>
       </c>
       <c r="D66" t="n">
-        <v>-1.0132</v>
+        <v>-0.9973</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8941</v>
+        <v>-0.8595</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.7752</v>
+        <v>-0.7406</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.7752</v>
+        <v>-0.7406</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7752</v>
+        <v>-0.7406</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.7752</v>
+        <v>-0.7406</v>
       </c>
       <c r="N66" t="n">
         <v>111</v>
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.9012</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5203</v>
+        <v>-0.5026</v>
       </c>
       <c r="D67" t="n">
-        <v>-1.0164</v>
+        <v>-1.0023</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.9012</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.6857</v>
+        <v>-0.655</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.6857</v>
+        <v>-0.655</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.6857</v>
+        <v>-0.655</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.6857</v>
+        <v>-0.655</v>
       </c>
       <c r="N67" t="n">
         <v>48</v>
@@ -3532,28 +3532,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.0139</v>
+        <v>-0.9711</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5854</v>
+        <v>-0.5607</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.0667</v>
+        <v>-1.0482</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.0139</v>
+        <v>-0.9711</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.8831</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.8831</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.8831</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.8831</v>
       </c>
       <c r="N68" t="n">
         <v>69</v>
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.0462</v>
+        <v>-1.0742</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.604</v>
+        <v>-0.6202</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0811</v>
+        <v>-1.0951</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.0462</v>
+        <v>-1.0742</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.8572</v>
+        <v>-0.8852</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.8572</v>
+        <v>-0.8852</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.8572</v>
+        <v>-0.8852</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.8572</v>
+        <v>-0.8852</v>
       </c>
       <c r="N69" t="n">
         <v>69</v>
@@ -3620,7 +3620,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -3630,83 +3630,83 @@
         <v>-0.6468</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.1142</v>
+        <v>-1.1161</v>
       </c>
       <c r="E70" t="n">
         <v>-1.1203</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.7377</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.7377</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.7377</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.7377</v>
       </c>
       <c r="N70" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.1649</v>
+        <v>-1.125</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.6725</v>
+        <v>-0.6495</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.1342</v>
+        <v>-1.1183</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.1649</v>
+        <v>-1.125</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.7823</v>
+        <v>-0.5173</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.7823</v>
+        <v>-0.5173</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7823</v>
+        <v>-0.5173</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.7823</v>
+        <v>-0.5173</v>
       </c>
       <c r="N71" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72">
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.2535</v>
+        <v>-1.2218</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.7237</v>
+        <v>-0.7054</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1737</v>
+        <v>-1.1624</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.2535</v>
+        <v>-1.2218</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.0206</v>
+        <v>-0.9889</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.0206</v>
+        <v>-0.9889</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.0206</v>
+        <v>-0.9889</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.0206</v>
+        <v>-0.9889</v>
       </c>
       <c r="N72" t="n">
         <v>71</v>
@@ -3762,31 +3762,31 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.4061</v>
+        <v>-1.427</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.8118</v>
+        <v>-0.8239</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.2419</v>
+        <v>-1.2559</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.4061</v>
+        <v>-1.427</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.6474</v>
+        <v>-0.6575</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.4721</v>
+        <v>-0.4829</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.6474</v>
+        <v>-0.6575</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.6641</v>
+        <v>-0.6751</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.4721</v>
+        <v>-0.4829</v>
       </c>
       <c r="K73" t="n">
         <v>116</v>
@@ -3795,7 +3795,7 @@
         <v>64</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.1362</v>
+        <v>-1.158</v>
       </c>
       <c r="N73" t="n">
         <v>180</v>
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.6227</v>
+        <v>-1.6005</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.9368</v>
+        <v>-0.924</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.3386</v>
+        <v>-1.3349</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.6227</v>
+        <v>-1.6005</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.3329</v>
+        <v>-1.3107</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.3329</v>
+        <v>-1.3107</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.3329</v>
+        <v>-1.3107</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.3329</v>
+        <v>-1.3107</v>
       </c>
       <c r="N74" t="n">
         <v>48</v>
@@ -3854,31 +3854,31 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.8906</v>
+        <v>-1.8821</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.0915</v>
+        <v>-1.0866</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.4583</v>
+        <v>-1.4632</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.8906</v>
+        <v>-1.8821</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.4528</v>
+        <v>-1.4311</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.2903</v>
+        <v>-0.3035</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.4528</v>
+        <v>-1.4311</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.4528</v>
+        <v>-1.4311</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.2903</v>
+        <v>-0.3035</v>
       </c>
       <c r="K75" t="n">
         <v>53</v>
@@ -3887,7 +3887,7 @@
         <v>174</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.7431</v>
+        <v>-1.7346</v>
       </c>
       <c r="N75" t="n">
         <v>227</v>
@@ -3900,31 +3900,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-2.0961</v>
+        <v>-2.1314</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.2102</v>
+        <v>-1.2305</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.5501</v>
+        <v>-1.5767</v>
       </c>
       <c r="E76" t="n">
-        <v>-2.0961</v>
+        <v>-2.1314</v>
       </c>
       <c r="F76" t="n">
-        <v>-2.1116</v>
+        <v>-2.1349</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2016</v>
+        <v>0.1896</v>
       </c>
       <c r="H76" t="n">
-        <v>-2.1116</v>
+        <v>-2.1349</v>
       </c>
       <c r="I76" t="n">
-        <v>-2.1116</v>
+        <v>-2.1349</v>
       </c>
       <c r="J76" t="n">
-        <v>0.2016</v>
+        <v>0.1896</v>
       </c>
       <c r="K76" t="n">
         <v>53</v>
@@ -3933,7 +3933,7 @@
         <v>51</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.91</v>
+        <v>-1.9453</v>
       </c>
       <c r="N76" t="n">
         <v>104</v>
@@ -4039,10 +4039,10 @@
         <v>1.33</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4595</v>
+        <v>0.3928</v>
       </c>
       <c r="J2" t="n">
-        <v>13.785</v>
+        <v>11.784</v>
       </c>
     </row>
     <row r="3">
@@ -4079,10 +4079,10 @@
         <v>1.29</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4142</v>
+        <v>0.35</v>
       </c>
       <c r="J3" t="n">
-        <v>12.426</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="4">
@@ -4119,10 +4119,10 @@
         <v>1.08</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1492</v>
+        <v>0.1146</v>
       </c>
       <c r="J4" t="n">
-        <v>4.476</v>
+        <v>3.438</v>
       </c>
     </row>
     <row r="5">
@@ -4159,10 +4159,10 @@
         <v>1.07</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1341</v>
+        <v>0.1021</v>
       </c>
       <c r="J5" t="n">
-        <v>4.023</v>
+        <v>3.063</v>
       </c>
     </row>
     <row r="6">
@@ -4199,10 +4199,10 @@
         <v>0.74</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.319</v>
+        <v>-0.3031</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.57</v>
+        <v>-9.093</v>
       </c>
     </row>
     <row r="7">
@@ -4239,10 +4239,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0819</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>2.457</v>
+        <v>2.028</v>
       </c>
     </row>
     <row r="8">
@@ -4279,10 +4279,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0608</v>
+        <v>0.0485</v>
       </c>
       <c r="J8" t="n">
-        <v>1.824</v>
+        <v>1.455</v>
       </c>
     </row>
     <row r="9">
@@ -4319,10 +4319,10 @@
         <v>0.99</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0236</v>
+        <v>-0.0174</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.708</v>
+        <v>-0.522</v>
       </c>
     </row>
     <row r="10">
@@ -4359,10 +4359,10 @@
         <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0704</v>
+        <v>-0.057</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.112</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="11">
@@ -4399,10 +4399,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.209</v>
+        <v>-0.1885</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.27</v>
+        <v>-5.655</v>
       </c>
     </row>
     <row r="12">
@@ -4439,10 +4439,10 @@
         <v>1.36</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7542</v>
+        <v>0.7136</v>
       </c>
       <c r="J12" t="n">
-        <v>14.3298</v>
+        <v>13.5584</v>
       </c>
     </row>
     <row r="13">
@@ -4479,10 +4479,10 @@
         <v>0.95</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0722</v>
+        <v>-0.0602</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.3718</v>
+        <v>-1.1438</v>
       </c>
     </row>
     <row r="14">
@@ -4519,10 +4519,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3411</v>
+        <v>-0.3254</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.4809</v>
+        <v>-6.1826</v>
       </c>
     </row>
     <row r="15">
@@ -4559,10 +4559,10 @@
         <v>0.61</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4134</v>
+        <v>-0.4032</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.8546</v>
+        <v>-7.6608</v>
       </c>
     </row>
     <row r="16">
@@ -4599,10 +4599,10 @@
         <v>0.59</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4312</v>
+        <v>-0.4226</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.1928</v>
+        <v>-8.029400000000001</v>
       </c>
     </row>
     <row r="17">
@@ -4639,10 +4639,10 @@
         <v>1.71</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4743</v>
+        <v>1.5084</v>
       </c>
       <c r="J17" t="n">
-        <v>28.0117</v>
+        <v>28.6596</v>
       </c>
     </row>
     <row r="18">
@@ -4679,10 +4679,10 @@
         <v>1.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2873</v>
+        <v>1.3141</v>
       </c>
       <c r="J18" t="n">
-        <v>24.4587</v>
+        <v>24.9679</v>
       </c>
     </row>
     <row r="19">
@@ -4719,10 +4719,10 @@
         <v>1.49</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0912</v>
+        <v>1.0953</v>
       </c>
       <c r="J19" t="n">
-        <v>20.7328</v>
+        <v>20.8107</v>
       </c>
     </row>
     <row r="20">
@@ -4759,10 +4759,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2258</v>
+        <v>-0.1937</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.2902</v>
+        <v>-3.6803</v>
       </c>
     </row>
     <row r="21">
@@ -4799,10 +4799,10 @@
         <v>0.85</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5268</v>
+        <v>-0.4917</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.0092</v>
+        <v>-9.3423</v>
       </c>
     </row>
     <row r="22">
@@ -4839,10 +4839,10 @@
         <v>1.19</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4697</v>
+        <v>0.4186</v>
       </c>
       <c r="J22" t="n">
-        <v>8.924300000000001</v>
+        <v>7.9534</v>
       </c>
     </row>
     <row r="23">
@@ -4879,10 +4879,10 @@
         <v>1.08</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2546</v>
+        <v>0.211</v>
       </c>
       <c r="J23" t="n">
-        <v>4.8374</v>
+        <v>4.009</v>
       </c>
     </row>
     <row r="24">
@@ -4919,10 +4919,10 @@
         <v>0.7</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3309</v>
+        <v>-0.3146</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.2871</v>
+        <v>-5.9774</v>
       </c>
     </row>
     <row r="25">
@@ -4959,10 +4959,10 @@
         <v>0.66</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3674</v>
+        <v>-0.3534</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.9806</v>
+        <v>-6.7146</v>
       </c>
     </row>
     <row r="26">
@@ -4999,10 +4999,10 @@
         <v>0.52</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4913</v>
+        <v>-0.4897</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.3347</v>
+        <v>-9.3043</v>
       </c>
     </row>
     <row r="27">
@@ -5039,10 +5039,10 @@
         <v>1.73</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5082</v>
+        <v>1.5404</v>
       </c>
       <c r="J27" t="n">
-        <v>28.6558</v>
+        <v>29.2676</v>
       </c>
     </row>
     <row r="28">
@@ -5079,10 +5079,10 @@
         <v>1.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1114</v>
+        <v>1.1173</v>
       </c>
       <c r="J28" t="n">
-        <v>21.1166</v>
+        <v>21.2287</v>
       </c>
     </row>
     <row r="29">
@@ -5119,10 +5119,10 @@
         <v>1.32</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7761</v>
+        <v>0.7557</v>
       </c>
       <c r="J29" t="n">
-        <v>14.7459</v>
+        <v>14.3583</v>
       </c>
     </row>
     <row r="30">
@@ -5159,10 +5159,10 @@
         <v>1.17</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4632</v>
+        <v>0.432</v>
       </c>
       <c r="J30" t="n">
-        <v>8.800800000000001</v>
+        <v>8.208</v>
       </c>
     </row>
     <row r="31">
@@ -5199,10 +5199,10 @@
         <v>0.84</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5494</v>
+        <v>-0.5149</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.4386</v>
+        <v>-9.783099999999999</v>
       </c>
     </row>
     <row r="32">
@@ -5239,10 +5239,10 @@
         <v>2.21</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0077</v>
+        <v>0.9472</v>
       </c>
       <c r="J32" t="n">
-        <v>14.1078</v>
+        <v>13.2608</v>
       </c>
     </row>
     <row r="33">
@@ -5279,10 +5279,10 @@
         <v>1.73</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7048</v>
+        <v>0.6607</v>
       </c>
       <c r="J33" t="n">
-        <v>9.8672</v>
+        <v>9.2498</v>
       </c>
     </row>
     <row r="34">
@@ -5319,10 +5319,10 @@
         <v>1.5</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5508</v>
+        <v>0.5203</v>
       </c>
       <c r="J34" t="n">
-        <v>7.7112</v>
+        <v>7.2842</v>
       </c>
     </row>
     <row r="35">
@@ -5359,10 +5359,10 @@
         <v>1.27</v>
       </c>
       <c r="I35" t="n">
-        <v>0.352</v>
+        <v>0.2993</v>
       </c>
       <c r="J35" t="n">
-        <v>4.928</v>
+        <v>4.1902</v>
       </c>
     </row>
     <row r="36">
@@ -5399,10 +5399,10 @@
         <v>1.19</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2577</v>
+        <v>0.2118</v>
       </c>
       <c r="J36" t="n">
-        <v>3.6078</v>
+        <v>2.9652</v>
       </c>
     </row>
     <row r="37">
@@ -5439,10 +5439,10 @@
         <v>1.08</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2759</v>
+        <v>0.2935</v>
       </c>
       <c r="J37" t="n">
-        <v>3.8626</v>
+        <v>4.109</v>
       </c>
     </row>
     <row r="38">
@@ -5479,10 +5479,10 @@
         <v>0.7</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3099</v>
+        <v>-0.2983</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.3386</v>
+        <v>-4.1762</v>
       </c>
     </row>
     <row r="39">
@@ -5519,10 +5519,10 @@
         <v>0.59</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4063</v>
+        <v>-0.3973</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.6882</v>
+        <v>-5.5622</v>
       </c>
     </row>
     <row r="40">
@@ -5559,10 +5559,10 @@
         <v>0.44</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5381</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.5334</v>
+        <v>-7.5712</v>
       </c>
     </row>
     <row r="41">
@@ -5599,10 +5599,10 @@
         <v>0.37</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5995</v>
+        <v>-0.6113</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.393000000000001</v>
+        <v>-8.558199999999999</v>
       </c>
     </row>
     <row r="42">
@@ -5639,10 +5639,10 @@
         <v>1.13</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3339</v>
+        <v>0.282</v>
       </c>
       <c r="J42" t="n">
-        <v>7.0119</v>
+        <v>5.922</v>
       </c>
     </row>
     <row r="43">
@@ -5679,10 +5679,10 @@
         <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1432</v>
+        <v>0.1093</v>
       </c>
       <c r="J43" t="n">
-        <v>3.0072</v>
+        <v>2.2953</v>
       </c>
     </row>
     <row r="44">
@@ -5719,10 +5719,10 @@
         <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1432</v>
+        <v>0.1093</v>
       </c>
       <c r="J44" t="n">
-        <v>3.0072</v>
+        <v>2.2953</v>
       </c>
     </row>
     <row r="45">
@@ -5759,10 +5759,10 @@
         <v>0.76</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2818</v>
+        <v>-0.2631</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.9178</v>
+        <v>-5.5251</v>
       </c>
     </row>
     <row r="46">
@@ -5799,10 +5799,10 @@
         <v>0.53</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4893</v>
+        <v>-0.4883</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.2753</v>
+        <v>-10.2543</v>
       </c>
     </row>
     <row r="47">
@@ -5839,10 +5839,10 @@
         <v>1.56</v>
       </c>
       <c r="I47" t="n">
-        <v>1.0251</v>
+        <v>1.0134</v>
       </c>
       <c r="J47" t="n">
-        <v>21.5271</v>
+        <v>21.2814</v>
       </c>
     </row>
     <row r="48">
@@ -5879,10 +5879,10 @@
         <v>1.47</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9038</v>
+        <v>0.8894</v>
       </c>
       <c r="J48" t="n">
-        <v>18.9798</v>
+        <v>18.6774</v>
       </c>
     </row>
     <row r="49">
@@ -5919,10 +5919,10 @@
         <v>1.2</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5121</v>
+        <v>0.504</v>
       </c>
       <c r="J49" t="n">
-        <v>10.7541</v>
+        <v>10.584</v>
       </c>
     </row>
     <row r="50">
@@ -5959,10 +5959,10 @@
         <v>1.17</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4621</v>
+        <v>0.4386</v>
       </c>
       <c r="J50" t="n">
-        <v>9.7041</v>
+        <v>9.210599999999999</v>
       </c>
     </row>
     <row r="51">
@@ -5999,10 +5999,10 @@
         <v>0.91</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3637</v>
+        <v>-0.3244</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.6377</v>
+        <v>-6.8124</v>
       </c>
     </row>
     <row r="52">
@@ -6039,10 +6039,10 @@
         <v>1.36</v>
       </c>
       <c r="I52" t="n">
-        <v>0.658</v>
+        <v>0.633</v>
       </c>
       <c r="J52" t="n">
-        <v>11.844</v>
+        <v>11.394</v>
       </c>
     </row>
     <row r="53">
@@ -6079,10 +6079,10 @@
         <v>0.82</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2212</v>
+        <v>-0.2017</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.9816</v>
+        <v>-3.6306</v>
       </c>
     </row>
     <row r="54">
@@ -6119,10 +6119,10 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2606</v>
+        <v>-0.2414</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.6908</v>
+        <v>-4.3452</v>
       </c>
     </row>
     <row r="55">
@@ -6159,10 +6159,10 @@
         <v>0.73</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3082</v>
+        <v>-0.2906</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.5476</v>
+        <v>-5.2308</v>
       </c>
     </row>
     <row r="56">
@@ -6199,10 +6199,10 @@
         <v>0.71</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3269</v>
+        <v>-0.3102</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.8842</v>
+        <v>-5.5836</v>
       </c>
     </row>
     <row r="57">
@@ -6239,10 +6239,10 @@
         <v>2.12</v>
       </c>
       <c r="I57" t="n">
-        <v>1.703</v>
+        <v>1.7465</v>
       </c>
       <c r="J57" t="n">
-        <v>30.654</v>
+        <v>31.437</v>
       </c>
     </row>
     <row r="58">
@@ -6279,10 +6279,10 @@
         <v>1.53</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9729</v>
+        <v>0.9607</v>
       </c>
       <c r="J58" t="n">
-        <v>17.5122</v>
+        <v>17.2926</v>
       </c>
     </row>
     <row r="59">
@@ -6319,10 +6319,10 @@
         <v>1.24</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5683</v>
+        <v>0.5644</v>
       </c>
       <c r="J59" t="n">
-        <v>10.2294</v>
+        <v>10.1592</v>
       </c>
     </row>
     <row r="60">
@@ -6359,10 +6359,10 @@
         <v>0.93</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3189</v>
+        <v>-0.2826</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.7402</v>
+        <v>-5.0868</v>
       </c>
     </row>
     <row r="61">
@@ -6399,10 +6399,10 @@
         <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5524</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.943199999999999</v>
+        <v>-9.3348</v>
       </c>
     </row>
     <row r="62">
@@ -6439,10 +6439,10 @@
         <v>2.88</v>
       </c>
       <c r="I62" t="n">
-        <v>2.4557</v>
+        <v>2.5795</v>
       </c>
       <c r="J62" t="n">
-        <v>41.7469</v>
+        <v>43.8515</v>
       </c>
     </row>
     <row r="63">
@@ -6479,10 +6479,10 @@
         <v>1.89</v>
       </c>
       <c r="I63" t="n">
-        <v>1.3768</v>
+        <v>1.3857</v>
       </c>
       <c r="J63" t="n">
-        <v>23.4056</v>
+        <v>23.5569</v>
       </c>
     </row>
     <row r="64">
@@ -6519,10 +6519,10 @@
         <v>1.58</v>
       </c>
       <c r="I64" t="n">
-        <v>1.0091</v>
+        <v>1.005</v>
       </c>
       <c r="J64" t="n">
-        <v>17.1547</v>
+        <v>17.085</v>
       </c>
     </row>
     <row r="65">
@@ -6559,10 +6559,10 @@
         <v>0.91</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4101</v>
+        <v>-0.3819</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.9717</v>
+        <v>-6.4923</v>
       </c>
     </row>
     <row r="66">
@@ -6599,10 +6599,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8307</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.1219</v>
+        <v>-14.0267</v>
       </c>
     </row>
     <row r="67">
@@ -6639,10 +6639,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.0573</v>
+        <v>-0.0416</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.9741</v>
+        <v>-0.7072000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -6679,10 +6679,10 @@
         <v>0.75</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2709</v>
+        <v>-0.2569</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.6053</v>
+        <v>-4.3673</v>
       </c>
     </row>
     <row r="69">
@@ -6719,10 +6719,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3255</v>
+        <v>-0.3122</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.5335</v>
+        <v>-5.3074</v>
       </c>
     </row>
     <row r="70">
@@ -6759,10 +6759,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4402</v>
+        <v>-0.4323</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.4834</v>
+        <v>-7.3491</v>
       </c>
     </row>
     <row r="71">
@@ -6799,10 +6799,10 @@
         <v>0.52</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4754</v>
+        <v>-0.4709</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.081799999999999</v>
+        <v>-8.0053</v>
       </c>
     </row>
     <row r="72">
@@ -6839,10 +6839,10 @@
         <v>1.61</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0979</v>
+        <v>1.0892</v>
       </c>
       <c r="J72" t="n">
-        <v>21.958</v>
+        <v>21.784</v>
       </c>
     </row>
     <row r="73">
@@ -6879,10 +6879,10 @@
         <v>1.57</v>
       </c>
       <c r="I73" t="n">
-        <v>1.0448</v>
+        <v>1.0337</v>
       </c>
       <c r="J73" t="n">
-        <v>20.896</v>
+        <v>20.674</v>
       </c>
     </row>
     <row r="74">
@@ -6919,10 +6919,10 @@
         <v>1.35</v>
       </c>
       <c r="I74" t="n">
-        <v>0.74</v>
+        <v>0.7259</v>
       </c>
       <c r="J74" t="n">
-        <v>14.8</v>
+        <v>14.518</v>
       </c>
     </row>
     <row r="75">
@@ -6959,10 +6959,10 @@
         <v>1.1</v>
       </c>
       <c r="I75" t="n">
-        <v>0.305</v>
+        <v>0.2729</v>
       </c>
       <c r="J75" t="n">
-        <v>6.1</v>
+        <v>5.458</v>
       </c>
     </row>
     <row r="76">
@@ -6999,10 +6999,10 @@
         <v>0.53</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.1916</v>
+        <v>-1.222</v>
       </c>
       <c r="J76" t="n">
-        <v>-23.832</v>
+        <v>-24.44</v>
       </c>
     </row>
     <row r="77">
@@ -7039,10 +7039,10 @@
         <v>1.35</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6549</v>
+        <v>0.632</v>
       </c>
       <c r="J77" t="n">
-        <v>13.098</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="78">
@@ -7079,10 +7079,10 @@
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0256</v>
+        <v>0.02</v>
       </c>
       <c r="J78" t="n">
-        <v>0.512</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="79">
@@ -7119,10 +7119,10 @@
         <v>0.71</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3242</v>
+        <v>-0.3075</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.484</v>
+        <v>-6.15</v>
       </c>
     </row>
     <row r="80">
@@ -7159,10 +7159,10 @@
         <v>0.64</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3881</v>
+        <v>-0.3756</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.762</v>
+        <v>-7.512</v>
       </c>
     </row>
     <row r="81">
@@ -7199,10 +7199,10 @@
         <v>0.57</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4502</v>
+        <v>-0.4438</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.004</v>
+        <v>-8.875999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -7239,10 +7239,10 @@
         <v>1.35</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7359</v>
       </c>
       <c r="J82" t="n">
-        <v>17.2845</v>
+        <v>16.9257</v>
       </c>
     </row>
     <row r="83">
@@ -7279,10 +7279,10 @@
         <v>1.2</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5206</v>
+        <v>0.5097</v>
       </c>
       <c r="J83" t="n">
-        <v>11.9738</v>
+        <v>11.7231</v>
       </c>
     </row>
     <row r="84">
@@ -7319,10 +7319,10 @@
         <v>1.15</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4357</v>
+        <v>0.402</v>
       </c>
       <c r="J84" t="n">
-        <v>10.0211</v>
+        <v>9.246</v>
       </c>
     </row>
     <row r="85">
@@ -7359,10 +7359,10 @@
         <v>1.07</v>
       </c>
       <c r="I85" t="n">
-        <v>0.235</v>
+        <v>0.2045</v>
       </c>
       <c r="J85" t="n">
-        <v>5.405</v>
+        <v>4.7035</v>
       </c>
     </row>
     <row r="86">
@@ -7399,10 +7399,10 @@
         <v>1.04</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1444</v>
+        <v>0.1202</v>
       </c>
       <c r="J86" t="n">
-        <v>3.3212</v>
+        <v>2.7646</v>
       </c>
     </row>
     <row r="87">
@@ -7439,10 +7439,10 @@
         <v>1.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5708</v>
+        <v>0.5465</v>
       </c>
       <c r="J87" t="n">
-        <v>13.1284</v>
+        <v>12.5695</v>
       </c>
     </row>
     <row r="88">
@@ -7479,10 +7479,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.021</v>
+        <v>-0.0156</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.483</v>
+        <v>-0.3588</v>
       </c>
     </row>
     <row r="89">
@@ -7519,10 +7519,10 @@
         <v>0.93</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1069</v>
+        <v>-0.0907</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.4587</v>
+        <v>-2.0861</v>
       </c>
     </row>
     <row r="90">
@@ -7559,10 +7559,10 @@
         <v>0.79</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2563</v>
+        <v>-0.2366</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.8949</v>
+        <v>-5.4418</v>
       </c>
     </row>
     <row r="91">
@@ -7599,10 +7599,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3692</v>
+        <v>-0.3556</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.4916</v>
+        <v>-8.178800000000001</v>
       </c>
     </row>
     <row r="92">
@@ -7639,10 +7639,10 @@
         <v>1.81</v>
       </c>
       <c r="I92" t="n">
-        <v>1.3706</v>
+        <v>1.3836</v>
       </c>
       <c r="J92" t="n">
-        <v>38.3768</v>
+        <v>38.7408</v>
       </c>
     </row>
     <row r="93">
@@ -7679,10 +7679,10 @@
         <v>1.34</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7329</v>
+        <v>0.7179</v>
       </c>
       <c r="J93" t="n">
-        <v>20.5212</v>
+        <v>20.1012</v>
       </c>
     </row>
     <row r="94">
@@ -7719,10 +7719,10 @@
         <v>1.17</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4702</v>
+        <v>0.446</v>
       </c>
       <c r="J94" t="n">
-        <v>13.1656</v>
+        <v>12.488</v>
       </c>
     </row>
     <row r="95">
@@ -7759,10 +7759,10 @@
         <v>0.98</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.132</v>
+        <v>-0.1048</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.696</v>
+        <v>-2.9344</v>
       </c>
     </row>
     <row r="96">
@@ -7799,10 +7799,10 @@
         <v>0.62</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.0076</v>
+        <v>-1.0101</v>
       </c>
       <c r="J96" t="n">
-        <v>-28.2128</v>
+        <v>-28.2828</v>
       </c>
     </row>
     <row r="97">
@@ -7839,10 +7839,10 @@
         <v>1.49</v>
       </c>
       <c r="I97" t="n">
-        <v>0.787</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="J97" t="n">
-        <v>22.036</v>
+        <v>21.1848</v>
       </c>
     </row>
     <row r="98">
@@ -7879,10 +7879,10 @@
         <v>0.93</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1069</v>
+        <v>-0.0907</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.9932</v>
+        <v>-2.5396</v>
       </c>
     </row>
     <row r="99">
@@ -7919,10 +7919,10 @@
         <v>0.92</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1187</v>
+        <v>-0.1016</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.3236</v>
+        <v>-2.8448</v>
       </c>
     </row>
     <row r="100">
@@ -7959,10 +7959,10 @@
         <v>0.67</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3692</v>
+        <v>-0.3556</v>
       </c>
       <c r="J100" t="n">
-        <v>-10.3376</v>
+        <v>-9.956799999999999</v>
       </c>
     </row>
     <row r="101">
@@ -7999,10 +7999,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3692</v>
+        <v>-0.3556</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.3376</v>
+        <v>-9.956799999999999</v>
       </c>
     </row>
     <row r="102">
@@ -8039,10 +8039,10 @@
         <v>1.88</v>
       </c>
       <c r="I102" t="n">
-        <v>1.4436</v>
+        <v>1.4618</v>
       </c>
       <c r="J102" t="n">
-        <v>28.872</v>
+        <v>29.236</v>
       </c>
     </row>
     <row r="103">
@@ -8079,10 +8079,10 @@
         <v>1.43</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8537</v>
+        <v>0.8385</v>
       </c>
       <c r="J103" t="n">
-        <v>17.074</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="104">
@@ -8119,10 +8119,10 @@
         <v>1.39</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7973</v>
+        <v>0.7823</v>
       </c>
       <c r="J104" t="n">
-        <v>15.946</v>
+        <v>15.646</v>
       </c>
     </row>
     <row r="105">
@@ -8159,10 +8159,10 @@
         <v>0.83</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5607</v>
+        <v>-0.5244</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.214</v>
+        <v>-10.488</v>
       </c>
     </row>
     <row r="106">
@@ -8199,10 +8199,10 @@
         <v>0.63</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.9942</v>
+        <v>-0.9965000000000001</v>
       </c>
       <c r="J106" t="n">
-        <v>-19.884</v>
+        <v>-19.93</v>
       </c>
     </row>
     <row r="107">
@@ -8239,10 +8239,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5654</v>
+        <v>0.5405</v>
       </c>
       <c r="J107" t="n">
-        <v>11.308</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="108">
@@ -8279,10 +8279,10 @@
         <v>1.06</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1774</v>
+        <v>0.1386</v>
       </c>
       <c r="J108" t="n">
-        <v>3.548</v>
+        <v>2.772</v>
       </c>
     </row>
     <row r="109">
@@ -8319,10 +8319,10 @@
         <v>1.01</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0487</v>
+        <v>0.0325</v>
       </c>
       <c r="J109" t="n">
-        <v>0.974</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="110">
@@ -8359,10 +8359,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2971</v>
+        <v>-0.2788</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.942</v>
+        <v>-5.576</v>
       </c>
     </row>
     <row r="111">
@@ -8399,10 +8399,10 @@
         <v>0.67</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3713</v>
+        <v>-0.358</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.426</v>
+        <v>-7.16</v>
       </c>
     </row>
     <row r="112">
@@ -8439,10 +8439,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5369</v>
+        <v>0.569</v>
       </c>
       <c r="J112" t="n">
-        <v>12.8856</v>
+        <v>13.656</v>
       </c>
     </row>
     <row r="113">
@@ -8479,10 +8479,10 @@
         <v>1.29</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4547</v>
+        <v>0.4665</v>
       </c>
       <c r="J113" t="n">
-        <v>10.9128</v>
+        <v>11.196</v>
       </c>
     </row>
     <row r="114">
@@ -8519,10 +8519,10 @@
         <v>1.04</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1006</v>
+        <v>0.0852</v>
       </c>
       <c r="J114" t="n">
-        <v>2.4144</v>
+        <v>2.0448</v>
       </c>
     </row>
     <row r="115">
@@ -8559,10 +8559,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2401</v>
+        <v>-0.2199</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.7624</v>
+        <v>-5.2776</v>
       </c>
     </row>
     <row r="116">
@@ -8599,10 +8599,10 @@
         <v>0.35</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6451</v>
+        <v>-0.6701</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.4824</v>
+        <v>-16.0824</v>
       </c>
     </row>
     <row r="117">
@@ -8639,10 +8639,10 @@
         <v>1.3</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4262</v>
+        <v>0.3627</v>
       </c>
       <c r="J117" t="n">
-        <v>10.2288</v>
+        <v>8.704800000000001</v>
       </c>
     </row>
     <row r="118">
@@ -8679,10 +8679,10 @@
         <v>1.12</v>
       </c>
       <c r="I118" t="n">
-        <v>0.206</v>
+        <v>0.1623</v>
       </c>
       <c r="J118" t="n">
-        <v>4.944</v>
+        <v>3.8952</v>
       </c>
     </row>
     <row r="119">
@@ -8719,10 +8719,10 @@
         <v>1.11</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1924</v>
+        <v>0.1506</v>
       </c>
       <c r="J119" t="n">
-        <v>4.6176</v>
+        <v>3.6144</v>
       </c>
     </row>
     <row r="120">
@@ -8759,10 +8759,10 @@
         <v>1.01</v>
       </c>
       <c r="I120" t="n">
-        <v>0.0253</v>
+        <v>0.0167</v>
       </c>
       <c r="J120" t="n">
-        <v>0.6072</v>
+        <v>0.4008</v>
       </c>
     </row>
     <row r="121">
@@ -8799,10 +8799,10 @@
         <v>0.9</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1544</v>
+        <v>-0.1344</v>
       </c>
       <c r="J121" t="n">
-        <v>-3.7056</v>
+        <v>-3.2256</v>
       </c>
     </row>
     <row r="122">
@@ -8839,10 +8839,10 @@
         <v>1.57</v>
       </c>
       <c r="I122" t="n">
-        <v>1.043</v>
+        <v>1.0319</v>
       </c>
       <c r="J122" t="n">
-        <v>20.86</v>
+        <v>20.638</v>
       </c>
     </row>
     <row r="123">
@@ -8879,10 +8879,10 @@
         <v>1.4</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8102</v>
+        <v>0.7953</v>
       </c>
       <c r="J123" t="n">
-        <v>16.204</v>
+        <v>15.906</v>
       </c>
     </row>
     <row r="124">
@@ -8919,10 +8919,10 @@
         <v>1.15</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4261</v>
+        <v>0.3945</v>
       </c>
       <c r="J124" t="n">
-        <v>8.522</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="125">
@@ -8959,10 +8959,10 @@
         <v>1.07</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2219</v>
+        <v>0.1927</v>
       </c>
       <c r="J125" t="n">
-        <v>4.438</v>
+        <v>3.854</v>
       </c>
     </row>
     <row r="126">
@@ -8999,10 +8999,10 @@
         <v>1.01</v>
       </c>
       <c r="I126" t="n">
-        <v>0.0193</v>
+        <v>0.0094</v>
       </c>
       <c r="J126" t="n">
-        <v>0.386</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="127">
@@ -9039,10 +9039,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0708</v>
       </c>
       <c r="J127" t="n">
-        <v>-1.672</v>
+        <v>-1.416</v>
       </c>
     </row>
     <row r="128">
@@ -9079,10 +9079,10 @@
         <v>0.91</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.121</v>
+        <v>-0.106</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.42</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="129">
@@ -9119,10 +9119,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1872</v>
+        <v>-0.1699</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.744</v>
+        <v>-3.398</v>
       </c>
     </row>
     <row r="130">
@@ -9159,10 +9159,10 @@
         <v>0.74</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2932</v>
+        <v>-0.2755</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.864</v>
+        <v>-5.51</v>
       </c>
     </row>
     <row r="131">
@@ -9199,10 +9199,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3396</v>
+        <v>-0.3239</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.792</v>
+        <v>-6.478</v>
       </c>
     </row>
     <row r="132">
@@ -9239,10 +9239,10 @@
         <v>1.26</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3797</v>
+        <v>0.3178</v>
       </c>
       <c r="J132" t="n">
-        <v>15.9474</v>
+        <v>13.3476</v>
       </c>
     </row>
     <row r="133">
@@ -9279,10 +9279,10 @@
         <v>1.19</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2954</v>
+        <v>0.2409</v>
       </c>
       <c r="J133" t="n">
-        <v>12.4068</v>
+        <v>10.1178</v>
       </c>
     </row>
     <row r="134">
@@ -9319,10 +9319,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2317</v>
+        <v>0.1847</v>
       </c>
       <c r="J134" t="n">
-        <v>9.731400000000001</v>
+        <v>7.7574</v>
       </c>
     </row>
     <row r="135">
@@ -9359,10 +9359,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1186</v>
+        <v>0.0893</v>
       </c>
       <c r="J135" t="n">
-        <v>4.9812</v>
+        <v>3.7506</v>
       </c>
     </row>
     <row r="136">
@@ -9399,10 +9399,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2101</v>
+        <v>-0.1898</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.824199999999999</v>
+        <v>-7.9716</v>
       </c>
     </row>
     <row r="137">
@@ -9439,10 +9439,10 @@
         <v>1.13</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2384</v>
+        <v>0.2232</v>
       </c>
       <c r="J137" t="n">
-        <v>10.0128</v>
+        <v>9.3744</v>
       </c>
     </row>
     <row r="138">
@@ -9479,10 +9479,10 @@
         <v>1.09</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1787</v>
+        <v>0.1624</v>
       </c>
       <c r="J138" t="n">
-        <v>7.5054</v>
+        <v>6.8208</v>
       </c>
     </row>
     <row r="139">
@@ -9519,10 +9519,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.095</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="J139" t="n">
-        <v>3.99</v>
+        <v>3.4104</v>
       </c>
     </row>
     <row r="140">
@@ -9559,10 +9559,10 @@
         <v>1.01</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0322</v>
+        <v>0.025</v>
       </c>
       <c r="J140" t="n">
-        <v>1.3524</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="141">
@@ -9599,10 +9599,10 @@
         <v>0.87</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1827</v>
+        <v>-0.1621</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.6734</v>
+        <v>-6.8082</v>
       </c>
     </row>
     <row r="142">
@@ -9639,10 +9639,10 @@
         <v>1.61</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9376</v>
+        <v>0.9156</v>
       </c>
       <c r="J142" t="n">
-        <v>18.752</v>
+        <v>18.312</v>
       </c>
     </row>
     <row r="143">
@@ -9679,10 +9679,10 @@
         <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0188</v>
+        <v>0.0137</v>
       </c>
       <c r="J143" t="n">
-        <v>0.376</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="144">
@@ -9719,10 +9719,10 @@
         <v>0.63</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3999</v>
+        <v>-0.3887</v>
       </c>
       <c r="J144" t="n">
-        <v>-7.998</v>
+        <v>-7.774</v>
       </c>
     </row>
     <row r="145">
@@ -9759,10 +9759,10 @@
         <v>0.61</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4177</v>
+        <v>-0.4082</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.353999999999999</v>
+        <v>-8.164</v>
       </c>
     </row>
     <row r="146">
@@ -9799,10 +9799,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4617</v>
+        <v>-0.4569</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.234</v>
+        <v>-9.138</v>
       </c>
     </row>
     <row r="147">
@@ -9839,10 +9839,10 @@
         <v>1.95</v>
       </c>
       <c r="I147" t="n">
-        <v>1.5324</v>
+        <v>1.5607</v>
       </c>
       <c r="J147" t="n">
-        <v>30.648</v>
+        <v>31.214</v>
       </c>
     </row>
     <row r="148">
@@ -9879,10 +9879,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7409</v>
+        <v>0.7266</v>
       </c>
       <c r="J148" t="n">
-        <v>14.818</v>
+        <v>14.532</v>
       </c>
     </row>
     <row r="149">
@@ -9919,10 +9919,10 @@
         <v>1.2</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.5067</v>
       </c>
       <c r="J149" t="n">
-        <v>10.312</v>
+        <v>10.134</v>
       </c>
     </row>
     <row r="150">
@@ -9959,10 +9959,10 @@
         <v>0.91</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3577</v>
+        <v>-0.3175</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.154</v>
+        <v>-6.35</v>
       </c>
     </row>
     <row r="151">
@@ -9999,10 +9999,10 @@
         <v>0.72</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8064</v>
+        <v>-0.7875</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.128</v>
+        <v>-15.75</v>
       </c>
     </row>
     <row r="152">
@@ -10039,10 +10039,10 @@
         <v>1.09</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2909</v>
+        <v>0.2479</v>
       </c>
       <c r="J152" t="n">
-        <v>5.2362</v>
+        <v>4.4622</v>
       </c>
     </row>
     <row r="153">
@@ -10079,10 +10079,10 @@
         <v>0.9</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1278</v>
+        <v>-0.1128</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.3004</v>
+        <v>-2.0304</v>
       </c>
     </row>
     <row r="154">
@@ -10119,10 +10119,10 @@
         <v>0.77</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2615</v>
+        <v>-0.2443</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.707</v>
+        <v>-4.3974</v>
       </c>
     </row>
     <row r="155">
@@ -10159,10 +10159,10 @@
         <v>0.6</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4168</v>
+        <v>-0.4067</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.5024</v>
+        <v>-7.3206</v>
       </c>
     </row>
     <row r="156">
@@ -10199,10 +10199,10 @@
         <v>0.59</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4257</v>
+        <v>-0.4164</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.6626</v>
+        <v>-7.4952</v>
       </c>
     </row>
     <row r="157">
@@ -10239,10 +10239,10 @@
         <v>1.51</v>
       </c>
       <c r="I157" t="n">
-        <v>0.957</v>
+        <v>0.9436</v>
       </c>
       <c r="J157" t="n">
-        <v>17.226</v>
+        <v>16.9848</v>
       </c>
     </row>
     <row r="158">
@@ -10279,10 +10279,10 @@
         <v>1.33</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7065</v>
+        <v>0.6944</v>
       </c>
       <c r="J158" t="n">
-        <v>12.717</v>
+        <v>12.4992</v>
       </c>
     </row>
     <row r="159">
@@ -10319,10 +10319,10 @@
         <v>1.27</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6192</v>
+        <v>0.6108</v>
       </c>
       <c r="J159" t="n">
-        <v>11.1456</v>
+        <v>10.9944</v>
       </c>
     </row>
     <row r="160">
@@ -10359,10 +10359,10 @@
         <v>1.22</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5434</v>
+        <v>0.5387</v>
       </c>
       <c r="J160" t="n">
-        <v>9.7812</v>
+        <v>9.6966</v>
       </c>
     </row>
     <row r="161">
@@ -10399,10 +10399,10 @@
         <v>1.01</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0146</v>
+        <v>0.0044</v>
       </c>
       <c r="J161" t="n">
-        <v>0.2628</v>
+        <v>0.07920000000000001</v>
       </c>
     </row>
     <row r="162">
@@ -10439,10 +10439,10 @@
         <v>1.45</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7217</v>
+        <v>0.6885</v>
       </c>
       <c r="J162" t="n">
-        <v>15.1557</v>
+        <v>14.4585</v>
       </c>
     </row>
     <row r="163">
@@ -10479,10 +10479,10 @@
         <v>1.15</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3437</v>
+        <v>0.2903</v>
       </c>
       <c r="J163" t="n">
-        <v>7.2177</v>
+        <v>6.0963</v>
       </c>
     </row>
     <row r="164">
@@ -10519,10 +10519,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2504</v>
+        <v>0.2043</v>
       </c>
       <c r="J164" t="n">
-        <v>5.2584</v>
+        <v>4.2903</v>
       </c>
     </row>
     <row r="165">
@@ -10559,10 +10559,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1813</v>
+        <v>-0.1607</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.8073</v>
+        <v>-3.3747</v>
       </c>
     </row>
     <row r="166">
@@ -10599,10 +10599,10 @@
         <v>0.49</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5322</v>
+        <v>-0.5387</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.1762</v>
+        <v>-11.3127</v>
       </c>
     </row>
     <row r="167">
@@ -10639,10 +10639,10 @@
         <v>1.68</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2088</v>
+        <v>1.2086</v>
       </c>
       <c r="J167" t="n">
-        <v>25.3848</v>
+        <v>25.3806</v>
       </c>
     </row>
     <row r="168">
@@ -10679,10 +10679,10 @@
         <v>1.67</v>
       </c>
       <c r="I168" t="n">
-        <v>1.1955</v>
+        <v>1.1944</v>
       </c>
       <c r="J168" t="n">
-        <v>25.1055</v>
+        <v>25.0824</v>
       </c>
     </row>
     <row r="169">
@@ -10719,10 +10719,10 @@
         <v>1.05</v>
       </c>
       <c r="I169" t="n">
-        <v>0.176</v>
+        <v>0.1492</v>
       </c>
       <c r="J169" t="n">
-        <v>3.696</v>
+        <v>3.1332</v>
       </c>
     </row>
     <row r="170">
@@ -10759,10 +10759,10 @@
         <v>0.78</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6644</v>
+        <v>-0.632</v>
       </c>
       <c r="J170" t="n">
-        <v>-13.9524</v>
+        <v>-13.272</v>
       </c>
     </row>
     <row r="171">
@@ -10799,10 +10799,10 @@
         <v>0.63</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.984</v>
+        <v>-0.9829</v>
       </c>
       <c r="J171" t="n">
-        <v>-20.664</v>
+        <v>-20.6409</v>
       </c>
     </row>
     <row r="172">
@@ -10839,10 +10839,10 @@
         <v>1.34</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4641</v>
+        <v>0.4061</v>
       </c>
       <c r="J172" t="n">
-        <v>13.923</v>
+        <v>12.183</v>
       </c>
     </row>
     <row r="173">
@@ -10879,10 +10879,10 @@
         <v>1.29</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4159</v>
+        <v>0.3522</v>
       </c>
       <c r="J173" t="n">
-        <v>12.477</v>
+        <v>10.566</v>
       </c>
     </row>
     <row r="174">
@@ -10919,10 +10919,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3339</v>
+        <v>0.2756</v>
       </c>
       <c r="J174" t="n">
-        <v>10.017</v>
+        <v>8.268000000000001</v>
       </c>
     </row>
     <row r="175">
@@ -10959,10 +10959,10 @@
         <v>0.82</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2399</v>
+        <v>-0.22</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.197</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="176">
@@ -10999,10 +10999,10 @@
         <v>0.76</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2988</v>
+        <v>-0.2815</v>
       </c>
       <c r="J176" t="n">
-        <v>-8.964</v>
+        <v>-8.445</v>
       </c>
     </row>
     <row r="177">
@@ -11039,10 +11039,10 @@
         <v>1.29</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4446</v>
+        <v>0.4514</v>
       </c>
       <c r="J177" t="n">
-        <v>13.338</v>
+        <v>13.542</v>
       </c>
     </row>
     <row r="178">
@@ -11079,10 +11079,10 @@
         <v>1.07</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1465</v>
+        <v>0.1305</v>
       </c>
       <c r="J178" t="n">
-        <v>4.395</v>
+        <v>3.915</v>
       </c>
     </row>
     <row r="179">
@@ -11119,10 +11119,10 @@
         <v>1.05</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1127</v>
+        <v>0.0979</v>
       </c>
       <c r="J179" t="n">
-        <v>3.381</v>
+        <v>2.937</v>
       </c>
     </row>
     <row r="180">
@@ -11159,10 +11159,10 @@
         <v>1</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0017</v>
+        <v>-0.0009</v>
       </c>
       <c r="J180" t="n">
-        <v>-0.051</v>
+        <v>-0.027</v>
       </c>
     </row>
     <row r="181">
@@ -11199,10 +11199,10 @@
         <v>0.75</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3038</v>
+        <v>-0.2863</v>
       </c>
       <c r="J181" t="n">
-        <v>-9.114000000000001</v>
+        <v>-8.589</v>
       </c>
     </row>
     <row r="182">
@@ -11239,10 +11239,10 @@
         <v>1.17</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4697</v>
+        <v>0.4425</v>
       </c>
       <c r="J182" t="n">
-        <v>8.454599999999999</v>
+        <v>7.965</v>
       </c>
     </row>
     <row r="183">
@@ -11279,10 +11279,10 @@
         <v>0.73</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2934</v>
+        <v>-0.2783</v>
       </c>
       <c r="J183" t="n">
-        <v>-5.2812</v>
+        <v>-5.0094</v>
       </c>
     </row>
     <row r="184">
@@ -11319,10 +11319,10 @@
         <v>0.71</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.311</v>
+        <v>-0.2961</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.598</v>
+        <v>-5.3298</v>
       </c>
     </row>
     <row r="185">
@@ -11359,10 +11359,10 @@
         <v>0.57</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4362</v>
+        <v>-0.4279</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.8516</v>
+        <v>-7.7022</v>
       </c>
     </row>
     <row r="186">
@@ -11399,10 +11399,10 @@
         <v>0.47</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5239</v>
+        <v>-0.5254</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.430199999999999</v>
+        <v>-9.4572</v>
       </c>
     </row>
     <row r="187">
@@ -11439,10 +11439,10 @@
         <v>1.47</v>
       </c>
       <c r="I187" t="n">
-        <v>0.8911</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="J187" t="n">
-        <v>16.0398</v>
+        <v>15.813</v>
       </c>
     </row>
     <row r="188">
@@ -11479,10 +11479,10 @@
         <v>1.46</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8777</v>
+        <v>0.8651</v>
       </c>
       <c r="J188" t="n">
-        <v>15.7986</v>
+        <v>15.5718</v>
       </c>
     </row>
     <row r="189">
@@ -11519,10 +11519,10 @@
         <v>1.34</v>
       </c>
       <c r="I189" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.7046</v>
       </c>
       <c r="J189" t="n">
-        <v>12.8556</v>
+        <v>12.6828</v>
       </c>
     </row>
     <row r="190">
@@ -11559,10 +11559,10 @@
         <v>1.33</v>
       </c>
       <c r="I190" t="n">
-        <v>0.7002</v>
+        <v>0.6911</v>
       </c>
       <c r="J190" t="n">
-        <v>12.6036</v>
+        <v>12.4398</v>
       </c>
     </row>
     <row r="191">
@@ -11599,10 +11599,10 @@
         <v>1.13</v>
       </c>
       <c r="I191" t="n">
-        <v>0.3628</v>
+        <v>0.3308</v>
       </c>
       <c r="J191" t="n">
-        <v>6.5304</v>
+        <v>5.9544</v>
       </c>
     </row>
     <row r="192">
@@ -11639,10 +11639,10 @@
         <v>1.69</v>
       </c>
       <c r="I192" t="n">
-        <v>1.3518</v>
+        <v>1.3751</v>
       </c>
       <c r="J192" t="n">
-        <v>29.7396</v>
+        <v>30.2522</v>
       </c>
     </row>
     <row r="193">
@@ -11679,10 +11679,10 @@
         <v>1.2</v>
       </c>
       <c r="I193" t="n">
-        <v>0.543</v>
+        <v>0.51</v>
       </c>
       <c r="J193" t="n">
-        <v>11.946</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="194">
@@ -11719,10 +11719,10 @@
         <v>1.08</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2527</v>
+        <v>0.2221</v>
       </c>
       <c r="J194" t="n">
-        <v>5.5594</v>
+        <v>4.8862</v>
       </c>
     </row>
     <row r="195">
@@ -11759,10 +11759,10 @@
         <v>1.08</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2527</v>
+        <v>0.2221</v>
       </c>
       <c r="J195" t="n">
-        <v>5.5594</v>
+        <v>4.8862</v>
       </c>
     </row>
     <row r="196">
@@ -11799,10 +11799,10 @@
         <v>1.07</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2246</v>
+        <v>0.1953</v>
       </c>
       <c r="J196" t="n">
-        <v>4.9412</v>
+        <v>4.2966</v>
       </c>
     </row>
     <row r="197">
@@ -11839,10 +11839,10 @@
         <v>0.97</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.0489</v>
+        <v>-0.0393</v>
       </c>
       <c r="J197" t="n">
-        <v>-1.0758</v>
+        <v>-0.8646</v>
       </c>
     </row>
     <row r="198">
@@ -11879,10 +11879,10 @@
         <v>0.97</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.0489</v>
+        <v>-0.0393</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.0758</v>
+        <v>-0.8646</v>
       </c>
     </row>
     <row r="199">
@@ -11919,10 +11919,10 @@
         <v>0.87</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1703</v>
+        <v>-0.1518</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.7466</v>
+        <v>-3.3396</v>
       </c>
     </row>
     <row r="200">
@@ -11959,10 +11959,10 @@
         <v>0.86</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1807</v>
+        <v>-0.1619</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.9754</v>
+        <v>-3.5618</v>
       </c>
     </row>
     <row r="201">
@@ -11999,10 +11999,10 @@
         <v>0.74</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.299</v>
+        <v>-0.281</v>
       </c>
       <c r="J201" t="n">
-        <v>-6.578</v>
+        <v>-6.182</v>
       </c>
     </row>
     <row r="202">
@@ -12039,10 +12039,10 @@
         <v>1.66</v>
       </c>
       <c r="I202" t="n">
-        <v>1.3332</v>
+        <v>1.3574</v>
       </c>
       <c r="J202" t="n">
-        <v>27.9972</v>
+        <v>28.5054</v>
       </c>
     </row>
     <row r="203">
@@ -12079,10 +12079,10 @@
         <v>1.27</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7014</v>
+        <v>0.6697</v>
       </c>
       <c r="J203" t="n">
-        <v>14.7294</v>
+        <v>14.0637</v>
       </c>
     </row>
     <row r="204">
@@ -12119,10 +12119,10 @@
         <v>1.15</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4395</v>
+        <v>0.4024</v>
       </c>
       <c r="J204" t="n">
-        <v>9.2295</v>
+        <v>8.4504</v>
       </c>
     </row>
     <row r="205">
@@ -12159,10 +12159,10 @@
         <v>0.89</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3975</v>
+        <v>-0.3554</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.3475</v>
+        <v>-7.4634</v>
       </c>
     </row>
     <row r="206">
@@ -12199,10 +12199,10 @@
         <v>0.78</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6623</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.9083</v>
+        <v>-13.2195</v>
       </c>
     </row>
     <row r="207">
@@ -12239,10 +12239,10 @@
         <v>1.42</v>
       </c>
       <c r="I207" t="n">
-        <v>0.8097</v>
+        <v>0.7642</v>
       </c>
       <c r="J207" t="n">
-        <v>17.0037</v>
+        <v>16.0482</v>
       </c>
     </row>
     <row r="208">
@@ -12279,10 +12279,10 @@
         <v>0.87</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1735</v>
+        <v>-0.154</v>
       </c>
       <c r="J208" t="n">
-        <v>-3.6435</v>
+        <v>-3.234</v>
       </c>
     </row>
     <row r="209">
@@ -12319,10 +12319,10 @@
         <v>0.84</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2049</v>
+        <v>-0.1849</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.3029</v>
+        <v>-3.8829</v>
       </c>
     </row>
     <row r="210">
@@ -12359,10 +12359,10 @@
         <v>0.77</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2746</v>
+        <v>-0.2555</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.7666</v>
+        <v>-5.3655</v>
       </c>
     </row>
     <row r="211">
@@ -12399,10 +12399,10 @@
         <v>0.72</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.322</v>
+        <v>-0.3051</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.762</v>
+        <v>-6.4071</v>
       </c>
     </row>
     <row r="212">
@@ -12439,10 +12439,10 @@
         <v>1.04</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1476</v>
+        <v>0.1135</v>
       </c>
       <c r="J212" t="n">
-        <v>5.0184</v>
+        <v>3.859</v>
       </c>
     </row>
     <row r="213">
@@ -12479,10 +12479,10 @@
         <v>0.9</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1383</v>
+        <v>-0.1214</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.7022</v>
+        <v>-4.1276</v>
       </c>
     </row>
     <row r="214">
@@ -12519,10 +12519,10 @@
         <v>0.9</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1383</v>
+        <v>-0.1214</v>
       </c>
       <c r="J214" t="n">
-        <v>-4.7022</v>
+        <v>-4.1276</v>
       </c>
     </row>
     <row r="215">
@@ -12559,10 +12559,10 @@
         <v>0.87</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1703</v>
+        <v>-0.1518</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.7902</v>
+        <v>-5.1612</v>
       </c>
     </row>
     <row r="216">
@@ -12599,10 +12599,10 @@
         <v>0.7</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3364</v>
+        <v>-0.3203</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.4376</v>
+        <v>-10.8902</v>
       </c>
     </row>
     <row r="217">
@@ -12639,10 +12639,10 @@
         <v>1.44</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0269</v>
+        <v>1.0285</v>
       </c>
       <c r="J217" t="n">
-        <v>34.9146</v>
+        <v>34.969</v>
       </c>
     </row>
     <row r="218">
@@ -12679,10 +12679,10 @@
         <v>1.32</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8025</v>
+        <v>0.777</v>
       </c>
       <c r="J218" t="n">
-        <v>27.285</v>
+        <v>26.418</v>
       </c>
     </row>
     <row r="219">
@@ -12719,10 +12719,10 @@
         <v>1.3</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7617</v>
+        <v>0.7336</v>
       </c>
       <c r="J219" t="n">
-        <v>25.8978</v>
+        <v>24.9424</v>
       </c>
     </row>
     <row r="220">
@@ -12759,10 +12759,10 @@
         <v>0.89</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.399</v>
+        <v>-0.357</v>
       </c>
       <c r="J220" t="n">
-        <v>-13.566</v>
+        <v>-12.138</v>
       </c>
     </row>
     <row r="221">
@@ -12799,10 +12799,10 @@
         <v>0.84</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5241</v>
+        <v>-0.4844</v>
       </c>
       <c r="J221" t="n">
-        <v>-17.8194</v>
+        <v>-16.4696</v>
       </c>
     </row>
     <row r="222">
@@ -12839,10 +12839,10 @@
         <v>1.44</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0473</v>
+        <v>1.0534</v>
       </c>
       <c r="J222" t="n">
-        <v>31.419</v>
+        <v>31.602</v>
       </c>
     </row>
     <row r="223">
@@ -12879,10 +12879,10 @@
         <v>1.09</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3003</v>
+        <v>0.2634</v>
       </c>
       <c r="J223" t="n">
-        <v>9.009</v>
+        <v>7.902</v>
       </c>
     </row>
     <row r="224">
@@ -12919,10 +12919,10 @@
         <v>0.97</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.15</v>
+        <v>-0.1191</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.5</v>
+        <v>-3.573</v>
       </c>
     </row>
     <row r="225">
@@ -12959,10 +12959,10 @@
         <v>0.96</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1837</v>
+        <v>-0.1495</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.511</v>
+        <v>-4.485</v>
       </c>
     </row>
     <row r="226">
@@ -12999,10 +12999,10 @@
         <v>0.95</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2156</v>
+        <v>-0.1788</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.468</v>
+        <v>-5.364</v>
       </c>
     </row>
     <row r="227">
@@ -13039,10 +13039,10 @@
         <v>1.14</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3234</v>
+        <v>0.2714</v>
       </c>
       <c r="J227" t="n">
-        <v>9.702</v>
+        <v>8.141999999999999</v>
       </c>
     </row>
     <row r="228">
@@ -13079,10 +13079,10 @@
         <v>1.04</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1217</v>
+        <v>0.0925</v>
       </c>
       <c r="J228" t="n">
-        <v>3.651</v>
+        <v>2.775</v>
       </c>
     </row>
     <row r="229">
@@ -13119,10 +13119,10 @@
         <v>1.02</v>
       </c>
       <c r="I229" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0516</v>
       </c>
       <c r="J229" t="n">
-        <v>2.142</v>
+        <v>1.548</v>
       </c>
     </row>
     <row r="230">
@@ -13159,10 +13159,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0516</v>
       </c>
       <c r="J230" t="n">
-        <v>2.142</v>
+        <v>1.548</v>
       </c>
     </row>
     <row r="231">
@@ -13199,10 +13199,10 @@
         <v>0.9</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.149</v>
+        <v>-0.1292</v>
       </c>
       <c r="J231" t="n">
-        <v>-4.47</v>
+        <v>-3.876</v>
       </c>
     </row>
     <row r="232">
@@ -13239,10 +13239,10 @@
         <v>2.47</v>
       </c>
       <c r="I232" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J232" t="n">
-        <v>29.058</v>
+        <v>29.727</v>
       </c>
     </row>
     <row r="233">
@@ -13279,10 +13279,10 @@
         <v>1.73</v>
       </c>
       <c r="I233" t="n">
-        <v>1.3401</v>
+        <v>1.3647</v>
       </c>
       <c r="J233" t="n">
-        <v>20.1015</v>
+        <v>20.4705</v>
       </c>
     </row>
     <row r="234">
@@ -13319,10 +13319,10 @@
         <v>1.62</v>
       </c>
       <c r="I234" t="n">
-        <v>1.2069</v>
+        <v>1.2279</v>
       </c>
       <c r="J234" t="n">
-        <v>18.1035</v>
+        <v>18.4185</v>
       </c>
     </row>
     <row r="235">
@@ -13359,10 +13359,10 @@
         <v>1.04</v>
       </c>
       <c r="I235" t="n">
-        <v>0.0828</v>
+        <v>0.0533</v>
       </c>
       <c r="J235" t="n">
-        <v>1.242</v>
+        <v>0.7995</v>
       </c>
     </row>
     <row r="236">
@@ -13399,10 +13399,10 @@
         <v>0.95</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.291</v>
+        <v>-0.2642</v>
       </c>
       <c r="J236" t="n">
-        <v>-4.365</v>
+        <v>-3.963</v>
       </c>
     </row>
     <row r="237">
@@ -13439,10 +13439,10 @@
         <v>1.01</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1557</v>
+        <v>0.1502</v>
       </c>
       <c r="J237" t="n">
-        <v>2.3355</v>
+        <v>2.253</v>
       </c>
     </row>
     <row r="238">
@@ -13479,10 +13479,10 @@
         <v>0.67</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3391</v>
+        <v>-0.3278</v>
       </c>
       <c r="J238" t="n">
-        <v>-5.0865</v>
+        <v>-4.917</v>
       </c>
     </row>
     <row r="239">
@@ -13519,10 +13519,10 @@
         <v>0.55</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4431</v>
+        <v>-0.4359</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.6465</v>
+        <v>-6.5385</v>
       </c>
     </row>
     <row r="240">
@@ -13559,10 +13559,10 @@
         <v>0.51</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4783</v>
+        <v>-0.4741</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.1745</v>
+        <v>-7.1115</v>
       </c>
     </row>
     <row r="241">
@@ -13599,10 +13599,10 @@
         <v>0.5</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4871</v>
+        <v>-0.4838</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.3065</v>
+        <v>-7.257</v>
       </c>
     </row>
     <row r="242">
@@ -13639,10 +13639,10 @@
         <v>0.95</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.056</v>
+        <v>-0.0432</v>
       </c>
       <c r="J242" t="n">
-        <v>-1.008</v>
+        <v>-0.7776</v>
       </c>
     </row>
     <row r="243">
@@ -13679,10 +13679,10 @@
         <v>0.9</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1205</v>
+        <v>-0.1054</v>
       </c>
       <c r="J243" t="n">
-        <v>-2.169</v>
+        <v>-1.8972</v>
       </c>
     </row>
     <row r="244">
@@ -13719,10 +13719,10 @@
         <v>0.74</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2855</v>
+        <v>-0.2698</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.139</v>
+        <v>-4.8564</v>
       </c>
     </row>
     <row r="245">
@@ -13759,10 +13759,10 @@
         <v>0.63</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3848</v>
+        <v>-0.3724</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.9264</v>
+        <v>-6.7032</v>
       </c>
     </row>
     <row r="246">
@@ -13799,10 +13799,10 @@
         <v>0.51</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4909</v>
+        <v>-0.4884</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.8362</v>
+        <v>-8.7912</v>
       </c>
     </row>
     <row r="247">
@@ -13839,10 +13839,10 @@
         <v>1.8</v>
       </c>
       <c r="I247" t="n">
-        <v>1.4468</v>
+        <v>1.4746</v>
       </c>
       <c r="J247" t="n">
-        <v>26.0424</v>
+        <v>26.5428</v>
       </c>
     </row>
     <row r="248">
@@ -13879,10 +13879,10 @@
         <v>1.54</v>
       </c>
       <c r="I248" t="n">
-        <v>1.1214</v>
+        <v>1.1367</v>
       </c>
       <c r="J248" t="n">
-        <v>20.1852</v>
+        <v>20.4606</v>
       </c>
     </row>
     <row r="249">
@@ -13919,10 +13919,10 @@
         <v>1.32</v>
       </c>
       <c r="I249" t="n">
-        <v>0.7644</v>
+        <v>0.7482</v>
       </c>
       <c r="J249" t="n">
-        <v>13.7592</v>
+        <v>13.4676</v>
       </c>
     </row>
     <row r="250">
@@ -13959,10 +13959,10 @@
         <v>1.28</v>
       </c>
       <c r="I250" t="n">
-        <v>0.6846</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="J250" t="n">
-        <v>12.3228</v>
+        <v>11.9484</v>
       </c>
     </row>
     <row r="251">
@@ -13999,10 +13999,10 @@
         <v>1.15</v>
       </c>
       <c r="I251" t="n">
-        <v>0.4002</v>
+        <v>0.3685</v>
       </c>
       <c r="J251" t="n">
-        <v>7.2036</v>
+        <v>6.633</v>
       </c>
     </row>
     <row r="252">
@@ -14039,10 +14039,10 @@
         <v>1.96</v>
       </c>
       <c r="I252" t="n">
-        <v>1.3554</v>
+        <v>1.3533</v>
       </c>
       <c r="J252" t="n">
-        <v>28.4634</v>
+        <v>28.4193</v>
       </c>
     </row>
     <row r="253">
@@ -14079,10 +14079,10 @@
         <v>1.04</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1149</v>
+        <v>0.0888</v>
       </c>
       <c r="J253" t="n">
-        <v>2.4129</v>
+        <v>1.8648</v>
       </c>
     </row>
     <row r="254">
@@ -14119,10 +14119,10 @@
         <v>1.01</v>
       </c>
       <c r="I254" t="n">
-        <v>0.033</v>
+        <v>0.023</v>
       </c>
       <c r="J254" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="255">
@@ -14159,10 +14159,10 @@
         <v>0.95</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0769</v>
       </c>
       <c r="J255" t="n">
-        <v>-1.9698</v>
+        <v>-1.6149</v>
       </c>
     </row>
     <row r="256">
@@ -14199,10 +14199,10 @@
         <v>0.52</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.5173</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.7646</v>
+        <v>-10.8633</v>
       </c>
     </row>
     <row r="257">
@@ -14239,10 +14239,10 @@
         <v>1.42</v>
       </c>
       <c r="I257" t="n">
-        <v>0.9928</v>
+        <v>0.9882</v>
       </c>
       <c r="J257" t="n">
-        <v>20.8488</v>
+        <v>20.7522</v>
       </c>
     </row>
     <row r="258">
@@ -14279,10 +14279,10 @@
         <v>1.34</v>
       </c>
       <c r="I258" t="n">
-        <v>0.8413</v>
+        <v>0.8187</v>
       </c>
       <c r="J258" t="n">
-        <v>17.6673</v>
+        <v>17.1927</v>
       </c>
     </row>
     <row r="259">
@@ -14319,10 +14319,10 @@
         <v>1.16</v>
       </c>
       <c r="I259" t="n">
-        <v>0.461</v>
+        <v>0.4245</v>
       </c>
       <c r="J259" t="n">
-        <v>9.680999999999999</v>
+        <v>8.9145</v>
       </c>
     </row>
     <row r="260">
@@ -14359,10 +14359,10 @@
         <v>1.06</v>
       </c>
       <c r="I260" t="n">
-        <v>0.2058</v>
+        <v>0.177</v>
       </c>
       <c r="J260" t="n">
-        <v>4.3218</v>
+        <v>3.717</v>
       </c>
     </row>
     <row r="261">
@@ -14399,10 +14399,10 @@
         <v>0.84</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5252</v>
+        <v>-0.4857</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.0292</v>
+        <v>-10.1997</v>
       </c>
     </row>
     <row r="262">
@@ -14439,10 +14439,10 @@
         <v>1.45</v>
       </c>
       <c r="I262" t="n">
-        <v>1.0358</v>
+        <v>1.0389</v>
       </c>
       <c r="J262" t="n">
-        <v>22.7876</v>
+        <v>22.8558</v>
       </c>
     </row>
     <row r="263">
@@ -14479,10 +14479,10 @@
         <v>1.3</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7557</v>
+        <v>0.7282</v>
       </c>
       <c r="J263" t="n">
-        <v>16.6254</v>
+        <v>16.0204</v>
       </c>
     </row>
     <row r="264">
@@ -14519,10 +14519,10 @@
         <v>1.18</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5034</v>
+        <v>0.4681</v>
       </c>
       <c r="J264" t="n">
-        <v>11.0748</v>
+        <v>10.2982</v>
       </c>
     </row>
     <row r="265">
@@ -14559,10 +14559,10 @@
         <v>1.06</v>
       </c>
       <c r="I265" t="n">
-        <v>0.2021</v>
+        <v>0.1737</v>
       </c>
       <c r="J265" t="n">
-        <v>4.4462</v>
+        <v>3.8214</v>
       </c>
     </row>
     <row r="266">
@@ -14599,10 +14599,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2653</v>
+        <v>-0.2269</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.8366</v>
+        <v>-4.9918</v>
       </c>
     </row>
     <row r="267">
@@ -14639,10 +14639,10 @@
         <v>1.83</v>
       </c>
       <c r="I267" t="n">
-        <v>1.2899</v>
+        <v>1.2994</v>
       </c>
       <c r="J267" t="n">
-        <v>28.3778</v>
+        <v>28.5868</v>
       </c>
     </row>
     <row r="268">
@@ -14679,10 +14679,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5679</v>
+        <v>0.5107</v>
       </c>
       <c r="J268" t="n">
-        <v>12.4938</v>
+        <v>11.2354</v>
       </c>
     </row>
     <row r="269">
@@ -14719,10 +14719,10 @@
         <v>0.63</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.4054</v>
+        <v>-0.395</v>
       </c>
       <c r="J269" t="n">
-        <v>-8.918799999999999</v>
+        <v>-8.69</v>
       </c>
     </row>
     <row r="270">
@@ -14759,10 +14759,10 @@
         <v>0.63</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4054</v>
+        <v>-0.395</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.918799999999999</v>
+        <v>-8.69</v>
       </c>
     </row>
     <row r="271">
@@ -14799,10 +14799,10 @@
         <v>0.33</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6592</v>
+        <v>-0.6865</v>
       </c>
       <c r="J271" t="n">
-        <v>-14.5024</v>
+        <v>-15.103</v>
       </c>
     </row>
     <row r="272">
@@ -14839,10 +14839,10 @@
         <v>2.14</v>
       </c>
       <c r="I272" t="n">
-        <v>1.8458</v>
+        <v>1.9103</v>
       </c>
       <c r="J272" t="n">
-        <v>31.3786</v>
+        <v>32.4751</v>
       </c>
     </row>
     <row r="273">
@@ -14879,10 +14879,10 @@
         <v>1.5</v>
       </c>
       <c r="I273" t="n">
-        <v>1.068</v>
+        <v>1.0811</v>
       </c>
       <c r="J273" t="n">
-        <v>18.156</v>
+        <v>18.3787</v>
       </c>
     </row>
     <row r="274">
@@ -14919,10 +14919,10 @@
         <v>1.23</v>
       </c>
       <c r="I274" t="n">
-        <v>0.5785</v>
+        <v>0.5527</v>
       </c>
       <c r="J274" t="n">
-        <v>9.8345</v>
+        <v>9.395899999999999</v>
       </c>
     </row>
     <row r="275">
@@ -14959,10 +14959,10 @@
         <v>1.19</v>
       </c>
       <c r="I275" t="n">
-        <v>0.4908</v>
+        <v>0.4615</v>
       </c>
       <c r="J275" t="n">
-        <v>8.3436</v>
+        <v>7.8455</v>
       </c>
     </row>
     <row r="276">
@@ -14999,10 +14999,10 @@
         <v>1.09</v>
       </c>
       <c r="I276" t="n">
-        <v>0.2472</v>
+        <v>0.215</v>
       </c>
       <c r="J276" t="n">
-        <v>4.2024</v>
+        <v>3.655</v>
       </c>
     </row>
     <row r="277">
@@ -15039,10 +15039,10 @@
         <v>1.1</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3502</v>
+        <v>0.3152</v>
       </c>
       <c r="J277" t="n">
-        <v>5.9534</v>
+        <v>5.3584</v>
       </c>
     </row>
     <row r="278">
@@ -15079,10 +15079,10 @@
         <v>0.91</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.1009</v>
+        <v>-0.0852</v>
       </c>
       <c r="J278" t="n">
-        <v>-1.7153</v>
+        <v>-1.4484</v>
       </c>
     </row>
     <row r="279">
@@ -15119,10 +15119,10 @@
         <v>0.64</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3715</v>
+        <v>-0.3589</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.3155</v>
+        <v>-6.1013</v>
       </c>
     </row>
     <row r="280">
@@ -15159,10 +15159,10 @@
         <v>0.49</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.504</v>
+        <v>-0.5028</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.568</v>
+        <v>-8.547599999999999</v>
       </c>
     </row>
     <row r="281">
@@ -15199,10 +15199,10 @@
         <v>0.41</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5735</v>
+        <v>-0.5821</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.749499999999999</v>
+        <v>-9.8957</v>
       </c>
     </row>
     <row r="282">
@@ -15239,10 +15239,10 @@
         <v>2.16</v>
       </c>
       <c r="I282" t="n">
-        <v>1.8657</v>
+        <v>1.9322</v>
       </c>
       <c r="J282" t="n">
-        <v>31.7169</v>
+        <v>32.8474</v>
       </c>
     </row>
     <row r="283">
@@ -15279,10 +15279,10 @@
         <v>1.76</v>
       </c>
       <c r="I283" t="n">
-        <v>1.3937</v>
+        <v>1.4185</v>
       </c>
       <c r="J283" t="n">
-        <v>23.6929</v>
+        <v>24.1145</v>
       </c>
     </row>
     <row r="284">
@@ -15319,10 +15319,10 @@
         <v>1.21</v>
       </c>
       <c r="I284" t="n">
-        <v>0.5334</v>
+        <v>0.5057</v>
       </c>
       <c r="J284" t="n">
-        <v>9.0678</v>
+        <v>8.5969</v>
       </c>
     </row>
     <row r="285">
@@ -15359,10 +15359,10 @@
         <v>1.18</v>
       </c>
       <c r="I285" t="n">
-        <v>0.4664</v>
+        <v>0.4363</v>
       </c>
       <c r="J285" t="n">
-        <v>7.9288</v>
+        <v>7.4171</v>
       </c>
     </row>
     <row r="286">
@@ -15399,10 +15399,10 @@
         <v>0.9</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4175</v>
+        <v>-0.3838</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.0975</v>
+        <v>-6.5246</v>
       </c>
     </row>
     <row r="287">
@@ -15439,10 +15439,10 @@
         <v>1.04</v>
       </c>
       <c r="I287" t="n">
-        <v>0.1642</v>
+        <v>0.1303</v>
       </c>
       <c r="J287" t="n">
-        <v>2.7914</v>
+        <v>2.2151</v>
       </c>
     </row>
     <row r="288">
@@ -15479,10 +15479,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0833</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.4161</v>
+        <v>-1.1985</v>
       </c>
     </row>
     <row r="289">
@@ -15519,10 +15519,10 @@
         <v>0.82</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2167</v>
+        <v>-0.1987</v>
       </c>
       <c r="J289" t="n">
-        <v>-3.6839</v>
+        <v>-3.3779</v>
       </c>
     </row>
     <row r="290">
@@ -15559,10 +15559,10 @@
         <v>0.74</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.293</v>
+        <v>-0.2753</v>
       </c>
       <c r="J290" t="n">
-        <v>-4.981</v>
+        <v>-4.6801</v>
       </c>
     </row>
     <row r="291">
@@ -15599,10 +15599,10 @@
         <v>0.58</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4383</v>
+        <v>-0.4304</v>
       </c>
       <c r="J291" t="n">
-        <v>-7.4511</v>
+        <v>-7.3168</v>
       </c>
     </row>
     <row r="292">
@@ -15639,10 +15639,10 @@
         <v>1.93</v>
       </c>
       <c r="I292" t="n">
-        <v>1.5852</v>
+        <v>1.6231</v>
       </c>
       <c r="J292" t="n">
-        <v>25.3632</v>
+        <v>25.9696</v>
       </c>
     </row>
     <row r="293">
@@ -15679,10 +15679,10 @@
         <v>1.62</v>
       </c>
       <c r="I293" t="n">
-        <v>1.2122</v>
+        <v>1.2315</v>
       </c>
       <c r="J293" t="n">
-        <v>19.3952</v>
+        <v>19.704</v>
       </c>
     </row>
     <row r="294">
@@ -15719,10 +15719,10 @@
         <v>1.47</v>
       </c>
       <c r="I294" t="n">
-        <v>1.0209</v>
+        <v>1.032</v>
       </c>
       <c r="J294" t="n">
-        <v>16.3344</v>
+        <v>16.512</v>
       </c>
     </row>
     <row r="295">
@@ -15759,10 +15759,10 @@
         <v>1.37</v>
       </c>
       <c r="I295" t="n">
-        <v>0.8489</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="J295" t="n">
-        <v>13.5824</v>
+        <v>13.4592</v>
       </c>
     </row>
     <row r="296">
@@ -15799,10 +15799,10 @@
         <v>1.15</v>
       </c>
       <c r="I296" t="n">
-        <v>0.3871</v>
+        <v>0.3544</v>
       </c>
       <c r="J296" t="n">
-        <v>6.1936</v>
+        <v>5.6704</v>
       </c>
     </row>
     <row r="297">
@@ -15839,10 +15839,10 @@
         <v>0.91</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.1153</v>
+        <v>-0.1007</v>
       </c>
       <c r="J297" t="n">
-        <v>-1.8448</v>
+        <v>-1.6112</v>
       </c>
     </row>
     <row r="298">
@@ -15879,10 +15879,10 @@
         <v>0.88</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1502</v>
+        <v>-0.1346</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.4032</v>
+        <v>-2.1536</v>
       </c>
     </row>
     <row r="299">
@@ -15919,10 +15919,10 @@
         <v>0.87</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1614</v>
+        <v>-0.1455</v>
       </c>
       <c r="J299" t="n">
-        <v>-2.5824</v>
+        <v>-2.328</v>
       </c>
     </row>
     <row r="300">
@@ -15959,10 +15959,10 @@
         <v>0.67</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3534</v>
+        <v>-0.3387</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.6544</v>
+        <v>-5.4192</v>
       </c>
     </row>
     <row r="301">
@@ -15999,10 +15999,10 @@
         <v>0.6</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4163</v>
+        <v>-0.4062</v>
       </c>
       <c r="J301" t="n">
-        <v>-6.6608</v>
+        <v>-6.4992</v>
       </c>
     </row>
     <row r="302">
@@ -16039,10 +16039,10 @@
         <v>1.99</v>
       </c>
       <c r="I302" t="n">
-        <v>1.7821</v>
+        <v>1.8616</v>
       </c>
       <c r="J302" t="n">
-        <v>42.7704</v>
+        <v>44.6784</v>
       </c>
     </row>
     <row r="303">
@@ -16079,10 +16079,10 @@
         <v>1.43</v>
       </c>
       <c r="I303" t="n">
-        <v>1.0281</v>
+        <v>1.0306</v>
       </c>
       <c r="J303" t="n">
-        <v>24.6744</v>
+        <v>24.7344</v>
       </c>
     </row>
     <row r="304">
@@ -16119,10 +16119,10 @@
         <v>0.95</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2178</v>
+        <v>-0.1809</v>
       </c>
       <c r="J304" t="n">
-        <v>-5.2272</v>
+        <v>-4.3416</v>
       </c>
     </row>
     <row r="305">
@@ -16159,10 +16159,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I305" t="n">
-        <v>-1.114</v>
+        <v>-1.1283</v>
       </c>
       <c r="J305" t="n">
-        <v>-26.736</v>
+        <v>-27.0792</v>
       </c>
     </row>
     <row r="306">
@@ -16199,10 +16199,10 @@
         <v>0.54</v>
       </c>
       <c r="I306" t="n">
-        <v>-1.1534</v>
+        <v>-1.1737</v>
       </c>
       <c r="J306" t="n">
-        <v>-27.6816</v>
+        <v>-28.1688</v>
       </c>
     </row>
     <row r="307">
@@ -16239,10 +16239,10 @@
         <v>1.48</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8495</v>
+        <v>0.7983</v>
       </c>
       <c r="J307" t="n">
-        <v>20.388</v>
+        <v>19.1592</v>
       </c>
     </row>
     <row r="308">
@@ -16279,10 +16279,10 @@
         <v>1.19</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4042</v>
+        <v>0.3482</v>
       </c>
       <c r="J308" t="n">
-        <v>9.700799999999999</v>
+        <v>8.3568</v>
       </c>
     </row>
     <row r="309">
@@ -16319,10 +16319,10 @@
         <v>0.99</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0293</v>
+        <v>-0.0209</v>
       </c>
       <c r="J309" t="n">
-        <v>-0.7032</v>
+        <v>-0.5016</v>
       </c>
     </row>
     <row r="310">
@@ -16359,10 +16359,10 @@
         <v>0.93</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1165</v>
+        <v>-0.098</v>
       </c>
       <c r="J310" t="n">
-        <v>-2.796</v>
+        <v>-2.352</v>
       </c>
     </row>
     <row r="311">
@@ -16399,10 +16399,10 @@
         <v>0.71</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3436</v>
+        <v>-0.329</v>
       </c>
       <c r="J311" t="n">
-        <v>-8.2464</v>
+        <v>-7.896</v>
       </c>
     </row>
     <row r="312">
@@ -16439,10 +16439,10 @@
         <v>1.8</v>
       </c>
       <c r="I312" t="n">
-        <v>1.4449</v>
+        <v>1.4726</v>
       </c>
       <c r="J312" t="n">
-        <v>26.0082</v>
+        <v>26.5068</v>
       </c>
     </row>
     <row r="313">
@@ -16479,10 +16479,10 @@
         <v>1.42</v>
       </c>
       <c r="I313" t="n">
-        <v>0.9489</v>
+        <v>0.9469</v>
       </c>
       <c r="J313" t="n">
-        <v>17.0802</v>
+        <v>17.0442</v>
       </c>
     </row>
     <row r="314">
@@ -16519,10 +16519,10 @@
         <v>1.4</v>
       </c>
       <c r="I314" t="n">
-        <v>0.9142</v>
+        <v>0.9085</v>
       </c>
       <c r="J314" t="n">
-        <v>16.4556</v>
+        <v>16.353</v>
       </c>
     </row>
     <row r="315">
@@ -16559,10 +16559,10 @@
         <v>1.26</v>
       </c>
       <c r="I315" t="n">
-        <v>0.6421</v>
+        <v>0.6192</v>
       </c>
       <c r="J315" t="n">
-        <v>11.5578</v>
+        <v>11.1456</v>
       </c>
     </row>
     <row r="316">
@@ -16599,10 +16599,10 @@
         <v>1.26</v>
       </c>
       <c r="I316" t="n">
-        <v>0.6421</v>
+        <v>0.6192</v>
       </c>
       <c r="J316" t="n">
-        <v>11.5578</v>
+        <v>11.1456</v>
       </c>
     </row>
     <row r="317">
@@ -16639,10 +16639,10 @@
         <v>1.46</v>
       </c>
       <c r="I317" t="n">
-        <v>0.8969</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="J317" t="n">
-        <v>16.1442</v>
+        <v>15.5772</v>
       </c>
     </row>
     <row r="318">
@@ -16679,10 +16679,10 @@
         <v>0.88</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1591</v>
+        <v>-0.1415</v>
       </c>
       <c r="J318" t="n">
-        <v>-2.8638</v>
+        <v>-2.547</v>
       </c>
     </row>
     <row r="319">
@@ -16719,10 +16719,10 @@
         <v>0.85</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1899</v>
+        <v>-0.1712</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.4182</v>
+        <v>-3.0816</v>
       </c>
     </row>
     <row r="320">
@@ -16759,10 +16759,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3441</v>
+        <v>-0.3285</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.1938</v>
+        <v>-5.913</v>
       </c>
     </row>
     <row r="321">
@@ -16799,10 +16799,10 @@
         <v>0.46</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5463</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.833399999999999</v>
+        <v>-9.952199999999999</v>
       </c>
     </row>
     <row r="322">
@@ -16839,10 +16839,10 @@
         <v>1.51</v>
       </c>
       <c r="I322" t="n">
-        <v>1.1307</v>
+        <v>1.1437</v>
       </c>
       <c r="J322" t="n">
-        <v>27.1368</v>
+        <v>27.4488</v>
       </c>
     </row>
     <row r="323">
@@ -16879,10 +16879,10 @@
         <v>1.43</v>
       </c>
       <c r="I323" t="n">
-        <v>1.0139</v>
+        <v>1.0132</v>
       </c>
       <c r="J323" t="n">
-        <v>24.3336</v>
+        <v>24.3168</v>
       </c>
     </row>
     <row r="324">
@@ -16919,10 +16919,10 @@
         <v>1.05</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1787</v>
+        <v>0.1516</v>
       </c>
       <c r="J324" t="n">
-        <v>4.2888</v>
+        <v>3.6384</v>
       </c>
     </row>
     <row r="325">
@@ -16959,10 +16959,10 @@
         <v>0.91</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3434</v>
+        <v>-0.3017</v>
       </c>
       <c r="J325" t="n">
-        <v>-8.2416</v>
+        <v>-7.2408</v>
       </c>
     </row>
     <row r="326">
@@ -16999,10 +16999,10 @@
         <v>0.83</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5458</v>
+        <v>-0.5068</v>
       </c>
       <c r="J326" t="n">
-        <v>-13.0992</v>
+        <v>-12.1632</v>
       </c>
     </row>
     <row r="327">
@@ -17039,10 +17039,10 @@
         <v>1.11</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2933</v>
+        <v>0.2438</v>
       </c>
       <c r="J327" t="n">
-        <v>7.0392</v>
+        <v>5.8512</v>
       </c>
     </row>
     <row r="328">
@@ -17079,10 +17079,10 @@
         <v>1.11</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2933</v>
+        <v>0.2438</v>
       </c>
       <c r="J328" t="n">
-        <v>7.0392</v>
+        <v>5.8512</v>
       </c>
     </row>
     <row r="329">
@@ -17119,10 +17119,10 @@
         <v>1.01</v>
       </c>
       <c r="I329" t="n">
-        <v>0.0581</v>
+        <v>0.0399</v>
       </c>
       <c r="J329" t="n">
-        <v>1.3944</v>
+        <v>0.9576</v>
       </c>
     </row>
     <row r="330">
@@ -17159,10 +17159,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2336</v>
+        <v>-0.2138</v>
       </c>
       <c r="J330" t="n">
-        <v>-5.6064</v>
+        <v>-5.1312</v>
       </c>
     </row>
     <row r="331">
@@ -17199,10 +17199,10 @@
         <v>0.49</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5241</v>
+        <v>-0.5279</v>
       </c>
       <c r="J331" t="n">
-        <v>-12.5784</v>
+        <v>-12.6696</v>
       </c>
     </row>
     <row r="332">
@@ -17239,10 +17239,10 @@
         <v>1.69</v>
       </c>
       <c r="I332" t="n">
-        <v>1.3131</v>
+        <v>1.3335</v>
       </c>
       <c r="J332" t="n">
-        <v>23.6358</v>
+        <v>24.003</v>
       </c>
     </row>
     <row r="333">
@@ -17279,10 +17279,10 @@
         <v>1.54</v>
       </c>
       <c r="I333" t="n">
-        <v>1.1226</v>
+        <v>1.1377</v>
       </c>
       <c r="J333" t="n">
-        <v>20.2068</v>
+        <v>20.4786</v>
       </c>
     </row>
     <row r="334">
@@ -17319,10 +17319,10 @@
         <v>1.48</v>
       </c>
       <c r="I334" t="n">
-        <v>1.043</v>
+        <v>1.0526</v>
       </c>
       <c r="J334" t="n">
-        <v>18.774</v>
+        <v>18.9468</v>
       </c>
     </row>
     <row r="335">
@@ -17359,10 +17359,10 @@
         <v>1.27</v>
       </c>
       <c r="I335" t="n">
-        <v>0.6656</v>
+        <v>0.6435</v>
       </c>
       <c r="J335" t="n">
-        <v>11.9808</v>
+        <v>11.583</v>
       </c>
     </row>
     <row r="336">
@@ -17399,10 +17399,10 @@
         <v>1.06</v>
       </c>
       <c r="I336" t="n">
-        <v>0.1661</v>
+        <v>0.1368</v>
       </c>
       <c r="J336" t="n">
-        <v>2.9898</v>
+        <v>2.4624</v>
       </c>
     </row>
     <row r="337">
@@ -17439,10 +17439,10 @@
         <v>1.1</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3049</v>
+        <v>0.2596</v>
       </c>
       <c r="J337" t="n">
-        <v>5.4882</v>
+        <v>4.6728</v>
       </c>
     </row>
     <row r="338">
@@ -17479,10 +17479,10 @@
         <v>0.9</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1304</v>
+        <v>-0.1152</v>
       </c>
       <c r="J338" t="n">
-        <v>-2.3472</v>
+        <v>-2.0736</v>
       </c>
     </row>
     <row r="339">
@@ -17519,10 +17519,10 @@
         <v>0.68</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.3468</v>
+        <v>-0.3316</v>
       </c>
       <c r="J339" t="n">
-        <v>-6.2424</v>
+        <v>-5.9688</v>
       </c>
     </row>
     <row r="340">
@@ -17559,10 +17559,10 @@
         <v>0.68</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3468</v>
+        <v>-0.3316</v>
       </c>
       <c r="J340" t="n">
-        <v>-6.2424</v>
+        <v>-5.9688</v>
       </c>
     </row>
     <row r="341">
@@ -17599,10 +17599,10 @@
         <v>0.68</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3468</v>
+        <v>-0.3316</v>
       </c>
       <c r="J341" t="n">
-        <v>-6.2424</v>
+        <v>-5.9688</v>
       </c>
     </row>
     <row r="342">
@@ -17639,10 +17639,10 @@
         <v>1.38</v>
       </c>
       <c r="I342" t="n">
-        <v>0.5563</v>
+        <v>0.5742</v>
       </c>
       <c r="J342" t="n">
-        <v>13.3512</v>
+        <v>13.7808</v>
       </c>
     </row>
     <row r="343">
@@ -17679,10 +17679,10 @@
         <v>1.06</v>
       </c>
       <c r="I343" t="n">
-        <v>0.1295</v>
+        <v>0.1142</v>
       </c>
       <c r="J343" t="n">
-        <v>3.108</v>
+        <v>2.7408</v>
       </c>
     </row>
     <row r="344">
@@ -17719,10 +17719,10 @@
         <v>1.01</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0316</v>
+        <v>0.0246</v>
       </c>
       <c r="J344" t="n">
-        <v>0.7584</v>
+        <v>0.5904</v>
       </c>
     </row>
     <row r="345">
@@ -17759,10 +17759,10 @@
         <v>0.89</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1614</v>
+        <v>-0.1411</v>
       </c>
       <c r="J345" t="n">
-        <v>-3.8736</v>
+        <v>-3.3864</v>
       </c>
     </row>
     <row r="346">
@@ -17799,10 +17799,10 @@
         <v>0.84</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2151</v>
+        <v>-0.1945</v>
       </c>
       <c r="J346" t="n">
-        <v>-5.1624</v>
+        <v>-4.668</v>
       </c>
     </row>
     <row r="347">
@@ -17839,10 +17839,10 @@
         <v>1.78</v>
       </c>
       <c r="I347" t="n">
-        <v>0.9304</v>
+        <v>0.8717</v>
       </c>
       <c r="J347" t="n">
-        <v>22.3296</v>
+        <v>20.9208</v>
       </c>
     </row>
     <row r="348">
@@ -17879,10 +17879,10 @@
         <v>1.17</v>
       </c>
       <c r="I348" t="n">
-        <v>0.2725</v>
+        <v>0.2202</v>
       </c>
       <c r="J348" t="n">
-        <v>6.54</v>
+        <v>5.2848</v>
       </c>
     </row>
     <row r="349">
@@ -17919,10 +17919,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.1055</v>
+        <v>-0.0878</v>
       </c>
       <c r="J349" t="n">
-        <v>-2.532</v>
+        <v>-2.1072</v>
       </c>
     </row>
     <row r="350">
@@ -17959,10 +17959,10 @@
         <v>0.82</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2394</v>
+        <v>-0.2195</v>
       </c>
       <c r="J350" t="n">
-        <v>-5.7456</v>
+        <v>-5.268</v>
       </c>
     </row>
     <row r="351">
@@ -17999,10 +17999,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3635</v>
+        <v>-0.3508</v>
       </c>
       <c r="J351" t="n">
-        <v>-8.724</v>
+        <v>-8.4192</v>
       </c>
     </row>
     <row r="352">
@@ -18039,10 +18039,10 @@
         <v>1.78</v>
       </c>
       <c r="I352" t="n">
-        <v>1.4596</v>
+        <v>1.4903</v>
       </c>
       <c r="J352" t="n">
-        <v>29.192</v>
+        <v>29.806</v>
       </c>
     </row>
     <row r="353">
@@ -18079,10 +18079,10 @@
         <v>1.46</v>
       </c>
       <c r="I353" t="n">
-        <v>1.0373</v>
+        <v>1.0413</v>
       </c>
       <c r="J353" t="n">
-        <v>20.746</v>
+        <v>20.826</v>
       </c>
     </row>
     <row r="354">
@@ -18119,10 +18119,10 @@
         <v>1.2</v>
       </c>
       <c r="I354" t="n">
-        <v>0.5394</v>
+        <v>0.5077</v>
       </c>
       <c r="J354" t="n">
-        <v>10.788</v>
+        <v>10.154</v>
       </c>
     </row>
     <row r="355">
@@ -18159,10 +18159,10 @@
         <v>0.92</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.3345</v>
+        <v>-0.2953</v>
       </c>
       <c r="J355" t="n">
-        <v>-6.69</v>
+        <v>-5.906</v>
       </c>
     </row>
     <row r="356">
@@ -18199,10 +18199,10 @@
         <v>0.9</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.389</v>
+        <v>-0.3493</v>
       </c>
       <c r="J356" t="n">
-        <v>-7.78</v>
+        <v>-6.986</v>
       </c>
     </row>
     <row r="357">
@@ -18239,10 +18239,10 @@
         <v>1.05</v>
       </c>
       <c r="I357" t="n">
-        <v>0.1697</v>
+        <v>0.1323</v>
       </c>
       <c r="J357" t="n">
-        <v>3.394</v>
+        <v>2.646</v>
       </c>
     </row>
     <row r="358">
@@ -18279,10 +18279,10 @@
         <v>0.93</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.1039</v>
+        <v>-0.089</v>
       </c>
       <c r="J358" t="n">
-        <v>-2.078</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="359">
@@ -18319,10 +18319,10 @@
         <v>0.87</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.1708</v>
+        <v>-0.1521</v>
       </c>
       <c r="J359" t="n">
-        <v>-3.416</v>
+        <v>-3.042</v>
       </c>
     </row>
     <row r="360">
@@ -18359,10 +18359,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.2321</v>
+        <v>-0.2124</v>
       </c>
       <c r="J360" t="n">
-        <v>-4.642</v>
+        <v>-4.248</v>
       </c>
     </row>
     <row r="361">
@@ -18399,10 +18399,10 @@
         <v>0.79</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.2518</v>
+        <v>-0.2324</v>
       </c>
       <c r="J361" t="n">
-        <v>-5.036</v>
+        <v>-4.648</v>
       </c>
     </row>
     <row r="362">
@@ -18439,10 +18439,10 @@
         <v>1.49</v>
       </c>
       <c r="I362" t="n">
-        <v>1.0686</v>
+        <v>1.0783</v>
       </c>
       <c r="J362" t="n">
-        <v>19.2348</v>
+        <v>19.4094</v>
       </c>
     </row>
     <row r="363">
@@ -18479,10 +18479,10 @@
         <v>1.47</v>
       </c>
       <c r="I363" t="n">
-        <v>1.0404</v>
+        <v>1.0465</v>
       </c>
       <c r="J363" t="n">
-        <v>18.7272</v>
+        <v>18.837</v>
       </c>
     </row>
     <row r="364">
@@ -18519,10 +18519,10 @@
         <v>1.22</v>
       </c>
       <c r="I364" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5448</v>
       </c>
       <c r="J364" t="n">
-        <v>10.3158</v>
+        <v>9.8064</v>
       </c>
     </row>
     <row r="365">
@@ -18559,10 +18559,10 @@
         <v>1.22</v>
       </c>
       <c r="I365" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5448</v>
       </c>
       <c r="J365" t="n">
-        <v>10.3158</v>
+        <v>9.8064</v>
       </c>
     </row>
     <row r="366">
@@ -18599,10 +18599,10 @@
         <v>1.2</v>
       </c>
       <c r="I366" t="n">
-        <v>0.5296</v>
+        <v>0.5</v>
       </c>
       <c r="J366" t="n">
-        <v>9.5328</v>
+        <v>9</v>
       </c>
     </row>
     <row r="367">
@@ -18639,10 +18639,10 @@
         <v>1.21</v>
       </c>
       <c r="I367" t="n">
-        <v>0.4733</v>
+        <v>0.4167</v>
       </c>
       <c r="J367" t="n">
-        <v>8.519399999999999</v>
+        <v>7.5006</v>
       </c>
     </row>
     <row r="368">
@@ -18679,10 +18679,10 @@
         <v>1.21</v>
       </c>
       <c r="I368" t="n">
-        <v>0.4733</v>
+        <v>0.4167</v>
       </c>
       <c r="J368" t="n">
-        <v>8.519399999999999</v>
+        <v>7.5006</v>
       </c>
     </row>
     <row r="369">
@@ -18719,10 +18719,10 @@
         <v>0.97</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.0528</v>
+        <v>-0.0425</v>
       </c>
       <c r="J369" t="n">
-        <v>-0.9504</v>
+        <v>-0.765</v>
       </c>
     </row>
     <row r="370">
@@ -18759,10 +18759,10 @@
         <v>0.79</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.2545</v>
+        <v>-0.2349</v>
       </c>
       <c r="J370" t="n">
-        <v>-4.581</v>
+        <v>-4.2282</v>
       </c>
     </row>
     <row r="371">
@@ -18799,10 +18799,10 @@
         <v>0.41</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.607</v>
       </c>
       <c r="J371" t="n">
-        <v>-10.6596</v>
+        <v>-10.926</v>
       </c>
     </row>
     <row r="372">
@@ -18839,10 +18839,10 @@
         <v>1.51</v>
       </c>
       <c r="I372" t="n">
-        <v>1.1359</v>
+        <v>1.1495</v>
       </c>
       <c r="J372" t="n">
-        <v>32.9411</v>
+        <v>33.3355</v>
       </c>
     </row>
     <row r="373">
@@ -18879,10 +18879,10 @@
         <v>1.45</v>
       </c>
       <c r="I373" t="n">
-        <v>1.0504</v>
+        <v>1.0561</v>
       </c>
       <c r="J373" t="n">
-        <v>30.4616</v>
+        <v>30.6269</v>
       </c>
     </row>
     <row r="374">
@@ -18919,10 +18919,10 @@
         <v>1.2</v>
       </c>
       <c r="I374" t="n">
-        <v>0.5557</v>
+        <v>0.5179</v>
       </c>
       <c r="J374" t="n">
-        <v>16.1153</v>
+        <v>15.0191</v>
       </c>
     </row>
     <row r="375">
@@ -18959,10 +18959,10 @@
         <v>0.77</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.6804</v>
+        <v>-0.6483</v>
       </c>
       <c r="J375" t="n">
-        <v>-19.7316</v>
+        <v>-18.8007</v>
       </c>
     </row>
     <row r="376">
@@ -18999,10 +18999,10 @@
         <v>0.7</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.8328</v>
+        <v>-0.8136</v>
       </c>
       <c r="J376" t="n">
-        <v>-24.1512</v>
+        <v>-23.5944</v>
       </c>
     </row>
     <row r="377">
@@ -19039,10 +19039,10 @@
         <v>1.48</v>
       </c>
       <c r="I377" t="n">
-        <v>0.8591</v>
+        <v>0.8098</v>
       </c>
       <c r="J377" t="n">
-        <v>24.9139</v>
+        <v>23.4842</v>
       </c>
     </row>
     <row r="378">
@@ -19079,10 +19079,10 @@
         <v>1.26</v>
       </c>
       <c r="I378" t="n">
-        <v>0.5258</v>
+        <v>0.4663</v>
       </c>
       <c r="J378" t="n">
-        <v>15.2482</v>
+        <v>13.5227</v>
       </c>
     </row>
     <row r="379">
@@ -19119,10 +19119,10 @@
         <v>0.96</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.0599</v>
       </c>
       <c r="J379" t="n">
-        <v>-2.1692</v>
+        <v>-1.7371</v>
       </c>
     </row>
     <row r="380">
@@ -19159,10 +19159,10 @@
         <v>0.8</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.2551</v>
+        <v>-0.2354</v>
       </c>
       <c r="J380" t="n">
-        <v>-7.3979</v>
+        <v>-6.8266</v>
       </c>
     </row>
     <row r="381">
@@ -19199,10 +19199,10 @@
         <v>0.65</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3955</v>
+        <v>-0.3852</v>
       </c>
       <c r="J381" t="n">
-        <v>-11.4695</v>
+        <v>-11.1708</v>
       </c>
     </row>
     <row r="382">
@@ -19239,10 +19239,10 @@
         <v>1.75</v>
       </c>
       <c r="I382" t="n">
-        <v>1.4483</v>
+        <v>1.4816</v>
       </c>
       <c r="J382" t="n">
-        <v>34.7592</v>
+        <v>35.5584</v>
       </c>
     </row>
     <row r="383">
@@ -19279,10 +19279,10 @@
         <v>1.31</v>
       </c>
       <c r="I383" t="n">
-        <v>0.7817</v>
+        <v>0.7549</v>
       </c>
       <c r="J383" t="n">
-        <v>18.7608</v>
+        <v>18.1176</v>
       </c>
     </row>
     <row r="384">
@@ -19319,10 +19319,10 @@
         <v>1.14</v>
       </c>
       <c r="I384" t="n">
-        <v>0.4154</v>
+        <v>0.379</v>
       </c>
       <c r="J384" t="n">
-        <v>9.9696</v>
+        <v>9.096</v>
       </c>
     </row>
     <row r="385">
@@ -19359,10 +19359,10 @@
         <v>1.12</v>
       </c>
       <c r="I385" t="n">
-        <v>0.3671</v>
+        <v>0.3317</v>
       </c>
       <c r="J385" t="n">
-        <v>8.8104</v>
+        <v>7.9608</v>
       </c>
     </row>
     <row r="386">
@@ -19399,10 +19399,10 @@
         <v>0.48</v>
       </c>
       <c r="I386" t="n">
-        <v>-1.2788</v>
+        <v>-1.3213</v>
       </c>
       <c r="J386" t="n">
-        <v>-30.6912</v>
+        <v>-31.7112</v>
       </c>
     </row>
     <row r="387">
@@ -19439,10 +19439,10 @@
         <v>1.34</v>
       </c>
       <c r="I387" t="n">
-        <v>0.6642</v>
+        <v>0.6072</v>
       </c>
       <c r="J387" t="n">
-        <v>15.9408</v>
+        <v>14.5728</v>
       </c>
     </row>
     <row r="388">
@@ -19479,10 +19479,10 @@
         <v>1.1</v>
       </c>
       <c r="I388" t="n">
-        <v>0.2551</v>
+        <v>0.2081</v>
       </c>
       <c r="J388" t="n">
-        <v>6.1224</v>
+        <v>4.9944</v>
       </c>
     </row>
     <row r="389">
@@ -19519,10 +19519,10 @@
         <v>0.91</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.1342</v>
+        <v>-0.1153</v>
       </c>
       <c r="J389" t="n">
-        <v>-3.2208</v>
+        <v>-2.7672</v>
       </c>
     </row>
     <row r="390">
@@ -19559,10 +19559,10 @@
         <v>0.82</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.2311</v>
+        <v>-0.2107</v>
       </c>
       <c r="J390" t="n">
-        <v>-5.5464</v>
+        <v>-5.0568</v>
       </c>
     </row>
     <row r="391">
@@ -19599,10 +19599,10 @@
         <v>0.76</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.2901</v>
+        <v>-0.2717</v>
       </c>
       <c r="J391" t="n">
-        <v>-6.9624</v>
+        <v>-6.5208</v>
       </c>
     </row>
     <row r="392">
@@ -19639,10 +19639,10 @@
         <v>1.93</v>
       </c>
       <c r="I392" t="n">
-        <v>1.6878</v>
+        <v>1.7494</v>
       </c>
       <c r="J392" t="n">
-        <v>40.5072</v>
+        <v>41.9856</v>
       </c>
     </row>
     <row r="393">
@@ -19679,10 +19679,10 @@
         <v>1.36</v>
       </c>
       <c r="I393" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.8694</v>
       </c>
       <c r="J393" t="n">
-        <v>21.3264</v>
+        <v>20.8656</v>
       </c>
     </row>
     <row r="394">
@@ -19719,10 +19719,10 @@
         <v>1.01</v>
       </c>
       <c r="I394" t="n">
-        <v>0.0376</v>
+        <v>0.0273</v>
       </c>
       <c r="J394" t="n">
-        <v>0.9024</v>
+        <v>0.6552</v>
       </c>
     </row>
     <row r="395">
@@ -19759,10 +19759,10 @@
         <v>0.83</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.544</v>
+        <v>-0.5046</v>
       </c>
       <c r="J395" t="n">
-        <v>-13.056</v>
+        <v>-12.1104</v>
       </c>
     </row>
     <row r="396">
@@ -19799,10 +19799,10 @@
         <v>0.55</v>
       </c>
       <c r="I396" t="n">
-        <v>-1.14</v>
+        <v>-1.1595</v>
       </c>
       <c r="J396" t="n">
-        <v>-27.36</v>
+        <v>-27.828</v>
       </c>
     </row>
     <row r="397">
@@ -19839,10 +19839,10 @@
         <v>1.12</v>
       </c>
       <c r="I397" t="n">
-        <v>0.3065</v>
+        <v>0.2556</v>
       </c>
       <c r="J397" t="n">
-        <v>7.356</v>
+        <v>6.1344</v>
       </c>
     </row>
     <row r="398">
@@ -19879,10 +19879,10 @@
         <v>0.99</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.0204</v>
+        <v>-0.0152</v>
       </c>
       <c r="J398" t="n">
-        <v>-0.4896</v>
+        <v>-0.3648</v>
       </c>
     </row>
     <row r="399">
@@ -19919,10 +19919,10 @@
         <v>0.95</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.0818</v>
+        <v>-0.0679</v>
       </c>
       <c r="J399" t="n">
-        <v>-1.9632</v>
+        <v>-1.6296</v>
       </c>
     </row>
     <row r="400">
@@ -19959,10 +19959,10 @@
         <v>0.95</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.0818</v>
+        <v>-0.0679</v>
       </c>
       <c r="J400" t="n">
-        <v>-1.9632</v>
+        <v>-1.6296</v>
       </c>
     </row>
     <row r="401">
@@ -19999,10 +19999,10 @@
         <v>0.64</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.3957</v>
+        <v>-0.3844</v>
       </c>
       <c r="J401" t="n">
-        <v>-9.4968</v>
+        <v>-9.2256</v>
       </c>
     </row>
     <row r="402">
@@ -20039,10 +20039,10 @@
         <v>1.28</v>
       </c>
       <c r="I402" t="n">
-        <v>0.7269</v>
+        <v>0.6959</v>
       </c>
       <c r="J402" t="n">
-        <v>21.0801</v>
+        <v>20.1811</v>
       </c>
     </row>
     <row r="403">
@@ -20079,10 +20079,10 @@
         <v>1.25</v>
       </c>
       <c r="I403" t="n">
-        <v>0.6636</v>
+        <v>0.6294</v>
       </c>
       <c r="J403" t="n">
-        <v>19.2444</v>
+        <v>18.2526</v>
       </c>
     </row>
     <row r="404">
@@ -20119,10 +20119,10 @@
         <v>1.13</v>
       </c>
       <c r="I404" t="n">
-        <v>0.3948</v>
+        <v>0.3572</v>
       </c>
       <c r="J404" t="n">
-        <v>11.4492</v>
+        <v>10.3588</v>
       </c>
     </row>
     <row r="405">
@@ -20159,10 +20159,10 @@
         <v>1.07</v>
       </c>
       <c r="I405" t="n">
-        <v>0.2402</v>
+        <v>0.2086</v>
       </c>
       <c r="J405" t="n">
-        <v>6.9658</v>
+        <v>6.0494</v>
       </c>
     </row>
     <row r="406">
@@ -20199,10 +20199,10 @@
         <v>0.92</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.3128</v>
+        <v>-0.2716</v>
       </c>
       <c r="J406" t="n">
-        <v>-9.071199999999999</v>
+        <v>-7.8764</v>
       </c>
     </row>
     <row r="407">
@@ -20239,10 +20239,10 @@
         <v>1.41</v>
       </c>
       <c r="I407" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7145</v>
       </c>
       <c r="J407" t="n">
-        <v>22.2604</v>
+        <v>20.7205</v>
       </c>
     </row>
     <row r="408">
@@ -20279,10 +20279,10 @@
         <v>1.14</v>
       </c>
       <c r="I408" t="n">
-        <v>0.3289</v>
+        <v>0.2762</v>
       </c>
       <c r="J408" t="n">
-        <v>9.5381</v>
+        <v>8.0098</v>
       </c>
     </row>
     <row r="409">
@@ -20319,10 +20319,10 @@
         <v>1.03</v>
       </c>
       <c r="I409" t="n">
-        <v>0.1005</v>
+        <v>0.0742</v>
       </c>
       <c r="J409" t="n">
-        <v>2.9145</v>
+        <v>2.1518</v>
       </c>
     </row>
     <row r="410">
@@ -20359,10 +20359,10 @@
         <v>0.7</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.3473</v>
+        <v>-0.3325</v>
       </c>
       <c r="J410" t="n">
-        <v>-10.0717</v>
+        <v>-9.6425</v>
       </c>
     </row>
     <row r="411">
@@ -20399,10 +20399,10 @@
         <v>0.7</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3473</v>
+        <v>-0.3325</v>
       </c>
       <c r="J411" t="n">
-        <v>-10.0717</v>
+        <v>-9.6425</v>
       </c>
     </row>
   </sheetData>
